--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="AJ27" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="AJ13" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="AJ11" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -10429,7 +10429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10796,8 +10796,53 @@
         </is>
       </c>
     </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26T16:17:41+08:00</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23 至 2026-07-26</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>本次检索未发现符合收录标准的新文书。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M7"/>
+  <autoFilter ref="A1:M8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -10429,7 +10429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10841,8 +10841,53 @@
         </is>
       </c>
     </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26T16:26:38+08:00</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23 至 2026-07-26</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>本次检索未发现符合收录标准的新文书。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M8"/>
+  <autoFilter ref="A1:M9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -15,12 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日运行日志" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文书汇总'!$A$1:$AJ$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'完整文书'!$A$1:$AJ$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文书汇总'!$A$1:$AJ$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'完整文书'!$A$1:$AJ$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ27"/>
+  <dimension ref="A1:AJ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -785,7 +785,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>46229</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>46229</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>46229</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>46229</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>46229</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>46229</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>46229</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>46229</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>46229</v>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>46229</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>46229</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>46229</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
@@ -4005,20 +4005,288 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7e3d4a321440d6a7</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>DOC-bed9330343ed06af</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>91120116300738701X</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>920146.9399999999</v>
+      </c>
+      <c r="S28" s="3" t="n"/>
+      <c r="T28" s="3" t="n"/>
+      <c r="U28" s="3" t="n"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W28" s="4" t="n"/>
+      <c r="X28" s="4" t="n"/>
+      <c r="Y28" s="4" t="n"/>
+      <c r="Z28" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AA28" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE28" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF28" s="2" t="inlineStr"/>
+      <c r="AG28" s="2" t="inlineStr"/>
+      <c r="AH28" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+        </is>
+      </c>
+      <c r="AI28" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ28" s="2" t="inlineStr">
+        <is>
+          <t>页面未提取到可确认的官方发布日期。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7e3d4a321440d6a7</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>DOC-388bd01c01bbb789</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>91120116300738701X</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>税务行政处罚决定书</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="n"/>
+      <c r="S29" s="3" t="n"/>
+      <c r="T29" s="3" t="n">
+        <v>131368.5</v>
+      </c>
+      <c r="U29" s="3" t="n"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W29" s="4" t="n"/>
+      <c r="X29" s="4" t="n"/>
+      <c r="Y29" s="4" t="n"/>
+      <c r="Z29" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AA29" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE29" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF29" s="2" t="inlineStr"/>
+      <c r="AG29" s="2" t="inlineStr"/>
+      <c r="AH29" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+        </is>
+      </c>
+      <c r="AI29" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ29" s="2" t="inlineStr">
+        <is>
+          <t>页面未提取到可确认的官方发布日期。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ27"/>
-  <conditionalFormatting sqref="AD2:AD27">
+  <autoFilter ref="A1:AJ29"/>
+  <conditionalFormatting sqref="AD2:AD29">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AD2="待核验"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI2:AI27">
+  <conditionalFormatting sqref="AI2:AI29">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>AND($AI2&lt;&gt;"正常",$AI2&lt;&gt;"附件正常")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AD2:AD27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AD2:AD29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"已核验,待核验,人工复核完成"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4059,6 +4327,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF25" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE26" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE27" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE28" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE29" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -4071,7 +4341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ13"/>
+  <dimension ref="A1:AJ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4386,7 +4656,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -4520,7 +4790,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -4652,7 +4922,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -4780,7 +5050,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -4918,7 +5188,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -5054,7 +5324,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -5186,7 +5456,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -5324,7 +5594,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -5466,7 +5736,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -5596,7 +5866,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -5724,7 +5994,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -5848,7 +6118,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -5888,20 +6158,288 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7e3d4a321440d6a7</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>DOC-bed9330343ed06af</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>91120116300738701X</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>920146.9399999999</v>
+      </c>
+      <c r="S14" s="3" t="n"/>
+      <c r="T14" s="3" t="n"/>
+      <c r="U14" s="3" t="n"/>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="n"/>
+      <c r="X14" s="4" t="n"/>
+      <c r="Y14" s="4" t="n"/>
+      <c r="Z14" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AA14" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE14" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+        </is>
+      </c>
+      <c r="AI14" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ14" s="2" t="inlineStr">
+        <is>
+          <t>页面未提取到可确认的官方发布日期。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7e3d4a321440d6a7</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>DOC-388bd01c01bbb789</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>91120116300738701X</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>税务行政处罚决定书</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="n"/>
+      <c r="S15" s="3" t="n"/>
+      <c r="T15" s="3" t="n">
+        <v>131368.5</v>
+      </c>
+      <c r="U15" s="3" t="n"/>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="n"/>
+      <c r="X15" s="4" t="n"/>
+      <c r="Y15" s="4" t="n"/>
+      <c r="Z15" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AA15" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD15" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE15" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+        </is>
+      </c>
+      <c r="AI15" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ15" s="2" t="inlineStr">
+        <is>
+          <t>页面未提取到可确认的官方发布日期。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ13"/>
-  <conditionalFormatting sqref="AD2:AD13">
+  <autoFilter ref="A1:AJ15"/>
+  <conditionalFormatting sqref="AD2:AD15">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AD2="待核验"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI2:AI13">
+  <conditionalFormatting sqref="AI2:AI15">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>AND($AI2&lt;&gt;"正常",$AI2&lt;&gt;"附件正常")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AD2:AD13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AD2:AD15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"已核验,待核验,人工复核完成"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5922,6 +6460,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF11" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE12" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE14" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE15" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -6239,7 +6779,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -6357,7 +6897,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -6479,7 +7019,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -6605,7 +7145,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -6731,7 +7271,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -6849,7 +7389,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -6971,7 +7511,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -7093,7 +7633,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -7215,7 +7755,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -7337,7 +7877,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -7459,7 +7999,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -7581,7 +8121,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -7699,7 +8239,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -7821,7 +8361,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -7915,7 +8455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ11"/>
+  <dimension ref="A1:AJ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8216,7 +8756,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -8342,7 +8882,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -8460,7 +9000,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -8582,7 +9122,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -8704,7 +9244,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -8822,7 +9362,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -8964,7 +9504,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -9106,7 +9646,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -9234,7 +9774,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -9358,7 +9898,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -9398,20 +9938,288 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7e3d4a321440d6a7</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>DOC-bed9330343ed06af</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>91120116300738701X</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>920146.9399999999</v>
+      </c>
+      <c r="S12" s="3" t="n"/>
+      <c r="T12" s="3" t="n"/>
+      <c r="U12" s="3" t="n"/>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="n"/>
+      <c r="X12" s="4" t="n"/>
+      <c r="Y12" s="4" t="n"/>
+      <c r="Z12" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AA12" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE12" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+        </is>
+      </c>
+      <c r="AI12" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ12" s="2" t="inlineStr">
+        <is>
+          <t>页面未提取到可确认的官方发布日期。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7e3d4a321440d6a7</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>DOC-388bd01c01bbb789</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>91120116300738701X</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>税务行政处罚决定书</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="n"/>
+      <c r="S13" s="3" t="n"/>
+      <c r="T13" s="3" t="n">
+        <v>131368.5</v>
+      </c>
+      <c r="U13" s="3" t="n"/>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W13" s="4" t="n"/>
+      <c r="X13" s="4" t="n"/>
+      <c r="Y13" s="4" t="n"/>
+      <c r="Z13" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AA13" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD13" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE13" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+        </is>
+      </c>
+      <c r="AI13" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ13" s="2" t="inlineStr">
+        <is>
+          <t>页面未提取到可确认的官方发布日期。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ11"/>
-  <conditionalFormatting sqref="AD2:AD11">
+  <autoFilter ref="A1:AJ13"/>
+  <conditionalFormatting sqref="AD2:AD13">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AD2="待核验"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI2:AI11">
+  <conditionalFormatting sqref="AI2:AI13">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>AND($AI2&lt;&gt;"正常",$AI2&lt;&gt;"附件正常")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AD2:AD11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AD2:AD13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"已核验,待核验,人工复核完成"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9429,6 +10237,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF9" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE10" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE12" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -9742,7 +10552,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -9868,7 +10678,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -9986,7 +10796,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -10108,7 +10918,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -10230,7 +11040,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -10348,7 +11158,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -10429,7 +11239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10886,8 +11696,57 @@
         </is>
       </c>
     </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27T15:38:15+08:00</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24 至 2026-07-27</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>已完成候选发现、逐条访问核验、去重、关联和历史数据增量写入。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M9"/>
+  <autoFilter ref="A1:M10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -785,7 +785,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>46229</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>46229</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>46229</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>46229</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>46229</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>46229</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>46229</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>46229</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>46229</v>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>46229</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>46229</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>46229</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>46230</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="AJ28" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。</t>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4233,7 @@
         <v>46230</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AJ29" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。</t>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4656,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>46230</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="AJ14" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。</t>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
         <v>46230</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="AJ15" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。</t>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>46230</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="AJ12" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。</t>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -10166,7 +10166,7 @@
         <v>46230</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="AJ13" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。</t>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -10552,7 +10552,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11745,8 +11745,53 @@
         </is>
       </c>
     </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:31:21+08:00</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25 至 2026-07-28</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>本次检索未发现符合收录标准的新文书。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M10"/>
+  <autoFilter ref="A1:M11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -785,7 +785,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>46229</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>46229</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>46229</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>46229</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>46229</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>46229</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>46229</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>46229</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>46229</v>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>46229</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>46229</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>46229</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>46230</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>46230</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>46230</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>46230</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>46230</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>46230</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11790,8 +11790,53 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29T14:36:32+08:00</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26 至 2026-07-29</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>本次检索未发现符合收录标准的新文书。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M11"/>
+  <autoFilter ref="A1:M12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -15,12 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日运行日志" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文书汇总'!$A$1:$AJ$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'完整文书'!$A$1:$AJ$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文书汇总'!$A$1:$AJ$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'完整文书'!$A$1:$AJ$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ29"/>
+  <dimension ref="A1:AJ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -705,49 +705,49 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CASE-3e050a699b29b0d0</t>
+          <t>CASE-89fc66bfc8dad80d</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>DOC-96a3089a0e2b37cd</t>
+          <t>DOC-6e5b966cd65a4366</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>河南省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>平顶山市</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
+          <t>北海市</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>银海区</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局平顶山市税务局第一稽查局</t>
+          <t>国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局平顶山市税务局第一稽查局</t>
+          <t>国家税务总局北海市税务局稽查局</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>汝州泰隆实业有限公司</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>91410482MA40K4KA3B</t>
-        </is>
-      </c>
+          <t>广西耿仁建材有限公司</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -756,40 +756,46 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>平税稽一局处〔2026〕1号</t>
+          <t>北市税稽处〔2026〕14号</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>平税稽一局处〔2026〕1号</t>
+          <t>北市税稽处〔2026〕14号</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>我局于2026年2月11日至2026年7月15日对你公司(地址:北海市银海区新世纪大道15号辰宸花园3幢二单元0901号)2026年1月1日至2026年1月31日期间的涉税情况进行了检查,违法事实及处理决定如下: (2)短时间开具大量大额发票且未申报 你公司未进行纳税申报,不缴或者少缴2026年1月增值税194612.47元,2026年1月城市维护建设税13622.87元,合计208235.34元。 根据《中华人民共和国税收征收管理法》第六十三条第一款规定,对上述行为定性为偷税,向你公司追缴少缴的2026年增值税194612.47元,城市维护建设税13622.87元,合计208235.34元。 1.根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)的规定,对你公司少缴所属期2026年1月的教育费附加5838.37元,予以追缴。 2.根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条的规定,对你公司少缴所属期2026年1月地方教育附加3892.25元,予以追缴。 根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司少缴的税款从税款滞纳之日起至实际缴纳税款之日止按日加收滞纳税款万分之五的滞纳金,滞纳金由金三系统自动计算加收。 (四)你公司无法联系且实地核查无实际生产地址、无生产能力、查无下落,短期开票金额大,无法核实资金流,未进行纳税申报,根据《国家税务总局关于走逃(失联)企业开具增值税专用发票认定处理有关问题的公告》(国家税务总局公告2016年第76号),将你公司按走逃(失联)处理,根据《中华人民共和国发票管理办法》(国函〔1993〕174号)第二十一条第(一)项,你公司无生产能力,却为他人开具与实际经营业务情况不符的发票,属于虚开发票的行为。</t>
+        </is>
+      </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>增值税、个人所得税</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="n"/>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>208235.34</v>
+      </c>
       <c r="S2" s="3" t="n"/>
       <c r="T2" s="3" t="n"/>
       <c r="U2" s="3" t="n"/>
       <c r="V2" s="2" t="inlineStr"/>
       <c r="W2" s="4" t="n"/>
       <c r="X2" s="4" t="n">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="Y2" s="4" t="n"/>
       <c r="Z2" s="4" t="n">
-        <v>46229</v>
+        <v>46233</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -811,7 +817,7 @@
       <c r="AG2" s="2" t="inlineStr"/>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局平顶山市税务局第一稽查局关于送达汝州泰隆实业有限公司《税务处理决定书》的公告 - 国家税务总局平顶山市税务局</t>
+          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕14号)_国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="AI2" s="2" t="inlineStr">
@@ -819,55 +825,51 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
+      <c r="AJ2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CASE-365e8a924cf64611</t>
+          <t>CASE-3e050a699b29b0d0</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>DOC-4d14eba16f9aa8a0</t>
+          <t>DOC-96a3089a0e2b37cd</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>平顶山市</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局平顶山市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局平顶山市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>贵州博泰工贸有限公司</t>
+          <t>汝州泰隆实业有限公司</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>91520115587255589F</t>
+          <t>91410482MA40K4KA3B</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
@@ -878,17 +880,21 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕38号</t>
+          <t>平税稽一局处〔2026〕1号</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕38号</t>
+          <t>平税稽一局处〔2026〕1号</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>增值税、个人所得税</t>
+        </is>
+      </c>
       <c r="R3" s="3" t="n"/>
       <c r="S3" s="3" t="n"/>
       <c r="T3" s="3" t="n"/>
@@ -896,14 +902,14 @@
       <c r="V3" s="2" t="inlineStr"/>
       <c r="W3" s="4" t="n"/>
       <c r="X3" s="4" t="n">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="Y3" s="4" t="n"/>
       <c r="Z3" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -917,7 +923,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE3" s="5" t="inlineStr">
@@ -929,12 +935,12 @@
       <c r="AG3" s="2" t="inlineStr"/>
       <c r="AH3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书、税务行政处罚决定书的公告</t>
+          <t>国家税务总局平顶山市税务局第一稽查局关于送达汝州泰隆实业有限公司《税务处理决定书》的公告 - 国家税务总局平顶山市税务局</t>
         </is>
       </c>
       <c r="AI3" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ3" s="2" t="inlineStr">
@@ -945,47 +951,47 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CASE-7b9a26f2ac401107</t>
+          <t>CASE-365e8a924cf64611</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>DOC-f6c6ea472b2ca04a</t>
+          <t>DOC-4d14eba16f9aa8a0</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>三明市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局三明市税务局第一稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局三明市税务局第一稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>三明众祥房地产开发有限公司</t>
+          <t>贵州博泰工贸有限公司</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>91350400678473231W</t>
+          <t>91520115587255589F</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
@@ -996,50 +1002,36 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>明税一稽处〔2026〕20号</t>
+          <t>筑税三稽处〔2026〕38号</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>明税一稽处〔2026〕20号</t>
+          <t>筑税三稽处〔2026〕38号</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2016年期间,在没有真实业务情况下,取得重庆市博海建设工程(集团)有限公司、福建九九建设有限公司三明分公司开具的不符合规定的发票,发票金额400252379元,在企业所得税税前扣除,造成少缴纳企业所得税100063094.75元,该行为违反《中华人民共和国税收征收管理法》(2015年4月24日主席令第二十三号修改)第六十三条第一款 纳税人伪造、变造、隐匿、擅自销毁账簿、记账凭证,或者在账簿上多列支出或者不列、少列收入,或者经税务机关通知申报而拒不申报或者进行虚假的纳税申报,不缴或者少缴应纳税款的,是偷税。 对纳税人偷税的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款; 之规定,对你公司在账上多列支出,造成少缴企业所得税100063094.75元的行为认定为偷税。 之规定,对你公司少缴的企业所得税从滞纳之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>企业所得税</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>100063094.75</v>
-      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="3" t="n"/>
       <c r="S4" s="3" t="n"/>
       <c r="T4" s="3" t="n"/>
       <c r="U4" s="3" t="n"/>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>据《中华人民共和国税收征收管理法实施细则》第106条规定,将该文书予以公告送达,自公告之日起满30日视为送达。</t>
-        </is>
-      </c>
+      <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="4" t="n"/>
       <c r="X4" s="4" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="Y4" s="4" t="n"/>
       <c r="Z4" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1049,7 +1041,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE4" s="5" t="inlineStr">
@@ -1061,14 +1053,12 @@
       <c r="AG4" s="2" t="inlineStr"/>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>关于送达三明众祥房地产开发有限公司 《税务处理决定书》的公告 _
- 其他公告 _
- 国家税务总局三明市税务局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书、税务行政处罚决定书的公告</t>
         </is>
       </c>
       <c r="AI4" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>页面已删除</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr">
@@ -1079,16 +1069,16 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CASE-31e4a827dfd253f2</t>
+          <t>CASE-7b9a26f2ac401107</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>DOC-3ec54358fce2350d</t>
+          <t>DOC-f6c6ea472b2ca04a</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1098,28 +1088,28 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>福州市</t>
+          <t>三明市</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局三明市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局三明市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>福州顺路汽车运输有限公司</t>
+          <t>三明众祥房地产开发有限公司</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>91350102MA31MF6611</t>
+          <t>91350400678473231W</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
@@ -1130,46 +1120,46 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽处〔2026〕137号</t>
+          <t>明税一稽处〔2026〕20号</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽处〔2026〕137号</t>
+          <t>明税一稽处〔2026〕20号</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>我局于2025年7月10日起对你公司(地址:福建省闽侯县青口镇祥宏南路922号)2023年1月1日至2024年12月31日期间的发票涉税情况进行检查,违法事实及处理决定如下: (二)你公司取得毕节七星关区辰楚汽车服务部(个人独资)、毕节七星关锦悦汽车服务部(个人独资)、贵州杨亭汽车销售有限公司、贵州楠鑫汽车销售有限公司已证实虚开的35份机动车发票。 (二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 (三)根据《中华人民共和国企业所得税法》第五条、第八条、《企业所得税税前扣除凭证管理办法》(国家税务总局公告2018年第28号发布)第四条、第十二条的规定,你公司取得上述虚开的发票不得作为税前扣除凭证。</t>
+          <t>情况进行了检查,违法事实及处理决定如下: 2016年期间,在没有真实业务情况下,取得重庆市博海建设工程(集团)有限公司、福建九九建设有限公司三明分公司开具的不符合规定的发票,发票金额400252379元,在企业所得税税前扣除,造成少缴纳企业所得税100063094.75元,该行为违反《中华人民共和国税收征收管理法》(2015年4月24日主席令第二十三号修改)第六十三条第一款 纳税人伪造、变造、隐匿、擅自销毁账簿、记账凭证,或者在账簿上多列支出或者不列、少列收入,或者经税务机关通知申报而拒不申报或者进行虚假的纳税申报,不缴或者少缴应纳税款的,是偷税。 对纳税人偷税的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款; 之规定,对你公司在账上多列支出,造成少缴企业所得税100063094.75元的行为认定为偷税。 之规定,对你公司少缴的企业所得税从滞纳之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
+          <t>企业所得税</t>
         </is>
       </c>
       <c r="R5" s="3" t="n">
-        <v>3778.22</v>
+        <v>100063094.75</v>
       </c>
       <c r="S5" s="3" t="n"/>
       <c r="T5" s="3" t="n"/>
       <c r="U5" s="3" t="n"/>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>(二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期城市维护建设税124.75元。 根据《征收教育费附加的暂行规定》第二条、第三条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期教育费附加53.47元。 根据《福建省人民政府关于调整地方教育附加征收标准等有关问题的通知》(闽政文〔2011〕230号)第一条、第二条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期地方教育附加35.64元。</t>
+          <t>据《中华人民共和国税收征收管理法实施细则》第106条规定,将该文书予以公告送达,自公告之日起满30日视为送达。</t>
         </is>
       </c>
       <c r="W5" s="4" t="n"/>
       <c r="X5" s="4" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1195,140 +1185,148 @@
       <c r="AG5" s="2" t="inlineStr"/>
       <c r="AH5" s="2" t="inlineStr">
         <is>
+          <t>关于送达三明众祥房地产开发有限公司 《税务处理决定书》的公告 _
+ 其他公告 _
+ 国家税务总局三明市税务局</t>
+        </is>
+      </c>
+      <c r="AI5" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>CASE-31e4a827dfd253f2</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>DOC-3ec54358fce2350d</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>福建省</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>福州市</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局福州市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局福州市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>福州顺路汽车运输有限公司</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>91350102MA31MF6611</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>榕税一稽处〔2026〕137号</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>榕税一稽处〔2026〕137号</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>我局于2025年7月10日起对你公司(地址:福建省闽侯县青口镇祥宏南路922号)2023年1月1日至2024年12月31日期间的发票涉税情况进行检查,违法事实及处理决定如下: (二)你公司取得毕节七星关区辰楚汽车服务部(个人独资)、毕节七星关锦悦汽车服务部(个人独资)、贵州杨亭汽车销售有限公司、贵州楠鑫汽车销售有限公司已证实虚开的35份机动车发票。 (二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 (三)根据《中华人民共和国企业所得税法》第五条、第八条、《企业所得税税前扣除凭证管理办法》(国家税务总局公告2018年第28号发布)第四条、第十二条的规定,你公司取得上述虚开的发票不得作为税前扣除凭证。</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>3778.22</v>
+      </c>
+      <c r="S6" s="3" t="n"/>
+      <c r="T6" s="3" t="n"/>
+      <c r="U6" s="3" t="n"/>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>(二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期城市维护建设税124.75元。 根据《征收教育费附加的暂行规定》第二条、第三条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期教育费附加53.47元。 根据《福建省人民政府关于调整地方教育附加征收标准等有关问题的通知》(闽政文〔2011〕230号)第一条、第二条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期地方教育附加35.64元。</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="n"/>
+      <c r="X6" s="4" t="n">
+        <v>46218</v>
+      </c>
+      <c r="Y6" s="4" t="n"/>
+      <c r="Z6" s="4" t="n">
+        <v>46229</v>
+      </c>
+      <c r="AA6" s="4" t="n">
+        <v>46233</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AE6" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
           <t>关于送达福州顺路汽车运输有限公司《税务处理决定书》的公告 _
  其他类 _
  国家税务总局福州市税务局</t>
         </is>
       </c>
-      <c r="AI5" s="2" t="inlineStr">
+      <c r="AI6" s="2" t="inlineStr">
         <is>
           <t>正常</t>
-        </is>
-      </c>
-      <c r="AJ5" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>CASE-089a3b9692e76ac4</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>DOC-d21cdc5988b1e304</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>江苏省</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>淮安市</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局江苏省税务局</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局淮安市税务局稽查局</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>淮安市百亦金商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>91320804MA1WEH7Y3U</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>税务处理决定书</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽处〔2026〕26号</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽处〔2026〕26号</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽罚〔2026〕6号</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="3" t="n"/>
-      <c r="S6" s="3" t="n"/>
-      <c r="T6" s="3" t="n"/>
-      <c r="U6" s="3" t="n"/>
-      <c r="V6" s="2" t="inlineStr"/>
-      <c r="W6" s="4" t="n"/>
-      <c r="X6" s="4" t="n">
-        <v>46216</v>
-      </c>
-      <c r="Y6" s="4" t="n"/>
-      <c r="Z6" s="4" t="n">
-        <v>46229</v>
-      </c>
-      <c r="AA6" s="4" t="n">
-        <v>46232</v>
-      </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>仅公告送达/仅文号线索</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>已核验</t>
-        </is>
-      </c>
-      <c r="AE6" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF6" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
-      <c r="AG6" s="2" t="inlineStr"/>
-      <c r="AH6" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
-        </is>
-      </c>
-      <c r="AI6" s="2" t="inlineStr">
-        <is>
-          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="inlineStr">
@@ -1339,7 +1337,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
@@ -1348,7 +1346,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>DOC-9f8e8958d8ff89b6</t>
+          <t>DOC-d21cdc5988b1e304</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1385,12 +1383,12 @@
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>淮税稽罚〔2026〕6号</t>
+          <t>淮税稽处〔2026〕26号</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1419,7 +1417,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1465,99 +1463,91 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CASE-3f564fd9992b1ae3</t>
+          <t>CASE-089a3b9692e76ac4</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DOC-c34e1d13286aafe2</t>
+          <t>DOC-9f8e8958d8ff89b6</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>泉州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局第二稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局第二稽查局</t>
+          <t>国家税务总局淮安市税务局稽查局</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>泉州隆鸿服装制造有限公司</t>
+          <t>淮安市百亦金商贸有限公司</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>91350525MA8U3U963L</t>
+          <t>91320804MA1WEH7Y3U</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>泉税二稽处〔2026〕107号</t>
+          <t>淮税稽罚〔2026〕6号</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>泉税二稽处〔2026〕107号</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>日对你公司税收违法事实依法作出《税务处理决定书》(泉税二稽处〔 涉税情况进行了检查,查明违法事实及处理决定如下: 年你公司在无真实货物交易的情况下,取得河南中弘纺织有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 年期间,你公司在无真实货物交易的情况下,取得开封兴旺纺织品有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 上述违法事实有检查人员实地检查资料、电话拨打记录、邮寄退回函件、《已证实虚开通知单》等相关受托协查资料、主管税务机关出具的《已抵扣证明》、《情况说明》和你公司的申报纳税资料、银行账户流水等 号第三次修订)第二十一条第二款第二项之规定,认定你公司让他人为自己虚开 号第二次修订)第九条和《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告〔 号)之规定,对你公司取得上述已证实虚开的 之规定,决定向你公司追缴少缴的城市维护建设税-增值税附征 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 规定,决定向你公司追缴少缴的教育费附加-增值税附征 规定,决定向你公司追缴少缴的地方教育附加-增值税附征</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
+          <t>淮税稽处〔2026〕26号</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>淮税稽罚〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
       <c r="R8" s="3" t="n"/>
       <c r="S8" s="3" t="n"/>
       <c r="T8" s="3" t="n"/>
       <c r="U8" s="3" t="n"/>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>由于你公司走逃失联、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 (五)根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司上述应补缴税款按税款所属时间从税款滞纳之日起按日加收万分之五滞纳金</t>
-        </is>
-      </c>
+      <c r="V8" s="2" t="inlineStr"/>
       <c r="W8" s="4" t="n"/>
       <c r="X8" s="4" t="n">
-        <v>46202</v>
+        <v>46216</v>
       </c>
       <c r="Y8" s="4" t="n"/>
       <c r="Z8" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1575,18 +1565,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AF8" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG8" s="2" t="inlineStr"/>
       <c r="AH8" s="2" t="inlineStr">
         <is>
-          <t>关于对泉州隆鸿服装制造有限公司《税务处理决定书》送达的公告 _
- 其他公告 _
- 国家税务总局泉州市税务局</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
         </is>
       </c>
       <c r="AI8" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="inlineStr">
@@ -1597,91 +1589,99 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>CASE-717dfe3250926214</t>
+          <t>CASE-3f564fd9992b1ae3</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DOC-7df9c075e55777a1</t>
+          <t>DOC-c34e1d13286aafe2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>泰州市</t>
+          <t>泉州市</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泰州市税务局第一稽查局</t>
+          <t>国家税务总局泉州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泰州市税务局第一稽查局</t>
+          <t>国家税务总局泉州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>靖江市长凌金属材料有限公司</t>
+          <t>泉州隆鸿服装制造有限公司</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91321282742461893K</t>
+          <t>91350525MA8U3U963L</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>泰税一稽罚〔2025〕54号</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>泰税一稽罚〔2025〕54号</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
+          <t>泉税二稽处〔2026〕107号</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>泉税二稽处〔2026〕107号</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>日对你公司税收违法事实依法作出《税务处理决定书》(泉税二稽处〔 涉税情况进行了检查,查明违法事实及处理决定如下: 年你公司在无真实货物交易的情况下,取得河南中弘纺织有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 年期间,你公司在无真实货物交易的情况下,取得开封兴旺纺织品有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 上述违法事实有检查人员实地检查资料、电话拨打记录、邮寄退回函件、《已证实虚开通知单》等相关受托协查资料、主管税务机关出具的《已抵扣证明》、《情况说明》和你公司的申报纳税资料、银行账户流水等 号第三次修订)第二十一条第二款第二项之规定,认定你公司让他人为自己虚开 号第二次修订)第九条和《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告〔 号)之规定,对你公司取得上述已证实虚开的 之规定,决定向你公司追缴少缴的城市维护建设税-增值税附征 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 规定,决定向你公司追缴少缴的教育费附加-增值税附征 规定,决定向你公司追缴少缴的地方教育附加-增值税附征</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
       <c r="R9" s="3" t="n"/>
       <c r="S9" s="3" t="n"/>
       <c r="T9" s="3" t="n"/>
       <c r="U9" s="3" t="n"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>接上级通知,经我局研究决定,撤销上述《税务行政处罚决定书》。</t>
+          <t>由于你公司走逃失联、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 (五)根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司上述应补缴税款按税款所属时间从税款滞纳之日起按日加收万分之五滞纳金</t>
         </is>
       </c>
       <c r="W9" s="4" t="n"/>
       <c r="X9" s="4" t="n">
-        <v>46191</v>
+        <v>46202</v>
       </c>
       <c r="Y9" s="4" t="n"/>
       <c r="Z9" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1703,7 +1703,9 @@
       <c r="AG9" s="2" t="inlineStr"/>
       <c r="AH9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 关于撤销《税务行政处罚决定书》的公告</t>
+          <t>关于对泉州隆鸿服装制造有限公司《税务处理决定书》送达的公告 _
+ 其他公告 _
+ 国家税务总局泉州市税务局</t>
         </is>
       </c>
       <c r="AI9" s="2" t="inlineStr">
@@ -1713,101 +1715,97 @@
       </c>
       <c r="AJ9" s="2" t="inlineStr">
         <is>
-          <t>官方页面显示该决定书已被撤销。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CASE-a62e569c195adc3c</t>
+          <t>CASE-717dfe3250926214</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DOC-b1dda915d4e6117d</t>
+          <t>DOC-7df9c075e55777a1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>遵义市</t>
+          <t>泰州市</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局泰州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局泰州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>贵州服格定商贸有限公司</t>
+          <t>靖江市长凌金属材料有限公司</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>91520302MABUEHN034</t>
+          <t>91321282742461893K</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>遵税一稽处〔2026〕30号</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>遵税一稽处〔2026〕30号</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>增值税</t>
-        </is>
-      </c>
+          <t>泰税一稽罚〔2025〕54号</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>泰税一稽罚〔2025〕54号</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
       <c r="R10" s="3" t="n"/>
       <c r="S10" s="3" t="n"/>
       <c r="T10" s="3" t="n"/>
       <c r="U10" s="3" t="n"/>
-      <c r="V10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>接上级通知,经我局研究决定,撤销上述《税务行政处罚决定书》。</t>
+        </is>
+      </c>
       <c r="W10" s="4" t="n"/>
       <c r="X10" s="4" t="n">
-        <v>46185</v>
+        <v>46191</v>
       </c>
       <c r="Y10" s="4" t="n"/>
       <c r="Z10" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1817,7 +1815,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE10" s="5" t="inlineStr">
@@ -1829,61 +1827,65 @@
       <c r="AG10" s="2" t="inlineStr"/>
       <c r="AH10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 关于撤销《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI10" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ10" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>官方页面显示该决定书已被撤销。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>CASE-13a8aac51595155a</t>
+          <t>CASE-a62e569c195adc3c</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>DOC-7189c9a2cee8e8ce</t>
+          <t>DOC-b1dda915d4e6117d</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>温州市</t>
+          <t>遵义市</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局遵义市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局遵义市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>温作潘</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr"/>
+          <t>贵州服格定商贸有限公司</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>91520302MABUEHN034</t>
+        </is>
+      </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1892,21 +1894,25 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>温税三稽处〔2026〕100号</t>
+          <t>遵税一稽处〔2026〕30号</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>温税三稽处〔2026〕100号</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>温税三稽罚〔2026〕65号</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
+          <t>遵税一稽处〔2026〕30号</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>增值税</t>
+        </is>
+      </c>
       <c r="R11" s="3" t="n"/>
       <c r="S11" s="3" t="n"/>
       <c r="T11" s="3" t="n"/>
@@ -1914,18 +1920,18 @@
       <c r="V11" s="2" t="inlineStr"/>
       <c r="W11" s="4" t="n"/>
       <c r="X11" s="4" t="n">
-        <v>46175</v>
+        <v>46185</v>
       </c>
       <c r="Y11" s="4" t="n"/>
       <c r="Z11" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1935,7 +1941,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE11" s="5" t="inlineStr">
@@ -1943,20 +1949,16 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF11" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF11" s="2" t="inlineStr"/>
       <c r="AG11" s="2" t="inlineStr"/>
       <c r="AH11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
+          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
         </is>
       </c>
       <c r="AI11" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>页面已删除</t>
         </is>
       </c>
       <c r="AJ11" s="2" t="inlineStr">
@@ -1967,7 +1969,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
@@ -1976,7 +1978,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>DOC-02fc2468fd0396a6</t>
+          <t>DOC-7189c9a2cee8e8ce</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2009,12 +2011,12 @@
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>温税三稽罚〔2026〕65号</t>
+          <t>温税三稽处〔2026〕100号</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2043,7 +2045,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -2089,66 +2091,66 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CASE-f8625e66b291a216</t>
+          <t>CASE-13a8aac51595155a</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>DOC-7970511393924720</t>
+          <t>DOC-02fc2468fd0396a6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>温州市</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>贵州翰缤商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>91520114MAAK1C546F</t>
-        </is>
-      </c>
+          <t>温作潘</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>筑税二稽处〔2026〕27号</t>
+          <t>温税三稽罚〔2026〕65号</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>筑税二稽处〔2026〕27号</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr"/>
+          <t>温税三稽处〔2026〕100号</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>温税三稽罚〔2026〕65号</t>
+        </is>
+      </c>
       <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr"/>
       <c r="R13" s="3" t="n"/>
@@ -2158,14 +2160,14 @@
       <c r="V13" s="2" t="inlineStr"/>
       <c r="W13" s="4" t="n"/>
       <c r="X13" s="4" t="n">
-        <v>46156</v>
+        <v>46175</v>
       </c>
       <c r="Y13" s="4" t="n"/>
       <c r="Z13" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -2179,7 +2181,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE13" s="5" t="inlineStr">
@@ -2187,16 +2189,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AF13" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG13" s="2" t="inlineStr"/>
       <c r="AH13" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局关于送达《税务处理决定书》的公告</t>
+          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
         </is>
       </c>
       <c r="AI13" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ13" s="2" t="inlineStr">
@@ -2207,16 +2213,16 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASE-0f4867f7b70d12f3</t>
+          <t>CASE-f8625e66b291a216</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DOC-6f25d6b79e123d03</t>
+          <t>DOC-7970511393924720</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2232,22 +2238,22 @@
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局贵阳市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局贵阳市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>贵州铂朗物流有限公司</t>
+          <t>贵州翰缤商贸有限公司</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>91520115MAAK0DB335</t>
+          <t>91520114MAAK1C546F</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
@@ -2258,19 +2264,15 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
+          <t>筑税二稽处〔2026〕27号</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>筑税三稽罚〔2026〕22号</t>
-        </is>
-      </c>
+          <t>筑税二稽处〔2026〕27号</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
       <c r="R14" s="3" t="n"/>
@@ -2280,14 +2282,14 @@
       <c r="V14" s="2" t="inlineStr"/>
       <c r="W14" s="4" t="n"/>
       <c r="X14" s="4" t="n">
-        <v>46122</v>
+        <v>46156</v>
       </c>
       <c r="Y14" s="4" t="n"/>
       <c r="Z14" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -2313,7 +2315,7 @@
       <c r="AG14" s="2" t="inlineStr"/>
       <c r="AH14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
+          <t>国家税务总局贵阳市税务局第二稽查局关于送达《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI14" s="2" t="inlineStr">
@@ -2329,7 +2331,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
@@ -2338,7 +2340,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>DOC-e8233eb0e06b6e3e</t>
+          <t>DOC-6f25d6b79e123d03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2375,12 +2377,12 @@
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽罚〔2026〕22号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2409,7 +2411,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -2451,68 +2453,68 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CASE-136615addd5d0c0e</t>
+          <t>CASE-0f4867f7b70d12f3</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>DOC-551df7dc5c028b27</t>
+          <t>DOC-e8233eb0e06b6e3e</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>来宾市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>广西欣瑞木业有限公司</t>
+          <t>贵州铂朗物流有限公司</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>91451322MAD89XWX07</t>
+          <t>91520115MAAK0DB335</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr"/>
@@ -2524,14 +2526,14 @@
       <c r="V16" s="2" t="inlineStr"/>
       <c r="W16" s="4" t="n"/>
       <c r="X16" s="4" t="n">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="Y16" s="4" t="n"/>
       <c r="Z16" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -2545,7 +2547,7 @@
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE16" s="5" t="inlineStr">
@@ -2557,12 +2559,12 @@
       <c r="AG16" s="2" t="inlineStr"/>
       <c r="AH16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
         </is>
       </c>
       <c r="AI16" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>页面已删除</t>
         </is>
       </c>
       <c r="AJ16" s="2" t="inlineStr">
@@ -2573,7 +2575,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
@@ -2582,7 +2584,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>DOC-21f0193b66d5c3e9</t>
+          <t>DOC-551df7dc5c028b27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2619,12 +2621,12 @@
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>来市税二稽处〔2026〕6号</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2653,7 +2655,7 @@
         <v>46229</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -2695,47 +2697,47 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CASE-393a878d93a22709</t>
+          <t>CASE-136615addd5d0c0e</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>DOC-cda8cba853896b18</t>
+          <t>DOC-21f0193b66d5c3e9</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>广州市</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>番禺区</t>
-        </is>
-      </c>
+          <t>来宾市</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>广州赞荣服装有限公司</t>
+          <t>广西欣瑞木业有限公司</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>91440113MA59AJFJ1J</t>
+          <t>91451322MAD89XWX07</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
@@ -2746,13 +2748,17 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>穗番税退罚字〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>来市税二稽罚〔2026〕4号</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>来市税二稽处〔2026〕6号</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>穗番税退罚字〔2026〕1号</t>
+          <t>来市税二稽罚〔2026〕4号</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr"/>
@@ -2764,14 +2770,14 @@
       <c r="V18" s="2" t="inlineStr"/>
       <c r="W18" s="4" t="n"/>
       <c r="X18" s="4" t="n">
-        <v>46091</v>
+        <v>46119</v>
       </c>
       <c r="Y18" s="4" t="n"/>
       <c r="Z18" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -2785,7 +2791,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE18" s="5" t="inlineStr">
@@ -2793,131 +2799,107 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF18" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF18" s="2" t="inlineStr"/>
       <c r="AG18" s="2" t="inlineStr"/>
       <c r="AH18" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
+          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
         </is>
       </c>
       <c r="AI18" s="2" t="inlineStr">
         <is>
-          <t>内容不匹配</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ18" s="2" t="inlineStr">
         <is>
-          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CASE-f94bf08964abff5a</t>
+          <t>CASE-393a878d93a22709</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>DOC-4574b1aadef8f30d</t>
+          <t>DOC-cda8cba853896b18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>广东省</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
+          <t>广州市</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>番禺区</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局常州市税务局稽查局</t>
-        </is>
-      </c>
+          <t>国家税务总局广州市番禺区税务局</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>常州市文杰车辆配件厂</t>
+          <t>广州赞荣服装有限公司</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>91320411799075280A</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>朱某</t>
-        </is>
-      </c>
+          <t>91440113MA59AJFJ1J</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕73号</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>常税稽处〔2026〕73号</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公 月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>179137.12</v>
-      </c>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="3" t="n"/>
       <c r="S19" s="3" t="n"/>
       <c r="T19" s="3" t="n"/>
       <c r="U19" s="3" t="n"/>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市 份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元,</t>
-        </is>
-      </c>
-      <c r="W19" s="4" t="n">
-        <v>46044</v>
-      </c>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="4" t="n"/>
       <c r="X19" s="4" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="Y19" s="4" t="n"/>
       <c r="Z19" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2927,7 +2909,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE19" s="5" t="inlineStr">
@@ -2943,32 +2925,32 @@
       <c r="AG19" s="2" t="inlineStr"/>
       <c r="AH19" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
+          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
         </is>
       </c>
       <c r="AI19" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>内容不匹配</t>
         </is>
       </c>
       <c r="AJ19" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CASE-0b4a4519ba4f5ad9</t>
+          <t>CASE-f94bf08964abff5a</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>DOC-5376b9bae81cfc82</t>
+          <t>DOC-4574b1aadef8f30d</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2994,15 +2976,19 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>常州好佳车辆配件有限公司</t>
+          <t>常州市文杰车辆配件厂</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>91320411094264460B</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
+          <t>91320411799075280A</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>朱某</t>
+        </is>
+      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
           <t>税务处理决定书</t>
@@ -3010,36 +2996,52 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕71号</t>
+          <t>常税稽处〔2026〕73号</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕71号</t>
+          <t>常税稽处〔2026〕73号</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="3" t="n"/>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公 月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>179137.12</v>
+      </c>
       <c r="S20" s="3" t="n"/>
       <c r="T20" s="3" t="n"/>
       <c r="U20" s="3" t="n"/>
-      <c r="V20" s="2" t="inlineStr"/>
-      <c r="W20" s="4" t="n"/>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市 份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元,</t>
+        </is>
+      </c>
+      <c r="W20" s="4" t="n">
+        <v>46044</v>
+      </c>
       <c r="X20" s="4" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="Y20" s="4" t="n"/>
       <c r="Z20" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -3065,7 +3067,7 @@
       <c r="AG20" s="2" t="inlineStr"/>
       <c r="AH20" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州好佳车辆配件有限公司《税务处理决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI20" s="2" t="inlineStr">
@@ -3081,16 +3083,16 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CASE-61b9b55a9d3357c7</t>
+          <t>CASE-0b4a4519ba4f5ad9</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>DOC-1228a9c92b2b0632</t>
+          <t>DOC-5376b9bae81cfc82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3106,22 +3108,22 @@
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局常州市税务局稽查局</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>常州市三鹏机械有限公司</t>
+          <t>常州好佳车辆配件有限公司</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>91320404732260748Q</t>
+          <t>91320411094264460B</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
@@ -3132,50 +3134,36 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
+          <t>常税稽处〔2026〕71号</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>常税稽一罚〔2026〕14号</t>
-        </is>
-      </c>
+          <t>常税稽处〔2026〕71号</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>63464.09</v>
-      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="3" t="n"/>
       <c r="S21" s="3" t="n"/>
       <c r="T21" s="3" t="n"/>
       <c r="U21" s="3" t="n"/>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
-        </is>
-      </c>
+      <c r="V21" s="2" t="inlineStr"/>
       <c r="W21" s="4" t="n"/>
       <c r="X21" s="4" t="n">
-        <v>46066</v>
+        <v>46087</v>
       </c>
       <c r="Y21" s="4" t="n"/>
       <c r="Z21" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3193,16 +3181,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AF21" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG21" s="2" t="inlineStr"/>
       <c r="AH21" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州好佳车辆配件有限公司《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI21" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ21" s="2" t="inlineStr">
@@ -3213,7 +3205,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
@@ -3222,7 +3214,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>DOC-b97456a64b153f67</t>
+          <t>DOC-1228a9c92b2b0632</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3259,12 +3251,12 @@
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>常税稽一罚〔2026〕14号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3283,11 +3275,11 @@
           <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R22" s="3" t="n"/>
+      <c r="R22" s="3" t="n">
+        <v>63464.09</v>
+      </c>
       <c r="S22" s="3" t="n"/>
-      <c r="T22" s="3" t="n">
-        <v>20000</v>
-      </c>
+      <c r="T22" s="3" t="n"/>
       <c r="U22" s="3" t="n"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
@@ -3303,7 +3295,7 @@
         <v>46229</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
@@ -3345,103 +3337,97 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CASE-f78ec1a594442165</t>
+          <t>CASE-61b9b55a9d3357c7</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>DOC-fbbe4a664b14f54b</t>
+          <t>DOC-b97456a64b153f67</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>安顺市</t>
+          <t>常州市</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
+          <t>常州市三鹏机械有限公司</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>91520423MA6DLH799Q</t>
+          <t>91320404732260748Q</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一罚〔2026〕14号</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
-        </is>
-      </c>
+          <t>常税稽一罚〔2026〕14号</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="n">
-        <v>64884.41</v>
-      </c>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="n"/>
       <c r="S23" s="3" t="n"/>
-      <c r="T23" s="3" t="n"/>
+      <c r="T23" s="3" t="n">
+        <v>20000</v>
+      </c>
       <c r="U23" s="3" t="n"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
-      <c r="W23" s="4" t="n">
-        <v>45898</v>
-      </c>
+          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
+        </is>
+      </c>
+      <c r="W23" s="4" t="n"/>
       <c r="X23" s="4" t="n">
-        <v>46043</v>
+        <v>46066</v>
       </c>
       <c r="Y23" s="4" t="n"/>
       <c r="Z23" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
@@ -3455,7 +3441,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE23" s="5" t="inlineStr">
@@ -3463,15 +3449,11 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF23" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF23" s="2" t="inlineStr"/>
       <c r="AG23" s="2" t="inlineStr"/>
       <c r="AH23" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI23" s="2" t="inlineStr">
@@ -3481,13 +3463,13 @@
       </c>
       <c r="AJ23" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
@@ -3496,7 +3478,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>DOC-9a828a6048b54b6c</t>
+          <t>DOC-fbbe4a664b14f54b</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3533,27 +3515,27 @@
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
           <t>安市税稽罚〔2026〕1号</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>安市税稽处〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3561,11 +3543,11 @@
           <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R24" s="3" t="n"/>
+      <c r="R24" s="3" t="n">
+        <v>64884.41</v>
+      </c>
       <c r="S24" s="3" t="n"/>
-      <c r="T24" s="3" t="n">
-        <v>200000</v>
-      </c>
+      <c r="T24" s="3" t="n"/>
       <c r="U24" s="3" t="n"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
@@ -3583,7 +3565,7 @@
         <v>46229</v>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
@@ -3623,97 +3605,109 @@
       </c>
       <c r="AJ24" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CASE-fe959d4c6c52d910</t>
+          <t>CASE-f78ec1a594442165</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>DOC-f2643f2a0719d8d1</t>
+          <t>DOC-9a828a6048b54b6c</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>南宁市</t>
+          <t>安顺市</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局稽查局</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>南宁洪谦金贸易有限公司</t>
+          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>91450103MA5K9WHY7U</t>
+          <t>91520423MA6DLH799Q</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>南市税一稽处〔2026〕2号</t>
+          <t>安市税稽罚〔2026〕1号</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>南市税一稽处〔2026〕2号</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr"/>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽罚〔2026〕1号</t>
+        </is>
+      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>经我局2025年10月29日至2025年12月8日对你公司(地址:南宁市青秀区云景路11号春晖花园C区3栋2单元1606号)2015年12月2日至2016年12月31日期间的涉税情况进行了检查,你(单位)存在以下违法事实: 经查询你公司向税务机关报备的银行账号:广西北部湾银行南宁市财富国际支行800099398800015,经函询广西北部湾银行南宁市财富国际支行,存在以下问题: 上述行为属于开具与实际经营业务情况不符的增值税发票,违反了《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第587号修改)第二十二条第一款、第二款第(一)项的规定,属于虚开发票行为。</t>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
+          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R25" s="3" t="n"/>
       <c r="S25" s="3" t="n"/>
-      <c r="T25" s="3" t="n"/>
+      <c r="T25" s="3" t="n">
+        <v>200000</v>
+      </c>
       <c r="U25" s="3" t="n"/>
-      <c r="V25" s="2" t="inlineStr"/>
-      <c r="W25" s="4" t="n"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="W25" s="4" t="n">
+        <v>45898</v>
+      </c>
       <c r="X25" s="4" t="n">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="Y25" s="4" t="n"/>
       <c r="Z25" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
@@ -3727,7 +3721,7 @@
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE25" s="5" t="inlineStr">
@@ -3743,61 +3737,65 @@
       <c r="AG25" s="2" t="inlineStr"/>
       <c r="AH25" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局税务文书送达公告_国家税务总局南宁市税务局</t>
+          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI25" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ25" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CASE-1983d97878508732</t>
+          <t>CASE-fe959d4c6c52d910</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>DOC-f9760895b4f08cc2</t>
+          <t>DOC-f2643f2a0719d8d1</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>二连浩特市</t>
+          <t>南宁市</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局</t>
+          <t>国家税务总局南宁市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局稽查局</t>
+          <t>国家税务总局南宁市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>二连市坤益腾金属有限公司</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr"/>
+          <t>南宁洪谦金贸易有限公司</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>91450103MA5K9WHY7U</t>
+        </is>
+      </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
@@ -3806,18 +3804,18 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
+          <t>南市税一稽处〔2026〕2号</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
+          <t>南市税一稽处〔2026〕2号</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
+          <t>经我局2025年10月29日至2025年12月8日对你公司(地址:南宁市青秀区云景路11号春晖花园C区3栋2单元1606号)2015年12月2日至2016年12月31日期间的涉税情况进行了检查,你(单位)存在以下违法事实: 经查询你公司向税务机关报备的银行账号:广西北部湾银行南宁市财富国际支行800099398800015,经函询广西北部湾银行南宁市财富国际支行,存在以下问题: 上述行为属于开具与实际经营业务情况不符的增值税发票,违反了《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第587号修改)第二十二条第一款、第二款第(一)项的规定,属于虚开发票行为。</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3829,19 +3827,17 @@
       <c r="S26" s="3" t="n"/>
       <c r="T26" s="3" t="n"/>
       <c r="U26" s="3" t="n"/>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
-        </is>
-      </c>
+      <c r="V26" s="2" t="inlineStr"/>
       <c r="W26" s="4" t="n"/>
-      <c r="X26" s="4" t="n"/>
+      <c r="X26" s="4" t="n">
+        <v>46031</v>
+      </c>
       <c r="Y26" s="4" t="n"/>
       <c r="Z26" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
@@ -3855,7 +3851,7 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE26" s="5" t="inlineStr">
@@ -3863,36 +3859,40 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF26" s="2" t="inlineStr"/>
+      <c r="AF26" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG26" s="2" t="inlineStr"/>
       <c r="AH26" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>国家税务总局南宁市税务局第一稽查局税务文书送达公告_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI26" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ26" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CASE-d4b6986f3f97cd28</t>
+          <t>CASE-1983d97878508732</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>DOC-442cf3d9a5280c12</t>
+          <t>DOC-f9760895b4f08cc2</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3902,19 +3902,23 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>鄂尔多斯市</t>
+          <t>二连浩特市</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局二连浩特市税务局</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>第二稽查局</t>
+          <t>国家税务总局二连浩特市税务局稽查局</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>廖礼平</t>
+          <t>二连市坤益腾金属有限公司</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -3926,36 +3930,32 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
+          <t>二税稽处〔2025〕1号</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
+          <t>二税稽处〔2025〕1号</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
+          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>个人所得税、印花税</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="n">
-        <v>15072487.5</v>
-      </c>
-      <c r="S27" s="3" t="n">
-        <v>1046925</v>
-      </c>
+          <t>增值税</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="n"/>
+      <c r="S27" s="3" t="n"/>
       <c r="T27" s="3" t="n"/>
       <c r="U27" s="3" t="n"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
+          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
         </is>
       </c>
       <c r="W27" s="4" t="n"/>
@@ -3965,7 +3965,7 @@
         <v>46229</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
@@ -4001,55 +4001,47 @@
       </c>
       <c r="AJ27" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
+          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CASE-7e3d4a321440d6a7</t>
+          <t>CASE-d4b6986f3f97cd28</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>DOC-bed9330343ed06af</t>
+          <t>DOC-442cf3d9a5280c12</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>鄂尔多斯市</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
-        </is>
-      </c>
+      <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
+          <t>第二稽查局</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>天津展达科技有限公司</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>91120116300738701X</t>
-        </is>
-      </c>
+          <t>廖礼平</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
@@ -4058,48 +4050,46 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
+          <t>鄂税二稽处〔2023〕29号</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
+          <t>鄂税二稽处〔2023〕29号</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+          <t>个人所得税、印花税</t>
         </is>
       </c>
       <c r="R28" s="3" t="n">
-        <v>920146.9399999999</v>
-      </c>
-      <c r="S28" s="3" t="n"/>
+        <v>15072487.5</v>
+      </c>
+      <c r="S28" s="3" t="n">
+        <v>1046925</v>
+      </c>
       <c r="T28" s="3" t="n"/>
       <c r="U28" s="3" t="n"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
         </is>
       </c>
       <c r="W28" s="4" t="n"/>
       <c r="X28" s="4" t="n"/>
       <c r="Y28" s="4" t="n"/>
       <c r="Z28" s="4" t="n">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
@@ -4125,7 +4115,7 @@
       <c r="AG28" s="2" t="inlineStr"/>
       <c r="AH28" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="AI28" s="2" t="inlineStr">
@@ -4135,13 +4125,13 @@
       </c>
       <c r="AJ28" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
@@ -4150,7 +4140,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>DOC-388bd01c01bbb789</t>
+          <t>DOC-bed9330343ed06af</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -4187,24 +4177,24 @@
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
           <t>津税一稽罚〔2023〕21号</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
           <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
@@ -4215,11 +4205,11 @@
           <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R29" s="3" t="n"/>
+      <c r="R29" s="3" t="n">
+        <v>920146.9399999999</v>
+      </c>
       <c r="S29" s="3" t="n"/>
-      <c r="T29" s="3" t="n">
-        <v>131368.5</v>
-      </c>
+      <c r="T29" s="3" t="n"/>
       <c r="U29" s="3" t="n"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
@@ -4233,7 +4223,7 @@
         <v>46230</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
@@ -4273,20 +4263,154 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7e3d4a321440d6a7</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>DOC-388bd01c01bbb789</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>91120116300738701X</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>税务行政处罚决定书</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="n"/>
+      <c r="S30" s="3" t="n"/>
+      <c r="T30" s="3" t="n">
+        <v>131368.5</v>
+      </c>
+      <c r="U30" s="3" t="n"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W30" s="4" t="n"/>
+      <c r="X30" s="4" t="n"/>
+      <c r="Y30" s="4" t="n"/>
+      <c r="Z30" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AA30" s="4" t="n">
+        <v>46233</v>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE30" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF30" s="2" t="inlineStr"/>
+      <c r="AG30" s="2" t="inlineStr"/>
+      <c r="AH30" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+        </is>
+      </c>
+      <c r="AI30" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ30" s="2" t="inlineStr">
+        <is>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ29"/>
-  <conditionalFormatting sqref="AD2:AD29">
+  <autoFilter ref="A1:AJ30"/>
+  <conditionalFormatting sqref="AD2:AD30">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AD2="待核验"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI2:AI29">
+  <conditionalFormatting sqref="AI2:AI30">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>AND($AI2&lt;&gt;"正常",$AI2&lt;&gt;"附件正常")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AD2:AD29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AD2:AD30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"已核验,待核验,人工复核完成"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4296,39 +4420,40 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF6" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF7" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF8" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE9" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE10" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE11" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF11" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE12" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF12" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE12" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF12" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF13" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE14" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE15" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE16" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE17" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE18" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF18" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE19" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF19" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE20" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF20" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE21" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE19" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF19" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE20" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF20" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE21" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF21" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE22" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE23" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF23" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE24" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF24" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE25" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF25" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE26" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE24" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF24" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE25" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF25" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE26" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF26" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE27" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE28" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE29" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE30" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -4341,7 +4466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ15"/>
+  <dimension ref="A1:AJ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4566,49 +4691,49 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CASE-7b9a26f2ac401107</t>
+          <t>CASE-89fc66bfc8dad80d</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>DOC-f6c6ea472b2ca04a</t>
+          <t>DOC-6e5b966cd65a4366</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>三明市</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
+          <t>北海市</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>银海区</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局三明市税务局第一稽查局</t>
+          <t>国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局三明市税务局第一稽查局</t>
+          <t>国家税务总局北海市税务局稽查局</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>三明众祥房地产开发有限公司</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>91350400678473231W</t>
-        </is>
-      </c>
+          <t>广西耿仁建材有限公司</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -4617,46 +4742,42 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>明税一稽处〔2026〕20号</t>
+          <t>北市税稽处〔2026〕14号</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>明税一稽处〔2026〕20号</t>
+          <t>北市税稽处〔2026〕14号</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2016年期间,在没有真实业务情况下,取得重庆市博海建设工程(集团)有限公司、福建九九建设有限公司三明分公司开具的不符合规定的发票,发票金额400252379元,在企业所得税税前扣除,造成少缴纳企业所得税100063094.75元,该行为违反《中华人民共和国税收征收管理法》(2015年4月24日主席令第二十三号修改)第六十三条第一款 纳税人伪造、变造、隐匿、擅自销毁账簿、记账凭证,或者在账簿上多列支出或者不列、少列收入,或者经税务机关通知申报而拒不申报或者进行虚假的纳税申报,不缴或者少缴应纳税款的,是偷税。 对纳税人偷税的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款; 之规定,对你公司在账上多列支出,造成少缴企业所得税100063094.75元的行为认定为偷税。 之规定,对你公司少缴的企业所得税从滞纳之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
+          <t>我局于2026年2月11日至2026年7月15日对你公司(地址:北海市银海区新世纪大道15号辰宸花园3幢二单元0901号)2026年1月1日至2026年1月31日期间的涉税情况进行了检查,违法事实及处理决定如下: (2)短时间开具大量大额发票且未申报 你公司未进行纳税申报,不缴或者少缴2026年1月增值税194612.47元,2026年1月城市维护建设税13622.87元,合计208235.34元。 根据《中华人民共和国税收征收管理法》第六十三条第一款规定,对上述行为定性为偷税,向你公司追缴少缴的2026年增值税194612.47元,城市维护建设税13622.87元,合计208235.34元。 1.根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)的规定,对你公司少缴所属期2026年1月的教育费附加5838.37元,予以追缴。 2.根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条的规定,对你公司少缴所属期2026年1月地方教育附加3892.25元,予以追缴。 根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司少缴的税款从税款滞纳之日起至实际缴纳税款之日止按日加收滞纳税款万分之五的滞纳金,滞纳金由金三系统自动计算加收。 (四)你公司无法联系且实地核查无实际生产地址、无生产能力、查无下落,短期开票金额大,无法核实资金流,未进行纳税申报,根据《国家税务总局关于走逃(失联)企业开具增值税专用发票认定处理有关问题的公告》(国家税务总局公告2016年第76号),将你公司按走逃(失联)处理,根据《中华人民共和国发票管理办法》(国函〔1993〕174号)第二十一条第(一)项,你公司无生产能力,却为他人开具与实际经营业务情况不符的发票,属于虚开发票的行为。</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>企业所得税</t>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R2" s="3" t="n">
-        <v>100063094.75</v>
+        <v>208235.34</v>
       </c>
       <c r="S2" s="3" t="n"/>
       <c r="T2" s="3" t="n"/>
       <c r="U2" s="3" t="n"/>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>据《中华人民共和国税收征收管理法实施细则》第106条规定,将该文书予以公告送达,自公告之日起满30日视为送达。</t>
-        </is>
-      </c>
+      <c r="V2" s="2" t="inlineStr"/>
       <c r="W2" s="4" t="n"/>
       <c r="X2" s="4" t="n">
-        <v>46223</v>
+        <v>46232</v>
       </c>
       <c r="Y2" s="4" t="n"/>
       <c r="Z2" s="4" t="n">
-        <v>46229</v>
+        <v>46233</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -4682,9 +4803,7 @@
       <c r="AG2" s="2" t="inlineStr"/>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>关于送达三明众祥房地产开发有限公司 《税务处理决定书》的公告 _
- 其他公告 _
- 国家税务总局三明市税务局</t>
+          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕14号)_国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="AI2" s="2" t="inlineStr">
@@ -4692,24 +4811,20 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
+      <c r="AJ2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CASE-31e4a827dfd253f2</t>
+          <t>CASE-7b9a26f2ac401107</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>DOC-3ec54358fce2350d</t>
+          <t>DOC-f6c6ea472b2ca04a</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -4719,28 +4834,28 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>福州市</t>
+          <t>三明市</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局三明市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局三明市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>福州顺路汽车运输有限公司</t>
+          <t>三明众祥房地产开发有限公司</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>91350102MA31MF6611</t>
+          <t>91350400678473231W</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
@@ -4751,46 +4866,46 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽处〔2026〕137号</t>
+          <t>明税一稽处〔2026〕20号</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽处〔2026〕137号</t>
+          <t>明税一稽处〔2026〕20号</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>我局于2025年7月10日起对你公司(地址:福建省闽侯县青口镇祥宏南路922号)2023年1月1日至2024年12月31日期间的发票涉税情况进行检查,违法事实及处理决定如下: (二)你公司取得毕节七星关区辰楚汽车服务部(个人独资)、毕节七星关锦悦汽车服务部(个人独资)、贵州杨亭汽车销售有限公司、贵州楠鑫汽车销售有限公司已证实虚开的35份机动车发票。 (二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 (三)根据《中华人民共和国企业所得税法》第五条、第八条、《企业所得税税前扣除凭证管理办法》(国家税务总局公告2018年第28号发布)第四条、第十二条的规定,你公司取得上述虚开的发票不得作为税前扣除凭证。</t>
+          <t>情况进行了检查,违法事实及处理决定如下: 2016年期间,在没有真实业务情况下,取得重庆市博海建设工程(集团)有限公司、福建九九建设有限公司三明分公司开具的不符合规定的发票,发票金额400252379元,在企业所得税税前扣除,造成少缴纳企业所得税100063094.75元,该行为违反《中华人民共和国税收征收管理法》(2015年4月24日主席令第二十三号修改)第六十三条第一款 纳税人伪造、变造、隐匿、擅自销毁账簿、记账凭证,或者在账簿上多列支出或者不列、少列收入,或者经税务机关通知申报而拒不申报或者进行虚假的纳税申报,不缴或者少缴应纳税款的,是偷税。 对纳税人偷税的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款; 之规定,对你公司在账上多列支出,造成少缴企业所得税100063094.75元的行为认定为偷税。 之规定,对你公司少缴的企业所得税从滞纳之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
+          <t>企业所得税</t>
         </is>
       </c>
       <c r="R3" s="3" t="n">
-        <v>3778.22</v>
+        <v>100063094.75</v>
       </c>
       <c r="S3" s="3" t="n"/>
       <c r="T3" s="3" t="n"/>
       <c r="U3" s="3" t="n"/>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>(二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期城市维护建设税124.75元。 根据《征收教育费附加的暂行规定》第二条、第三条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期教育费附加53.47元。 根据《福建省人民政府关于调整地方教育附加征收标准等有关问题的通知》(闽政文〔2011〕230号)第一条、第二条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期地方教育附加35.64元。</t>
+          <t>据《中华人民共和国税收征收管理法实施细则》第106条规定,将该文书予以公告送达,自公告之日起满30日视为送达。</t>
         </is>
       </c>
       <c r="W3" s="4" t="n"/>
       <c r="X3" s="4" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="Y3" s="4" t="n"/>
       <c r="Z3" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -4816,9 +4931,9 @@
       <c r="AG3" s="2" t="inlineStr"/>
       <c r="AH3" s="2" t="inlineStr">
         <is>
-          <t>关于送达福州顺路汽车运输有限公司《税务处理决定书》的公告 _
- 其他类 _
- 国家税务总局福州市税务局</t>
+          <t>关于送达三明众祥房地产开发有限公司 《税务处理决定书》的公告 _
+ 其他公告 _
+ 国家税务总局三明市税务局</t>
         </is>
       </c>
       <c r="AI3" s="2" t="inlineStr">
@@ -4834,16 +4949,16 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CASE-3f564fd9992b1ae3</t>
+          <t>CASE-31e4a827dfd253f2</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>DOC-c34e1d13286aafe2</t>
+          <t>DOC-3ec54358fce2350d</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -4853,28 +4968,28 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>泉州市</t>
+          <t>福州市</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局第二稽查局</t>
+          <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局第二稽查局</t>
+          <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>泉州隆鸿服装制造有限公司</t>
+          <t>福州顺路汽车运输有限公司</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>91350525MA8U3U963L</t>
+          <t>91350102MA31MF6611</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
@@ -4885,18 +5000,18 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>泉税二稽处〔2026〕107号</t>
+          <t>榕税一稽处〔2026〕137号</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>泉税二稽处〔2026〕107号</t>
+          <t>榕税一稽处〔2026〕137号</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>日对你公司税收违法事实依法作出《税务处理决定书》(泉税二稽处〔 涉税情况进行了检查,查明违法事实及处理决定如下: 年你公司在无真实货物交易的情况下,取得河南中弘纺织有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 年期间,你公司在无真实货物交易的情况下,取得开封兴旺纺织品有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 上述违法事实有检查人员实地检查资料、电话拨打记录、邮寄退回函件、《已证实虚开通知单》等相关受托协查资料、主管税务机关出具的《已抵扣证明》、《情况说明》和你公司的申报纳税资料、银行账户流水等 号第三次修订)第二十一条第二款第二项之规定,认定你公司让他人为自己虚开 号第二次修订)第九条和《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告〔 号)之规定,对你公司取得上述已证实虚开的 之规定,决定向你公司追缴少缴的城市维护建设税-增值税附征 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 规定,决定向你公司追缴少缴的教育费附加-增值税附征 规定,决定向你公司追缴少缴的地方教育附加-增值税附征</t>
+          <t>我局于2025年7月10日起对你公司(地址:福建省闽侯县青口镇祥宏南路922号)2023年1月1日至2024年12月31日期间的发票涉税情况进行检查,违法事实及处理决定如下: (二)你公司取得毕节七星关区辰楚汽车服务部(个人独资)、毕节七星关锦悦汽车服务部(个人独资)、贵州杨亭汽车销售有限公司、贵州楠鑫汽车销售有限公司已证实虚开的35份机动车发票。 (二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 (三)根据《中华人民共和国企业所得税法》第五条、第八条、《企业所得税税前扣除凭证管理办法》(国家税务总局公告2018年第28号发布)第四条、第十二条的规定,你公司取得上述虚开的发票不得作为税前扣除凭证。</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4904,25 +5019,27 @@
           <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R4" s="3" t="n"/>
+      <c r="R4" s="3" t="n">
+        <v>3778.22</v>
+      </c>
       <c r="S4" s="3" t="n"/>
       <c r="T4" s="3" t="n"/>
       <c r="U4" s="3" t="n"/>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>由于你公司走逃失联、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 (五)根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司上述应补缴税款按税款所属时间从税款滞纳之日起按日加收万分之五滞纳金</t>
+          <t>(二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期城市维护建设税124.75元。 根据《征收教育费附加的暂行规定》第二条、第三条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期教育费附加53.47元。 根据《福建省人民政府关于调整地方教育附加征收标准等有关问题的通知》(闽政文〔2011〕230号)第一条、第二条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期地方教育附加35.64元。</t>
         </is>
       </c>
       <c r="W4" s="4" t="n"/>
       <c r="X4" s="4" t="n">
-        <v>46202</v>
+        <v>46218</v>
       </c>
       <c r="Y4" s="4" t="n"/>
       <c r="Z4" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -4948,9 +5065,9 @@
       <c r="AG4" s="2" t="inlineStr"/>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>关于对泉州隆鸿服装制造有限公司《税务处理决定书》送达的公告 _
- 其他公告 _
- 国家税务总局泉州市税务局</t>
+          <t>关于送达福州顺路汽车运输有限公司《税务处理决定书》的公告 _
+ 其他类 _
+ 国家税务总局福州市税务局</t>
         </is>
       </c>
       <c r="AI4" s="2" t="inlineStr">
@@ -4966,47 +5083,47 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CASE-a62e569c195adc3c</t>
+          <t>CASE-3f564fd9992b1ae3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>DOC-b1dda915d4e6117d</t>
+          <t>DOC-c34e1d13286aafe2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>遵义市</t>
+          <t>泉州市</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局泉州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局泉州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>贵州服格定商贸有限公司</t>
+          <t>泉州隆鸿服装制造有限公司</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>91520302MABUEHN034</t>
+          <t>91350525MA8U3U963L</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
@@ -5017,40 +5134,44 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>遵税一稽处〔2026〕30号</t>
+          <t>泉税二稽处〔2026〕107号</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>遵税一稽处〔2026〕30号</t>
+          <t>泉税二稽处〔2026〕107号</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
+          <t>日对你公司税收违法事实依法作出《税务处理决定书》(泉税二稽处〔 涉税情况进行了检查,查明违法事实及处理决定如下: 年你公司在无真实货物交易的情况下,取得河南中弘纺织有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 年期间,你公司在无真实货物交易的情况下,取得开封兴旺纺织品有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 上述违法事实有检查人员实地检查资料、电话拨打记录、邮寄退回函件、《已证实虚开通知单》等相关受托协查资料、主管税务机关出具的《已抵扣证明》、《情况说明》和你公司的申报纳税资料、银行账户流水等 号第三次修订)第二十一条第二款第二项之规定,认定你公司让他人为自己虚开 号第二次修订)第九条和《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告〔 号)之规定,对你公司取得上述已证实虚开的 之规定,决定向你公司追缴少缴的城市维护建设税-增值税附征 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 规定,决定向你公司追缴少缴的教育费附加-增值税附征 规定,决定向你公司追缴少缴的地方教育附加-增值税附征</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
+          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R5" s="3" t="n"/>
       <c r="S5" s="3" t="n"/>
       <c r="T5" s="3" t="n"/>
       <c r="U5" s="3" t="n"/>
-      <c r="V5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>由于你公司走逃失联、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 (五)根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司上述应补缴税款按税款所属时间从税款滞纳之日起按日加收万分之五滞纳金</t>
+        </is>
+      </c>
       <c r="W5" s="4" t="n"/>
       <c r="X5" s="4" t="n">
-        <v>46185</v>
+        <v>46202</v>
       </c>
       <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -5064,7 +5185,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE5" s="5" t="inlineStr">
@@ -5076,12 +5197,14 @@
       <c r="AG5" s="2" t="inlineStr"/>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
+          <t>关于对泉州隆鸿服装制造有限公司《税务处理决定书》送达的公告 _
+ 其他公告 _
+ 国家税务总局泉州市税务局</t>
         </is>
       </c>
       <c r="AI5" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr">
@@ -5092,54 +5215,50 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>CASE-f94bf08964abff5a</t>
+          <t>CASE-a62e569c195adc3c</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>DOC-4574b1aadef8f30d</t>
+          <t>DOC-b1dda915d4e6117d</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
+          <t>遵义市</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
+          <t>国家税务总局遵义市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局稽查局</t>
+          <t>国家税务总局遵义市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>常州市文杰车辆配件厂</t>
+          <t>贵州服格定商贸有限公司</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>91320411799075280A</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>朱某</t>
-        </is>
-      </c>
+          <t>91520302MABUEHN034</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>税务处理决定书</t>
@@ -5147,48 +5266,40 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕73号</t>
+          <t>遵税一稽处〔2026〕30号</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕73号</t>
+          <t>遵税一稽处〔2026〕30号</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公 月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
+          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>179137.12</v>
-      </c>
+          <t>增值税</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="n"/>
       <c r="S6" s="3" t="n"/>
       <c r="T6" s="3" t="n"/>
       <c r="U6" s="3" t="n"/>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市 份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元,</t>
-        </is>
-      </c>
-      <c r="W6" s="4" t="n">
-        <v>46044</v>
-      </c>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="4" t="n"/>
       <c r="X6" s="4" t="n">
-        <v>46090</v>
+        <v>46185</v>
       </c>
       <c r="Y6" s="4" t="n"/>
       <c r="Z6" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -5202,7 +5313,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE6" s="5" t="inlineStr">
@@ -5210,20 +5321,16 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF6" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF6" s="2" t="inlineStr"/>
       <c r="AG6" s="2" t="inlineStr"/>
       <c r="AH6" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
+          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
         </is>
       </c>
       <c r="AI6" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>页面已删除</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="inlineStr">
@@ -5234,16 +5341,16 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CASE-61b9b55a9d3357c7</t>
+          <t>CASE-f94bf08964abff5a</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>DOC-1228a9c92b2b0632</t>
+          <t>DOC-4574b1aadef8f30d</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -5259,25 +5366,29 @@
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局常州市税务局稽查局</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>常州市三鹏机械有限公司</t>
+          <t>常州市文杰车辆配件厂</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>91320404732260748Q</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
+          <t>91320411799075280A</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>朱某</t>
+        </is>
+      </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
           <t>税务处理决定书</t>
@@ -5285,46 +5396,48 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
+          <t>常税稽处〔2026〕73号</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>常税稽一罚〔2026〕14号</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
+          <t>常税稽处〔2026〕73号</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公 月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
+        </is>
+      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R7" s="3" t="n">
-        <v>63464.09</v>
+        <v>179137.12</v>
       </c>
       <c r="S7" s="3" t="n"/>
       <c r="T7" s="3" t="n"/>
       <c r="U7" s="3" t="n"/>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
-        </is>
-      </c>
-      <c r="W7" s="4" t="n"/>
+          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市 份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元,</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="n">
+        <v>46044</v>
+      </c>
       <c r="X7" s="4" t="n">
-        <v>46066</v>
+        <v>46090</v>
       </c>
       <c r="Y7" s="4" t="n"/>
       <c r="Z7" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -5346,16 +5459,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AF7" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG7" s="2" t="inlineStr"/>
       <c r="AH7" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI7" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr">
@@ -5366,7 +5483,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -5375,7 +5492,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DOC-b97456a64b153f67</t>
+          <t>DOC-1228a9c92b2b0632</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -5412,12 +5529,12 @@
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>常税稽一罚〔2026〕14号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5436,11 +5553,11 @@
           <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R8" s="3" t="n"/>
+      <c r="R8" s="3" t="n">
+        <v>63464.09</v>
+      </c>
       <c r="S8" s="3" t="n"/>
-      <c r="T8" s="3" t="n">
-        <v>20000</v>
-      </c>
+      <c r="T8" s="3" t="n"/>
       <c r="U8" s="3" t="n"/>
       <c r="V8" s="2" t="inlineStr">
         <is>
@@ -5456,7 +5573,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -5498,103 +5615,97 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>CASE-f78ec1a594442165</t>
+          <t>CASE-61b9b55a9d3357c7</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DOC-fbbe4a664b14f54b</t>
+          <t>DOC-b97456a64b153f67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>安顺市</t>
+          <t>常州市</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
+          <t>常州市三鹏机械有限公司</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91520423MA6DLH799Q</t>
+          <t>91320404732260748Q</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一罚〔2026〕14号</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
-        </is>
-      </c>
+          <t>常税稽一罚〔2026〕14号</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>64884.41</v>
-      </c>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="n"/>
       <c r="S9" s="3" t="n"/>
-      <c r="T9" s="3" t="n"/>
+      <c r="T9" s="3" t="n">
+        <v>20000</v>
+      </c>
       <c r="U9" s="3" t="n"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
-      <c r="W9" s="4" t="n">
-        <v>45898</v>
-      </c>
+          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="n"/>
       <c r="X9" s="4" t="n">
-        <v>46043</v>
+        <v>46066</v>
       </c>
       <c r="Y9" s="4" t="n"/>
       <c r="Z9" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -5608,7 +5719,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE9" s="5" t="inlineStr">
@@ -5616,15 +5727,11 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF9" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF9" s="2" t="inlineStr"/>
       <c r="AG9" s="2" t="inlineStr"/>
       <c r="AH9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI9" s="2" t="inlineStr">
@@ -5634,13 +5741,13 @@
       </c>
       <c r="AJ9" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -5649,7 +5756,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DOC-9a828a6048b54b6c</t>
+          <t>DOC-fbbe4a664b14f54b</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -5686,27 +5793,27 @@
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>安市税稽罚〔2026〕1号</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>安市税稽处〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5714,11 +5821,11 @@
           <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R10" s="3" t="n"/>
+      <c r="R10" s="3" t="n">
+        <v>64884.41</v>
+      </c>
       <c r="S10" s="3" t="n"/>
-      <c r="T10" s="3" t="n">
-        <v>200000</v>
-      </c>
+      <c r="T10" s="3" t="n"/>
       <c r="U10" s="3" t="n"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
@@ -5736,7 +5843,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -5776,97 +5883,109 @@
       </c>
       <c r="AJ10" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>CASE-fe959d4c6c52d910</t>
+          <t>CASE-f78ec1a594442165</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>DOC-f2643f2a0719d8d1</t>
+          <t>DOC-9a828a6048b54b6c</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>南宁市</t>
+          <t>安顺市</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局稽查局</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>南宁洪谦金贸易有限公司</t>
+          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91450103MA5K9WHY7U</t>
+          <t>91520423MA6DLH799Q</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>南市税一稽处〔2026〕2号</t>
+          <t>安市税稽罚〔2026〕1号</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>南市税一稽处〔2026〕2号</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr"/>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽罚〔2026〕1号</t>
+        </is>
+      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>经我局2025年10月29日至2025年12月8日对你公司(地址:南宁市青秀区云景路11号春晖花园C区3栋2单元1606号)2015年12月2日至2016年12月31日期间的涉税情况进行了检查,你(单位)存在以下违法事实: 经查询你公司向税务机关报备的银行账号:广西北部湾银行南宁市财富国际支行800099398800015,经函询广西北部湾银行南宁市财富国际支行,存在以下问题: 上述行为属于开具与实际经营业务情况不符的增值税发票,违反了《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第587号修改)第二十二条第一款、第二款第(一)项的规定,属于虚开发票行为。</t>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
+          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R11" s="3" t="n"/>
       <c r="S11" s="3" t="n"/>
-      <c r="T11" s="3" t="n"/>
+      <c r="T11" s="3" t="n">
+        <v>200000</v>
+      </c>
       <c r="U11" s="3" t="n"/>
-      <c r="V11" s="2" t="inlineStr"/>
-      <c r="W11" s="4" t="n"/>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="n">
+        <v>45898</v>
+      </c>
       <c r="X11" s="4" t="n">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="Y11" s="4" t="n"/>
       <c r="Z11" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -5880,7 +5999,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE11" s="5" t="inlineStr">
@@ -5896,61 +6015,65 @@
       <c r="AG11" s="2" t="inlineStr"/>
       <c r="AH11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局税务文书送达公告_国家税务总局南宁市税务局</t>
+          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI11" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ11" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CASE-1983d97878508732</t>
+          <t>CASE-fe959d4c6c52d910</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>DOC-f9760895b4f08cc2</t>
+          <t>DOC-f2643f2a0719d8d1</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>二连浩特市</t>
+          <t>南宁市</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局</t>
+          <t>国家税务总局南宁市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局稽查局</t>
+          <t>国家税务总局南宁市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>二连市坤益腾金属有限公司</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
+          <t>南宁洪谦金贸易有限公司</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>91450103MA5K9WHY7U</t>
+        </is>
+      </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
@@ -5959,18 +6082,18 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
+          <t>南市税一稽处〔2026〕2号</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
+          <t>南市税一稽处〔2026〕2号</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
+          <t>经我局2025年10月29日至2025年12月8日对你公司(地址:南宁市青秀区云景路11号春晖花园C区3栋2单元1606号)2015年12月2日至2016年12月31日期间的涉税情况进行了检查,你(单位)存在以下违法事实: 经查询你公司向税务机关报备的银行账号:广西北部湾银行南宁市财富国际支行800099398800015,经函询广西北部湾银行南宁市财富国际支行,存在以下问题: 上述行为属于开具与实际经营业务情况不符的增值税发票,违反了《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第587号修改)第二十二条第一款、第二款第(一)项的规定,属于虚开发票行为。</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5982,19 +6105,17 @@
       <c r="S12" s="3" t="n"/>
       <c r="T12" s="3" t="n"/>
       <c r="U12" s="3" t="n"/>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
-        </is>
-      </c>
+      <c r="V12" s="2" t="inlineStr"/>
       <c r="W12" s="4" t="n"/>
-      <c r="X12" s="4" t="n"/>
+      <c r="X12" s="4" t="n">
+        <v>46031</v>
+      </c>
       <c r="Y12" s="4" t="n"/>
       <c r="Z12" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -6008,7 +6129,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE12" s="5" t="inlineStr">
@@ -6016,36 +6137,40 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AF12" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG12" s="2" t="inlineStr"/>
       <c r="AH12" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>国家税务总局南宁市税务局第一稽查局税务文书送达公告_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI12" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ12" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CASE-d4b6986f3f97cd28</t>
+          <t>CASE-1983d97878508732</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>DOC-442cf3d9a5280c12</t>
+          <t>DOC-f9760895b4f08cc2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -6055,19 +6180,23 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>鄂尔多斯市</t>
+          <t>二连浩特市</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局二连浩特市税务局</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>第二稽查局</t>
+          <t>国家税务总局二连浩特市税务局稽查局</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>廖礼平</t>
+          <t>二连市坤益腾金属有限公司</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
@@ -6079,36 +6208,32 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
+          <t>二税稽处〔2025〕1号</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
+          <t>二税稽处〔2025〕1号</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
+          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>个人所得税、印花税</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="n">
-        <v>15072487.5</v>
-      </c>
-      <c r="S13" s="3" t="n">
-        <v>1046925</v>
-      </c>
+          <t>增值税</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="n"/>
+      <c r="S13" s="3" t="n"/>
       <c r="T13" s="3" t="n"/>
       <c r="U13" s="3" t="n"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
+          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
         </is>
       </c>
       <c r="W13" s="4" t="n"/>
@@ -6118,7 +6243,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -6154,55 +6279,47 @@
       </c>
       <c r="AJ13" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
+          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASE-7e3d4a321440d6a7</t>
+          <t>CASE-d4b6986f3f97cd28</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DOC-bed9330343ed06af</t>
+          <t>DOC-442cf3d9a5280c12</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>鄂尔多斯市</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
-        </is>
-      </c>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
+          <t>第二稽查局</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>天津展达科技有限公司</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>91120116300738701X</t>
-        </is>
-      </c>
+          <t>廖礼平</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -6211,48 +6328,46 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
+          <t>鄂税二稽处〔2023〕29号</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
+          <t>鄂税二稽处〔2023〕29号</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+          <t>个人所得税、印花税</t>
         </is>
       </c>
       <c r="R14" s="3" t="n">
-        <v>920146.9399999999</v>
-      </c>
-      <c r="S14" s="3" t="n"/>
+        <v>15072487.5</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>1046925</v>
+      </c>
       <c r="T14" s="3" t="n"/>
       <c r="U14" s="3" t="n"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
         </is>
       </c>
       <c r="W14" s="4" t="n"/>
       <c r="X14" s="4" t="n"/>
       <c r="Y14" s="4" t="n"/>
       <c r="Z14" s="4" t="n">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -6278,7 +6393,7 @@
       <c r="AG14" s="2" t="inlineStr"/>
       <c r="AH14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="AI14" s="2" t="inlineStr">
@@ -6288,13 +6403,13 @@
       </c>
       <c r="AJ14" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
@@ -6303,7 +6418,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>DOC-388bd01c01bbb789</t>
+          <t>DOC-bed9330343ed06af</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -6340,24 +6455,24 @@
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
           <t>津税一稽罚〔2023〕21号</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
           <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
@@ -6368,11 +6483,11 @@
           <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R15" s="3" t="n"/>
+      <c r="R15" s="3" t="n">
+        <v>920146.9399999999</v>
+      </c>
       <c r="S15" s="3" t="n"/>
-      <c r="T15" s="3" t="n">
-        <v>131368.5</v>
-      </c>
+      <c r="T15" s="3" t="n"/>
       <c r="U15" s="3" t="n"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
@@ -6386,7 +6501,7 @@
         <v>46230</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -6426,20 +6541,154 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7e3d4a321440d6a7</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>DOC-388bd01c01bbb789</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>91120116300738701X</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>税务行政处罚决定书</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="n"/>
+      <c r="S16" s="3" t="n"/>
+      <c r="T16" s="3" t="n">
+        <v>131368.5</v>
+      </c>
+      <c r="U16" s="3" t="n"/>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W16" s="4" t="n"/>
+      <c r="X16" s="4" t="n"/>
+      <c r="Y16" s="4" t="n"/>
+      <c r="Z16" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AA16" s="4" t="n">
+        <v>46233</v>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE16" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+        </is>
+      </c>
+      <c r="AI16" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ16" s="2" t="inlineStr">
+        <is>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ15"/>
-  <conditionalFormatting sqref="AD2:AD15">
+  <autoFilter ref="A1:AJ16"/>
+  <conditionalFormatting sqref="AD2:AD16">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AD2="待核验"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI2:AI15">
+  <conditionalFormatting sqref="AI2:AI16">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>AND($AI2&lt;&gt;"正常",$AI2&lt;&gt;"附件正常")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AD2:AD15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AD2:AD16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"已核验,待核验,人工复核完成"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6449,19 +6698,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF6" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF7" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF10" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE11" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF11" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE12" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE10" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE11" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE12" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF12" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE14" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE15" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE16" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -6779,7 +7029,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -6897,7 +7147,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -7019,7 +7269,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -7145,7 +7395,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -7271,7 +7521,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -7389,7 +7639,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -7511,7 +7761,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -7633,7 +7883,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -7755,7 +8005,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -7877,7 +8127,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -7999,7 +8249,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -8121,7 +8371,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -8239,7 +8489,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -8361,7 +8611,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -8756,7 +9006,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -8882,7 +9132,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -9000,7 +9250,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -9122,7 +9372,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -9244,7 +9494,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -9362,7 +9612,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -9504,7 +9754,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -9646,7 +9896,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -9774,7 +10024,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -9898,7 +10148,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -10032,7 +10282,7 @@
         <v>46230</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -10166,7 +10416,7 @@
         <v>46230</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -10552,7 +10802,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -10678,7 +10928,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -10796,7 +11046,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -10918,7 +11168,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -11040,7 +11290,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -11158,7 +11408,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -11239,7 +11489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11835,8 +12085,57 @@
         </is>
       </c>
     </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30T14:32:59+08:00</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27 至 2026-07-30</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>广西耿仁建材有限公司</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>已完成候选发现、逐条访问核验、去重、关联和历史数据增量写入。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M12"/>
+  <autoFilter ref="A1:M13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -15,12 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日运行日志" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文书汇总'!$A$1:$AJ$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'完整文书'!$A$1:$AJ$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文书汇总'!$A$1:$AJ$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'完整文书'!$A$1:$AJ$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ30"/>
+  <dimension ref="A1:AJ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -791,7 +791,7 @@
         <v>46233</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -825,51 +825,59 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CASE-3e050a699b29b0d0</t>
+          <t>CASE-eb9cfd5295d501e5</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>DOC-96a3089a0e2b37cd</t>
+          <t>DOC-4a8cf53b445afc63</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>河南省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>平顶山市</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
+          <t>北海市</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>海城区</t>
+        </is>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局平顶山市税务局第一稽查局</t>
+          <t>国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局平顶山市税务局第一稽查局</t>
+          <t>国家税务总局北海市税务局稽查局</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>汝州泰隆实业有限公司</t>
+          <t>广西轩易科技有限公司</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>91410482MA40K4KA3B</t>
+          <t>91450500MAK3N9UJ2T</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
@@ -880,40 +888,50 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>平税稽一局处〔2026〕1号</t>
+          <t>北市税稽处〔2026〕6号</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>平税稽一局处〔2026〕1号</t>
+          <t>北市税稽处〔2026〕6号</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>我局于2026年1月23日起对你公司(地址:北海市海城区北部湾东路“金宝小区”B幢B804号20北海汇算账商务秘书有限公司托管)2025年12月11日至2025年12月31日期间的涉税情况进行了检查,发现你公司存在税收违法行为,原《税务处理决定书》(北市税稽处〔2026〕6号)认定的违法事实有误,经重新调查核实,违法事实及处理决定如下: 经查询,你公司2026年1月20日通过网络方式零申报所属期2025年10月1日-2025年12月31日的增值税、城市维护建设税及附加,入库税款0元,申报金额与实际不符,存在虚假申报的情况。 你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 (一)根据《中华人民共和国发票管理办法》(财政部令第6号发布,经国务院令第587号、第709号、第764号修订)第二十一条第二款第(一)项的规定,认定你公司为他人开具与实际经营业务情况不符的前述13份增值税普通电子发票为虚开发票(金额合计571550.49元,税额合计5715.51元,价税合计577266.00元)。 根据《中华人民共和国税收征收管理法》第三十二条、第六十三条第一款、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,已构成偷税,向你公司追缴少缴的税款合计5915.56元,并从滞纳税款之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>增值税、个人所得税</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="n"/>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>6058.46</v>
+      </c>
       <c r="S3" s="3" t="n"/>
       <c r="T3" s="3" t="n"/>
       <c r="U3" s="3" t="n"/>
-      <c r="V3" s="2" t="inlineStr"/>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《中华人民共和国城市维护建设税法》(中华人民共和国主席令第五十一号)第一条、第二条、第四条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×7%×50%=200.05元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)、《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×3%×50%=85.74元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳地方教育附加5715.51×2%×50%=57.16元。</t>
+        </is>
+      </c>
       <c r="W3" s="4" t="n"/>
       <c r="X3" s="4" t="n">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="Y3" s="4" t="n"/>
       <c r="Z3" s="4" t="n">
-        <v>46229</v>
+        <v>46234</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -935,7 +953,7 @@
       <c r="AG3" s="2" t="inlineStr"/>
       <c r="AH3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局平顶山市税务局第一稽查局关于送达汝州泰隆实业有限公司《税务处理决定书》的公告 - 国家税务总局平顶山市税务局</t>
+          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕13号)_国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="AI3" s="2" t="inlineStr">
@@ -945,53 +963,53 @@
       </c>
       <c r="AJ3" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>字段“决定书文号”存在冲突:保留原值“北市税稽处〔2026〕6号”,新值“北市税稽处〔2026〕13号”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CASE-365e8a924cf64611</t>
+          <t>CASE-3e050a699b29b0d0</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>DOC-4d14eba16f9aa8a0</t>
+          <t>DOC-96a3089a0e2b37cd</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>平顶山市</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局平顶山市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局平顶山市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>贵州博泰工贸有限公司</t>
+          <t>汝州泰隆实业有限公司</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>91520115587255589F</t>
+          <t>91410482MA40K4KA3B</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
@@ -1002,17 +1020,21 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕38号</t>
+          <t>平税稽一局处〔2026〕1号</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕38号</t>
+          <t>平税稽一局处〔2026〕1号</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>增值税、个人所得税</t>
+        </is>
+      </c>
       <c r="R4" s="3" t="n"/>
       <c r="S4" s="3" t="n"/>
       <c r="T4" s="3" t="n"/>
@@ -1020,14 +1042,14 @@
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="4" t="n"/>
       <c r="X4" s="4" t="n">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="Y4" s="4" t="n"/>
       <c r="Z4" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1041,7 +1063,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE4" s="5" t="inlineStr">
@@ -1053,12 +1075,12 @@
       <c r="AG4" s="2" t="inlineStr"/>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书、税务行政处罚决定书的公告</t>
+          <t>国家税务总局平顶山市税务局第一稽查局关于送达汝州泰隆实业有限公司《税务处理决定书》的公告 - 国家税务总局平顶山市税务局</t>
         </is>
       </c>
       <c r="AI4" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr">
@@ -1069,47 +1091,47 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CASE-7b9a26f2ac401107</t>
+          <t>CASE-365e8a924cf64611</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>DOC-f6c6ea472b2ca04a</t>
+          <t>DOC-4d14eba16f9aa8a0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>三明市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局三明市税务局第一稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局三明市税务局第一稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>三明众祥房地产开发有限公司</t>
+          <t>贵州博泰工贸有限公司</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>91350400678473231W</t>
+          <t>91520115587255589F</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
@@ -1120,50 +1142,36 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>明税一稽处〔2026〕20号</t>
+          <t>筑税三稽处〔2026〕38号</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>明税一稽处〔2026〕20号</t>
+          <t>筑税三稽处〔2026〕38号</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2016年期间,在没有真实业务情况下,取得重庆市博海建设工程(集团)有限公司、福建九九建设有限公司三明分公司开具的不符合规定的发票,发票金额400252379元,在企业所得税税前扣除,造成少缴纳企业所得税100063094.75元,该行为违反《中华人民共和国税收征收管理法》(2015年4月24日主席令第二十三号修改)第六十三条第一款 纳税人伪造、变造、隐匿、擅自销毁账簿、记账凭证,或者在账簿上多列支出或者不列、少列收入,或者经税务机关通知申报而拒不申报或者进行虚假的纳税申报,不缴或者少缴应纳税款的,是偷税。 对纳税人偷税的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款; 之规定,对你公司在账上多列支出,造成少缴企业所得税100063094.75元的行为认定为偷税。 之规定,对你公司少缴的企业所得税从滞纳之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>企业所得税</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>100063094.75</v>
-      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="3" t="n"/>
       <c r="S5" s="3" t="n"/>
       <c r="T5" s="3" t="n"/>
       <c r="U5" s="3" t="n"/>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>据《中华人民共和国税收征收管理法实施细则》第106条规定,将该文书予以公告送达,自公告之日起满30日视为送达。</t>
-        </is>
-      </c>
+      <c r="V5" s="2" t="inlineStr"/>
       <c r="W5" s="4" t="n"/>
       <c r="X5" s="4" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1173,7 +1181,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE5" s="5" t="inlineStr">
@@ -1185,14 +1193,12 @@
       <c r="AG5" s="2" t="inlineStr"/>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>关于送达三明众祥房地产开发有限公司 《税务处理决定书》的公告 _
- 其他公告 _
- 国家税务总局三明市税务局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书、税务行政处罚决定书的公告</t>
         </is>
       </c>
       <c r="AI5" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>页面已删除</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr">
@@ -1203,16 +1209,16 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>CASE-31e4a827dfd253f2</t>
+          <t>CASE-7b9a26f2ac401107</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>DOC-3ec54358fce2350d</t>
+          <t>DOC-f6c6ea472b2ca04a</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1222,28 +1228,28 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>福州市</t>
+          <t>三明市</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局三明市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局三明市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>福州顺路汽车运输有限公司</t>
+          <t>三明众祥房地产开发有限公司</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>91350102MA31MF6611</t>
+          <t>91350400678473231W</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
@@ -1254,46 +1260,46 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽处〔2026〕137号</t>
+          <t>明税一稽处〔2026〕20号</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽处〔2026〕137号</t>
+          <t>明税一稽处〔2026〕20号</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>我局于2025年7月10日起对你公司(地址:福建省闽侯县青口镇祥宏南路922号)2023年1月1日至2024年12月31日期间的发票涉税情况进行检查,违法事实及处理决定如下: (二)你公司取得毕节七星关区辰楚汽车服务部(个人独资)、毕节七星关锦悦汽车服务部(个人独资)、贵州杨亭汽车销售有限公司、贵州楠鑫汽车销售有限公司已证实虚开的35份机动车发票。 (二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 (三)根据《中华人民共和国企业所得税法》第五条、第八条、《企业所得税税前扣除凭证管理办法》(国家税务总局公告2018年第28号发布)第四条、第十二条的规定,你公司取得上述虚开的发票不得作为税前扣除凭证。</t>
+          <t>情况进行了检查,违法事实及处理决定如下: 2016年期间,在没有真实业务情况下,取得重庆市博海建设工程(集团)有限公司、福建九九建设有限公司三明分公司开具的不符合规定的发票,发票金额400252379元,在企业所得税税前扣除,造成少缴纳企业所得税100063094.75元,该行为违反《中华人民共和国税收征收管理法》(2015年4月24日主席令第二十三号修改)第六十三条第一款 纳税人伪造、变造、隐匿、擅自销毁账簿、记账凭证,或者在账簿上多列支出或者不列、少列收入,或者经税务机关通知申报而拒不申报或者进行虚假的纳税申报,不缴或者少缴应纳税款的,是偷税。 对纳税人偷税的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款; 之规定,对你公司在账上多列支出,造成少缴企业所得税100063094.75元的行为认定为偷税。 之规定,对你公司少缴的企业所得税从滞纳之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
+          <t>企业所得税</t>
         </is>
       </c>
       <c r="R6" s="3" t="n">
-        <v>3778.22</v>
+        <v>100063094.75</v>
       </c>
       <c r="S6" s="3" t="n"/>
       <c r="T6" s="3" t="n"/>
       <c r="U6" s="3" t="n"/>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>(二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期城市维护建设税124.75元。 根据《征收教育费附加的暂行规定》第二条、第三条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期教育费附加53.47元。 根据《福建省人民政府关于调整地方教育附加征收标准等有关问题的通知》(闽政文〔2011〕230号)第一条、第二条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期地方教育附加35.64元。</t>
+          <t>据《中华人民共和国税收征收管理法实施细则》第106条规定,将该文书予以公告送达,自公告之日起满30日视为送达。</t>
         </is>
       </c>
       <c r="W6" s="4" t="n"/>
       <c r="X6" s="4" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="Y6" s="4" t="n"/>
       <c r="Z6" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1319,140 +1325,148 @@
       <c r="AG6" s="2" t="inlineStr"/>
       <c r="AH6" s="2" t="inlineStr">
         <is>
+          <t>关于送达三明众祥房地产开发有限公司 《税务处理决定书》的公告 _
+ 其他公告 _
+ 国家税务总局三明市税务局</t>
+        </is>
+      </c>
+      <c r="AI6" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ6" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>CASE-31e4a827dfd253f2</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>DOC-3ec54358fce2350d</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>福建省</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>福州市</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局福州市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局福州市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>福州顺路汽车运输有限公司</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>91350102MA31MF6611</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>榕税一稽处〔2026〕137号</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>榕税一稽处〔2026〕137号</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>我局于2025年7月10日起对你公司(地址:福建省闽侯县青口镇祥宏南路922号)2023年1月1日至2024年12月31日期间的发票涉税情况进行检查,违法事实及处理决定如下: (二)你公司取得毕节七星关区辰楚汽车服务部(个人独资)、毕节七星关锦悦汽车服务部(个人独资)、贵州杨亭汽车销售有限公司、贵州楠鑫汽车销售有限公司已证实虚开的35份机动车发票。 (二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 (三)根据《中华人民共和国企业所得税法》第五条、第八条、《企业所得税税前扣除凭证管理办法》(国家税务总局公告2018年第28号发布)第四条、第十二条的规定,你公司取得上述虚开的发票不得作为税前扣除凭证。</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>3778.22</v>
+      </c>
+      <c r="S7" s="3" t="n"/>
+      <c r="T7" s="3" t="n"/>
+      <c r="U7" s="3" t="n"/>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>(二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期城市维护建设税124.75元。 根据《征收教育费附加的暂行规定》第二条、第三条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期教育费附加53.47元。 根据《福建省人民政府关于调整地方教育附加征收标准等有关问题的通知》(闽政文〔2011〕230号)第一条、第二条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期地方教育附加35.64元。</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="n"/>
+      <c r="X7" s="4" t="n">
+        <v>46218</v>
+      </c>
+      <c r="Y7" s="4" t="n"/>
+      <c r="Z7" s="4" t="n">
+        <v>46229</v>
+      </c>
+      <c r="AA7" s="4" t="n">
+        <v>46234</v>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AE7" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr">
+        <is>
           <t>关于送达福州顺路汽车运输有限公司《税务处理决定书》的公告 _
  其他类 _
  国家税务总局福州市税务局</t>
         </is>
       </c>
-      <c r="AI6" s="2" t="inlineStr">
+      <c r="AI7" s="2" t="inlineStr">
         <is>
           <t>正常</t>
-        </is>
-      </c>
-      <c r="AJ6" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>CASE-089a3b9692e76ac4</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>DOC-d21cdc5988b1e304</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>江苏省</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>淮安市</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局江苏省税务局</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局淮安市税务局稽查局</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>淮安市百亦金商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>91320804MA1WEH7Y3U</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>税务处理决定书</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽处〔2026〕26号</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽处〔2026〕26号</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽罚〔2026〕6号</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="3" t="n"/>
-      <c r="S7" s="3" t="n"/>
-      <c r="T7" s="3" t="n"/>
-      <c r="U7" s="3" t="n"/>
-      <c r="V7" s="2" t="inlineStr"/>
-      <c r="W7" s="4" t="n"/>
-      <c r="X7" s="4" t="n">
-        <v>46216</v>
-      </c>
-      <c r="Y7" s="4" t="n"/>
-      <c r="Z7" s="4" t="n">
-        <v>46229</v>
-      </c>
-      <c r="AA7" s="4" t="n">
-        <v>46233</v>
-      </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>仅公告送达/仅文号线索</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD7" s="2" t="inlineStr">
-        <is>
-          <t>已核验</t>
-        </is>
-      </c>
-      <c r="AE7" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF7" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
-      <c r="AG7" s="2" t="inlineStr"/>
-      <c r="AH7" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
-        </is>
-      </c>
-      <c r="AI7" s="2" t="inlineStr">
-        <is>
-          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr">
@@ -1463,7 +1477,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -1472,7 +1486,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DOC-9f8e8958d8ff89b6</t>
+          <t>DOC-d21cdc5988b1e304</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1509,12 +1523,12 @@
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>淮税稽罚〔2026〕6号</t>
+          <t>淮税稽处〔2026〕26号</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1543,7 +1557,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1589,99 +1603,91 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>CASE-3f564fd9992b1ae3</t>
+          <t>CASE-089a3b9692e76ac4</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DOC-c34e1d13286aafe2</t>
+          <t>DOC-9f8e8958d8ff89b6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>泉州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局第二稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局第二稽查局</t>
+          <t>国家税务总局淮安市税务局稽查局</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>泉州隆鸿服装制造有限公司</t>
+          <t>淮安市百亦金商贸有限公司</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91350525MA8U3U963L</t>
+          <t>91320804MA1WEH7Y3U</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>泉税二稽处〔2026〕107号</t>
+          <t>淮税稽罚〔2026〕6号</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>泉税二稽处〔2026〕107号</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>日对你公司税收违法事实依法作出《税务处理决定书》(泉税二稽处〔 涉税情况进行了检查,查明违法事实及处理决定如下: 年你公司在无真实货物交易的情况下,取得河南中弘纺织有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 年期间,你公司在无真实货物交易的情况下,取得开封兴旺纺织品有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 上述违法事实有检查人员实地检查资料、电话拨打记录、邮寄退回函件、《已证实虚开通知单》等相关受托协查资料、主管税务机关出具的《已抵扣证明》、《情况说明》和你公司的申报纳税资料、银行账户流水等 号第三次修订)第二十一条第二款第二项之规定,认定你公司让他人为自己虚开 号第二次修订)第九条和《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告〔 号)之规定,对你公司取得上述已证实虚开的 之规定,决定向你公司追缴少缴的城市维护建设税-增值税附征 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 规定,决定向你公司追缴少缴的教育费附加-增值税附征 规定,决定向你公司追缴少缴的地方教育附加-增值税附征</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
+          <t>淮税稽处〔2026〕26号</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>淮税稽罚〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
       <c r="R9" s="3" t="n"/>
       <c r="S9" s="3" t="n"/>
       <c r="T9" s="3" t="n"/>
       <c r="U9" s="3" t="n"/>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>由于你公司走逃失联、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 (五)根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司上述应补缴税款按税款所属时间从税款滞纳之日起按日加收万分之五滞纳金</t>
-        </is>
-      </c>
+      <c r="V9" s="2" t="inlineStr"/>
       <c r="W9" s="4" t="n"/>
       <c r="X9" s="4" t="n">
-        <v>46202</v>
+        <v>46216</v>
       </c>
       <c r="Y9" s="4" t="n"/>
       <c r="Z9" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1699,18 +1705,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AF9" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG9" s="2" t="inlineStr"/>
       <c r="AH9" s="2" t="inlineStr">
         <is>
-          <t>关于对泉州隆鸿服装制造有限公司《税务处理决定书》送达的公告 _
- 其他公告 _
- 国家税务总局泉州市税务局</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
         </is>
       </c>
       <c r="AI9" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr">
@@ -1721,91 +1729,99 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CASE-717dfe3250926214</t>
+          <t>CASE-3f564fd9992b1ae3</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DOC-7df9c075e55777a1</t>
+          <t>DOC-c34e1d13286aafe2</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>泰州市</t>
+          <t>泉州市</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泰州市税务局第一稽查局</t>
+          <t>国家税务总局泉州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泰州市税务局第一稽查局</t>
+          <t>国家税务总局泉州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>靖江市长凌金属材料有限公司</t>
+          <t>泉州隆鸿服装制造有限公司</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>91321282742461893K</t>
+          <t>91350525MA8U3U963L</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>泰税一稽罚〔2025〕54号</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>泰税一稽罚〔2025〕54号</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>泉税二稽处〔2026〕107号</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>泉税二稽处〔2026〕107号</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>日对你公司税收违法事实依法作出《税务处理决定书》(泉税二稽处〔 涉税情况进行了检查,查明违法事实及处理决定如下: 年你公司在无真实货物交易的情况下,取得河南中弘纺织有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 年期间,你公司在无真实货物交易的情况下,取得开封兴旺纺织品有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 上述违法事实有检查人员实地检查资料、电话拨打记录、邮寄退回函件、《已证实虚开通知单》等相关受托协查资料、主管税务机关出具的《已抵扣证明》、《情况说明》和你公司的申报纳税资料、银行账户流水等 号第三次修订)第二十一条第二款第二项之规定,认定你公司让他人为自己虚开 号第二次修订)第九条和《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告〔 号)之规定,对你公司取得上述已证实虚开的 之规定,决定向你公司追缴少缴的城市维护建设税-增值税附征 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 规定,决定向你公司追缴少缴的教育费附加-增值税附征 规定,决定向你公司追缴少缴的地方教育附加-增值税附征</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
       <c r="R10" s="3" t="n"/>
       <c r="S10" s="3" t="n"/>
       <c r="T10" s="3" t="n"/>
       <c r="U10" s="3" t="n"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>接上级通知,经我局研究决定,撤销上述《税务行政处罚决定书》。</t>
+          <t>由于你公司走逃失联、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 (五)根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司上述应补缴税款按税款所属时间从税款滞纳之日起按日加收万分之五滞纳金</t>
         </is>
       </c>
       <c r="W10" s="4" t="n"/>
       <c r="X10" s="4" t="n">
-        <v>46191</v>
+        <v>46202</v>
       </c>
       <c r="Y10" s="4" t="n"/>
       <c r="Z10" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1827,7 +1843,9 @@
       <c r="AG10" s="2" t="inlineStr"/>
       <c r="AH10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 关于撤销《税务行政处罚决定书》的公告</t>
+          <t>关于对泉州隆鸿服装制造有限公司《税务处理决定书》送达的公告 _
+ 其他公告 _
+ 国家税务总局泉州市税务局</t>
         </is>
       </c>
       <c r="AI10" s="2" t="inlineStr">
@@ -1837,101 +1855,97 @@
       </c>
       <c r="AJ10" s="2" t="inlineStr">
         <is>
-          <t>官方页面显示该决定书已被撤销。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>CASE-a62e569c195adc3c</t>
+          <t>CASE-717dfe3250926214</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>DOC-b1dda915d4e6117d</t>
+          <t>DOC-7df9c075e55777a1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>遵义市</t>
+          <t>泰州市</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局泰州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局泰州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>贵州服格定商贸有限公司</t>
+          <t>靖江市长凌金属材料有限公司</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91520302MABUEHN034</t>
+          <t>91321282742461893K</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>遵税一稽处〔2026〕30号</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>遵税一稽处〔2026〕30号</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>增值税</t>
-        </is>
-      </c>
+          <t>泰税一稽罚〔2025〕54号</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>泰税一稽罚〔2025〕54号</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
       <c r="R11" s="3" t="n"/>
       <c r="S11" s="3" t="n"/>
       <c r="T11" s="3" t="n"/>
       <c r="U11" s="3" t="n"/>
-      <c r="V11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>接上级通知,经我局研究决定,撤销上述《税务行政处罚决定书》。</t>
+        </is>
+      </c>
       <c r="W11" s="4" t="n"/>
       <c r="X11" s="4" t="n">
-        <v>46185</v>
+        <v>46191</v>
       </c>
       <c r="Y11" s="4" t="n"/>
       <c r="Z11" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1941,7 +1955,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE11" s="5" t="inlineStr">
@@ -1953,61 +1967,65 @@
       <c r="AG11" s="2" t="inlineStr"/>
       <c r="AH11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 关于撤销《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI11" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ11" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>官方页面显示该决定书已被撤销。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CASE-13a8aac51595155a</t>
+          <t>CASE-a62e569c195adc3c</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>DOC-7189c9a2cee8e8ce</t>
+          <t>DOC-b1dda915d4e6117d</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>温州市</t>
+          <t>遵义市</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局遵义市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局遵义市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>温作潘</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
+          <t>贵州服格定商贸有限公司</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>91520302MABUEHN034</t>
+        </is>
+      </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
@@ -2016,21 +2034,25 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>温税三稽处〔2026〕100号</t>
+          <t>遵税一稽处〔2026〕30号</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>温税三稽处〔2026〕100号</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>温税三稽罚〔2026〕65号</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+          <t>遵税一稽处〔2026〕30号</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>增值税</t>
+        </is>
+      </c>
       <c r="R12" s="3" t="n"/>
       <c r="S12" s="3" t="n"/>
       <c r="T12" s="3" t="n"/>
@@ -2038,18 +2060,18 @@
       <c r="V12" s="2" t="inlineStr"/>
       <c r="W12" s="4" t="n"/>
       <c r="X12" s="4" t="n">
-        <v>46175</v>
+        <v>46185</v>
       </c>
       <c r="Y12" s="4" t="n"/>
       <c r="Z12" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2059,7 +2081,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE12" s="5" t="inlineStr">
@@ -2067,20 +2089,16 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF12" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF12" s="2" t="inlineStr"/>
       <c r="AG12" s="2" t="inlineStr"/>
       <c r="AH12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
+          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
         </is>
       </c>
       <c r="AI12" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>页面已删除</t>
         </is>
       </c>
       <c r="AJ12" s="2" t="inlineStr">
@@ -2091,7 +2109,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
@@ -2100,7 +2118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>DOC-02fc2468fd0396a6</t>
+          <t>DOC-7189c9a2cee8e8ce</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2133,12 +2151,12 @@
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>温税三稽罚〔2026〕65号</t>
+          <t>温税三稽处〔2026〕100号</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2167,7 +2185,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -2213,66 +2231,66 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASE-f8625e66b291a216</t>
+          <t>CASE-13a8aac51595155a</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DOC-7970511393924720</t>
+          <t>DOC-02fc2468fd0396a6</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>温州市</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>贵州翰缤商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>91520114MAAK1C546F</t>
-        </is>
-      </c>
+          <t>温作潘</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>筑税二稽处〔2026〕27号</t>
+          <t>温税三稽罚〔2026〕65号</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>筑税二稽处〔2026〕27号</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr"/>
+          <t>温税三稽处〔2026〕100号</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>温税三稽罚〔2026〕65号</t>
+        </is>
+      </c>
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
       <c r="R14" s="3" t="n"/>
@@ -2282,14 +2300,14 @@
       <c r="V14" s="2" t="inlineStr"/>
       <c r="W14" s="4" t="n"/>
       <c r="X14" s="4" t="n">
-        <v>46156</v>
+        <v>46175</v>
       </c>
       <c r="Y14" s="4" t="n"/>
       <c r="Z14" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -2303,7 +2321,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE14" s="5" t="inlineStr">
@@ -2311,16 +2329,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AF14" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG14" s="2" t="inlineStr"/>
       <c r="AH14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局关于送达《税务处理决定书》的公告</t>
+          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
         </is>
       </c>
       <c r="AI14" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ14" s="2" t="inlineStr">
@@ -2331,16 +2353,16 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CASE-0f4867f7b70d12f3</t>
+          <t>CASE-f8625e66b291a216</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>DOC-6f25d6b79e123d03</t>
+          <t>DOC-7970511393924720</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2356,22 +2378,22 @@
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局贵阳市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局贵阳市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>贵州铂朗物流有限公司</t>
+          <t>贵州翰缤商贸有限公司</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>91520115MAAK0DB335</t>
+          <t>91520114MAAK1C546F</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
@@ -2382,19 +2404,15 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
+          <t>筑税二稽处〔2026〕27号</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>筑税三稽罚〔2026〕22号</t>
-        </is>
-      </c>
+          <t>筑税二稽处〔2026〕27号</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr"/>
       <c r="R15" s="3" t="n"/>
@@ -2404,14 +2422,14 @@
       <c r="V15" s="2" t="inlineStr"/>
       <c r="W15" s="4" t="n"/>
       <c r="X15" s="4" t="n">
-        <v>46122</v>
+        <v>46156</v>
       </c>
       <c r="Y15" s="4" t="n"/>
       <c r="Z15" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -2437,7 +2455,7 @@
       <c r="AG15" s="2" t="inlineStr"/>
       <c r="AH15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
+          <t>国家税务总局贵阳市税务局第二稽查局关于送达《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI15" s="2" t="inlineStr">
@@ -2453,7 +2471,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
@@ -2462,7 +2480,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>DOC-e8233eb0e06b6e3e</t>
+          <t>DOC-6f25d6b79e123d03</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2499,12 +2517,12 @@
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽罚〔2026〕22号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2533,7 +2551,7 @@
         <v>46229</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -2575,68 +2593,68 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CASE-136615addd5d0c0e</t>
+          <t>CASE-0f4867f7b70d12f3</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>DOC-551df7dc5c028b27</t>
+          <t>DOC-e8233eb0e06b6e3e</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>来宾市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>广西欣瑞木业有限公司</t>
+          <t>贵州铂朗物流有限公司</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>91451322MAD89XWX07</t>
+          <t>91520115MAAK0DB335</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr"/>
@@ -2648,14 +2666,14 @@
       <c r="V17" s="2" t="inlineStr"/>
       <c r="W17" s="4" t="n"/>
       <c r="X17" s="4" t="n">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="Y17" s="4" t="n"/>
       <c r="Z17" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -2669,7 +2687,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE17" s="5" t="inlineStr">
@@ -2681,12 +2699,12 @@
       <c r="AG17" s="2" t="inlineStr"/>
       <c r="AH17" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
         </is>
       </c>
       <c r="AI17" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>页面已删除</t>
         </is>
       </c>
       <c r="AJ17" s="2" t="inlineStr">
@@ -2697,7 +2715,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
@@ -2706,7 +2724,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>DOC-21f0193b66d5c3e9</t>
+          <t>DOC-551df7dc5c028b27</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2743,12 +2761,12 @@
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>来市税二稽处〔2026〕6号</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2777,7 +2795,7 @@
         <v>46229</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -2819,47 +2837,47 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CASE-393a878d93a22709</t>
+          <t>CASE-136615addd5d0c0e</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>DOC-cda8cba853896b18</t>
+          <t>DOC-21f0193b66d5c3e9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>广州市</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>番禺区</t>
-        </is>
-      </c>
+          <t>来宾市</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
+        </is>
+      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>广州赞荣服装有限公司</t>
+          <t>广西欣瑞木业有限公司</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>91440113MA59AJFJ1J</t>
+          <t>91451322MAD89XWX07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
@@ -2870,13 +2888,17 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>穗番税退罚字〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t>来市税二稽罚〔2026〕4号</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>来市税二稽处〔2026〕6号</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>穗番税退罚字〔2026〕1号</t>
+          <t>来市税二稽罚〔2026〕4号</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr"/>
@@ -2888,14 +2910,14 @@
       <c r="V19" s="2" t="inlineStr"/>
       <c r="W19" s="4" t="n"/>
       <c r="X19" s="4" t="n">
-        <v>46091</v>
+        <v>46119</v>
       </c>
       <c r="Y19" s="4" t="n"/>
       <c r="Z19" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -2909,7 +2931,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE19" s="5" t="inlineStr">
@@ -2917,131 +2939,107 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF19" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF19" s="2" t="inlineStr"/>
       <c r="AG19" s="2" t="inlineStr"/>
       <c r="AH19" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
+          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
         </is>
       </c>
       <c r="AI19" s="2" t="inlineStr">
         <is>
-          <t>内容不匹配</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ19" s="2" t="inlineStr">
         <is>
-          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CASE-f94bf08964abff5a</t>
+          <t>CASE-393a878d93a22709</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>DOC-4574b1aadef8f30d</t>
+          <t>DOC-cda8cba853896b18</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>广东省</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
+          <t>广州市</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>番禺区</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局常州市税务局稽查局</t>
-        </is>
-      </c>
+          <t>国家税务总局广州市番禺区税务局</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>常州市文杰车辆配件厂</t>
+          <t>广州赞荣服装有限公司</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>91320411799075280A</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>朱某</t>
-        </is>
-      </c>
+          <t>91440113MA59AJFJ1J</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕73号</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>常税稽处〔2026〕73号</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公 月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R20" s="3" t="n">
-        <v>179137.12</v>
-      </c>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="3" t="n"/>
       <c r="S20" s="3" t="n"/>
       <c r="T20" s="3" t="n"/>
       <c r="U20" s="3" t="n"/>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市 份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元,</t>
-        </is>
-      </c>
-      <c r="W20" s="4" t="n">
-        <v>46044</v>
-      </c>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="4" t="n"/>
       <c r="X20" s="4" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="Y20" s="4" t="n"/>
       <c r="Z20" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -3051,7 +3049,7 @@
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE20" s="5" t="inlineStr">
@@ -3067,32 +3065,32 @@
       <c r="AG20" s="2" t="inlineStr"/>
       <c r="AH20" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
+          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
         </is>
       </c>
       <c r="AI20" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>内容不匹配</t>
         </is>
       </c>
       <c r="AJ20" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CASE-0b4a4519ba4f5ad9</t>
+          <t>CASE-f94bf08964abff5a</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>DOC-5376b9bae81cfc82</t>
+          <t>DOC-4574b1aadef8f30d</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3118,15 +3116,19 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>常州好佳车辆配件有限公司</t>
+          <t>常州市文杰车辆配件厂</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>91320411094264460B</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr"/>
+          <t>91320411799075280A</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>朱某</t>
+        </is>
+      </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
           <t>税务处理决定书</t>
@@ -3134,36 +3136,52 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕71号</t>
+          <t>常税稽处〔2026〕73号</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕71号</t>
+          <t>常税稽处〔2026〕73号</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="3" t="n"/>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公 月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>179137.12</v>
+      </c>
       <c r="S21" s="3" t="n"/>
       <c r="T21" s="3" t="n"/>
       <c r="U21" s="3" t="n"/>
-      <c r="V21" s="2" t="inlineStr"/>
-      <c r="W21" s="4" t="n"/>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市 份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元,</t>
+        </is>
+      </c>
+      <c r="W21" s="4" t="n">
+        <v>46044</v>
+      </c>
       <c r="X21" s="4" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="Y21" s="4" t="n"/>
       <c r="Z21" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3189,7 +3207,7 @@
       <c r="AG21" s="2" t="inlineStr"/>
       <c r="AH21" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州好佳车辆配件有限公司《税务处理决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI21" s="2" t="inlineStr">
@@ -3205,16 +3223,16 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CASE-61b9b55a9d3357c7</t>
+          <t>CASE-0b4a4519ba4f5ad9</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>DOC-1228a9c92b2b0632</t>
+          <t>DOC-5376b9bae81cfc82</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3230,22 +3248,22 @@
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局常州市税务局稽查局</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>常州市三鹏机械有限公司</t>
+          <t>常州好佳车辆配件有限公司</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>91320404732260748Q</t>
+          <t>91320411094264460B</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
@@ -3256,50 +3274,36 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
+          <t>常税稽处〔2026〕71号</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>常税稽一罚〔2026〕14号</t>
-        </is>
-      </c>
+          <t>常税稽处〔2026〕71号</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr"/>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="n">
-        <v>63464.09</v>
-      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="3" t="n"/>
       <c r="S22" s="3" t="n"/>
       <c r="T22" s="3" t="n"/>
       <c r="U22" s="3" t="n"/>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
-        </is>
-      </c>
+      <c r="V22" s="2" t="inlineStr"/>
       <c r="W22" s="4" t="n"/>
       <c r="X22" s="4" t="n">
-        <v>46066</v>
+        <v>46087</v>
       </c>
       <c r="Y22" s="4" t="n"/>
       <c r="Z22" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3317,16 +3321,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AF22" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG22" s="2" t="inlineStr"/>
       <c r="AH22" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州好佳车辆配件有限公司《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI22" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ22" s="2" t="inlineStr">
@@ -3337,7 +3345,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
@@ -3346,7 +3354,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>DOC-b97456a64b153f67</t>
+          <t>DOC-1228a9c92b2b0632</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3383,12 +3391,12 @@
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>常税稽一罚〔2026〕14号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3407,11 +3415,11 @@
           <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R23" s="3" t="n"/>
+      <c r="R23" s="3" t="n">
+        <v>63464.09</v>
+      </c>
       <c r="S23" s="3" t="n"/>
-      <c r="T23" s="3" t="n">
-        <v>20000</v>
-      </c>
+      <c r="T23" s="3" t="n"/>
       <c r="U23" s="3" t="n"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
@@ -3427,7 +3435,7 @@
         <v>46229</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
@@ -3469,103 +3477,97 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CASE-f78ec1a594442165</t>
+          <t>CASE-61b9b55a9d3357c7</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>DOC-fbbe4a664b14f54b</t>
+          <t>DOC-b97456a64b153f67</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>安顺市</t>
+          <t>常州市</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
+          <t>常州市三鹏机械有限公司</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>91520423MA6DLH799Q</t>
+          <t>91320404732260748Q</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一罚〔2026〕14号</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
-        </is>
-      </c>
+          <t>常税稽一罚〔2026〕14号</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R24" s="3" t="n">
-        <v>64884.41</v>
-      </c>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="n"/>
       <c r="S24" s="3" t="n"/>
-      <c r="T24" s="3" t="n"/>
+      <c r="T24" s="3" t="n">
+        <v>20000</v>
+      </c>
       <c r="U24" s="3" t="n"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
-      <c r="W24" s="4" t="n">
-        <v>45898</v>
-      </c>
+          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
+        </is>
+      </c>
+      <c r="W24" s="4" t="n"/>
       <c r="X24" s="4" t="n">
-        <v>46043</v>
+        <v>46066</v>
       </c>
       <c r="Y24" s="4" t="n"/>
       <c r="Z24" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
@@ -3579,7 +3581,7 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE24" s="5" t="inlineStr">
@@ -3587,15 +3589,11 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF24" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF24" s="2" t="inlineStr"/>
       <c r="AG24" s="2" t="inlineStr"/>
       <c r="AH24" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI24" s="2" t="inlineStr">
@@ -3605,13 +3603,13 @@
       </c>
       <c r="AJ24" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
@@ -3620,7 +3618,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>DOC-9a828a6048b54b6c</t>
+          <t>DOC-fbbe4a664b14f54b</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3657,27 +3655,27 @@
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
           <t>安市税稽罚〔2026〕1号</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>安市税稽处〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3685,11 +3683,11 @@
           <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R25" s="3" t="n"/>
+      <c r="R25" s="3" t="n">
+        <v>64884.41</v>
+      </c>
       <c r="S25" s="3" t="n"/>
-      <c r="T25" s="3" t="n">
-        <v>200000</v>
-      </c>
+      <c r="T25" s="3" t="n"/>
       <c r="U25" s="3" t="n"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
@@ -3707,7 +3705,7 @@
         <v>46229</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
@@ -3747,97 +3745,109 @@
       </c>
       <c r="AJ25" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CASE-fe959d4c6c52d910</t>
+          <t>CASE-f78ec1a594442165</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>DOC-f2643f2a0719d8d1</t>
+          <t>DOC-9a828a6048b54b6c</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>南宁市</t>
+          <t>安顺市</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局稽查局</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>南宁洪谦金贸易有限公司</t>
+          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>91450103MA5K9WHY7U</t>
+          <t>91520423MA6DLH799Q</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>南市税一稽处〔2026〕2号</t>
+          <t>安市税稽罚〔2026〕1号</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>南市税一稽处〔2026〕2号</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr"/>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽罚〔2026〕1号</t>
+        </is>
+      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>经我局2025年10月29日至2025年12月8日对你公司(地址:南宁市青秀区云景路11号春晖花园C区3栋2单元1606号)2015年12月2日至2016年12月31日期间的涉税情况进行了检查,你(单位)存在以下违法事实: 经查询你公司向税务机关报备的银行账号:广西北部湾银行南宁市财富国际支行800099398800015,经函询广西北部湾银行南宁市财富国际支行,存在以下问题: 上述行为属于开具与实际经营业务情况不符的增值税发票,违反了《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第587号修改)第二十二条第一款、第二款第(一)项的规定,属于虚开发票行为。</t>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
+          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R26" s="3" t="n"/>
       <c r="S26" s="3" t="n"/>
-      <c r="T26" s="3" t="n"/>
+      <c r="T26" s="3" t="n">
+        <v>200000</v>
+      </c>
       <c r="U26" s="3" t="n"/>
-      <c r="V26" s="2" t="inlineStr"/>
-      <c r="W26" s="4" t="n"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="W26" s="4" t="n">
+        <v>45898</v>
+      </c>
       <c r="X26" s="4" t="n">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="Y26" s="4" t="n"/>
       <c r="Z26" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
@@ -3851,7 +3861,7 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE26" s="5" t="inlineStr">
@@ -3867,61 +3877,65 @@
       <c r="AG26" s="2" t="inlineStr"/>
       <c r="AH26" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局税务文书送达公告_国家税务总局南宁市税务局</t>
+          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI26" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ26" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CASE-1983d97878508732</t>
+          <t>CASE-fe959d4c6c52d910</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>DOC-f9760895b4f08cc2</t>
+          <t>DOC-f2643f2a0719d8d1</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>二连浩特市</t>
+          <t>南宁市</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局</t>
+          <t>国家税务总局南宁市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局稽查局</t>
+          <t>国家税务总局南宁市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>二连市坤益腾金属有限公司</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr"/>
+          <t>南宁洪谦金贸易有限公司</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>91450103MA5K9WHY7U</t>
+        </is>
+      </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
@@ -3930,18 +3944,18 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
+          <t>南市税一稽处〔2026〕2号</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
+          <t>南市税一稽处〔2026〕2号</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
+          <t>经我局2025年10月29日至2025年12月8日对你公司(地址:南宁市青秀区云景路11号春晖花园C区3栋2单元1606号)2015年12月2日至2016年12月31日期间的涉税情况进行了检查,你(单位)存在以下违法事实: 经查询你公司向税务机关报备的银行账号:广西北部湾银行南宁市财富国际支行800099398800015,经函询广西北部湾银行南宁市财富国际支行,存在以下问题: 上述行为属于开具与实际经营业务情况不符的增值税发票,违反了《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第587号修改)第二十二条第一款、第二款第(一)项的规定,属于虚开发票行为。</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3953,19 +3967,17 @@
       <c r="S27" s="3" t="n"/>
       <c r="T27" s="3" t="n"/>
       <c r="U27" s="3" t="n"/>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
-        </is>
-      </c>
+      <c r="V27" s="2" t="inlineStr"/>
       <c r="W27" s="4" t="n"/>
-      <c r="X27" s="4" t="n"/>
+      <c r="X27" s="4" t="n">
+        <v>46031</v>
+      </c>
       <c r="Y27" s="4" t="n"/>
       <c r="Z27" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
@@ -3979,7 +3991,7 @@
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE27" s="5" t="inlineStr">
@@ -3987,36 +3999,40 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF27" s="2" t="inlineStr"/>
+      <c r="AF27" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG27" s="2" t="inlineStr"/>
       <c r="AH27" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>国家税务总局南宁市税务局第一稽查局税务文书送达公告_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI27" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ27" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CASE-d4b6986f3f97cd28</t>
+          <t>CASE-1983d97878508732</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>DOC-442cf3d9a5280c12</t>
+          <t>DOC-f9760895b4f08cc2</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -4026,19 +4042,23 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>鄂尔多斯市</t>
+          <t>二连浩特市</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局二连浩特市税务局</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>第二稽查局</t>
+          <t>国家税务总局二连浩特市税务局稽查局</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>廖礼平</t>
+          <t>二连市坤益腾金属有限公司</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -4050,36 +4070,32 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
+          <t>二税稽处〔2025〕1号</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
+          <t>二税稽处〔2025〕1号</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
+          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>个人所得税、印花税</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="n">
-        <v>15072487.5</v>
-      </c>
-      <c r="S28" s="3" t="n">
-        <v>1046925</v>
-      </c>
+          <t>增值税</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="n"/>
+      <c r="S28" s="3" t="n"/>
       <c r="T28" s="3" t="n"/>
       <c r="U28" s="3" t="n"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
+          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
         </is>
       </c>
       <c r="W28" s="4" t="n"/>
@@ -4089,7 +4105,7 @@
         <v>46229</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
@@ -4125,55 +4141,47 @@
       </c>
       <c r="AJ28" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
+          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CASE-7e3d4a321440d6a7</t>
+          <t>CASE-d4b6986f3f97cd28</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>DOC-bed9330343ed06af</t>
+          <t>DOC-442cf3d9a5280c12</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>鄂尔多斯市</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
-        </is>
-      </c>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
+          <t>第二稽查局</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>天津展达科技有限公司</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>91120116300738701X</t>
-        </is>
-      </c>
+          <t>廖礼平</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -4182,48 +4190,46 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
+          <t>鄂税二稽处〔2023〕29号</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
+          <t>鄂税二稽处〔2023〕29号</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+          <t>个人所得税、印花税</t>
         </is>
       </c>
       <c r="R29" s="3" t="n">
-        <v>920146.9399999999</v>
-      </c>
-      <c r="S29" s="3" t="n"/>
+        <v>15072487.5</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>1046925</v>
+      </c>
       <c r="T29" s="3" t="n"/>
       <c r="U29" s="3" t="n"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
         </is>
       </c>
       <c r="W29" s="4" t="n"/>
       <c r="X29" s="4" t="n"/>
       <c r="Y29" s="4" t="n"/>
       <c r="Z29" s="4" t="n">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
@@ -4249,7 +4255,7 @@
       <c r="AG29" s="2" t="inlineStr"/>
       <c r="AH29" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="AI29" s="2" t="inlineStr">
@@ -4259,13 +4265,13 @@
       </c>
       <c r="AJ29" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
@@ -4274,7 +4280,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>DOC-388bd01c01bbb789</t>
+          <t>DOC-bed9330343ed06af</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4311,24 +4317,24 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
           <t>津税一稽罚〔2023〕21号</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
           <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
@@ -4339,11 +4345,11 @@
           <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R30" s="3" t="n"/>
+      <c r="R30" s="3" t="n">
+        <v>920146.9399999999</v>
+      </c>
       <c r="S30" s="3" t="n"/>
-      <c r="T30" s="3" t="n">
-        <v>131368.5</v>
-      </c>
+      <c r="T30" s="3" t="n"/>
       <c r="U30" s="3" t="n"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
@@ -4357,7 +4363,7 @@
         <v>46230</v>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
@@ -4397,20 +4403,154 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7e3d4a321440d6a7</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>DOC-388bd01c01bbb789</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>91120116300738701X</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>税务行政处罚决定书</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="n"/>
+      <c r="S31" s="3" t="n"/>
+      <c r="T31" s="3" t="n">
+        <v>131368.5</v>
+      </c>
+      <c r="U31" s="3" t="n"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W31" s="4" t="n"/>
+      <c r="X31" s="4" t="n"/>
+      <c r="Y31" s="4" t="n"/>
+      <c r="Z31" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AA31" s="4" t="n">
+        <v>46234</v>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE31" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF31" s="2" t="inlineStr"/>
+      <c r="AG31" s="2" t="inlineStr"/>
+      <c r="AH31" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+        </is>
+      </c>
+      <c r="AI31" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ31" s="2" t="inlineStr">
+        <is>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ30"/>
-  <conditionalFormatting sqref="AD2:AD30">
+  <autoFilter ref="A1:AJ31"/>
+  <conditionalFormatting sqref="AD2:AD31">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AD2="待核验"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI2:AI30">
+  <conditionalFormatting sqref="AI2:AI31">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>AND($AI2&lt;&gt;"正常",$AI2&lt;&gt;"附件正常")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AD2:AD30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AD2:AD31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"已核验,待核验,人工复核完成"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4421,39 +4561,40 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF7" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF8" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF9" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE10" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE11" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE12" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF12" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF13" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE14" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF13" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE14" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF14" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE15" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE16" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE17" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE18" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE19" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF19" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE20" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF20" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE21" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF21" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE22" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE20" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF20" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE21" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF21" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE22" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF22" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE23" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE24" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF24" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE25" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF25" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE26" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF26" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE27" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE25" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF25" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE26" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF26" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE27" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF27" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE28" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE29" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE30" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE31" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -4466,7 +4607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ16"/>
+  <dimension ref="A1:AJ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4777,7 +4918,7 @@
         <v>46233</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -4811,51 +4952,59 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CASE-7b9a26f2ac401107</t>
+          <t>CASE-eb9cfd5295d501e5</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>DOC-f6c6ea472b2ca04a</t>
+          <t>DOC-4a8cf53b445afc63</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>三明市</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
+          <t>北海市</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>海城区</t>
+        </is>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局三明市税务局第一稽查局</t>
+          <t>国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局三明市税务局第一稽查局</t>
+          <t>国家税务总局北海市税务局稽查局</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>三明众祥房地产开发有限公司</t>
+          <t>广西轩易科技有限公司</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>91350400678473231W</t>
+          <t>91450500MAK3N9UJ2T</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
@@ -4866,46 +5015,46 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>明税一稽处〔2026〕20号</t>
+          <t>北市税稽处〔2026〕6号</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>明税一稽处〔2026〕20号</t>
+          <t>北市税稽处〔2026〕6号</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2016年期间,在没有真实业务情况下,取得重庆市博海建设工程(集团)有限公司、福建九九建设有限公司三明分公司开具的不符合规定的发票,发票金额400252379元,在企业所得税税前扣除,造成少缴纳企业所得税100063094.75元,该行为违反《中华人民共和国税收征收管理法》(2015年4月24日主席令第二十三号修改)第六十三条第一款 纳税人伪造、变造、隐匿、擅自销毁账簿、记账凭证,或者在账簿上多列支出或者不列、少列收入,或者经税务机关通知申报而拒不申报或者进行虚假的纳税申报,不缴或者少缴应纳税款的,是偷税。 对纳税人偷税的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款; 之规定,对你公司在账上多列支出,造成少缴企业所得税100063094.75元的行为认定为偷税。 之规定,对你公司少缴的企业所得税从滞纳之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
+          <t>我局于2026年1月23日起对你公司(地址:北海市海城区北部湾东路“金宝小区”B幢B804号20北海汇算账商务秘书有限公司托管)2025年12月11日至2025年12月31日期间的涉税情况进行了检查,发现你公司存在税收违法行为,原《税务处理决定书》(北市税稽处〔2026〕6号)认定的违法事实有误,经重新调查核实,违法事实及处理决定如下: 经查询,你公司2026年1月20日通过网络方式零申报所属期2025年10月1日-2025年12月31日的增值税、城市维护建设税及附加,入库税款0元,申报金额与实际不符,存在虚假申报的情况。 你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 (一)根据《中华人民共和国发票管理办法》(财政部令第6号发布,经国务院令第587号、第709号、第764号修订)第二十一条第二款第(一)项的规定,认定你公司为他人开具与实际经营业务情况不符的前述13份增值税普通电子发票为虚开发票(金额合计571550.49元,税额合计5715.51元,价税合计577266.00元)。 根据《中华人民共和国税收征收管理法》第三十二条、第六十三条第一款、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,已构成偷税,向你公司追缴少缴的税款合计5915.56元,并从滞纳税款之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>企业所得税</t>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R3" s="3" t="n">
-        <v>100063094.75</v>
+        <v>6058.46</v>
       </c>
       <c r="S3" s="3" t="n"/>
       <c r="T3" s="3" t="n"/>
       <c r="U3" s="3" t="n"/>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>据《中华人民共和国税收征收管理法实施细则》第106条规定,将该文书予以公告送达,自公告之日起满30日视为送达。</t>
+          <t>你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《中华人民共和国城市维护建设税法》(中华人民共和国主席令第五十一号)第一条、第二条、第四条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×7%×50%=200.05元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)、《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×3%×50%=85.74元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳地方教育附加5715.51×2%×50%=57.16元。</t>
         </is>
       </c>
       <c r="W3" s="4" t="n"/>
       <c r="X3" s="4" t="n">
-        <v>46223</v>
+        <v>46232</v>
       </c>
       <c r="Y3" s="4" t="n"/>
       <c r="Z3" s="4" t="n">
-        <v>46229</v>
+        <v>46234</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -4931,9 +5080,7 @@
       <c r="AG3" s="2" t="inlineStr"/>
       <c r="AH3" s="2" t="inlineStr">
         <is>
-          <t>关于送达三明众祥房地产开发有限公司 《税务处理决定书》的公告 _
- 其他公告 _
- 国家税务总局三明市税务局</t>
+          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕13号)_国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="AI3" s="2" t="inlineStr">
@@ -4943,22 +5090,22 @@
       </c>
       <c r="AJ3" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>字段“决定书文号”存在冲突:保留原值“北市税稽处〔2026〕6号”,新值“北市税稽处〔2026〕13号”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CASE-31e4a827dfd253f2</t>
+          <t>CASE-7b9a26f2ac401107</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>DOC-3ec54358fce2350d</t>
+          <t>DOC-f6c6ea472b2ca04a</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -4968,28 +5115,28 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>福州市</t>
+          <t>三明市</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局三明市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局三明市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>福州顺路汽车运输有限公司</t>
+          <t>三明众祥房地产开发有限公司</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>91350102MA31MF6611</t>
+          <t>91350400678473231W</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
@@ -5000,46 +5147,46 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽处〔2026〕137号</t>
+          <t>明税一稽处〔2026〕20号</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽处〔2026〕137号</t>
+          <t>明税一稽处〔2026〕20号</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>我局于2025年7月10日起对你公司(地址:福建省闽侯县青口镇祥宏南路922号)2023年1月1日至2024年12月31日期间的发票涉税情况进行检查,违法事实及处理决定如下: (二)你公司取得毕节七星关区辰楚汽车服务部(个人独资)、毕节七星关锦悦汽车服务部(个人独资)、贵州杨亭汽车销售有限公司、贵州楠鑫汽车销售有限公司已证实虚开的35份机动车发票。 (二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 (三)根据《中华人民共和国企业所得税法》第五条、第八条、《企业所得税税前扣除凭证管理办法》(国家税务总局公告2018年第28号发布)第四条、第十二条的规定,你公司取得上述虚开的发票不得作为税前扣除凭证。</t>
+          <t>情况进行了检查,违法事实及处理决定如下: 2016年期间,在没有真实业务情况下,取得重庆市博海建设工程(集团)有限公司、福建九九建设有限公司三明分公司开具的不符合规定的发票,发票金额400252379元,在企业所得税税前扣除,造成少缴纳企业所得税100063094.75元,该行为违反《中华人民共和国税收征收管理法》(2015年4月24日主席令第二十三号修改)第六十三条第一款 纳税人伪造、变造、隐匿、擅自销毁账簿、记账凭证,或者在账簿上多列支出或者不列、少列收入,或者经税务机关通知申报而拒不申报或者进行虚假的纳税申报,不缴或者少缴应纳税款的,是偷税。 对纳税人偷税的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款; 之规定,对你公司在账上多列支出,造成少缴企业所得税100063094.75元的行为认定为偷税。 之规定,对你公司少缴的企业所得税从滞纳之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
+          <t>企业所得税</t>
         </is>
       </c>
       <c r="R4" s="3" t="n">
-        <v>3778.22</v>
+        <v>100063094.75</v>
       </c>
       <c r="S4" s="3" t="n"/>
       <c r="T4" s="3" t="n"/>
       <c r="U4" s="3" t="n"/>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>(二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期城市维护建设税124.75元。 根据《征收教育费附加的暂行规定》第二条、第三条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期教育费附加53.47元。 根据《福建省人民政府关于调整地方教育附加征收标准等有关问题的通知》(闽政文〔2011〕230号)第一条、第二条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期地方教育附加35.64元。</t>
+          <t>据《中华人民共和国税收征收管理法实施细则》第106条规定,将该文书予以公告送达,自公告之日起满30日视为送达。</t>
         </is>
       </c>
       <c r="W4" s="4" t="n"/>
       <c r="X4" s="4" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="Y4" s="4" t="n"/>
       <c r="Z4" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -5065,9 +5212,9 @@
       <c r="AG4" s="2" t="inlineStr"/>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>关于送达福州顺路汽车运输有限公司《税务处理决定书》的公告 _
- 其他类 _
- 国家税务总局福州市税务局</t>
+          <t>关于送达三明众祥房地产开发有限公司 《税务处理决定书》的公告 _
+ 其他公告 _
+ 国家税务总局三明市税务局</t>
         </is>
       </c>
       <c r="AI4" s="2" t="inlineStr">
@@ -5083,16 +5230,16 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CASE-3f564fd9992b1ae3</t>
+          <t>CASE-31e4a827dfd253f2</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>DOC-c34e1d13286aafe2</t>
+          <t>DOC-3ec54358fce2350d</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -5102,28 +5249,28 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>泉州市</t>
+          <t>福州市</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局第二稽查局</t>
+          <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局第二稽查局</t>
+          <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>泉州隆鸿服装制造有限公司</t>
+          <t>福州顺路汽车运输有限公司</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>91350525MA8U3U963L</t>
+          <t>91350102MA31MF6611</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
@@ -5134,18 +5281,18 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>泉税二稽处〔2026〕107号</t>
+          <t>榕税一稽处〔2026〕137号</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>泉税二稽处〔2026〕107号</t>
+          <t>榕税一稽处〔2026〕137号</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>日对你公司税收违法事实依法作出《税务处理决定书》(泉税二稽处〔 涉税情况进行了检查,查明违法事实及处理决定如下: 年你公司在无真实货物交易的情况下,取得河南中弘纺织有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 年期间,你公司在无真实货物交易的情况下,取得开封兴旺纺织品有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 上述违法事实有检查人员实地检查资料、电话拨打记录、邮寄退回函件、《已证实虚开通知单》等相关受托协查资料、主管税务机关出具的《已抵扣证明》、《情况说明》和你公司的申报纳税资料、银行账户流水等 号第三次修订)第二十一条第二款第二项之规定,认定你公司让他人为自己虚开 号第二次修订)第九条和《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告〔 号)之规定,对你公司取得上述已证实虚开的 之规定,决定向你公司追缴少缴的城市维护建设税-增值税附征 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 规定,决定向你公司追缴少缴的教育费附加-增值税附征 规定,决定向你公司追缴少缴的地方教育附加-增值税附征</t>
+          <t>我局于2025年7月10日起对你公司(地址:福建省闽侯县青口镇祥宏南路922号)2023年1月1日至2024年12月31日期间的发票涉税情况进行检查,违法事实及处理决定如下: (二)你公司取得毕节七星关区辰楚汽车服务部(个人独资)、毕节七星关锦悦汽车服务部(个人独资)、贵州杨亭汽车销售有限公司、贵州楠鑫汽车销售有限公司已证实虚开的35份机动车发票。 (二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 (三)根据《中华人民共和国企业所得税法》第五条、第八条、《企业所得税税前扣除凭证管理办法》(国家税务总局公告2018年第28号发布)第四条、第十二条的规定,你公司取得上述虚开的发票不得作为税前扣除凭证。</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5153,25 +5300,27 @@
           <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R5" s="3" t="n"/>
+      <c r="R5" s="3" t="n">
+        <v>3778.22</v>
+      </c>
       <c r="S5" s="3" t="n"/>
       <c r="T5" s="3" t="n"/>
       <c r="U5" s="3" t="n"/>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>由于你公司走逃失联、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 (五)根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司上述应补缴税款按税款所属时间从税款滞纳之日起按日加收万分之五滞纳金</t>
+          <t>(二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期城市维护建设税124.75元。 根据《征收教育费附加的暂行规定》第二条、第三条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期教育费附加53.47元。 根据《福建省人民政府关于调整地方教育附加征收标准等有关问题的通知》(闽政文〔2011〕230号)第一条、第二条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期地方教育附加35.64元。</t>
         </is>
       </c>
       <c r="W5" s="4" t="n"/>
       <c r="X5" s="4" t="n">
-        <v>46202</v>
+        <v>46218</v>
       </c>
       <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -5197,9 +5346,9 @@
       <c r="AG5" s="2" t="inlineStr"/>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>关于对泉州隆鸿服装制造有限公司《税务处理决定书》送达的公告 _
- 其他公告 _
- 国家税务总局泉州市税务局</t>
+          <t>关于送达福州顺路汽车运输有限公司《税务处理决定书》的公告 _
+ 其他类 _
+ 国家税务总局福州市税务局</t>
         </is>
       </c>
       <c r="AI5" s="2" t="inlineStr">
@@ -5215,47 +5364,47 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>CASE-a62e569c195adc3c</t>
+          <t>CASE-3f564fd9992b1ae3</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>DOC-b1dda915d4e6117d</t>
+          <t>DOC-c34e1d13286aafe2</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>遵义市</t>
+          <t>泉州市</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局泉州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局泉州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>贵州服格定商贸有限公司</t>
+          <t>泉州隆鸿服装制造有限公司</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>91520302MABUEHN034</t>
+          <t>91350525MA8U3U963L</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
@@ -5266,40 +5415,44 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>遵税一稽处〔2026〕30号</t>
+          <t>泉税二稽处〔2026〕107号</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>遵税一稽处〔2026〕30号</t>
+          <t>泉税二稽处〔2026〕107号</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
+          <t>日对你公司税收违法事实依法作出《税务处理决定书》(泉税二稽处〔 涉税情况进行了检查,查明违法事实及处理决定如下: 年你公司在无真实货物交易的情况下,取得河南中弘纺织有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 年期间,你公司在无真实货物交易的情况下,取得开封兴旺纺织品有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 上述违法事实有检查人员实地检查资料、电话拨打记录、邮寄退回函件、《已证实虚开通知单》等相关受托协查资料、主管税务机关出具的《已抵扣证明》、《情况说明》和你公司的申报纳税资料、银行账户流水等 号第三次修订)第二十一条第二款第二项之规定,认定你公司让他人为自己虚开 号第二次修订)第九条和《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告〔 号)之规定,对你公司取得上述已证实虚开的 之规定,决定向你公司追缴少缴的城市维护建设税-增值税附征 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 规定,决定向你公司追缴少缴的教育费附加-增值税附征 规定,决定向你公司追缴少缴的地方教育附加-增值税附征</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
+          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R6" s="3" t="n"/>
       <c r="S6" s="3" t="n"/>
       <c r="T6" s="3" t="n"/>
       <c r="U6" s="3" t="n"/>
-      <c r="V6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>由于你公司走逃失联、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 (五)根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司上述应补缴税款按税款所属时间从税款滞纳之日起按日加收万分之五滞纳金</t>
+        </is>
+      </c>
       <c r="W6" s="4" t="n"/>
       <c r="X6" s="4" t="n">
-        <v>46185</v>
+        <v>46202</v>
       </c>
       <c r="Y6" s="4" t="n"/>
       <c r="Z6" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -5313,7 +5466,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE6" s="5" t="inlineStr">
@@ -5325,12 +5478,14 @@
       <c r="AG6" s="2" t="inlineStr"/>
       <c r="AH6" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
+          <t>关于对泉州隆鸿服装制造有限公司《税务处理决定书》送达的公告 _
+ 其他公告 _
+ 国家税务总局泉州市税务局</t>
         </is>
       </c>
       <c r="AI6" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="inlineStr">
@@ -5341,54 +5496,50 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CASE-f94bf08964abff5a</t>
+          <t>CASE-a62e569c195adc3c</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>DOC-4574b1aadef8f30d</t>
+          <t>DOC-b1dda915d4e6117d</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
+          <t>遵义市</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
+          <t>国家税务总局遵义市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局稽查局</t>
+          <t>国家税务总局遵义市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>常州市文杰车辆配件厂</t>
+          <t>贵州服格定商贸有限公司</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>91320411799075280A</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>朱某</t>
-        </is>
-      </c>
+          <t>91520302MABUEHN034</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
           <t>税务处理决定书</t>
@@ -5396,48 +5547,40 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕73号</t>
+          <t>遵税一稽处〔2026〕30号</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕73号</t>
+          <t>遵税一稽处〔2026〕30号</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公 月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
+          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>179137.12</v>
-      </c>
+          <t>增值税</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="n"/>
       <c r="S7" s="3" t="n"/>
       <c r="T7" s="3" t="n"/>
       <c r="U7" s="3" t="n"/>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市 份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元,</t>
-        </is>
-      </c>
-      <c r="W7" s="4" t="n">
-        <v>46044</v>
-      </c>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="4" t="n"/>
       <c r="X7" s="4" t="n">
-        <v>46090</v>
+        <v>46185</v>
       </c>
       <c r="Y7" s="4" t="n"/>
       <c r="Z7" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -5451,7 +5594,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE7" s="5" t="inlineStr">
@@ -5459,20 +5602,16 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF7" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF7" s="2" t="inlineStr"/>
       <c r="AG7" s="2" t="inlineStr"/>
       <c r="AH7" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
+          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
         </is>
       </c>
       <c r="AI7" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>页面已删除</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr">
@@ -5483,16 +5622,16 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CASE-61b9b55a9d3357c7</t>
+          <t>CASE-f94bf08964abff5a</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DOC-1228a9c92b2b0632</t>
+          <t>DOC-4574b1aadef8f30d</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -5508,25 +5647,29 @@
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局常州市税务局稽查局</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>常州市三鹏机械有限公司</t>
+          <t>常州市文杰车辆配件厂</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>91320404732260748Q</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
+          <t>91320411799075280A</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>朱某</t>
+        </is>
+      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>税务处理决定书</t>
@@ -5534,46 +5677,48 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
+          <t>常税稽处〔2026〕73号</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>常税稽一罚〔2026〕14号</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
+          <t>常税稽处〔2026〕73号</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公 月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
+        </is>
+      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R8" s="3" t="n">
-        <v>63464.09</v>
+        <v>179137.12</v>
       </c>
       <c r="S8" s="3" t="n"/>
       <c r="T8" s="3" t="n"/>
       <c r="U8" s="3" t="n"/>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
-        </is>
-      </c>
-      <c r="W8" s="4" t="n"/>
+          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市 份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元,</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="n">
+        <v>46044</v>
+      </c>
       <c r="X8" s="4" t="n">
-        <v>46066</v>
+        <v>46090</v>
       </c>
       <c r="Y8" s="4" t="n"/>
       <c r="Z8" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -5595,16 +5740,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AF8" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG8" s="2" t="inlineStr"/>
       <c r="AH8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI8" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="inlineStr">
@@ -5615,7 +5764,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -5624,7 +5773,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DOC-b97456a64b153f67</t>
+          <t>DOC-1228a9c92b2b0632</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -5661,12 +5810,12 @@
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>常税稽一罚〔2026〕14号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5685,11 +5834,11 @@
           <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R9" s="3" t="n"/>
+      <c r="R9" s="3" t="n">
+        <v>63464.09</v>
+      </c>
       <c r="S9" s="3" t="n"/>
-      <c r="T9" s="3" t="n">
-        <v>20000</v>
-      </c>
+      <c r="T9" s="3" t="n"/>
       <c r="U9" s="3" t="n"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
@@ -5705,7 +5854,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -5747,103 +5896,97 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CASE-f78ec1a594442165</t>
+          <t>CASE-61b9b55a9d3357c7</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DOC-fbbe4a664b14f54b</t>
+          <t>DOC-b97456a64b153f67</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>安顺市</t>
+          <t>常州市</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
+          <t>常州市三鹏机械有限公司</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>91520423MA6DLH799Q</t>
+          <t>91320404732260748Q</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一罚〔2026〕14号</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
-        </is>
-      </c>
+          <t>常税稽一罚〔2026〕14号</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>64884.41</v>
-      </c>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="n"/>
       <c r="S10" s="3" t="n"/>
-      <c r="T10" s="3" t="n"/>
+      <c r="T10" s="3" t="n">
+        <v>20000</v>
+      </c>
       <c r="U10" s="3" t="n"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
-      <c r="W10" s="4" t="n">
-        <v>45898</v>
-      </c>
+          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
+        </is>
+      </c>
+      <c r="W10" s="4" t="n"/>
       <c r="X10" s="4" t="n">
-        <v>46043</v>
+        <v>46066</v>
       </c>
       <c r="Y10" s="4" t="n"/>
       <c r="Z10" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -5857,7 +6000,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE10" s="5" t="inlineStr">
@@ -5865,15 +6008,11 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF10" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF10" s="2" t="inlineStr"/>
       <c r="AG10" s="2" t="inlineStr"/>
       <c r="AH10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI10" s="2" t="inlineStr">
@@ -5883,13 +6022,13 @@
       </c>
       <c r="AJ10" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
@@ -5898,7 +6037,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>DOC-9a828a6048b54b6c</t>
+          <t>DOC-fbbe4a664b14f54b</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -5935,27 +6074,27 @@
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>安市税稽罚〔2026〕1号</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>安市税稽处〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5963,11 +6102,11 @@
           <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R11" s="3" t="n"/>
+      <c r="R11" s="3" t="n">
+        <v>64884.41</v>
+      </c>
       <c r="S11" s="3" t="n"/>
-      <c r="T11" s="3" t="n">
-        <v>200000</v>
-      </c>
+      <c r="T11" s="3" t="n"/>
       <c r="U11" s="3" t="n"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
@@ -5985,7 +6124,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -6025,97 +6164,109 @@
       </c>
       <c r="AJ11" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CASE-fe959d4c6c52d910</t>
+          <t>CASE-f78ec1a594442165</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>DOC-f2643f2a0719d8d1</t>
+          <t>DOC-9a828a6048b54b6c</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>南宁市</t>
+          <t>安顺市</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局稽查局</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>南宁洪谦金贸易有限公司</t>
+          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>91450103MA5K9WHY7U</t>
+          <t>91520423MA6DLH799Q</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>南市税一稽处〔2026〕2号</t>
+          <t>安市税稽罚〔2026〕1号</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>南市税一稽处〔2026〕2号</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr"/>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽罚〔2026〕1号</t>
+        </is>
+      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>经我局2025年10月29日至2025年12月8日对你公司(地址:南宁市青秀区云景路11号春晖花园C区3栋2单元1606号)2015年12月2日至2016年12月31日期间的涉税情况进行了检查,你(单位)存在以下违法事实: 经查询你公司向税务机关报备的银行账号:广西北部湾银行南宁市财富国际支行800099398800015,经函询广西北部湾银行南宁市财富国际支行,存在以下问题: 上述行为属于开具与实际经营业务情况不符的增值税发票,违反了《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第587号修改)第二十二条第一款、第二款第(一)项的规定,属于虚开发票行为。</t>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
+          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R12" s="3" t="n"/>
       <c r="S12" s="3" t="n"/>
-      <c r="T12" s="3" t="n"/>
+      <c r="T12" s="3" t="n">
+        <v>200000</v>
+      </c>
       <c r="U12" s="3" t="n"/>
-      <c r="V12" s="2" t="inlineStr"/>
-      <c r="W12" s="4" t="n"/>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="n">
+        <v>45898</v>
+      </c>
       <c r="X12" s="4" t="n">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="Y12" s="4" t="n"/>
       <c r="Z12" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -6129,7 +6280,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE12" s="5" t="inlineStr">
@@ -6145,61 +6296,65 @@
       <c r="AG12" s="2" t="inlineStr"/>
       <c r="AH12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局税务文书送达公告_国家税务总局南宁市税务局</t>
+          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI12" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ12" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CASE-1983d97878508732</t>
+          <t>CASE-fe959d4c6c52d910</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>DOC-f9760895b4f08cc2</t>
+          <t>DOC-f2643f2a0719d8d1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>二连浩特市</t>
+          <t>南宁市</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局</t>
+          <t>国家税务总局南宁市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局稽查局</t>
+          <t>国家税务总局南宁市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>二连市坤益腾金属有限公司</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr"/>
+          <t>南宁洪谦金贸易有限公司</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>91450103MA5K9WHY7U</t>
+        </is>
+      </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
@@ -6208,18 +6363,18 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
+          <t>南市税一稽处〔2026〕2号</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
+          <t>南市税一稽处〔2026〕2号</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
+          <t>经我局2025年10月29日至2025年12月8日对你公司(地址:南宁市青秀区云景路11号春晖花园C区3栋2单元1606号)2015年12月2日至2016年12月31日期间的涉税情况进行了检查,你(单位)存在以下违法事实: 经查询你公司向税务机关报备的银行账号:广西北部湾银行南宁市财富国际支行800099398800015,经函询广西北部湾银行南宁市财富国际支行,存在以下问题: 上述行为属于开具与实际经营业务情况不符的增值税发票,违反了《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第587号修改)第二十二条第一款、第二款第(一)项的规定,属于虚开发票行为。</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6231,19 +6386,17 @@
       <c r="S13" s="3" t="n"/>
       <c r="T13" s="3" t="n"/>
       <c r="U13" s="3" t="n"/>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
-        </is>
-      </c>
+      <c r="V13" s="2" t="inlineStr"/>
       <c r="W13" s="4" t="n"/>
-      <c r="X13" s="4" t="n"/>
+      <c r="X13" s="4" t="n">
+        <v>46031</v>
+      </c>
       <c r="Y13" s="4" t="n"/>
       <c r="Z13" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -6257,7 +6410,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE13" s="5" t="inlineStr">
@@ -6265,36 +6418,40 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AF13" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG13" s="2" t="inlineStr"/>
       <c r="AH13" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>国家税务总局南宁市税务局第一稽查局税务文书送达公告_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI13" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ13" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASE-d4b6986f3f97cd28</t>
+          <t>CASE-1983d97878508732</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DOC-442cf3d9a5280c12</t>
+          <t>DOC-f9760895b4f08cc2</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -6304,19 +6461,23 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>鄂尔多斯市</t>
+          <t>二连浩特市</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局二连浩特市税务局</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>第二稽查局</t>
+          <t>国家税务总局二连浩特市税务局稽查局</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>廖礼平</t>
+          <t>二连市坤益腾金属有限公司</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -6328,36 +6489,32 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
+          <t>二税稽处〔2025〕1号</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
+          <t>二税稽处〔2025〕1号</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
+          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>个人所得税、印花税</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>15072487.5</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>1046925</v>
-      </c>
+          <t>增值税</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="n"/>
+      <c r="S14" s="3" t="n"/>
       <c r="T14" s="3" t="n"/>
       <c r="U14" s="3" t="n"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
+          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
         </is>
       </c>
       <c r="W14" s="4" t="n"/>
@@ -6367,7 +6524,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -6403,55 +6560,47 @@
       </c>
       <c r="AJ14" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
+          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CASE-7e3d4a321440d6a7</t>
+          <t>CASE-d4b6986f3f97cd28</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>DOC-bed9330343ed06af</t>
+          <t>DOC-442cf3d9a5280c12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>鄂尔多斯市</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
-        </is>
-      </c>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
+          <t>第二稽查局</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>天津展达科技有限公司</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>91120116300738701X</t>
-        </is>
-      </c>
+          <t>廖礼平</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -6460,48 +6609,46 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
+          <t>鄂税二稽处〔2023〕29号</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
+          <t>鄂税二稽处〔2023〕29号</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+          <t>个人所得税、印花税</t>
         </is>
       </c>
       <c r="R15" s="3" t="n">
-        <v>920146.9399999999</v>
-      </c>
-      <c r="S15" s="3" t="n"/>
+        <v>15072487.5</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>1046925</v>
+      </c>
       <c r="T15" s="3" t="n"/>
       <c r="U15" s="3" t="n"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
         </is>
       </c>
       <c r="W15" s="4" t="n"/>
       <c r="X15" s="4" t="n"/>
       <c r="Y15" s="4" t="n"/>
       <c r="Z15" s="4" t="n">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6674,7 @@
       <c r="AG15" s="2" t="inlineStr"/>
       <c r="AH15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="AI15" s="2" t="inlineStr">
@@ -6537,13 +6684,13 @@
       </c>
       <c r="AJ15" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
@@ -6552,7 +6699,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>DOC-388bd01c01bbb789</t>
+          <t>DOC-bed9330343ed06af</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -6589,24 +6736,24 @@
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>津税一稽罚〔2023〕21号</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
           <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
@@ -6617,11 +6764,11 @@
           <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R16" s="3" t="n"/>
+      <c r="R16" s="3" t="n">
+        <v>920146.9399999999</v>
+      </c>
       <c r="S16" s="3" t="n"/>
-      <c r="T16" s="3" t="n">
-        <v>131368.5</v>
-      </c>
+      <c r="T16" s="3" t="n"/>
       <c r="U16" s="3" t="n"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
@@ -6635,7 +6782,7 @@
         <v>46230</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -6675,20 +6822,154 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7e3d4a321440d6a7</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>DOC-388bd01c01bbb789</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>91120116300738701X</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>税务行政处罚决定书</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="n"/>
+      <c r="S17" s="3" t="n"/>
+      <c r="T17" s="3" t="n">
+        <v>131368.5</v>
+      </c>
+      <c r="U17" s="3" t="n"/>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W17" s="4" t="n"/>
+      <c r="X17" s="4" t="n"/>
+      <c r="Y17" s="4" t="n"/>
+      <c r="Z17" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AA17" s="4" t="n">
+        <v>46234</v>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD17" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE17" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+        </is>
+      </c>
+      <c r="AI17" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ17" s="2" t="inlineStr">
+        <is>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ16"/>
-  <conditionalFormatting sqref="AD2:AD16">
+  <autoFilter ref="A1:AJ17"/>
+  <conditionalFormatting sqref="AD2:AD17">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AD2="待核验"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI2:AI16">
+  <conditionalFormatting sqref="AI2:AI17">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>AND($AI2&lt;&gt;"正常",$AI2&lt;&gt;"附件正常")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AD2:AD16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AD2:AD17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"已核验,待核验,人工复核完成"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6699,19 +6980,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF7" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF8" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE9" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE10" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE11" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF11" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE12" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF12" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF11" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE12" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF12" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF13" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE14" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE15" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE16" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE17" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -7029,7 +7311,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -7147,7 +7429,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -7269,7 +7551,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -7395,7 +7677,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -7521,7 +7803,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -7639,7 +7921,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -7761,7 +8043,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -7883,7 +8165,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -8005,7 +8287,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -8127,7 +8409,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -8249,7 +8531,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -8371,7 +8653,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -8489,7 +8771,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -8611,7 +8893,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -9006,7 +9288,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -9132,7 +9414,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -9250,7 +9532,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -9372,7 +9654,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -9494,7 +9776,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -9612,7 +9894,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -9754,7 +10036,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -9896,7 +10178,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -10024,7 +10306,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -10148,7 +10430,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -10282,7 +10564,7 @@
         <v>46230</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -10416,7 +10698,7 @@
         <v>46230</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -10802,7 +11084,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -10928,7 +11210,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -11046,7 +11328,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -11168,7 +11450,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -11290,7 +11572,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -11408,7 +11690,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -11489,7 +11771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12134,8 +12416,57 @@
         </is>
       </c>
     </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31T14:49:29+08:00</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28 至 2026-07-31</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>广西轩易科技有限公司</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>已完成候选发现、逐条访问核验、去重、关联和历史数据增量写入。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M13"/>
+  <autoFilter ref="A1:M14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -791,7 +791,7 @@
         <v>46233</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>46234</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
       </c>
       <c r="AJ3" s="2" t="inlineStr">
         <is>
-          <t>字段“决定书文号”存在冲突:保留原值“北市税稽处〔2026〕6号”,新值“北市税稽处〔2026〕13号”未静默覆盖。</t>
+          <t>字段“决定书文号”存在冲突:保留原值“北市税稽处〔2026〕6号”,新值“北市税稽处〔2026〕13号”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>46229</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>46229</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>46229</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>46229</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>46229</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>46229</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>46229</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>46229</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>46229</v>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>46229</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>46229</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>46229</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>46229</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>46229</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>46230</v>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>46230</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>46233</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>46234</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="AJ3" s="2" t="inlineStr">
         <is>
-          <t>字段“决定书文号”存在冲突:保留原值“北市税稽处〔2026〕6号”,新值“北市税稽处〔2026〕13号”未静默覆盖。</t>
+          <t>字段“决定书文号”存在冲突:保留原值“北市税稽处〔2026〕6号”,新值“北市税稽处〔2026〕13号”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>46230</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>46230</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>46230</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>46230</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12465,8 +12465,53 @@
         </is>
       </c>
     </row>
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01T14:34:47+08:00</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 至 2026-08-01</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>本次检索未发现符合收录标准的新文书。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M14"/>
+  <autoFilter ref="A1:M15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -15,12 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日运行日志" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文书汇总'!$A$1:$AJ$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文书汇总'!$A$1:$AJ$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'完整文书'!$A$1:$AJ$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ31"/>
+  <dimension ref="A1:AJ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -705,16 +705,16 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CASE-89fc66bfc8dad80d</t>
+          <t>CASE-119dcfa5a7c6b239</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>DOC-6e5b966cd65a4366</t>
+          <t>DOC-1a423a3cbfed9f3f</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -724,30 +724,30 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>北海市</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>银海区</t>
-        </is>
-      </c>
+          <t>南宁市</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局北海市税务局</t>
+          <t>国家税务总局南宁市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局北海市税务局稽查局</t>
+          <t>国家税务总局南宁市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>广西耿仁建材有限公司</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
+          <t>广西威曼能源科技有限公司</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>91450103MA5NJYGEXM</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -756,46 +756,40 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>北市税稽处〔2026〕14号</t>
+          <t>南市税三稽处〔2026〕19号</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>北市税稽处〔2026〕14号</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>我局于2026年2月11日至2026年7月15日对你公司(地址:北海市银海区新世纪大道15号辰宸花园3幢二单元0901号)2026年1月1日至2026年1月31日期间的涉税情况进行了检查,违法事实及处理决定如下: (2)短时间开具大量大额发票且未申报 你公司未进行纳税申报,不缴或者少缴2026年1月增值税194612.47元,2026年1月城市维护建设税13622.87元,合计208235.34元。 根据《中华人民共和国税收征收管理法》第六十三条第一款规定,对上述行为定性为偷税,向你公司追缴少缴的2026年增值税194612.47元,城市维护建设税13622.87元,合计208235.34元。 1.根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)的规定,对你公司少缴所属期2026年1月的教育费附加5838.37元,予以追缴。 2.根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条的规定,对你公司少缴所属期2026年1月地方教育附加3892.25元,予以追缴。 根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司少缴的税款从税款滞纳之日起至实际缴纳税款之日止按日加收滞纳税款万分之五的滞纳金,滞纳金由金三系统自动计算加收。 (四)你公司无法联系且实地核查无实际生产地址、无生产能力、查无下落,短期开票金额大,无法核实资金流,未进行纳税申报,根据《国家税务总局关于走逃(失联)企业开具增值税专用发票认定处理有关问题的公告》(国家税务总局公告2016年第76号),将你公司按走逃(失联)处理,根据《中华人民共和国发票管理办法》(国函〔1993〕174号)第二十一条第(一)项,你公司无生产能力,却为他人开具与实际经营业务情况不符的发票,属于虚开发票的行为。</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>208235.34</v>
-      </c>
+          <t>南市税三稽处〔2026〕19号</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>南市税三稽罚〔2026〕10号</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="3" t="n"/>
       <c r="S2" s="3" t="n"/>
       <c r="T2" s="3" t="n"/>
       <c r="U2" s="3" t="n"/>
       <c r="V2" s="2" t="inlineStr"/>
       <c r="W2" s="4" t="n"/>
       <c r="X2" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="Y2" s="4" t="n"/>
       <c r="Z2" s="4" t="n">
-        <v>46233</v>
+        <v>46236</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -813,36 +807,36 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr"/>
+      <c r="AF2" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG2" s="2" t="inlineStr"/>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕14号)_国家税务总局北海市税务局</t>
+          <t>国家税务总局南宁市税务局第三稽查局 税务文书送达公告_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI2" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="AJ2" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
+          <t>附件正常</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CASE-eb9cfd5295d501e5</t>
+          <t>CASE-119dcfa5a7c6b239</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>DOC-4a8cf53b445afc63</t>
+          <t>DOC-f8499a65abd851d8</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -852,86 +846,72 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>北海市</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>海城区</t>
-        </is>
-      </c>
+          <t>南宁市</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局北海市税务局</t>
+          <t>国家税务总局南宁市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局北海市税务局稽查局</t>
+          <t>国家税务总局南宁市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>广西轩易科技有限公司</t>
+          <t>广西威曼能源科技有限公司</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>91450500MAK3N9UJ2T</t>
+          <t>91450103MA5NJYGEXM</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>北市税稽处〔2026〕6号</t>
+          <t>南市税三稽罚〔2026〕10号</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>北市税稽处〔2026〕6号</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>我局于2026年1月23日起对你公司(地址:北海市海城区北部湾东路“金宝小区”B幢B804号20北海汇算账商务秘书有限公司托管)2025年12月11日至2025年12月31日期间的涉税情况进行了检查,发现你公司存在税收违法行为,原《税务处理决定书》(北市税稽处〔2026〕6号)认定的违法事实有误,经重新调查核实,违法事实及处理决定如下: 经查询,你公司2026年1月20日通过网络方式零申报所属期2025年10月1日-2025年12月31日的增值税、城市维护建设税及附加,入库税款0元,申报金额与实际不符,存在虚假申报的情况。 你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 (一)根据《中华人民共和国发票管理办法》(财政部令第6号发布,经国务院令第587号、第709号、第764号修订)第二十一条第二款第(一)项的规定,认定你公司为他人开具与实际经营业务情况不符的前述13份增值税普通电子发票为虚开发票(金额合计571550.49元,税额合计5715.51元,价税合计577266.00元)。 根据《中华人民共和国税收征收管理法》第三十二条、第六十三条第一款、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,已构成偷税,向你公司追缴少缴的税款合计5915.56元,并从滞纳税款之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>6058.46</v>
-      </c>
+          <t>南市税三稽处〔2026〕19号</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>南市税三稽罚〔2026〕10号</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="3" t="n"/>
       <c r="S3" s="3" t="n"/>
       <c r="T3" s="3" t="n"/>
       <c r="U3" s="3" t="n"/>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《中华人民共和国城市维护建设税法》(中华人民共和国主席令第五十一号)第一条、第二条、第四条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×7%×50%=200.05元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)、《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×3%×50%=85.74元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳地方教育附加5715.51×2%×50%=57.16元。</t>
-        </is>
-      </c>
+      <c r="V3" s="2" t="inlineStr"/>
       <c r="W3" s="4" t="n"/>
       <c r="X3" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="Y3" s="4" t="n"/>
       <c r="Z3" s="4" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -949,69 +929,69 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF3" s="2" t="inlineStr"/>
+      <c r="AF3" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG3" s="2" t="inlineStr"/>
       <c r="AH3" s="2" t="inlineStr">
         <is>
-          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕13号)_国家税务总局北海市税务局</t>
+          <t>国家税务总局南宁市税务局第三稽查局 税务文书送达公告_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI3" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="AJ3" s="2" t="inlineStr">
-        <is>
-          <t>字段“决定书文号”存在冲突:保留原值“北市税稽处〔2026〕6号”,新值“北市税稽处〔2026〕13号”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
+          <t>附件正常</t>
+        </is>
+      </c>
+      <c r="AJ3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CASE-3e050a699b29b0d0</t>
+          <t>CASE-89fc66bfc8dad80d</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>DOC-96a3089a0e2b37cd</t>
+          <t>DOC-6e5b966cd65a4366</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>河南省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>平顶山市</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
+          <t>北海市</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>银海区</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局平顶山市税务局第一稽查局</t>
+          <t>国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局平顶山市税务局第一稽查局</t>
+          <t>国家税务总局北海市税务局稽查局</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>汝州泰隆实业有限公司</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>91410482MA40K4KA3B</t>
-        </is>
-      </c>
+          <t>广西耿仁建材有限公司</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -1020,40 +1000,46 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>平税稽一局处〔2026〕1号</t>
+          <t>北市税稽处〔2026〕14号</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>平税稽一局处〔2026〕1号</t>
+          <t>北市税稽处〔2026〕14号</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>我局于2026年2月11日至2026年7月15日对你公司(地址:北海市银海区新世纪大道15号辰宸花园3幢二单元0901号)2026年1月1日至2026年1月31日期间的涉税情况进行了检查,违法事实及处理决定如下: (2)短时间开具大量大额发票且未申报 你公司未进行纳税申报,不缴或者少缴2026年1月增值税194612.47元,2026年1月城市维护建设税13622.87元,合计208235.34元。 根据《中华人民共和国税收征收管理法》第六十三条第一款规定,对上述行为定性为偷税,向你公司追缴少缴的2026年增值税194612.47元,城市维护建设税13622.87元,合计208235.34元。 1.根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)的规定,对你公司少缴所属期2026年1月的教育费附加5838.37元,予以追缴。 2.根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条的规定,对你公司少缴所属期2026年1月地方教育附加3892.25元,予以追缴。 根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司少缴的税款从税款滞纳之日起至实际缴纳税款之日止按日加收滞纳税款万分之五的滞纳金,滞纳金由金三系统自动计算加收。 (四)你公司无法联系且实地核查无实际生产地址、无生产能力、查无下落,短期开票金额大,无法核实资金流,未进行纳税申报,根据《国家税务总局关于走逃(失联)企业开具增值税专用发票认定处理有关问题的公告》(国家税务总局公告2016年第76号),将你公司按走逃(失联)处理,根据《中华人民共和国发票管理办法》(国函〔1993〕174号)第二十一条第(一)项,你公司无生产能力,却为他人开具与实际经营业务情况不符的发票,属于虚开发票的行为。</t>
+        </is>
+      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>增值税、个人所得税</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="n"/>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>208235.34</v>
+      </c>
       <c r="S4" s="3" t="n"/>
       <c r="T4" s="3" t="n"/>
       <c r="U4" s="3" t="n"/>
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="4" t="n"/>
       <c r="X4" s="4" t="n">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="Y4" s="4" t="n"/>
       <c r="Z4" s="4" t="n">
-        <v>46229</v>
+        <v>46233</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1075,7 +1061,7 @@
       <c r="AG4" s="2" t="inlineStr"/>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局平顶山市税务局第一稽查局关于送达汝州泰隆实业有限公司《税务处理决定书》的公告 - 国家税务总局平顶山市税务局</t>
+          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕14号)_国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="AI4" s="2" t="inlineStr">
@@ -1091,47 +1077,51 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CASE-365e8a924cf64611</t>
+          <t>CASE-eb9cfd5295d501e5</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>DOC-4d14eba16f9aa8a0</t>
+          <t>DOC-4a8cf53b445afc63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
+          <t>北海市</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>海城区</t>
+        </is>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局北海市税务局稽查局</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>贵州博泰工贸有限公司</t>
+          <t>广西轩易科技有限公司</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>91520115587255589F</t>
+          <t>91450500MAK3N9UJ2T</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
@@ -1142,36 +1132,50 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕38号</t>
+          <t>北市税稽处〔2026〕6号</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕38号</t>
+          <t>北市税稽处〔2026〕6号</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="3" t="n"/>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>我局于2026年1月23日起对你公司(地址:北海市海城区北部湾东路“金宝小区”B幢B804号20北海汇算账商务秘书有限公司托管)2025年12月11日至2025年12月31日期间的涉税情况进行了检查,发现你公司存在税收违法行为,原《税务处理决定书》(北市税稽处〔2026〕6号)认定的违法事实有误,经重新调查核实,违法事实及处理决定如下: 经查询,你公司2026年1月20日通过网络方式零申报所属期2025年10月1日-2025年12月31日的增值税、城市维护建设税及附加,入库税款0元,申报金额与实际不符,存在虚假申报的情况。 你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 (一)根据《中华人民共和国发票管理办法》(财政部令第6号发布,经国务院令第587号、第709号、第764号修订)第二十一条第二款第(一)项的规定,认定你公司为他人开具与实际经营业务情况不符的前述13份增值税普通电子发票为虚开发票(金额合计571550.49元,税额合计5715.51元,价税合计577266.00元)。 根据《中华人民共和国税收征收管理法》第三十二条、第六十三条第一款、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,已构成偷税,向你公司追缴少缴的税款合计5915.56元,并从滞纳税款之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>6058.46</v>
+      </c>
       <c r="S5" s="3" t="n"/>
       <c r="T5" s="3" t="n"/>
       <c r="U5" s="3" t="n"/>
-      <c r="V5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《中华人民共和国城市维护建设税法》(中华人民共和国主席令第五十一号)第一条、第二条、第四条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×7%×50%=200.05元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)、《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×3%×50%=85.74元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳地方教育附加5715.51×2%×50%=57.16元。</t>
+        </is>
+      </c>
       <c r="W5" s="4" t="n"/>
       <c r="X5" s="4" t="n">
-        <v>46224</v>
+        <v>46232</v>
       </c>
       <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n">
-        <v>46229</v>
+        <v>46234</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1181,7 +1185,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE5" s="5" t="inlineStr">
@@ -1193,63 +1197,63 @@
       <c r="AG5" s="2" t="inlineStr"/>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书、税务行政处罚决定书的公告</t>
+          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕13号)_国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="AI5" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>字段“决定书文号”存在冲突:保留原值“北市税稽处〔2026〕6号”,新值“北市税稽处〔2026〕13号”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>CASE-7b9a26f2ac401107</t>
+          <t>CASE-3e050a699b29b0d0</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>DOC-f6c6ea472b2ca04a</t>
+          <t>DOC-96a3089a0e2b37cd</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>三明市</t>
+          <t>平顶山市</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局三明市税务局第一稽查局</t>
+          <t>国家税务总局平顶山市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局三明市税务局第一稽查局</t>
+          <t>国家税务总局平顶山市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>三明众祥房地产开发有限公司</t>
+          <t>汝州泰隆实业有限公司</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>91350400678473231W</t>
+          <t>91410482MA40K4KA3B</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
@@ -1260,50 +1264,40 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>明税一稽处〔2026〕20号</t>
+          <t>平税稽一局处〔2026〕1号</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>明税一稽处〔2026〕20号</t>
+          <t>平税稽一局处〔2026〕1号</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2016年期间,在没有真实业务情况下,取得重庆市博海建设工程(集团)有限公司、福建九九建设有限公司三明分公司开具的不符合规定的发票,发票金额400252379元,在企业所得税税前扣除,造成少缴纳企业所得税100063094.75元,该行为违反《中华人民共和国税收征收管理法》(2015年4月24日主席令第二十三号修改)第六十三条第一款 纳税人伪造、变造、隐匿、擅自销毁账簿、记账凭证,或者在账簿上多列支出或者不列、少列收入,或者经税务机关通知申报而拒不申报或者进行虚假的纳税申报,不缴或者少缴应纳税款的,是偷税。 对纳税人偷税的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款; 之规定,对你公司在账上多列支出,造成少缴企业所得税100063094.75元的行为认定为偷税。 之规定,对你公司少缴的企业所得税从滞纳之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
+      <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>企业所得税</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>100063094.75</v>
-      </c>
+          <t>增值税、个人所得税</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="n"/>
       <c r="S6" s="3" t="n"/>
       <c r="T6" s="3" t="n"/>
       <c r="U6" s="3" t="n"/>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>据《中华人民共和国税收征收管理法实施细则》第106条规定,将该文书予以公告送达,自公告之日起满30日视为送达。</t>
-        </is>
-      </c>
+      <c r="V6" s="2" t="inlineStr"/>
       <c r="W6" s="4" t="n"/>
       <c r="X6" s="4" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="Y6" s="4" t="n"/>
       <c r="Z6" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1325,400 +1319,398 @@
       <c r="AG6" s="2" t="inlineStr"/>
       <c r="AH6" s="2" t="inlineStr">
         <is>
+          <t>国家税务总局平顶山市税务局第一稽查局关于送达汝州泰隆实业有限公司《税务处理决定书》的公告 - 国家税务总局平顶山市税务局</t>
+        </is>
+      </c>
+      <c r="AI6" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ6" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>CASE-365e8a924cf64611</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>DOC-4d14eba16f9aa8a0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>贵州省</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>贵阳市</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>贵州博泰工贸有限公司</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>91520115587255589F</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>筑税三稽处〔2026〕38号</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>筑税三稽处〔2026〕38号</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="3" t="n"/>
+      <c r="S7" s="3" t="n"/>
+      <c r="T7" s="3" t="n"/>
+      <c r="U7" s="3" t="n"/>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="4" t="n"/>
+      <c r="X7" s="4" t="n">
+        <v>46224</v>
+      </c>
+      <c r="Y7" s="4" t="n"/>
+      <c r="Z7" s="4" t="n">
+        <v>46229</v>
+      </c>
+      <c r="AA7" s="4" t="n">
+        <v>46236</v>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>仅公告送达/仅文号线索</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE7" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书、税务行政处罚决定书的公告</t>
+        </is>
+      </c>
+      <c r="AI7" s="2" t="inlineStr">
+        <is>
+          <t>页面已删除</t>
+        </is>
+      </c>
+      <c r="AJ7" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7b9a26f2ac401107</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>DOC-f6c6ea472b2ca04a</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>福建省</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>三明市</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局三明市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局三明市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>三明众祥房地产开发有限公司</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>91350400678473231W</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>明税一稽处〔2026〕20号</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>明税一稽处〔2026〕20号</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>情况进行了检查,违法事实及处理决定如下: 2016年期间,在没有真实业务情况下,取得重庆市博海建设工程(集团)有限公司、福建九九建设有限公司三明分公司开具的不符合规定的发票,发票金额400252379元,在企业所得税税前扣除,造成少缴纳企业所得税100063094.75元,该行为违反《中华人民共和国税收征收管理法》(2015年4月24日主席令第二十三号修改)第六十三条第一款 纳税人伪造、变造、隐匿、擅自销毁账簿、记账凭证,或者在账簿上多列支出或者不列、少列收入,或者经税务机关通知申报而拒不申报或者进行虚假的纳税申报,不缴或者少缴应纳税款的,是偷税。 对纳税人偷税的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款; 之规定,对你公司在账上多列支出,造成少缴企业所得税100063094.75元的行为认定为偷税。 之规定,对你公司少缴的企业所得税从滞纳之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>企业所得税</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>100063094.75</v>
+      </c>
+      <c r="S8" s="3" t="n"/>
+      <c r="T8" s="3" t="n"/>
+      <c r="U8" s="3" t="n"/>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>据《中华人民共和国税收征收管理法实施细则》第106条规定,将该文书予以公告送达,自公告之日起满30日视为送达。</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="n"/>
+      <c r="X8" s="4" t="n">
+        <v>46223</v>
+      </c>
+      <c r="Y8" s="4" t="n"/>
+      <c r="Z8" s="4" t="n">
+        <v>46229</v>
+      </c>
+      <c r="AA8" s="4" t="n">
+        <v>46236</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD8" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AE8" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr">
+        <is>
           <t>关于送达三明众祥房地产开发有限公司 《税务处理决定书》的公告 _
  其他公告 _
  国家税务总局三明市税务局</t>
         </is>
       </c>
-      <c r="AI6" s="2" t="inlineStr">
+      <c r="AI8" s="2" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ6" s="2" t="inlineStr">
+      <c r="AJ8" s="2" t="inlineStr">
         <is>
           <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
+    <row r="9">
+      <c r="A9" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>CASE-31e4a827dfd253f2</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>DOC-3ec54358fce2350d</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>福建省</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>福州市</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>福州顺路汽车运输有限公司</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>91350102MA31MF6611</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>税务处理决定书</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>榕税一稽处〔2026〕137号</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>榕税一稽处〔2026〕137号</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>我局于2025年7月10日起对你公司(地址:福建省闽侯县青口镇祥宏南路922号)2023年1月1日至2024年12月31日期间的发票涉税情况进行检查,违法事实及处理决定如下: (二)你公司取得毕节七星关区辰楚汽车服务部(个人独资)、毕节七星关锦悦汽车服务部(个人独资)、贵州杨亭汽车销售有限公司、贵州楠鑫汽车销售有限公司已证实虚开的35份机动车发票。 (二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 (三)根据《中华人民共和国企业所得税法》第五条、第八条、《企业所得税税前扣除凭证管理办法》(国家税务总局公告2018年第28号发布)第四条、第十二条的规定,你公司取得上述虚开的发票不得作为税前扣除凭证。</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R9" s="3" t="n">
         <v>3778.22</v>
       </c>
-      <c r="S7" s="3" t="n"/>
-      <c r="T7" s="3" t="n"/>
-      <c r="U7" s="3" t="n"/>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="S9" s="3" t="n"/>
+      <c r="T9" s="3" t="n"/>
+      <c r="U9" s="3" t="n"/>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>(二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期城市维护建设税124.75元。 根据《征收教育费附加的暂行规定》第二条、第三条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期教育费附加53.47元。 根据《福建省人民政府关于调整地方教育附加征收标准等有关问题的通知》(闽政文〔2011〕230号)第一条、第二条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期地方教育附加35.64元。</t>
         </is>
       </c>
-      <c r="W7" s="4" t="n"/>
-      <c r="X7" s="4" t="n">
+      <c r="W9" s="4" t="n"/>
+      <c r="X9" s="4" t="n">
         <v>46218</v>
       </c>
-      <c r="Y7" s="4" t="n"/>
-      <c r="Z7" s="4" t="n">
+      <c r="Y9" s="4" t="n"/>
+      <c r="Z9" s="4" t="n">
         <v>46229</v>
       </c>
-      <c r="AA7" s="4" t="n">
-        <v>46235</v>
-      </c>
-      <c r="AB7" s="2" t="inlineStr">
+      <c r="AA9" s="4" t="n">
+        <v>46236</v>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
         <is>
           <t>完整文书</t>
         </is>
       </c>
-      <c r="AC7" s="2" t="inlineStr">
+      <c r="AC9" s="2" t="inlineStr">
         <is>
           <t>税务机关官网</t>
         </is>
       </c>
-      <c r="AD7" s="2" t="inlineStr">
+      <c r="AD9" s="2" t="inlineStr">
         <is>
           <t>已核验</t>
         </is>
       </c>
-      <c r="AE7" s="5" t="inlineStr">
+      <c r="AE9" s="5" t="inlineStr">
         <is>
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF7" s="2" t="inlineStr"/>
-      <c r="AG7" s="2" t="inlineStr"/>
-      <c r="AH7" s="2" t="inlineStr">
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr">
         <is>
           <t>关于送达福州顺路汽车运输有限公司《税务处理决定书》的公告 _
  其他类 _
  国家税务总局福州市税务局</t>
         </is>
       </c>
-      <c r="AI7" s="2" t="inlineStr">
+      <c r="AI9" s="2" t="inlineStr">
         <is>
           <t>正常</t>
-        </is>
-      </c>
-      <c r="AJ7" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>CASE-089a3b9692e76ac4</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>DOC-d21cdc5988b1e304</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>江苏省</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>淮安市</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局江苏省税务局</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局淮安市税务局稽查局</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>淮安市百亦金商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>91320804MA1WEH7Y3U</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>税务处理决定书</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽处〔2026〕26号</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽处〔2026〕26号</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽罚〔2026〕6号</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="3" t="n"/>
-      <c r="S8" s="3" t="n"/>
-      <c r="T8" s="3" t="n"/>
-      <c r="U8" s="3" t="n"/>
-      <c r="V8" s="2" t="inlineStr"/>
-      <c r="W8" s="4" t="n"/>
-      <c r="X8" s="4" t="n">
-        <v>46216</v>
-      </c>
-      <c r="Y8" s="4" t="n"/>
-      <c r="Z8" s="4" t="n">
-        <v>46229</v>
-      </c>
-      <c r="AA8" s="4" t="n">
-        <v>46235</v>
-      </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>仅公告送达/仅文号线索</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD8" s="2" t="inlineStr">
-        <is>
-          <t>已核验</t>
-        </is>
-      </c>
-      <c r="AE8" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF8" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
-      <c r="AG8" s="2" t="inlineStr"/>
-      <c r="AH8" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
-        </is>
-      </c>
-      <c r="AI8" s="2" t="inlineStr">
-        <is>
-          <t>附件正常</t>
-        </is>
-      </c>
-      <c r="AJ8" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>CASE-089a3b9692e76ac4</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>DOC-9f8e8958d8ff89b6</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>江苏省</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>淮安市</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局江苏省税务局</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局淮安市税务局稽查局</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>淮安市百亦金商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>91320804MA1WEH7Y3U</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>税务行政处罚决定书</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽罚〔2026〕6号</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽处〔2026〕26号</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽罚〔2026〕6号</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="3" t="n"/>
-      <c r="S9" s="3" t="n"/>
-      <c r="T9" s="3" t="n"/>
-      <c r="U9" s="3" t="n"/>
-      <c r="V9" s="2" t="inlineStr"/>
-      <c r="W9" s="4" t="n"/>
-      <c r="X9" s="4" t="n">
-        <v>46216</v>
-      </c>
-      <c r="Y9" s="4" t="n"/>
-      <c r="Z9" s="4" t="n">
-        <v>46229</v>
-      </c>
-      <c r="AA9" s="4" t="n">
-        <v>46235</v>
-      </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>仅公告送达/仅文号线索</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD9" s="2" t="inlineStr">
-        <is>
-          <t>已核验</t>
-        </is>
-      </c>
-      <c r="AE9" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF9" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
-      <c r="AG9" s="2" t="inlineStr"/>
-      <c r="AH9" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
-        </is>
-      </c>
-      <c r="AI9" s="2" t="inlineStr">
-        <is>
-          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr">
@@ -1729,47 +1721,47 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CASE-3f564fd9992b1ae3</t>
+          <t>CASE-089a3b9692e76ac4</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DOC-c34e1d13286aafe2</t>
+          <t>DOC-d21cdc5988b1e304</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>泉州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局第二稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局第二稽查局</t>
+          <t>国家税务总局淮安市税务局稽查局</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>泉州隆鸿服装制造有限公司</t>
+          <t>淮安市百亦金商贸有限公司</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>91350525MA8U3U963L</t>
+          <t>91320804MA1WEH7Y3U</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
@@ -1780,48 +1772,40 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>泉税二稽处〔2026〕107号</t>
+          <t>淮税稽处〔2026〕26号</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>泉税二稽处〔2026〕107号</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>日对你公司税收违法事实依法作出《税务处理决定书》(泉税二稽处〔 涉税情况进行了检查,查明违法事实及处理决定如下: 年你公司在无真实货物交易的情况下,取得河南中弘纺织有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 年期间,你公司在无真实货物交易的情况下,取得开封兴旺纺织品有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 上述违法事实有检查人员实地检查资料、电话拨打记录、邮寄退回函件、《已证实虚开通知单》等相关受托协查资料、主管税务机关出具的《已抵扣证明》、《情况说明》和你公司的申报纳税资料、银行账户流水等 号第三次修订)第二十一条第二款第二项之规定,认定你公司让他人为自己虚开 号第二次修订)第九条和《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告〔 号)之规定,对你公司取得上述已证实虚开的 之规定,决定向你公司追缴少缴的城市维护建设税-增值税附征 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 规定,决定向你公司追缴少缴的教育费附加-增值税附征 规定,决定向你公司追缴少缴的地方教育附加-增值税附征</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
+          <t>淮税稽处〔2026〕26号</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>淮税稽罚〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
       <c r="R10" s="3" t="n"/>
       <c r="S10" s="3" t="n"/>
       <c r="T10" s="3" t="n"/>
       <c r="U10" s="3" t="n"/>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>由于你公司走逃失联、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 (五)根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司上述应补缴税款按税款所属时间从税款滞纳之日起按日加收万分之五滞纳金</t>
-        </is>
-      </c>
+      <c r="V10" s="2" t="inlineStr"/>
       <c r="W10" s="4" t="n"/>
       <c r="X10" s="4" t="n">
-        <v>46202</v>
+        <v>46216</v>
       </c>
       <c r="Y10" s="4" t="n"/>
       <c r="Z10" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1839,18 +1823,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AF10" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG10" s="2" t="inlineStr"/>
       <c r="AH10" s="2" t="inlineStr">
         <is>
-          <t>关于对泉州隆鸿服装制造有限公司《税务处理决定书》送达的公告 _
- 其他公告 _
- 国家税务总局泉州市税务局</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
         </is>
       </c>
       <c r="AI10" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ10" s="2" t="inlineStr">
@@ -1861,16 +1847,16 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>CASE-717dfe3250926214</t>
+          <t>CASE-089a3b9692e76ac4</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>DOC-7df9c075e55777a1</t>
+          <t>DOC-9f8e8958d8ff89b6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1880,28 +1866,28 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>泰州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泰州市税务局第一稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泰州市税务局第一稽查局</t>
+          <t>国家税务总局淮安市税务局稽查局</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>靖江市长凌金属材料有限公司</t>
+          <t>淮安市百亦金商贸有限公司</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91321282742461893K</t>
+          <t>91320804MA1WEH7Y3U</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
@@ -1912,13 +1898,17 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>泰税一稽罚〔2025〕54号</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>淮税稽罚〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>淮税稽处〔2026〕26号</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>泰税一稽罚〔2025〕54号</t>
+          <t>淮税稽罚〔2026〕6号</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr"/>
@@ -1927,21 +1917,17 @@
       <c r="S11" s="3" t="n"/>
       <c r="T11" s="3" t="n"/>
       <c r="U11" s="3" t="n"/>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>接上级通知,经我局研究决定,撤销上述《税务行政处罚决定书》。</t>
-        </is>
-      </c>
+      <c r="V11" s="2" t="inlineStr"/>
       <c r="W11" s="4" t="n"/>
       <c r="X11" s="4" t="n">
-        <v>46191</v>
+        <v>46216</v>
       </c>
       <c r="Y11" s="4" t="n"/>
       <c r="Z11" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -1963,67 +1949,71 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AF11" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG11" s="2" t="inlineStr"/>
       <c r="AH11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 关于撤销《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
         </is>
       </c>
       <c r="AI11" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ11" s="2" t="inlineStr">
         <is>
-          <t>官方页面显示该决定书已被撤销。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CASE-a62e569c195adc3c</t>
+          <t>CASE-3f564fd9992b1ae3</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>DOC-b1dda915d4e6117d</t>
+          <t>DOC-c34e1d13286aafe2</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>遵义市</t>
+          <t>泉州市</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局泉州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局泉州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>贵州服格定商贸有限公司</t>
+          <t>泉州隆鸿服装制造有限公司</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>91520302MABUEHN034</t>
+          <t>91350525MA8U3U963L</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2034,40 +2024,44 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>遵税一稽处〔2026〕30号</t>
+          <t>泉税二稽处〔2026〕107号</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>遵税一稽处〔2026〕30号</t>
+          <t>泉税二稽处〔2026〕107号</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
+          <t>日对你公司税收违法事实依法作出《税务处理决定书》(泉税二稽处〔 涉税情况进行了检查,查明违法事实及处理决定如下: 年你公司在无真实货物交易的情况下,取得河南中弘纺织有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 年期间,你公司在无真实货物交易的情况下,取得开封兴旺纺织品有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 上述违法事实有检查人员实地检查资料、电话拨打记录、邮寄退回函件、《已证实虚开通知单》等相关受托协查资料、主管税务机关出具的《已抵扣证明》、《情况说明》和你公司的申报纳税资料、银行账户流水等 号第三次修订)第二十一条第二款第二项之规定,认定你公司让他人为自己虚开 号第二次修订)第九条和《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告〔 号)之规定,对你公司取得上述已证实虚开的 之规定,决定向你公司追缴少缴的城市维护建设税-增值税附征 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 规定,决定向你公司追缴少缴的教育费附加-增值税附征 规定,决定向你公司追缴少缴的地方教育附加-增值税附征</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
+          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R12" s="3" t="n"/>
       <c r="S12" s="3" t="n"/>
       <c r="T12" s="3" t="n"/>
       <c r="U12" s="3" t="n"/>
-      <c r="V12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>由于你公司走逃失联、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 (五)根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司上述应补缴税款按税款所属时间从税款滞纳之日起按日加收万分之五滞纳金</t>
+        </is>
+      </c>
       <c r="W12" s="4" t="n"/>
       <c r="X12" s="4" t="n">
-        <v>46185</v>
+        <v>46202</v>
       </c>
       <c r="Y12" s="4" t="n"/>
       <c r="Z12" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -2081,7 +2075,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE12" s="5" t="inlineStr">
@@ -2093,12 +2087,14 @@
       <c r="AG12" s="2" t="inlineStr"/>
       <c r="AH12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
+          <t>关于对泉州隆鸿服装制造有限公司《税务处理决定书》送达的公告 _
+ 其他公告 _
+ 国家税务总局泉州市税务局</t>
         </is>
       </c>
       <c r="AI12" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ12" s="2" t="inlineStr">
@@ -2109,64 +2105,64 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CASE-13a8aac51595155a</t>
+          <t>CASE-717dfe3250926214</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>DOC-7189c9a2cee8e8ce</t>
+          <t>DOC-7df9c075e55777a1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>温州市</t>
+          <t>泰州市</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局泰州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局泰州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>温作潘</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr"/>
+          <t>靖江市长凌金属材料有限公司</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>91321282742461893K</t>
+        </is>
+      </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>温税三稽处〔2026〕100号</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>温税三稽处〔2026〕100号</t>
-        </is>
-      </c>
+          <t>泰税一稽罚〔2025〕54号</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>温税三稽罚〔2026〕65号</t>
+          <t>泰税一稽罚〔2025〕54号</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr"/>
@@ -2175,17 +2171,21 @@
       <c r="S13" s="3" t="n"/>
       <c r="T13" s="3" t="n"/>
       <c r="U13" s="3" t="n"/>
-      <c r="V13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>接上级通知,经我局研究决定,撤销上述《税务行政处罚决定书》。</t>
+        </is>
+      </c>
       <c r="W13" s="4" t="n"/>
       <c r="X13" s="4" t="n">
-        <v>46175</v>
+        <v>46191</v>
       </c>
       <c r="Y13" s="4" t="n"/>
       <c r="Z13" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -2207,92 +2207,96 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF13" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF13" s="2" t="inlineStr"/>
       <c r="AG13" s="2" t="inlineStr"/>
       <c r="AH13" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 关于撤销《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI13" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ13" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>官方页面显示该决定书已被撤销。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASE-13a8aac51595155a</t>
+          <t>CASE-a62e569c195adc3c</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DOC-02fc2468fd0396a6</t>
+          <t>DOC-b1dda915d4e6117d</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>温州市</t>
+          <t>遵义市</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局遵义市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局遵义市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>温作潘</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr"/>
+          <t>贵州服格定商贸有限公司</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>91520302MABUEHN034</t>
+        </is>
+      </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>温税三稽罚〔2026〕65号</t>
+          <t>遵税一稽处〔2026〕30号</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>温税三稽处〔2026〕100号</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>温税三稽罚〔2026〕65号</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
+          <t>遵税一稽处〔2026〕30号</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>增值税</t>
+        </is>
+      </c>
       <c r="R14" s="3" t="n"/>
       <c r="S14" s="3" t="n"/>
       <c r="T14" s="3" t="n"/>
@@ -2300,18 +2304,18 @@
       <c r="V14" s="2" t="inlineStr"/>
       <c r="W14" s="4" t="n"/>
       <c r="X14" s="4" t="n">
-        <v>46175</v>
+        <v>46185</v>
       </c>
       <c r="Y14" s="4" t="n"/>
       <c r="Z14" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2321,7 +2325,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE14" s="5" t="inlineStr">
@@ -2329,20 +2333,16 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF14" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF14" s="2" t="inlineStr"/>
       <c r="AG14" s="2" t="inlineStr"/>
       <c r="AH14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
+          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
         </is>
       </c>
       <c r="AI14" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>页面已删除</t>
         </is>
       </c>
       <c r="AJ14" s="2" t="inlineStr">
@@ -2353,49 +2353,45 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CASE-f8625e66b291a216</t>
+          <t>CASE-13a8aac51595155a</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>DOC-7970511393924720</t>
+          <t>DOC-7189c9a2cee8e8ce</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>温州市</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>贵州翰缤商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>91520114MAAK1C546F</t>
-        </is>
-      </c>
+          <t>温作潘</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -2404,15 +2400,19 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>筑税二稽处〔2026〕27号</t>
+          <t>温税三稽处〔2026〕100号</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>筑税二稽处〔2026〕27号</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
+          <t>温税三稽处〔2026〕100号</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>温税三稽罚〔2026〕65号</t>
+        </is>
+      </c>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr"/>
       <c r="R15" s="3" t="n"/>
@@ -2422,14 +2422,14 @@
       <c r="V15" s="2" t="inlineStr"/>
       <c r="W15" s="4" t="n"/>
       <c r="X15" s="4" t="n">
-        <v>46156</v>
+        <v>46175</v>
       </c>
       <c r="Y15" s="4" t="n"/>
       <c r="Z15" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE15" s="5" t="inlineStr">
@@ -2451,16 +2451,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AF15" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG15" s="2" t="inlineStr"/>
       <c r="AH15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局关于送达《税务处理决定书》的公告</t>
+          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
         </is>
       </c>
       <c r="AI15" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ15" s="2" t="inlineStr">
@@ -2471,68 +2475,64 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CASE-0f4867f7b70d12f3</t>
+          <t>CASE-13a8aac51595155a</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>DOC-6f25d6b79e123d03</t>
+          <t>DOC-02fc2468fd0396a6</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>温州市</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>贵州铂朗物流有限公司</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>91520115MAAK0DB335</t>
-        </is>
-      </c>
+          <t>温作潘</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
+          <t>温税三稽罚〔2026〕65号</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
+          <t>温税三稽处〔2026〕100号</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽罚〔2026〕22号</t>
+          <t>温税三稽罚〔2026〕65号</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr"/>
@@ -2544,14 +2544,14 @@
       <c r="V16" s="2" t="inlineStr"/>
       <c r="W16" s="4" t="n"/>
       <c r="X16" s="4" t="n">
-        <v>46122</v>
+        <v>46175</v>
       </c>
       <c r="Y16" s="4" t="n"/>
       <c r="Z16" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE16" s="5" t="inlineStr">
@@ -2573,16 +2573,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AF16" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG16" s="2" t="inlineStr"/>
       <c r="AH16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
+          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
         </is>
       </c>
       <c r="AI16" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ16" s="2" t="inlineStr">
@@ -2593,16 +2597,16 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CASE-0f4867f7b70d12f3</t>
+          <t>CASE-f8625e66b291a216</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>DOC-e8233eb0e06b6e3e</t>
+          <t>DOC-7970511393924720</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2618,45 +2622,41 @@
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局贵阳市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局贵阳市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>贵州铂朗物流有限公司</t>
+          <t>贵州翰缤商贸有限公司</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>91520115MAAK0DB335</t>
+          <t>91520114MAAK1C546F</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽罚〔2026〕22号</t>
+          <t>筑税二稽处〔2026〕27号</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>筑税三稽罚〔2026〕22号</t>
-        </is>
-      </c>
+          <t>筑税二稽处〔2026〕27号</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr"/>
       <c r="R17" s="3" t="n"/>
@@ -2666,14 +2666,14 @@
       <c r="V17" s="2" t="inlineStr"/>
       <c r="W17" s="4" t="n"/>
       <c r="X17" s="4" t="n">
-        <v>46122</v>
+        <v>46156</v>
       </c>
       <c r="Y17" s="4" t="n"/>
       <c r="Z17" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
       <c r="AG17" s="2" t="inlineStr"/>
       <c r="AH17" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
+          <t>国家税务总局贵阳市税务局第二稽查局关于送达《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI17" s="2" t="inlineStr">
@@ -2715,47 +2715,47 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CASE-136615addd5d0c0e</t>
+          <t>CASE-0f4867f7b70d12f3</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>DOC-551df7dc5c028b27</t>
+          <t>DOC-6f25d6b79e123d03</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>来宾市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>广西欣瑞木业有限公司</t>
+          <t>贵州铂朗物流有限公司</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>91451322MAD89XWX07</t>
+          <t>91520115MAAK0DB335</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
@@ -2766,17 +2766,17 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr"/>
@@ -2788,14 +2788,14 @@
       <c r="V18" s="2" t="inlineStr"/>
       <c r="W18" s="4" t="n"/>
       <c r="X18" s="4" t="n">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="Y18" s="4" t="n"/>
       <c r="Z18" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE18" s="5" t="inlineStr">
@@ -2821,12 +2821,12 @@
       <c r="AG18" s="2" t="inlineStr"/>
       <c r="AH18" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
         </is>
       </c>
       <c r="AI18" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>页面已删除</t>
         </is>
       </c>
       <c r="AJ18" s="2" t="inlineStr">
@@ -2837,47 +2837,47 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CASE-136615addd5d0c0e</t>
+          <t>CASE-0f4867f7b70d12f3</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>DOC-21f0193b66d5c3e9</t>
+          <t>DOC-e8233eb0e06b6e3e</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>来宾市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>广西欣瑞木业有限公司</t>
+          <t>贵州铂朗物流有限公司</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>91451322MAD89XWX07</t>
+          <t>91520115MAAK0DB335</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr"/>
@@ -2910,14 +2910,14 @@
       <c r="V19" s="2" t="inlineStr"/>
       <c r="W19" s="4" t="n"/>
       <c r="X19" s="4" t="n">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="Y19" s="4" t="n"/>
       <c r="Z19" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE19" s="5" t="inlineStr">
@@ -2943,12 +2943,12 @@
       <c r="AG19" s="2" t="inlineStr"/>
       <c r="AH19" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
         </is>
       </c>
       <c r="AI19" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>页面已删除</t>
         </is>
       </c>
       <c r="AJ19" s="2" t="inlineStr">
@@ -2959,64 +2959,68 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CASE-393a878d93a22709</t>
+          <t>CASE-136615addd5d0c0e</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>DOC-cda8cba853896b18</t>
+          <t>DOC-551df7dc5c028b27</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>广州市</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>番禺区</t>
-        </is>
-      </c>
+          <t>来宾市</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>广州赞荣服装有限公司</t>
+          <t>广西欣瑞木业有限公司</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>91440113MA59AJFJ1J</t>
+          <t>91451322MAD89XWX07</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>穗番税退罚字〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>来市税二稽处〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>来市税二稽处〔2026〕6号</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>穗番税退罚字〔2026〕1号</t>
+          <t>来市税二稽罚〔2026〕4号</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr"/>
@@ -3028,14 +3032,14 @@
       <c r="V20" s="2" t="inlineStr"/>
       <c r="W20" s="4" t="n"/>
       <c r="X20" s="4" t="n">
-        <v>46091</v>
+        <v>46119</v>
       </c>
       <c r="Y20" s="4" t="n"/>
       <c r="Z20" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -3049,7 +3053,7 @@
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE20" s="5" t="inlineStr">
@@ -3057,131 +3061,111 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF20" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF20" s="2" t="inlineStr"/>
       <c r="AG20" s="2" t="inlineStr"/>
       <c r="AH20" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
+          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
         </is>
       </c>
       <c r="AI20" s="2" t="inlineStr">
         <is>
-          <t>内容不匹配</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ20" s="2" t="inlineStr">
         <is>
-          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CASE-f94bf08964abff5a</t>
+          <t>CASE-136615addd5d0c0e</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>DOC-4574b1aadef8f30d</t>
+          <t>DOC-21f0193b66d5c3e9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
+          <t>来宾市</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局稽查局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>常州市文杰车辆配件厂</t>
+          <t>广西欣瑞木业有限公司</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>91320411799075280A</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>朱某</t>
-        </is>
-      </c>
+          <t>91451322MAD89XWX07</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕73号</t>
+          <t>来市税二稽罚〔2026〕4号</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕73号</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公 月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>179137.12</v>
-      </c>
+          <t>来市税二稽处〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>来市税二稽罚〔2026〕4号</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="3" t="n"/>
       <c r="S21" s="3" t="n"/>
       <c r="T21" s="3" t="n"/>
       <c r="U21" s="3" t="n"/>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市 份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元,</t>
-        </is>
-      </c>
-      <c r="W21" s="4" t="n">
-        <v>46044</v>
-      </c>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="4" t="n"/>
       <c r="X21" s="4" t="n">
-        <v>46090</v>
+        <v>46119</v>
       </c>
       <c r="Y21" s="4" t="n"/>
       <c r="Z21" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3199,20 +3183,16 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF21" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF21" s="2" t="inlineStr"/>
       <c r="AG21" s="2" t="inlineStr"/>
       <c r="AH21" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
+          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
         </is>
       </c>
       <c r="AI21" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ21" s="2" t="inlineStr">
@@ -3223,66 +3203,66 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CASE-0b4a4519ba4f5ad9</t>
+          <t>CASE-393a878d93a22709</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>DOC-5376b9bae81cfc82</t>
+          <t>DOC-cda8cba853896b18</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>广东省</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr"/>
+          <t>广州市</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>番禺区</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局常州市税务局稽查局</t>
-        </is>
-      </c>
+          <t>国家税务总局广州市番禺区税务局</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>常州好佳车辆配件有限公司</t>
+          <t>广州赞荣服装有限公司</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>91320411094264460B</t>
+          <t>91440113MA59AJFJ1J</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕71号</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>常税稽处〔2026〕71号</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr"/>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr"/>
       <c r="R22" s="3" t="n"/>
@@ -3292,14 +3272,14 @@
       <c r="V22" s="2" t="inlineStr"/>
       <c r="W22" s="4" t="n"/>
       <c r="X22" s="4" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="Y22" s="4" t="n"/>
       <c r="Z22" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
@@ -3313,7 +3293,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE22" s="5" t="inlineStr">
@@ -3329,32 +3309,32 @@
       <c r="AG22" s="2" t="inlineStr"/>
       <c r="AH22" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州好佳车辆配件有限公司《税务处理决定书》的公告</t>
+          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
         </is>
       </c>
       <c r="AI22" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>内容不匹配</t>
         </is>
       </c>
       <c r="AJ22" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CASE-61b9b55a9d3357c7</t>
+          <t>CASE-f94bf08964abff5a</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>DOC-1228a9c92b2b0632</t>
+          <t>DOC-4574b1aadef8f30d</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3370,25 +3350,29 @@
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局常州市税务局稽查局</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>常州市三鹏机械有限公司</t>
+          <t>常州市文杰车辆配件厂</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>91320404732260748Q</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr"/>
+          <t>91320411799075280A</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>朱某</t>
+        </is>
+      </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
           <t>税务处理决定书</t>
@@ -3396,46 +3380,48 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
+          <t>常税稽处〔2026〕73号</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>常税稽一罚〔2026〕14号</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr"/>
+          <t>常税稽处〔2026〕73号</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公 月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
+        </is>
+      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R23" s="3" t="n">
-        <v>63464.09</v>
+        <v>179137.12</v>
       </c>
       <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="n"/>
       <c r="U23" s="3" t="n"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
-        </is>
-      </c>
-      <c r="W23" s="4" t="n"/>
+          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市 份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元,</t>
+        </is>
+      </c>
+      <c r="W23" s="4" t="n">
+        <v>46044</v>
+      </c>
       <c r="X23" s="4" t="n">
-        <v>46066</v>
+        <v>46090</v>
       </c>
       <c r="Y23" s="4" t="n"/>
       <c r="Z23" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
@@ -3457,16 +3443,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF23" s="2" t="inlineStr"/>
+      <c r="AF23" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG23" s="2" t="inlineStr"/>
       <c r="AH23" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI23" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ23" s="2" t="inlineStr">
@@ -3477,16 +3467,16 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CASE-61b9b55a9d3357c7</t>
+          <t>CASE-0b4a4519ba4f5ad9</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>DOC-b97456a64b153f67</t>
+          <t>DOC-5376b9bae81cfc82</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3502,76 +3492,62 @@
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局常州市税务局稽查局</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>常州市三鹏机械有限公司</t>
+          <t>常州好佳车辆配件有限公司</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>91320404732260748Q</t>
+          <t>91320411094264460B</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>常税稽一罚〔2026〕14号</t>
+          <t>常税稽处〔2026〕71号</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>常税稽一罚〔2026〕14号</t>
-        </is>
-      </c>
+          <t>常税稽处〔2026〕71号</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr"/>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
       <c r="R24" s="3" t="n"/>
       <c r="S24" s="3" t="n"/>
-      <c r="T24" s="3" t="n">
-        <v>20000</v>
-      </c>
+      <c r="T24" s="3" t="n"/>
       <c r="U24" s="3" t="n"/>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
-        </is>
-      </c>
+      <c r="V24" s="2" t="inlineStr"/>
       <c r="W24" s="4" t="n"/>
       <c r="X24" s="4" t="n">
-        <v>46066</v>
+        <v>46087</v>
       </c>
       <c r="Y24" s="4" t="n"/>
       <c r="Z24" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3589,16 +3565,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF24" s="2" t="inlineStr"/>
+      <c r="AF24" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG24" s="2" t="inlineStr"/>
       <c r="AH24" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州好佳车辆配件有限公司《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI24" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ24" s="2" t="inlineStr">
@@ -3609,47 +3589,47 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CASE-f78ec1a594442165</t>
+          <t>CASE-61b9b55a9d3357c7</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>DOC-fbbe4a664b14f54b</t>
+          <t>DOC-1228a9c92b2b0632</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>安顺市</t>
+          <t>常州市</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
+          <t>常州市三鹏机械有限公司</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>91520423MA6DLH799Q</t>
+          <t>91320404732260748Q</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
@@ -3660,52 +3640,46 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
-        </is>
-      </c>
+          <t>常税稽一罚〔2026〕14号</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R25" s="3" t="n">
-        <v>64884.41</v>
+        <v>63464.09</v>
       </c>
       <c r="S25" s="3" t="n"/>
       <c r="T25" s="3" t="n"/>
       <c r="U25" s="3" t="n"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
-      <c r="W25" s="4" t="n">
-        <v>45898</v>
-      </c>
+          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
+        </is>
+      </c>
+      <c r="W25" s="4" t="n"/>
       <c r="X25" s="4" t="n">
-        <v>46043</v>
+        <v>46066</v>
       </c>
       <c r="Y25" s="4" t="n"/>
       <c r="Z25" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
@@ -3719,7 +3693,7 @@
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE25" s="5" t="inlineStr">
@@ -3727,15 +3701,11 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF25" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF25" s="2" t="inlineStr"/>
       <c r="AG25" s="2" t="inlineStr"/>
       <c r="AH25" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI25" s="2" t="inlineStr">
@@ -3745,53 +3715,53 @@
       </c>
       <c r="AJ25" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CASE-f78ec1a594442165</t>
+          <t>CASE-61b9b55a9d3357c7</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>DOC-9a828a6048b54b6c</t>
+          <t>DOC-b97456a64b153f67</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>安顺市</t>
+          <t>常州市</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
+          <t>常州市三鹏机械有限公司</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>91520423MA6DLH799Q</t>
+          <t>91320404732260748Q</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
@@ -3802,52 +3772,46 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>安市税稽罚〔2026〕1号</t>
+          <t>常税稽一罚〔2026〕14号</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
-        </is>
-      </c>
+          <t>常税稽一罚〔2026〕14号</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R26" s="3" t="n"/>
       <c r="S26" s="3" t="n"/>
       <c r="T26" s="3" t="n">
-        <v>200000</v>
+        <v>20000</v>
       </c>
       <c r="U26" s="3" t="n"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
-      <c r="W26" s="4" t="n">
-        <v>45898</v>
-      </c>
+          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
+        </is>
+      </c>
+      <c r="W26" s="4" t="n"/>
       <c r="X26" s="4" t="n">
-        <v>46043</v>
+        <v>46066</v>
       </c>
       <c r="Y26" s="4" t="n"/>
       <c r="Z26" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
@@ -3861,7 +3825,7 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE26" s="5" t="inlineStr">
@@ -3869,15 +3833,11 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF26" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF26" s="2" t="inlineStr"/>
       <c r="AG26" s="2" t="inlineStr"/>
       <c r="AH26" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI26" s="2" t="inlineStr">
@@ -3887,53 +3847,53 @@
       </c>
       <c r="AJ26" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CASE-fe959d4c6c52d910</t>
+          <t>CASE-f78ec1a594442165</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>DOC-f2643f2a0719d8d1</t>
+          <t>DOC-fbbe4a664b14f54b</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>南宁市</t>
+          <t>安顺市</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局稽查局</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>南宁洪谦金贸易有限公司</t>
+          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>91450103MA5K9WHY7U</t>
+          <t>91520423MA6DLH799Q</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
@@ -3944,40 +3904,52 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>南市税一稽处〔2026〕2号</t>
+          <t>安市税稽处〔2026〕1号</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>南市税一稽处〔2026〕2号</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr"/>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽罚〔2026〕1号</t>
+        </is>
+      </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>经我局2025年10月29日至2025年12月8日对你公司(地址:南宁市青秀区云景路11号春晖花园C区3栋2单元1606号)2015年12月2日至2016年12月31日期间的涉税情况进行了检查,你(单位)存在以下违法事实: 经查询你公司向税务机关报备的银行账号:广西北部湾银行南宁市财富国际支行800099398800015,经函询广西北部湾银行南宁市财富国际支行,存在以下问题: 上述行为属于开具与实际经营业务情况不符的增值税发票,违反了《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第587号修改)第二十二条第一款、第二款第(一)项的规定,属于虚开发票行为。</t>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="n"/>
+          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>64884.41</v>
+      </c>
       <c r="S27" s="3" t="n"/>
       <c r="T27" s="3" t="n"/>
       <c r="U27" s="3" t="n"/>
-      <c r="V27" s="2" t="inlineStr"/>
-      <c r="W27" s="4" t="n"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="W27" s="4" t="n">
+        <v>45898</v>
+      </c>
       <c r="X27" s="4" t="n">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="Y27" s="4" t="n"/>
       <c r="Z27" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
@@ -3991,7 +3963,7 @@
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE27" s="5" t="inlineStr">
@@ -4007,105 +3979,119 @@
       <c r="AG27" s="2" t="inlineStr"/>
       <c r="AH27" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局税务文书送达公告_国家税务总局南宁市税务局</t>
+          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI27" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ27" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CASE-1983d97878508732</t>
+          <t>CASE-f78ec1a594442165</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>DOC-f9760895b4f08cc2</t>
+          <t>DOC-9a828a6048b54b6c</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>二连浩特市</t>
+          <t>安顺市</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局</t>
+          <t>国家税务总局安顺市税务局</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局稽查局</t>
+          <t>国家税务总局安顺市税务局稽查局</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>二连市坤益腾金属有限公司</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr"/>
+          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>91520423MA6DLH799Q</t>
+        </is>
+      </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
+          <t>安市税稽罚〔2026〕1号</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr"/>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽罚〔2026〕1号</t>
+        </is>
+      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
+          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R28" s="3" t="n"/>
       <c r="S28" s="3" t="n"/>
-      <c r="T28" s="3" t="n"/>
+      <c r="T28" s="3" t="n">
+        <v>200000</v>
+      </c>
       <c r="U28" s="3" t="n"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
-        </is>
-      </c>
-      <c r="W28" s="4" t="n"/>
-      <c r="X28" s="4" t="n"/>
+          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="W28" s="4" t="n">
+        <v>45898</v>
+      </c>
+      <c r="X28" s="4" t="n">
+        <v>46043</v>
+      </c>
       <c r="Y28" s="4" t="n"/>
       <c r="Z28" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
@@ -4127,11 +4113,15 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF28" s="2" t="inlineStr"/>
+      <c r="AF28" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG28" s="2" t="inlineStr"/>
       <c r="AH28" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI28" s="2" t="inlineStr">
@@ -4141,47 +4131,55 @@
       </c>
       <c r="AJ28" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CASE-d4b6986f3f97cd28</t>
+          <t>CASE-fe959d4c6c52d910</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>DOC-442cf3d9a5280c12</t>
+          <t>DOC-f2643f2a0719d8d1</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>鄂尔多斯市</t>
+          <t>南宁市</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局南宁市税务局第一稽查局</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>第二稽查局</t>
+          <t>国家税务总局南宁市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>廖礼平</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr"/>
+          <t>南宁洪谦金贸易有限公司</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>91450103MA5K9WHY7U</t>
+        </is>
+      </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -4190,46 +4188,40 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
+          <t>南市税一稽处〔2026〕2号</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
+          <t>南市税一稽处〔2026〕2号</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
+          <t>经我局2025年10月29日至2025年12月8日对你公司(地址:南宁市青秀区云景路11号春晖花园C区3栋2单元1606号)2015年12月2日至2016年12月31日期间的涉税情况进行了检查,你(单位)存在以下违法事实: 经查询你公司向税务机关报备的银行账号:广西北部湾银行南宁市财富国际支行800099398800015,经函询广西北部湾银行南宁市财富国际支行,存在以下问题: 上述行为属于开具与实际经营业务情况不符的增值税发票,违反了《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第587号修改)第二十二条第一款、第二款第(一)项的规定,属于虚开发票行为。</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>个人所得税、印花税</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="n">
-        <v>15072487.5</v>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>1046925</v>
-      </c>
+          <t>增值税</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="n"/>
+      <c r="S29" s="3" t="n"/>
       <c r="T29" s="3" t="n"/>
       <c r="U29" s="3" t="n"/>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
-        </is>
-      </c>
+      <c r="V29" s="2" t="inlineStr"/>
       <c r="W29" s="4" t="n"/>
-      <c r="X29" s="4" t="n"/>
+      <c r="X29" s="4" t="n">
+        <v>46031</v>
+      </c>
       <c r="Y29" s="4" t="n"/>
       <c r="Z29" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
@@ -4243,7 +4235,7 @@
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE29" s="5" t="inlineStr">
@@ -4251,69 +4243,69 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF29" s="2" t="inlineStr"/>
+      <c r="AF29" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG29" s="2" t="inlineStr"/>
       <c r="AH29" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>国家税务总局南宁市税务局第一稽查局税务文书送达公告_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI29" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ29" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CASE-7e3d4a321440d6a7</t>
+          <t>CASE-1983d97878508732</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>DOC-bed9330343ed06af</t>
+          <t>DOC-f9760895b4f08cc2</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>二连浩特市</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
+          <t>国家税务总局二连浩特市税务局</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
+          <t>国家税务总局二连浩特市税务局稽查局</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>天津展达科技有限公司</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>91120116300738701X</t>
-        </is>
-      </c>
+          <t>二连市坤益腾金属有限公司</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
@@ -4322,48 +4314,42 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
+          <t>二税稽处〔2025〕1号</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
+          <t>二税稽处〔2025〕1号</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R30" s="3" t="n">
-        <v>920146.9399999999</v>
-      </c>
+          <t>增值税</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="n"/>
       <c r="S30" s="3" t="n"/>
       <c r="T30" s="3" t="n"/>
       <c r="U30" s="3" t="n"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
         </is>
       </c>
       <c r="W30" s="4" t="n"/>
       <c r="X30" s="4" t="n"/>
       <c r="Y30" s="4" t="n"/>
       <c r="Z30" s="4" t="n">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
@@ -4389,7 +4375,7 @@
       <c r="AG30" s="2" t="inlineStr"/>
       <c r="AH30" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="AI30" s="2" t="inlineStr">
@@ -4399,105 +4385,95 @@
       </c>
       <c r="AJ30" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CASE-7e3d4a321440d6a7</t>
+          <t>CASE-d4b6986f3f97cd28</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>DOC-388bd01c01bbb789</t>
+          <t>DOC-442cf3d9a5280c12</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>鄂尔多斯市</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
-        </is>
-      </c>
+      <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
+          <t>第二稽查局</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>天津展达科技有限公司</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>91120116300738701X</t>
-        </is>
-      </c>
+          <t>廖礼平</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>津税一稽罚〔2023〕21号</t>
+          <t>鄂税二稽处〔2023〕29号</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
+          <t>鄂税二稽处〔2023〕29号</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="n"/>
-      <c r="S31" s="3" t="n"/>
-      <c r="T31" s="3" t="n">
-        <v>131368.5</v>
-      </c>
+          <t>个人所得税、印花税</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>15072487.5</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>1046925</v>
+      </c>
+      <c r="T31" s="3" t="n"/>
       <c r="U31" s="3" t="n"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
         </is>
       </c>
       <c r="W31" s="4" t="n"/>
       <c r="X31" s="4" t="n"/>
       <c r="Y31" s="4" t="n"/>
       <c r="Z31" s="4" t="n">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
@@ -4523,78 +4499,350 @@
       <c r="AG31" s="2" t="inlineStr"/>
       <c r="AH31" s="2" t="inlineStr">
         <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="AI31" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ31" s="2" t="inlineStr">
+        <is>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7e3d4a321440d6a7</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>DOC-bed9330343ed06af</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>91120116300738701X</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>920146.9399999999</v>
+      </c>
+      <c r="S32" s="3" t="n"/>
+      <c r="T32" s="3" t="n"/>
+      <c r="U32" s="3" t="n"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W32" s="4" t="n"/>
+      <c r="X32" s="4" t="n"/>
+      <c r="Y32" s="4" t="n"/>
+      <c r="Z32" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AA32" s="4" t="n">
+        <v>46236</v>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE32" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF32" s="2" t="inlineStr"/>
+      <c r="AG32" s="2" t="inlineStr"/>
+      <c r="AH32" s="2" t="inlineStr">
+        <is>
           <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
-      <c r="AI31" s="2" t="inlineStr">
+      <c r="AI32" s="2" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ31" s="2" t="inlineStr">
+      <c r="AJ32" s="2" t="inlineStr">
+        <is>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7e3d4a321440d6a7</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>DOC-388bd01c01bbb789</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>91120116300738701X</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>税务行政处罚决定书</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="n"/>
+      <c r="S33" s="3" t="n"/>
+      <c r="T33" s="3" t="n">
+        <v>131368.5</v>
+      </c>
+      <c r="U33" s="3" t="n"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W33" s="4" t="n"/>
+      <c r="X33" s="4" t="n"/>
+      <c r="Y33" s="4" t="n"/>
+      <c r="Z33" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AA33" s="4" t="n">
+        <v>46236</v>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE33" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF33" s="2" t="inlineStr"/>
+      <c r="AG33" s="2" t="inlineStr"/>
+      <c r="AH33" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+        </is>
+      </c>
+      <c r="AI33" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ33" s="2" t="inlineStr">
         <is>
           <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ31"/>
-  <conditionalFormatting sqref="AD2:AD31">
+  <autoFilter ref="A1:AJ33"/>
+  <conditionalFormatting sqref="AD2:AD33">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AD2="待核验"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI2:AI31">
+  <conditionalFormatting sqref="AI2:AI33">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>AND($AI2&lt;&gt;"正常",$AI2&lt;&gt;"附件正常")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AD2:AD31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AD2:AD33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"已核验,待核验,人工复核完成"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE9" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE11" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE12" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF13" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE14" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF14" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE12" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE14" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE15" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE16" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE17" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE18" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE19" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE20" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF20" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE21" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF21" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF15" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE16" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF16" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE17" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE18" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE19" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE20" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE21" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE22" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF22" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE23" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE24" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE25" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF25" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE26" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF26" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF23" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE24" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF24" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE25" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE26" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE27" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF27" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE28" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE29" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE30" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE31" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF28" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE29" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF29" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE30" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE31" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE32" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE33" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -4918,7 +5166,7 @@
         <v>46233</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -5054,7 +5302,7 @@
         <v>46234</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -5186,7 +5434,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -5320,7 +5568,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -5452,7 +5700,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -5580,7 +5828,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -5718,7 +5966,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -5854,7 +6102,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -5986,7 +6234,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -6124,7 +6372,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -6266,7 +6514,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -6396,7 +6644,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -6524,7 +6772,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -6648,7 +6896,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -6782,7 +7030,7 @@
         <v>46230</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -6916,7 +7164,7 @@
         <v>46230</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -7006,7 +7254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ15"/>
+  <dimension ref="A1:AJ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7231,47 +7479,47 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CASE-3e050a699b29b0d0</t>
+          <t>CASE-119dcfa5a7c6b239</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>DOC-96a3089a0e2b37cd</t>
+          <t>DOC-1a423a3cbfed9f3f</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>河南省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>平顶山市</t>
+          <t>南宁市</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局平顶山市税务局第一稽查局</t>
+          <t>国家税务总局南宁市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局平顶山市税务局第一稽查局</t>
+          <t>国家税务总局南宁市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>汝州泰隆实业有限公司</t>
+          <t>广西威曼能源科技有限公司</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>91410482MA40K4KA3B</t>
+          <t>91450103MA5NJYGEXM</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
@@ -7282,21 +7530,21 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>平税稽一局处〔2026〕1号</t>
+          <t>南市税三稽处〔2026〕19号</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>平税稽一局处〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr"/>
+          <t>南市税三稽处〔2026〕19号</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>南市税三稽罚〔2026〕10号</t>
+        </is>
+      </c>
       <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>增值税、个人所得税</t>
-        </is>
-      </c>
+      <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="3" t="n"/>
       <c r="S2" s="3" t="n"/>
       <c r="T2" s="3" t="n"/>
@@ -7304,14 +7552,14 @@
       <c r="V2" s="2" t="inlineStr"/>
       <c r="W2" s="4" t="n"/>
       <c r="X2" s="4" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="Y2" s="4" t="n"/>
       <c r="Z2" s="4" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -7333,86 +7581,90 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr"/>
+      <c r="AF2" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG2" s="2" t="inlineStr"/>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局平顶山市税务局第一稽查局关于送达汝州泰隆实业有限公司《税务处理决定书》的公告 - 国家税务总局平顶山市税务局</t>
+          <t>国家税务总局南宁市税务局第三稽查局 税务文书送达公告_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI2" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="AJ2" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
+          <t>附件正常</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CASE-365e8a924cf64611</t>
+          <t>CASE-119dcfa5a7c6b239</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>DOC-4d14eba16f9aa8a0</t>
+          <t>DOC-f8499a65abd851d8</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>南宁市</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局南宁市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局南宁市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>贵州博泰工贸有限公司</t>
+          <t>广西威曼能源科技有限公司</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>91520115587255589F</t>
+          <t>91450103MA5NJYGEXM</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕38号</t>
+          <t>南市税三稽罚〔2026〕10号</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕38号</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
+          <t>南市税三稽处〔2026〕19号</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>南市税三稽罚〔2026〕10号</t>
+        </is>
+      </c>
       <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr"/>
       <c r="R3" s="3" t="n"/>
@@ -7422,14 +7674,14 @@
       <c r="V3" s="2" t="inlineStr"/>
       <c r="W3" s="4" t="n"/>
       <c r="X3" s="4" t="n">
-        <v>46224</v>
+        <v>46233</v>
       </c>
       <c r="Y3" s="4" t="n"/>
       <c r="Z3" s="4" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -7443,7 +7695,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE3" s="5" t="inlineStr">
@@ -7451,67 +7703,67 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF3" s="2" t="inlineStr"/>
+      <c r="AF3" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG3" s="2" t="inlineStr"/>
       <c r="AH3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书、税务行政处罚决定书的公告</t>
+          <t>国家税务总局南宁市税务局第三稽查局 税务文书送达公告_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI3" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
-        </is>
-      </c>
-      <c r="AJ3" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
+          <t>附件正常</t>
+        </is>
+      </c>
+      <c r="AJ3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CASE-089a3b9692e76ac4</t>
+          <t>CASE-3e050a699b29b0d0</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>DOC-d21cdc5988b1e304</t>
+          <t>DOC-96a3089a0e2b37cd</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>淮安市</t>
+          <t>平顶山市</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
+          <t>国家税务总局平顶山市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局淮安市税务局稽查局</t>
+          <t>国家税务总局平顶山市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>淮安市百亦金商贸有限公司</t>
+          <t>汝州泰隆实业有限公司</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>91320804MA1WEH7Y3U</t>
+          <t>91410482MA40K4KA3B</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
@@ -7522,21 +7774,21 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>淮税稽处〔2026〕26号</t>
+          <t>平税稽一局处〔2026〕1号</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>淮税稽处〔2026〕26号</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽罚〔2026〕6号</t>
-        </is>
-      </c>
+          <t>平税稽一局处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>增值税、个人所得税</t>
+        </is>
+      </c>
       <c r="R4" s="3" t="n"/>
       <c r="S4" s="3" t="n"/>
       <c r="T4" s="3" t="n"/>
@@ -7544,14 +7796,14 @@
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="4" t="n"/>
       <c r="X4" s="4" t="n">
-        <v>46216</v>
+        <v>46227</v>
       </c>
       <c r="Y4" s="4" t="n"/>
       <c r="Z4" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -7573,20 +7825,16 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF4" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF4" s="2" t="inlineStr"/>
       <c r="AG4" s="2" t="inlineStr"/>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
+          <t>国家税务总局平顶山市税务局第一稽查局关于送达汝州泰隆实业有限公司《税务处理决定书》的公告 - 国家税务总局平顶山市税务局</t>
         </is>
       </c>
       <c r="AI4" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr">
@@ -7597,70 +7845,66 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CASE-089a3b9692e76ac4</t>
+          <t>CASE-365e8a924cf64611</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>DOC-9f8e8958d8ff89b6</t>
+          <t>DOC-4d14eba16f9aa8a0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>淮安市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局淮安市税务局稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>淮安市百亦金商贸有限公司</t>
+          <t>贵州博泰工贸有限公司</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>91320804MA1WEH7Y3U</t>
+          <t>91520115587255589F</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>淮税稽罚〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕38号</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>淮税稽处〔2026〕26号</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽罚〔2026〕6号</t>
-        </is>
-      </c>
+          <t>筑税三稽处〔2026〕38号</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="3" t="n"/>
@@ -7670,14 +7914,14 @@
       <c r="V5" s="2" t="inlineStr"/>
       <c r="W5" s="4" t="n"/>
       <c r="X5" s="4" t="n">
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -7691,7 +7935,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE5" s="5" t="inlineStr">
@@ -7699,20 +7943,16 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF5" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF5" s="2" t="inlineStr"/>
       <c r="AG5" s="2" t="inlineStr"/>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书、税务行政处罚决定书的公告</t>
         </is>
       </c>
       <c r="AI5" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>页面已删除</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr">
@@ -7723,16 +7963,16 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>CASE-717dfe3250926214</t>
+          <t>CASE-089a3b9692e76ac4</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>DOC-7df9c075e55777a1</t>
+          <t>DOC-d21cdc5988b1e304</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -7742,45 +7982,49 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>泰州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泰州市税务局第一稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泰州市税务局第一稽查局</t>
+          <t>国家税务总局淮安市税务局稽查局</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>靖江市长凌金属材料有限公司</t>
+          <t>淮安市百亦金商贸有限公司</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>91321282742461893K</t>
+          <t>91320804MA1WEH7Y3U</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>泰税一稽罚〔2025〕54号</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>淮税稽处〔2026〕26号</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>淮税稽处〔2026〕26号</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>泰税一稽罚〔2025〕54号</t>
+          <t>淮税稽罚〔2026〕6号</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr"/>
@@ -7789,21 +8033,17 @@
       <c r="S6" s="3" t="n"/>
       <c r="T6" s="3" t="n"/>
       <c r="U6" s="3" t="n"/>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>接上级通知,经我局研究决定,撤销上述《税务行政处罚决定书》。</t>
-        </is>
-      </c>
+      <c r="V6" s="2" t="inlineStr"/>
       <c r="W6" s="4" t="n"/>
       <c r="X6" s="4" t="n">
-        <v>46191</v>
+        <v>46216</v>
       </c>
       <c r="Y6" s="4" t="n"/>
       <c r="Z6" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -7825,84 +8065,92 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AF6" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG6" s="2" t="inlineStr"/>
       <c r="AH6" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 关于撤销《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
         </is>
       </c>
       <c r="AI6" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="inlineStr">
         <is>
-          <t>官方页面显示该决定书已被撤销。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CASE-13a8aac51595155a</t>
+          <t>CASE-089a3b9692e76ac4</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>DOC-7189c9a2cee8e8ce</t>
+          <t>DOC-9f8e8958d8ff89b6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>温州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局淮安市税务局稽查局</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>温作潘</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr"/>
+          <t>淮安市百亦金商贸有限公司</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>91320804MA1WEH7Y3U</t>
+        </is>
+      </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>温税三稽处〔2026〕100号</t>
+          <t>淮税稽罚〔2026〕6号</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>温税三稽处〔2026〕100号</t>
+          <t>淮税稽处〔2026〕26号</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>温税三稽罚〔2026〕65号</t>
+          <t>淮税稽罚〔2026〕6号</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr"/>
@@ -7914,14 +8162,14 @@
       <c r="V7" s="2" t="inlineStr"/>
       <c r="W7" s="4" t="n"/>
       <c r="X7" s="4" t="n">
-        <v>46175</v>
+        <v>46216</v>
       </c>
       <c r="Y7" s="4" t="n"/>
       <c r="Z7" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -7951,7 +8199,7 @@
       <c r="AG7" s="2" t="inlineStr"/>
       <c r="AH7" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
         </is>
       </c>
       <c r="AI7" s="2" t="inlineStr">
@@ -7967,45 +8215,49 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CASE-13a8aac51595155a</t>
+          <t>CASE-717dfe3250926214</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DOC-02fc2468fd0396a6</t>
+          <t>DOC-7df9c075e55777a1</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>温州市</t>
+          <t>泰州市</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局泰州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局泰州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>温作潘</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr"/>
+          <t>靖江市长凌金属材料有限公司</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>91321282742461893K</t>
+        </is>
+      </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -8014,17 +8266,13 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>温税三稽罚〔2026〕65号</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>温税三稽处〔2026〕100号</t>
-        </is>
-      </c>
+          <t>泰税一稽罚〔2025〕54号</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>温税三稽罚〔2026〕65号</t>
+          <t>泰税一稽罚〔2025〕54号</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr"/>
@@ -8033,17 +8281,21 @@
       <c r="S8" s="3" t="n"/>
       <c r="T8" s="3" t="n"/>
       <c r="U8" s="3" t="n"/>
-      <c r="V8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>接上级通知,经我局研究决定,撤销上述《税务行政处罚决定书》。</t>
+        </is>
+      </c>
       <c r="W8" s="4" t="n"/>
       <c r="X8" s="4" t="n">
-        <v>46175</v>
+        <v>46191</v>
       </c>
       <c r="Y8" s="4" t="n"/>
       <c r="Z8" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -8065,73 +8317,65 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF8" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF8" s="2" t="inlineStr"/>
       <c r="AG8" s="2" t="inlineStr"/>
       <c r="AH8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 关于撤销《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI8" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>官方页面显示该决定书已被撤销。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>CASE-f8625e66b291a216</t>
+          <t>CASE-13a8aac51595155a</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DOC-7970511393924720</t>
+          <t>DOC-7189c9a2cee8e8ce</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>温州市</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>贵州翰缤商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>91520114MAAK1C546F</t>
-        </is>
-      </c>
+          <t>温作潘</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
@@ -8140,15 +8384,19 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>筑税二稽处〔2026〕27号</t>
+          <t>温税三稽处〔2026〕100号</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>筑税二稽处〔2026〕27号</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
+          <t>温税三稽处〔2026〕100号</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>温税三稽罚〔2026〕65号</t>
+        </is>
+      </c>
       <c r="P9" s="2" t="inlineStr"/>
       <c r="Q9" s="2" t="inlineStr"/>
       <c r="R9" s="3" t="n"/>
@@ -8158,14 +8406,14 @@
       <c r="V9" s="2" t="inlineStr"/>
       <c r="W9" s="4" t="n"/>
       <c r="X9" s="4" t="n">
-        <v>46156</v>
+        <v>46175</v>
       </c>
       <c r="Y9" s="4" t="n"/>
       <c r="Z9" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -8179,7 +8427,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE9" s="5" t="inlineStr">
@@ -8187,16 +8435,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AF9" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG9" s="2" t="inlineStr"/>
       <c r="AH9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局关于送达《税务处理决定书》的公告</t>
+          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
         </is>
       </c>
       <c r="AI9" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr">
@@ -8207,68 +8459,64 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CASE-0f4867f7b70d12f3</t>
+          <t>CASE-13a8aac51595155a</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DOC-6f25d6b79e123d03</t>
+          <t>DOC-02fc2468fd0396a6</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>温州市</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>贵州铂朗物流有限公司</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>91520115MAAK0DB335</t>
-        </is>
-      </c>
+          <t>温作潘</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
+          <t>温税三稽罚〔2026〕65号</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
+          <t>温税三稽处〔2026〕100号</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽罚〔2026〕22号</t>
+          <t>温税三稽罚〔2026〕65号</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr"/>
@@ -8280,14 +8528,14 @@
       <c r="V10" s="2" t="inlineStr"/>
       <c r="W10" s="4" t="n"/>
       <c r="X10" s="4" t="n">
-        <v>46122</v>
+        <v>46175</v>
       </c>
       <c r="Y10" s="4" t="n"/>
       <c r="Z10" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -8301,7 +8549,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE10" s="5" t="inlineStr">
@@ -8309,16 +8557,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AF10" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG10" s="2" t="inlineStr"/>
       <c r="AH10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
+          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
         </is>
       </c>
       <c r="AI10" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ10" s="2" t="inlineStr">
@@ -8329,16 +8581,16 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>CASE-0f4867f7b70d12f3</t>
+          <t>CASE-f8625e66b291a216</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>DOC-e8233eb0e06b6e3e</t>
+          <t>DOC-7970511393924720</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -8354,45 +8606,41 @@
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局贵阳市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局贵阳市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>贵州铂朗物流有限公司</t>
+          <t>贵州翰缤商贸有限公司</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91520115MAAK0DB335</t>
+          <t>91520114MAAK1C546F</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽罚〔2026〕22号</t>
+          <t>筑税二稽处〔2026〕27号</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>筑税三稽罚〔2026〕22号</t>
-        </is>
-      </c>
+          <t>筑税二稽处〔2026〕27号</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
       <c r="R11" s="3" t="n"/>
@@ -8402,14 +8650,14 @@
       <c r="V11" s="2" t="inlineStr"/>
       <c r="W11" s="4" t="n"/>
       <c r="X11" s="4" t="n">
-        <v>46122</v>
+        <v>46156</v>
       </c>
       <c r="Y11" s="4" t="n"/>
       <c r="Z11" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -8435,7 +8683,7 @@
       <c r="AG11" s="2" t="inlineStr"/>
       <c r="AH11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
+          <t>国家税务总局贵阳市税务局第二稽查局关于送达《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI11" s="2" t="inlineStr">
@@ -8451,47 +8699,47 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CASE-136615addd5d0c0e</t>
+          <t>CASE-0f4867f7b70d12f3</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>DOC-551df7dc5c028b27</t>
+          <t>DOC-6f25d6b79e123d03</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>来宾市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>广西欣瑞木业有限公司</t>
+          <t>贵州铂朗物流有限公司</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>91451322MAD89XWX07</t>
+          <t>91520115MAAK0DB335</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -8502,17 +8750,17 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr"/>
@@ -8524,14 +8772,14 @@
       <c r="V12" s="2" t="inlineStr"/>
       <c r="W12" s="4" t="n"/>
       <c r="X12" s="4" t="n">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="Y12" s="4" t="n"/>
       <c r="Z12" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -8545,7 +8793,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE12" s="5" t="inlineStr">
@@ -8557,12 +8805,12 @@
       <c r="AG12" s="2" t="inlineStr"/>
       <c r="AH12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
         </is>
       </c>
       <c r="AI12" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>页面已删除</t>
         </is>
       </c>
       <c r="AJ12" s="2" t="inlineStr">
@@ -8573,47 +8821,47 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CASE-136615addd5d0c0e</t>
+          <t>CASE-0f4867f7b70d12f3</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>DOC-21f0193b66d5c3e9</t>
+          <t>DOC-e8233eb0e06b6e3e</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>来宾市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>广西欣瑞木业有限公司</t>
+          <t>贵州铂朗物流有限公司</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>91451322MAD89XWX07</t>
+          <t>91520115MAAK0DB335</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
@@ -8624,17 +8872,17 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr"/>
@@ -8646,14 +8894,14 @@
       <c r="V13" s="2" t="inlineStr"/>
       <c r="W13" s="4" t="n"/>
       <c r="X13" s="4" t="n">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="Y13" s="4" t="n"/>
       <c r="Z13" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -8667,7 +8915,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE13" s="5" t="inlineStr">
@@ -8679,12 +8927,12 @@
       <c r="AG13" s="2" t="inlineStr"/>
       <c r="AH13" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
         </is>
       </c>
       <c r="AI13" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>页面已删除</t>
         </is>
       </c>
       <c r="AJ13" s="2" t="inlineStr">
@@ -8695,64 +8943,68 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASE-393a878d93a22709</t>
+          <t>CASE-136615addd5d0c0e</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DOC-cda8cba853896b18</t>
+          <t>DOC-551df7dc5c028b27</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>广州市</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>番禺区</t>
-        </is>
-      </c>
+          <t>来宾市</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>广州赞荣服装有限公司</t>
+          <t>广西欣瑞木业有限公司</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>91440113MA59AJFJ1J</t>
+          <t>91451322MAD89XWX07</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>穗番税退罚字〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>来市税二稽处〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>来市税二稽处〔2026〕6号</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>穗番税退罚字〔2026〕1号</t>
+          <t>来市税二稽罚〔2026〕4号</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr"/>
@@ -8764,14 +9016,14 @@
       <c r="V14" s="2" t="inlineStr"/>
       <c r="W14" s="4" t="n"/>
       <c r="X14" s="4" t="n">
-        <v>46091</v>
+        <v>46119</v>
       </c>
       <c r="Y14" s="4" t="n"/>
       <c r="Z14" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -8785,7 +9037,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE14" s="5" t="inlineStr">
@@ -8793,90 +9045,90 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF14" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF14" s="2" t="inlineStr"/>
       <c r="AG14" s="2" t="inlineStr"/>
       <c r="AH14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
+          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
         </is>
       </c>
       <c r="AI14" s="2" t="inlineStr">
         <is>
-          <t>内容不匹配</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ14" s="2" t="inlineStr">
         <is>
-          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CASE-0b4a4519ba4f5ad9</t>
+          <t>CASE-136615addd5d0c0e</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>DOC-5376b9bae81cfc82</t>
+          <t>DOC-21f0193b66d5c3e9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
+          <t>来宾市</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局稽查局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>常州好佳车辆配件有限公司</t>
+          <t>广西欣瑞木业有限公司</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>91320411094264460B</t>
+          <t>91451322MAD89XWX07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕71号</t>
+          <t>来市税二稽罚〔2026〕4号</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕71号</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
+          <t>来市税二稽处〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>来市税二稽罚〔2026〕4号</t>
+        </is>
+      </c>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr"/>
       <c r="R15" s="3" t="n"/>
@@ -8886,14 +9138,14 @@
       <c r="V15" s="2" t="inlineStr"/>
       <c r="W15" s="4" t="n"/>
       <c r="X15" s="4" t="n">
-        <v>46087</v>
+        <v>46119</v>
       </c>
       <c r="Y15" s="4" t="n"/>
       <c r="Z15" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -8915,66 +9167,310 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF15" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF15" s="2" t="inlineStr"/>
       <c r="AG15" s="2" t="inlineStr"/>
       <c r="AH15" s="2" t="inlineStr">
         <is>
+          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
+        </is>
+      </c>
+      <c r="AI15" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ15" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>CASE-393a878d93a22709</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>DOC-cda8cba853896b18</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>广州市</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>番禺区</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局广州市番禺区税务局</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>广州赞荣服装有限公司</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>91440113MA59AJFJ1J</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>税务行政处罚决定书</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="3" t="n"/>
+      <c r="S16" s="3" t="n"/>
+      <c r="T16" s="3" t="n"/>
+      <c r="U16" s="3" t="n"/>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="4" t="n"/>
+      <c r="X16" s="4" t="n">
+        <v>46091</v>
+      </c>
+      <c r="Y16" s="4" t="n"/>
+      <c r="Z16" s="4" t="n">
+        <v>46229</v>
+      </c>
+      <c r="AA16" s="4" t="n">
+        <v>46236</v>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>仅公告送达/仅文号线索</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE16" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF16" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
+        </is>
+      </c>
+      <c r="AI16" s="2" t="inlineStr">
+        <is>
+          <t>内容不匹配</t>
+        </is>
+      </c>
+      <c r="AJ16" s="2" t="inlineStr">
+        <is>
+          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>CASE-0b4a4519ba4f5ad9</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>DOC-5376b9bae81cfc82</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>江苏省</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>常州市</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局江苏省税务局</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局常州市税务局稽查局</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>常州好佳车辆配件有限公司</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>91320411094264460B</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>常税稽处〔2026〕71号</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>常税稽处〔2026〕71号</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="3" t="n"/>
+      <c r="S17" s="3" t="n"/>
+      <c r="T17" s="3" t="n"/>
+      <c r="U17" s="3" t="n"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="4" t="n"/>
+      <c r="X17" s="4" t="n">
+        <v>46087</v>
+      </c>
+      <c r="Y17" s="4" t="n"/>
+      <c r="Z17" s="4" t="n">
+        <v>46229</v>
+      </c>
+      <c r="AA17" s="4" t="n">
+        <v>46236</v>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>仅公告送达/仅文号线索</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD17" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AE17" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF17" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr">
+        <is>
           <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州好佳车辆配件有限公司《税务处理决定书》的公告</t>
         </is>
       </c>
-      <c r="AI15" s="2" t="inlineStr">
+      <c r="AI17" s="2" t="inlineStr">
         <is>
           <t>附件正常</t>
         </is>
       </c>
-      <c r="AJ15" s="2" t="inlineStr">
+      <c r="AJ17" s="2" t="inlineStr">
         <is>
           <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ15"/>
-  <conditionalFormatting sqref="AD2:AD15">
+  <autoFilter ref="A1:AJ17"/>
+  <conditionalFormatting sqref="AD2:AD17">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AD2="待核验"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI2:AI15">
+  <conditionalFormatting sqref="AI2:AI17">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>AND($AI2&lt;&gt;"正常",$AI2&lt;&gt;"附件正常")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AD2:AD15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AD2:AD17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"已核验,待核验,人工复核完成"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF4" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE5" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE5" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE6" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF7" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF8" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF7" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE9" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE10" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE11" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE12" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE14" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF14" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE15" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF15" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE10" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE11" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE12" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE14" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE15" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE16" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF16" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE17" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF17" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -9288,7 +9784,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -9414,7 +9910,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -9532,7 +10028,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -9654,7 +10150,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -9776,7 +10272,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -9894,7 +10390,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -10036,7 +10532,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -10178,7 +10674,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -10306,7 +10802,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -10430,7 +10926,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -10564,7 +11060,7 @@
         <v>46230</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -10698,7 +11194,7 @@
         <v>46230</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -11084,7 +11580,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -11210,7 +11706,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -11328,7 +11824,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -11450,7 +11946,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -11572,7 +12068,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -11690,7 +12186,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -11771,7 +12267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12510,8 +13006,57 @@
         </is>
       </c>
     </row>
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T14:38:13+08:00</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 至 2026-08-02</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>广西威曼能源科技有限公司</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>已完成候选发现、逐条访问核验、去重、关联和历史数据增量写入。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M15"/>
+  <autoFilter ref="A1:M16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -785,7 +785,7 @@
         <v>46236</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -823,7 +823,11 @@
           <t>附件正常</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -907,7 +911,7 @@
         <v>46236</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -945,7 +949,11 @@
           <t>附件正常</t>
         </is>
       </c>
-      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1035,7 +1043,7 @@
         <v>46233</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1171,7 +1179,7 @@
         <v>46234</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1293,7 +1301,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1411,7 +1419,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1543,7 +1551,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1677,7 +1685,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1801,7 +1809,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1927,7 +1935,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -2061,7 +2069,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -2185,7 +2193,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -2311,7 +2319,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -2429,7 +2437,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -2551,7 +2559,7 @@
         <v>46229</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -2673,7 +2681,7 @@
         <v>46229</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -2795,7 +2803,7 @@
         <v>46229</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -2917,7 +2925,7 @@
         <v>46229</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -3039,7 +3047,7 @@
         <v>46229</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -3161,7 +3169,7 @@
         <v>46229</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -3279,7 +3287,7 @@
         <v>46229</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
@@ -3421,7 +3429,7 @@
         <v>46229</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
@@ -3543,7 +3551,7 @@
         <v>46229</v>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
@@ -3679,7 +3687,7 @@
         <v>46229</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
@@ -3811,7 +3819,7 @@
         <v>46229</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
@@ -3949,7 +3957,7 @@
         <v>46229</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
@@ -4091,7 +4099,7 @@
         <v>46229</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
@@ -4221,7 +4229,7 @@
         <v>46229</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
@@ -4349,7 +4357,7 @@
         <v>46229</v>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
@@ -4473,7 +4481,7 @@
         <v>46229</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
@@ -4607,7 +4615,7 @@
         <v>46230</v>
       </c>
       <c r="AA32" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
@@ -4741,7 +4749,7 @@
         <v>46230</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
@@ -5166,7 +5174,7 @@
         <v>46233</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -5302,7 +5310,7 @@
         <v>46234</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -5434,7 +5442,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -5568,7 +5576,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -5700,7 +5708,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -5828,7 +5836,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -5966,7 +5974,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -6102,7 +6110,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -6234,7 +6242,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -6372,7 +6380,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -6514,7 +6522,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -6644,7 +6652,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -6772,7 +6780,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -6896,7 +6904,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -7030,7 +7038,7 @@
         <v>46230</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -7164,7 +7172,7 @@
         <v>46230</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -7559,7 +7567,7 @@
         <v>46236</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -7597,7 +7605,11 @@
           <t>附件正常</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -7681,7 +7693,7 @@
         <v>46236</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -7719,7 +7731,11 @@
           <t>附件正常</t>
         </is>
       </c>
-      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -7803,7 +7819,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -7921,7 +7937,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -8043,7 +8059,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -8169,7 +8185,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -8295,7 +8311,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -8413,7 +8429,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -8535,7 +8551,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -8657,7 +8673,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -8779,7 +8795,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -8901,7 +8917,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -9023,7 +9039,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -9145,7 +9161,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -9263,7 +9279,7 @@
         <v>46229</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -9385,7 +9401,7 @@
         <v>46229</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -9784,7 +9800,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -9910,7 +9926,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -10028,7 +10044,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -10150,7 +10166,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -10272,7 +10288,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -10390,7 +10406,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -10532,7 +10548,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -10674,7 +10690,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -10802,7 +10818,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -10926,7 +10942,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -11060,7 +11076,7 @@
         <v>46230</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -11194,7 +11210,7 @@
         <v>46230</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -11580,7 +11596,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -11706,7 +11722,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -11824,7 +11840,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -11946,7 +11962,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -12068,7 +12084,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -12186,7 +12202,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -12267,7 +12283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -13055,8 +13071,53 @@
         </is>
       </c>
     </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:33:31+08:00</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31 至 2026-08-03</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>本次检索未发现符合收录标准的新文书。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M16"/>
+  <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -785,7 +785,7 @@
         <v>46236</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>46236</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>46233</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>46234</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>46229</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>46229</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>46229</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>46229</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>46229</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>46229</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>46229</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>46229</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>46229</v>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>46229</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>46229</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>46229</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>46229</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>46229</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>46229</v>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>46229</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>46230</v>
       </c>
       <c r="AA32" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>46230</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>46233</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>46234</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>46230</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>46230</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>46236</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>46236</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>46229</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>46229</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>46230</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>46230</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         <v>46229</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>46229</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -13116,8 +13116,53 @@
         </is>
       </c>
     </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:32:07+08:00</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01 至 2026-08-04</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>本次检索未发现符合收录标准的新文书。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M17"/>
+  <autoFilter ref="A1:M18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -14549,7 +14549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -15529,8 +15529,57 @@
         </is>
       </c>
     </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:45:37+08:00</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28 至 2026-08-04</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/qzsswj/xxgk/sjxxgk/qtgg_23603/: ConnectionError: HTTPSConnectionPool(host='fujian.chinatax.gov.cn', port=443): Max retries exceeded with url: /qzsswj/xxgk/sjxxgk/qtgg_23603/ (Caused by NewConnectionError("HTTPSConnection(host='fujian.chinata...</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>本次检索未发现符合收录标准的新文书。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M20"/>
+  <autoFilter ref="A1:M21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -18,9 +18,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文书汇总'!$A$1:$AJ$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'完整文书'!$A$1:$AJ$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE14" s="5" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="AI14" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ14" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE21" s="5" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="AI21" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ21" s="2" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE24" s="5" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="AI24" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ24" s="2" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE25" s="5" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="AI25" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ25" s="2" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE26" s="5" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="AI26" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ26" s="2" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="AJ34" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。 字段“主要违法事实”存在冲突:保留原值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”,新值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="AJ35" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="AJ37" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="AJ38" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE10" s="5" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="AI10" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ10" s="2" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AJ14" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。 字段“主要违法事实”存在冲突:保留原值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”,新值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="AJ15" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8109,7 @@
       </c>
       <c r="AJ17" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="AJ18" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -9735,7 +9735,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE9" s="5" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="AI9" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE15" s="5" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="AI15" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ15" s="2" t="inlineStr">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE16" s="5" t="inlineStr">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="AI16" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ16" s="2" t="inlineStr">
@@ -10715,7 +10715,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE17" s="5" t="inlineStr">
@@ -10732,7 +10732,7 @@
       </c>
       <c r="AI17" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ17" s="2" t="inlineStr">
@@ -11289,7 +11289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ15"/>
+  <dimension ref="A1:AJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11750,66 +11750,66 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CASE-365e8a924cf64611</t>
+          <t>CASE-393a878d93a22709</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>DOC-4d14eba16f9aa8a0</t>
+          <t>DOC-cda8cba853896b18</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>广东省</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
+          <t>广州市</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>番禺区</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
-        </is>
-      </c>
+          <t>国家税务总局广州市番禺区税务局</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>贵州博泰工贸有限公司</t>
+          <t>广州赞荣服装有限公司</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>91520115587255589F</t>
+          <t>91440113MA59AJFJ1J</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕38号</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>筑税三稽处〔2026〕38号</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr"/>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
       <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr"/>
       <c r="R4" s="3" t="n"/>
@@ -11819,7 +11819,7 @@
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="4" t="n"/>
       <c r="X4" s="4" t="n">
-        <v>46224</v>
+        <v>46091</v>
       </c>
       <c r="Y4" s="4" t="n"/>
       <c r="Z4" s="4" t="n">
@@ -11848,36 +11848,40 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AF4" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG4" s="2" t="inlineStr"/>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书、税务行政处罚决定书的公告</t>
+          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
         </is>
       </c>
       <c r="AI4" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>内容不匹配</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CASE-a62e569c195adc3c</t>
+          <t>CASE-f78ec1a594442165</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>DOC-b1dda915d4e6117d</t>
+          <t>DOC-fbbe4a664b14f54b</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -11887,28 +11891,28 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>遵义市</t>
+          <t>安顺市</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局稽查局</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>贵州服格定商贸有限公司</t>
+          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>91520302MABUEHN034</t>
+          <t>91520423MA6DLH799Q</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
@@ -11919,33 +11923,45 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>遵税一稽处〔2026〕30号</t>
+          <t>安市税稽处〔2026〕1号</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>遵税一稽处〔2026〕30号</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr"/>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽罚〔2026〕1号</t>
+        </is>
+      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="n"/>
+          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>64884.41</v>
+      </c>
       <c r="S5" s="3" t="n"/>
       <c r="T5" s="3" t="n"/>
       <c r="U5" s="3" t="n"/>
-      <c r="V5" s="2" t="inlineStr"/>
-      <c r="W5" s="4" t="n"/>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>45898</v>
+      </c>
       <c r="X5" s="4" t="n">
-        <v>46185</v>
+        <v>46043</v>
       </c>
       <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n">
@@ -11974,36 +11990,40 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AF5" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG5" s="2" t="inlineStr"/>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
+          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI5" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。 字段“主要违法事实”存在冲突:保留原值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”,新值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>CASE-f8625e66b291a216</t>
+          <t>CASE-f78ec1a594442165</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>DOC-7970511393924720</t>
+          <t>DOC-9a828a6048b54b6c</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -12013,57 +12033,77 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>安顺市</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局</t>
+          <t>国家税务总局安顺市税务局</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局</t>
+          <t>国家税务总局安顺市税务局稽查局</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>贵州翰缤商贸有限公司</t>
+          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>91520114MAAK1C546F</t>
+          <t>91520423MA6DLH799Q</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>筑税二稽处〔2026〕27号</t>
+          <t>安市税稽罚〔2026〕1号</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>筑税二稽处〔2026〕27号</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽罚〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
       <c r="R6" s="3" t="n"/>
       <c r="S6" s="3" t="n"/>
-      <c r="T6" s="3" t="n"/>
+      <c r="T6" s="3" t="n">
+        <v>200000</v>
+      </c>
       <c r="U6" s="3" t="n"/>
-      <c r="V6" s="2" t="inlineStr"/>
-      <c r="W6" s="4" t="n"/>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="n">
+        <v>45898</v>
+      </c>
       <c r="X6" s="4" t="n">
-        <v>46156</v>
+        <v>46043</v>
       </c>
       <c r="Y6" s="4" t="n"/>
       <c r="Z6" s="4" t="n">
@@ -12074,7 +12114,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -12092,69 +12132,69 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AF6" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG6" s="2" t="inlineStr"/>
       <c r="AH6" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局关于送达《税务处理决定书》的公告</t>
+          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI6" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CASE-0f4867f7b70d12f3</t>
+          <t>CASE-1983d97878508732</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>DOC-6f25d6b79e123d03</t>
+          <t>DOC-f9760895b4f08cc2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>二连浩特市</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局二连浩特市税务局</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局二连浩特市税务局稽查局</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>贵州铂朗物流有限公司</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>91520115MAAK0DB335</t>
-        </is>
-      </c>
+          <t>二连市坤益腾金属有限公司</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -12163,30 +12203,36 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
+          <t>二税稽处〔2025〕1号</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>筑税三稽罚〔2026〕22号</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
+          <t>二税稽处〔2025〕1号</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>增值税</t>
+        </is>
+      </c>
       <c r="R7" s="3" t="n"/>
       <c r="S7" s="3" t="n"/>
       <c r="T7" s="3" t="n"/>
       <c r="U7" s="3" t="n"/>
-      <c r="V7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
+        </is>
+      </c>
       <c r="W7" s="4" t="n"/>
-      <c r="X7" s="4" t="n">
-        <v>46122</v>
-      </c>
+      <c r="X7" s="4" t="n"/>
       <c r="Y7" s="4" t="n"/>
       <c r="Z7" s="4" t="n">
         <v>46229</v>
@@ -12196,7 +12242,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -12218,97 +12264,99 @@
       <c r="AG7" s="2" t="inlineStr"/>
       <c r="AH7" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="AI7" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CASE-0f4867f7b70d12f3</t>
+          <t>CASE-d4b6986f3f97cd28</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DOC-e8233eb0e06b6e3e</t>
+          <t>DOC-442cf3d9a5280c12</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>鄂尔多斯市</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
-        </is>
-      </c>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>第二稽查局</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>贵州铂朗物流有限公司</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>91520115MAAK0DB335</t>
-        </is>
-      </c>
+          <t>廖礼平</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽罚〔2026〕22号</t>
+          <t>鄂税二稽处〔2023〕29号</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>筑税三稽罚〔2026〕22号</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="3" t="n"/>
-      <c r="S8" s="3" t="n"/>
+          <t>鄂税二稽处〔2023〕29号</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>个人所得税、印花税</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>15072487.5</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>1046925</v>
+      </c>
       <c r="T8" s="3" t="n"/>
       <c r="U8" s="3" t="n"/>
-      <c r="V8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
+        </is>
+      </c>
       <c r="W8" s="4" t="n"/>
-      <c r="X8" s="4" t="n">
-        <v>46122</v>
-      </c>
+      <c r="X8" s="4" t="n"/>
       <c r="Y8" s="4" t="n"/>
       <c r="Z8" s="4" t="n">
         <v>46229</v>
@@ -12318,7 +12366,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -12340,103 +12388,119 @@
       <c r="AG8" s="2" t="inlineStr"/>
       <c r="AH8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="AI8" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>CASE-393a878d93a22709</t>
+          <t>CASE-7e3d4a321440d6a7</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DOC-cda8cba853896b18</t>
+          <t>DOC-bed9330343ed06af</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>广州市</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>番禺区</t>
-        </is>
-      </c>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>广州赞荣服装有限公司</t>
+          <t>天津展达科技有限公司</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91440113MA59AJFJ1J</t>
+          <t>91120116300738701X</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>穗番税退罚字〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>穗番税退罚字〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="3" t="n"/>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>920146.9399999999</v>
+      </c>
       <c r="S9" s="3" t="n"/>
       <c r="T9" s="3" t="n"/>
       <c r="U9" s="3" t="n"/>
-      <c r="V9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
       <c r="W9" s="4" t="n"/>
-      <c r="X9" s="4" t="n">
-        <v>46091</v>
-      </c>
+      <c r="X9" s="4" t="n"/>
       <c r="Y9" s="4" t="n"/>
       <c r="Z9" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AA9" s="4" t="n">
         <v>46238</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -12454,124 +12518,116 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF9" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF9" s="2" t="inlineStr"/>
       <c r="AG9" s="2" t="inlineStr"/>
       <c r="AH9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
+          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI9" s="2" t="inlineStr">
         <is>
-          <t>内容不匹配</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr">
         <is>
-          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CASE-f78ec1a594442165</t>
+          <t>CASE-7e3d4a321440d6a7</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DOC-fbbe4a664b14f54b</t>
+          <t>DOC-388bd01c01bbb789</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>安顺市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局</t>
+          <t>国家税务总局天津市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局</t>
+          <t>国家税务总局天津市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
+          <t>天津展达科技有限公司</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>91520423MA6DLH799Q</t>
+          <t>91120116300738701X</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>津税一稽罚〔2023〕21号</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>津税一稽处〔2023〕59号</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>安市税稽罚〔2026〕1号</t>
+          <t>津税一稽罚〔2023〕21号</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>64884.41</v>
-      </c>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="n"/>
       <c r="S10" s="3" t="n"/>
-      <c r="T10" s="3" t="n"/>
+      <c r="T10" s="3" t="n">
+        <v>131368.5</v>
+      </c>
       <c r="U10" s="3" t="n"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
-      <c r="W10" s="4" t="n">
-        <v>45898</v>
-      </c>
-      <c r="X10" s="4" t="n">
-        <v>46043</v>
-      </c>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W10" s="4" t="n"/>
+      <c r="X10" s="4" t="n"/>
       <c r="Y10" s="4" t="n"/>
       <c r="Z10" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AA10" s="4" t="n">
         <v>46238</v>
@@ -12596,15 +12652,11 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF10" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF10" s="2" t="inlineStr"/>
       <c r="AG10" s="2" t="inlineStr"/>
       <c r="AH10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI10" s="2" t="inlineStr">
@@ -12613,683 +12665,25 @@
         </is>
       </c>
       <c r="AJ10" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>CASE-f78ec1a594442165</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>DOC-9a828a6048b54b6c</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>贵州省</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>安顺市</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局安顺市税务局</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局安顺市税务局稽查局</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>91520423MA6DLH799Q</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>税务行政处罚决定书</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>安市税稽处〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="n"/>
-      <c r="S11" s="3" t="n"/>
-      <c r="T11" s="3" t="n">
-        <v>200000</v>
-      </c>
-      <c r="U11" s="3" t="n"/>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="n">
-        <v>45898</v>
-      </c>
-      <c r="X11" s="4" t="n">
-        <v>46043</v>
-      </c>
-      <c r="Y11" s="4" t="n"/>
-      <c r="Z11" s="4" t="n">
-        <v>46229</v>
-      </c>
-      <c r="AA11" s="4" t="n">
-        <v>46238</v>
-      </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>完整文书</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD11" s="2" t="inlineStr">
-        <is>
-          <t>待核验</t>
-        </is>
-      </c>
-      <c r="AE11" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF11" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
-      <c r="AG11" s="2" t="inlineStr"/>
-      <c r="AH11" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
-        </is>
-      </c>
-      <c r="AI11" s="2" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="AJ11" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>CASE-1983d97878508732</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>DOC-f9760895b4f08cc2</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>内蒙古自治区</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>二连浩特市</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局二连浩特市税务局</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局二连浩特市税务局稽查局</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>二连市坤益腾金属有限公司</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>税务处理决定书</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>二税稽处〔2025〕1号</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>二税稽处〔2025〕1号</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>增值税</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="n"/>
-      <c r="S12" s="3" t="n"/>
-      <c r="T12" s="3" t="n"/>
-      <c r="U12" s="3" t="n"/>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
-        </is>
-      </c>
-      <c r="W12" s="4" t="n"/>
-      <c r="X12" s="4" t="n"/>
-      <c r="Y12" s="4" t="n"/>
-      <c r="Z12" s="4" t="n">
-        <v>46229</v>
-      </c>
-      <c r="AA12" s="4" t="n">
-        <v>46238</v>
-      </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>完整文书</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD12" s="2" t="inlineStr">
-        <is>
-          <t>待核验</t>
-        </is>
-      </c>
-      <c r="AE12" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF12" s="2" t="inlineStr"/>
-      <c r="AG12" s="2" t="inlineStr"/>
-      <c r="AH12" s="2" t="inlineStr">
-        <is>
-          <t>税务处理决定书</t>
-        </is>
-      </c>
-      <c r="AI12" s="2" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="AJ12" s="2" t="inlineStr">
-        <is>
-          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>CASE-d4b6986f3f97cd28</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>DOC-442cf3d9a5280c12</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>内蒙古自治区</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>鄂尔多斯市</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>第二稽查局</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>廖礼平</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>税务处理决定书</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>鄂税二稽处〔2023〕29号</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>鄂税二稽处〔2023〕29号</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>个人所得税、印花税</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="n">
-        <v>15072487.5</v>
-      </c>
-      <c r="S13" s="3" t="n">
-        <v>1046925</v>
-      </c>
-      <c r="T13" s="3" t="n"/>
-      <c r="U13" s="3" t="n"/>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
-        </is>
-      </c>
-      <c r="W13" s="4" t="n"/>
-      <c r="X13" s="4" t="n"/>
-      <c r="Y13" s="4" t="n"/>
-      <c r="Z13" s="4" t="n">
-        <v>46229</v>
-      </c>
-      <c r="AA13" s="4" t="n">
-        <v>46238</v>
-      </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>完整文书</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD13" s="2" t="inlineStr">
-        <is>
-          <t>待核验</t>
-        </is>
-      </c>
-      <c r="AE13" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF13" s="2" t="inlineStr"/>
-      <c r="AG13" s="2" t="inlineStr"/>
-      <c r="AH13" s="2" t="inlineStr">
-        <is>
-          <t>税务处理决定书</t>
-        </is>
-      </c>
-      <c r="AI13" s="2" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="AJ13" s="2" t="inlineStr">
-        <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>CASE-7e3d4a321440d6a7</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>DOC-bed9330343ed06af</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>天津市</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>天津市</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>天津展达科技有限公司</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>91120116300738701X</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>税务处理决定书</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>920146.9399999999</v>
-      </c>
-      <c r="S14" s="3" t="n"/>
-      <c r="T14" s="3" t="n"/>
-      <c r="U14" s="3" t="n"/>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
-        </is>
-      </c>
-      <c r="W14" s="4" t="n"/>
-      <c r="X14" s="4" t="n"/>
-      <c r="Y14" s="4" t="n"/>
-      <c r="Z14" s="4" t="n">
-        <v>46230</v>
-      </c>
-      <c r="AA14" s="4" t="n">
-        <v>46238</v>
-      </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>完整文书</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD14" s="2" t="inlineStr">
-        <is>
-          <t>待核验</t>
-        </is>
-      </c>
-      <c r="AE14" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF14" s="2" t="inlineStr"/>
-      <c r="AG14" s="2" t="inlineStr"/>
-      <c r="AH14" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
-        </is>
-      </c>
-      <c r="AI14" s="2" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="AJ14" s="2" t="inlineStr">
-        <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>CASE-7e3d4a321440d6a7</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>DOC-388bd01c01bbb789</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>天津市</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>天津市</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>天津展达科技有限公司</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>91120116300738701X</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>税务行政处罚决定书</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="n"/>
-      <c r="S15" s="3" t="n"/>
-      <c r="T15" s="3" t="n">
-        <v>131368.5</v>
-      </c>
-      <c r="U15" s="3" t="n"/>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
-        </is>
-      </c>
-      <c r="W15" s="4" t="n"/>
-      <c r="X15" s="4" t="n"/>
-      <c r="Y15" s="4" t="n"/>
-      <c r="Z15" s="4" t="n">
-        <v>46230</v>
-      </c>
-      <c r="AA15" s="4" t="n">
-        <v>46238</v>
-      </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>完整文书</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD15" s="2" t="inlineStr">
-        <is>
-          <t>待核验</t>
-        </is>
-      </c>
-      <c r="AE15" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF15" s="2" t="inlineStr"/>
-      <c r="AG15" s="2" t="inlineStr"/>
-      <c r="AH15" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
-        </is>
-      </c>
-      <c r="AI15" s="2" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="AJ15" s="2" t="inlineStr">
         <is>
           <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ15"/>
-  <conditionalFormatting sqref="AD2:AD15">
+  <autoFilter ref="A1:AJ10"/>
+  <conditionalFormatting sqref="AD2:AD10">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AD2="待核验"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI2:AI15">
+  <conditionalFormatting sqref="AI2:AI10">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>AND($AI2&lt;&gt;"正常",$AI2&lt;&gt;"附件正常")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AD2:AD15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AD2:AD10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"已核验,待核验,人工复核完成"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13297,20 +12691,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE10" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE11" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF11" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE12" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE14" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE15" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE10" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -13323,7 +12712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ9"/>
+  <dimension ref="A1:AJ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13784,66 +13173,66 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CASE-365e8a924cf64611</t>
+          <t>CASE-393a878d93a22709</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>DOC-4d14eba16f9aa8a0</t>
+          <t>DOC-cda8cba853896b18</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>广东省</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
+          <t>广州市</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>番禺区</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
-        </is>
-      </c>
+          <t>国家税务总局广州市番禺区税务局</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>贵州博泰工贸有限公司</t>
+          <t>广州赞荣服装有限公司</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>91520115587255589F</t>
+          <t>91440113MA59AJFJ1J</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕38号</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>筑税三稽处〔2026〕38号</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr"/>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
       <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr"/>
       <c r="R4" s="3" t="n"/>
@@ -13853,7 +13242,7 @@
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="4" t="n"/>
       <c r="X4" s="4" t="n">
-        <v>46224</v>
+        <v>46091</v>
       </c>
       <c r="Y4" s="4" t="n"/>
       <c r="Z4" s="4" t="n">
@@ -13882,648 +13271,42 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AF4" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG4" s="2" t="inlineStr"/>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书、税务行政处罚决定书的公告</t>
+          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
         </is>
       </c>
       <c r="AI4" s="2" t="inlineStr">
         <is>
-          <t>页面已删除</t>
+          <t>内容不匹配</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>CASE-a62e569c195adc3c</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>DOC-b1dda915d4e6117d</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>贵州省</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>遵义市</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>贵州服格定商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>91520302MABUEHN034</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>税务处理决定书</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>遵税一稽处〔2026〕30号</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>遵税一稽处〔2026〕30号</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>增值税</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="n"/>
-      <c r="S5" s="3" t="n"/>
-      <c r="T5" s="3" t="n"/>
-      <c r="U5" s="3" t="n"/>
-      <c r="V5" s="2" t="inlineStr"/>
-      <c r="W5" s="4" t="n"/>
-      <c r="X5" s="4" t="n">
-        <v>46185</v>
-      </c>
-      <c r="Y5" s="4" t="n"/>
-      <c r="Z5" s="4" t="n">
-        <v>46229</v>
-      </c>
-      <c r="AA5" s="4" t="n">
-        <v>46238</v>
-      </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>完整文书</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD5" s="2" t="inlineStr">
-        <is>
-          <t>待核验</t>
-        </is>
-      </c>
-      <c r="AE5" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF5" s="2" t="inlineStr"/>
-      <c r="AG5" s="2" t="inlineStr"/>
-      <c r="AH5" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
-        </is>
-      </c>
-      <c r="AI5" s="2" t="inlineStr">
-        <is>
-          <t>页面已删除</t>
-        </is>
-      </c>
-      <c r="AJ5" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>CASE-f8625e66b291a216</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>DOC-7970511393924720</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>贵州省</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>贵阳市</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局贵阳市税务局第二稽查局</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局贵阳市税务局第二稽查局</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>贵州翰缤商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>91520114MAAK1C546F</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>税务处理决定书</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>筑税二稽处〔2026〕27号</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>筑税二稽处〔2026〕27号</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="3" t="n"/>
-      <c r="S6" s="3" t="n"/>
-      <c r="T6" s="3" t="n"/>
-      <c r="U6" s="3" t="n"/>
-      <c r="V6" s="2" t="inlineStr"/>
-      <c r="W6" s="4" t="n"/>
-      <c r="X6" s="4" t="n">
-        <v>46156</v>
-      </c>
-      <c r="Y6" s="4" t="n"/>
-      <c r="Z6" s="4" t="n">
-        <v>46229</v>
-      </c>
-      <c r="AA6" s="4" t="n">
-        <v>46238</v>
-      </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>仅公告送达/仅文号线索</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>待核验</t>
-        </is>
-      </c>
-      <c r="AE6" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF6" s="2" t="inlineStr"/>
-      <c r="AG6" s="2" t="inlineStr"/>
-      <c r="AH6" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局贵阳市税务局第二稽查局关于送达《税务处理决定书》的公告</t>
-        </is>
-      </c>
-      <c r="AI6" s="2" t="inlineStr">
-        <is>
-          <t>页面已删除</t>
-        </is>
-      </c>
-      <c r="AJ6" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>CASE-0f4867f7b70d12f3</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>DOC-6f25d6b79e123d03</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>贵州省</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>贵阳市</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>贵州铂朗物流有限公司</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>91520115MAAK0DB335</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>税务处理决定书</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>筑税三稽处〔2026〕17号</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>筑税三稽处〔2026〕17号</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>筑税三稽罚〔2026〕22号</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="3" t="n"/>
-      <c r="S7" s="3" t="n"/>
-      <c r="T7" s="3" t="n"/>
-      <c r="U7" s="3" t="n"/>
-      <c r="V7" s="2" t="inlineStr"/>
-      <c r="W7" s="4" t="n"/>
-      <c r="X7" s="4" t="n">
-        <v>46122</v>
-      </c>
-      <c r="Y7" s="4" t="n"/>
-      <c r="Z7" s="4" t="n">
-        <v>46229</v>
-      </c>
-      <c r="AA7" s="4" t="n">
-        <v>46238</v>
-      </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>仅公告送达/仅文号线索</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD7" s="2" t="inlineStr">
-        <is>
-          <t>待核验</t>
-        </is>
-      </c>
-      <c r="AE7" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF7" s="2" t="inlineStr"/>
-      <c r="AG7" s="2" t="inlineStr"/>
-      <c r="AH7" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
-        </is>
-      </c>
-      <c r="AI7" s="2" t="inlineStr">
-        <is>
-          <t>页面已删除</t>
-        </is>
-      </c>
-      <c r="AJ7" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>CASE-0f4867f7b70d12f3</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>DOC-e8233eb0e06b6e3e</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>贵州省</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>贵阳市</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>贵州铂朗物流有限公司</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>91520115MAAK0DB335</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>税务行政处罚决定书</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>筑税三稽罚〔2026〕22号</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>筑税三稽处〔2026〕17号</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>筑税三稽罚〔2026〕22号</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="3" t="n"/>
-      <c r="S8" s="3" t="n"/>
-      <c r="T8" s="3" t="n"/>
-      <c r="U8" s="3" t="n"/>
-      <c r="V8" s="2" t="inlineStr"/>
-      <c r="W8" s="4" t="n"/>
-      <c r="X8" s="4" t="n">
-        <v>46122</v>
-      </c>
-      <c r="Y8" s="4" t="n"/>
-      <c r="Z8" s="4" t="n">
-        <v>46229</v>
-      </c>
-      <c r="AA8" s="4" t="n">
-        <v>46238</v>
-      </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>仅公告送达/仅文号线索</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD8" s="2" t="inlineStr">
-        <is>
-          <t>待核验</t>
-        </is>
-      </c>
-      <c r="AE8" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF8" s="2" t="inlineStr"/>
-      <c r="AG8" s="2" t="inlineStr"/>
-      <c r="AH8" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
-        </is>
-      </c>
-      <c r="AI8" s="2" t="inlineStr">
-        <is>
-          <t>页面已删除</t>
-        </is>
-      </c>
-      <c r="AJ8" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>CASE-393a878d93a22709</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>DOC-cda8cba853896b18</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>广东省</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>广州市</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>番禺区</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局广州市番禺区税务局</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>广州赞荣服装有限公司</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>91440113MA59AJFJ1J</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>税务行政处罚决定书</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>穗番税退罚字〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>穗番税退罚字〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="3" t="n"/>
-      <c r="S9" s="3" t="n"/>
-      <c r="T9" s="3" t="n"/>
-      <c r="U9" s="3" t="n"/>
-      <c r="V9" s="2" t="inlineStr"/>
-      <c r="W9" s="4" t="n"/>
-      <c r="X9" s="4" t="n">
-        <v>46091</v>
-      </c>
-      <c r="Y9" s="4" t="n"/>
-      <c r="Z9" s="4" t="n">
-        <v>46229</v>
-      </c>
-      <c r="AA9" s="4" t="n">
-        <v>46238</v>
-      </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>仅公告送达/仅文号线索</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD9" s="2" t="inlineStr">
-        <is>
-          <t>待核验</t>
-        </is>
-      </c>
-      <c r="AE9" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF9" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
-      <c r="AG9" s="2" t="inlineStr"/>
-      <c r="AH9" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
-        </is>
-      </c>
-      <c r="AI9" s="2" t="inlineStr">
-        <is>
-          <t>内容不匹配</t>
-        </is>
-      </c>
-      <c r="AJ9" s="2" t="inlineStr">
         <is>
           <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ9"/>
-  <conditionalFormatting sqref="AD2:AD9">
+  <autoFilter ref="A1:AJ4"/>
+  <conditionalFormatting sqref="AD2:AD4">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AD2="待核验"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI2:AI9">
+  <conditionalFormatting sqref="AI2:AI4">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>AND($AI2&lt;&gt;"正常",$AI2&lt;&gt;"附件正常")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AD2:AD9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AD2:AD4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"已核验,待核验,人工复核完成"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14531,12 +13314,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF4" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -14549,7 +13327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -15578,8 +14356,204 @@
         </is>
       </c>
     </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:34:42+08:00</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28 至 2026-08-04</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ProxyError: HTTPSConnectionPool(host='fujian.chinatax.gov.cn', port=443): Max retries exceeded with url: /fzsswj/xxgk/gsgg/qtl/ (Caused by ProxyError('Unable to connect to proxy', OSError('Tunnel connection failed: 502...</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>本次检索未发现符合收录标准的新文书。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:37:15+08:00</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28 至 2026-08-04</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ProxyError: HTTPSConnectionPool(host='fujian.chinatax.gov.cn', port=443): Max retries exceeded with url: /fzsswj/xxgk/gsgg/qtl/ (Caused by ProxyError('Unable to connect to proxy', OSError('Tunnel connection failed: 502...</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>本次检索未发现符合收录标准的新文书。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:40:35+08:00</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28 至 2026-08-04</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ProxyError: HTTPSConnectionPool(host='fujian.chinatax.gov.cn', port=443): Max retries exceeded with url: /fzsswj/xxgk/gsgg/qtl/ (Caused by ProxyError('Unable to connect to proxy', OSError('Tunnel connection failed: 502...</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>本次检索未发现符合收录标准的新文书。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:42:34+08:00</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28 至 2026-08-04</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ProxyError: HTTPSConnectionPool(host='fujian.chinatax.gov.cn', port=443): Max retries exceeded with url: /fzsswj/xxgk/gsgg/qtl/ (Caused by ProxyError('Unable to connect to proxy', OSError('Tunnel connection failed: 502...</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>本次检索未发现符合收录标准的新文书。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M21"/>
+  <autoFilter ref="A1:M25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -793,7 +793,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>46236</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>46236</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>46238</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>46238</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>46238</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>46233</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>46234</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>46238</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>46238</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>46238</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>46229</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>46229</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>46229</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>46229</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>46229</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>46229</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>46229</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>46229</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>46229</v>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46229</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>46229</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>46229</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>46229</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>46229</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>46229</v>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>46229</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>46229</v>
       </c>
       <c r="AA32" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>46229</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>46229</v>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>46229</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>46229</v>
       </c>
       <c r="AA36" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>46229</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>46229</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>46230</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>46230</v>
       </c>
       <c r="AA40" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>46233</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>46234</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>46238</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>46229</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>46229</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>46229</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>46230</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>46230</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>46236</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>46236</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>46238</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>46238</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>46238</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>46238</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>46229</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>46229</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>46229</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>46229</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>46229</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>46229</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         <v>46229</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>46230</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>46230</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14552,8 +14552,57 @@
         </is>
       </c>
     </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:38:52+08:00</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 至 2026-08-05</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinatax.gov.cn', port=443): Max retries exceeded with url: /fzsswj/xxgk/gsgg/qtl/ (Caused by NewConnectionError("HTTPSConnection(host='fujian.chinatax.gov.cn', port=44...</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>本次检索未发现符合收录标准的新文书。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M25"/>
+  <autoFilter ref="A1:M26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -18,9 +18,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文书汇总'!$A$1:$AJ$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'完整文书'!$A$1:$AJ$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE34" s="5" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="AI34" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ34" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE35" s="5" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="AI35" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ35" s="2" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE14" s="5" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="AI14" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ14" s="2" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE15" s="5" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="AI15" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ15" s="2" t="inlineStr">
@@ -11289,7 +11289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ10"/>
+  <dimension ref="A1:AJ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11872,49 +11872,45 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CASE-f78ec1a594442165</t>
+          <t>CASE-1983d97878508732</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>DOC-fbbe4a664b14f54b</t>
+          <t>DOC-f9760895b4f08cc2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>安顺市</t>
+          <t>二连浩特市</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局</t>
+          <t>国家税务总局二连浩特市税务局</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局</t>
+          <t>国家税务总局二连浩特市税务局稽查局</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>91520423MA6DLH799Q</t>
-        </is>
-      </c>
+          <t>二连市坤益腾金属有限公司</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -11923,46 +11919,36 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>二税稽处〔2025〕1号</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
+          <t>二税稽处〔2025〕1号</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
+          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>64884.41</v>
-      </c>
+          <t>增值税</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="n"/>
       <c r="S5" s="3" t="n"/>
       <c r="T5" s="3" t="n"/>
       <c r="U5" s="3" t="n"/>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
-      <c r="W5" s="4" t="n">
-        <v>45898</v>
-      </c>
-      <c r="X5" s="4" t="n">
-        <v>46043</v>
-      </c>
+          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="n"/>
+      <c r="X5" s="4" t="n"/>
       <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n">
         <v>46229</v>
@@ -11990,15 +11976,11 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF5" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF5" s="2" t="inlineStr"/>
       <c r="AG5" s="2" t="inlineStr"/>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="AI5" s="2" t="inlineStr">
@@ -12008,103 +11990,89 @@
       </c>
       <c r="AJ5" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。 字段“主要违法事实”存在冲突:保留原值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”,新值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”未静默覆盖。</t>
+          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>CASE-f78ec1a594442165</t>
+          <t>CASE-d4b6986f3f97cd28</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>DOC-9a828a6048b54b6c</t>
+          <t>DOC-442cf3d9a5280c12</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>安顺市</t>
+          <t>鄂尔多斯市</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局安顺市税务局</t>
-        </is>
-      </c>
+      <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局</t>
+          <t>第二稽查局</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>91520423MA6DLH799Q</t>
-        </is>
-      </c>
+          <t>廖礼平</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>安市税稽罚〔2026〕1号</t>
+          <t>鄂税二稽处〔2023〕29号</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
+          <t>鄂税二稽处〔2023〕29号</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
+          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="n"/>
-      <c r="S6" s="3" t="n"/>
-      <c r="T6" s="3" t="n">
-        <v>200000</v>
-      </c>
+          <t>个人所得税、印花税</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>15072487.5</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>1046925</v>
+      </c>
+      <c r="T6" s="3" t="n"/>
       <c r="U6" s="3" t="n"/>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
-      <c r="W6" s="4" t="n">
-        <v>45898</v>
-      </c>
-      <c r="X6" s="4" t="n">
-        <v>46043</v>
-      </c>
+          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="n"/>
+      <c r="X6" s="4" t="n"/>
       <c r="Y6" s="4" t="n"/>
       <c r="Z6" s="4" t="n">
         <v>46229</v>
@@ -12132,15 +12100,11 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF6" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF6" s="2" t="inlineStr"/>
       <c r="AG6" s="2" t="inlineStr"/>
       <c r="AH6" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="AI6" s="2" t="inlineStr">
@@ -12150,51 +12114,55 @@
       </c>
       <c r="AJ6" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。</t>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CASE-1983d97878508732</t>
+          <t>CASE-7e3d4a321440d6a7</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>DOC-f9760895b4f08cc2</t>
+          <t>DOC-bed9330343ed06af</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>二连浩特市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局</t>
+          <t>国家税务总局天津市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局稽查局</t>
+          <t>国家税务总局天津市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>二连市坤益腾金属有限公司</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr"/>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>91120116300738701X</t>
+        </is>
+      </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -12203,39 +12171,45 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
+          <t>津税一稽处〔2023〕59号</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr"/>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="n"/>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>920146.9399999999</v>
+      </c>
       <c r="S7" s="3" t="n"/>
       <c r="T7" s="3" t="n"/>
       <c r="U7" s="3" t="n"/>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
         </is>
       </c>
       <c r="W7" s="4" t="n"/>
       <c r="X7" s="4" t="n"/>
       <c r="Y7" s="4" t="n"/>
       <c r="Z7" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AA7" s="4" t="n">
         <v>46239</v>
@@ -12264,7 +12238,7 @@
       <c r="AG7" s="2" t="inlineStr"/>
       <c r="AH7" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI7" s="2" t="inlineStr">
@@ -12274,92 +12248,102 @@
       </c>
       <c r="AJ7" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。</t>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CASE-d4b6986f3f97cd28</t>
+          <t>CASE-7e3d4a321440d6a7</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DOC-442cf3d9a5280c12</t>
+          <t>DOC-388bd01c01bbb789</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>鄂尔多斯市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>第二稽查局</t>
+          <t>国家税务总局天津市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>廖礼平</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr"/>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>91120116300738701X</t>
+        </is>
+      </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
+          <t>津税一稽罚〔2023〕21号</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr"/>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>个人所得税、印花税</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>15072487.5</v>
-      </c>
-      <c r="S8" s="3" t="n">
-        <v>1046925</v>
-      </c>
-      <c r="T8" s="3" t="n"/>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="n"/>
+      <c r="S8" s="3" t="n"/>
+      <c r="T8" s="3" t="n">
+        <v>131368.5</v>
+      </c>
       <c r="U8" s="3" t="n"/>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
         </is>
       </c>
       <c r="W8" s="4" t="n"/>
       <c r="X8" s="4" t="n"/>
       <c r="Y8" s="4" t="n"/>
       <c r="Z8" s="4" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="AA8" s="4" t="n">
         <v>46239</v>
@@ -12388,7 +12372,7 @@
       <c r="AG8" s="2" t="inlineStr"/>
       <c r="AH8" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI8" s="2" t="inlineStr">
@@ -12397,293 +12381,25 @@
         </is>
       </c>
       <c r="AJ8" s="2" t="inlineStr">
-        <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>CASE-7e3d4a321440d6a7</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>DOC-bed9330343ed06af</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>天津市</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>天津市</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>天津展达科技有限公司</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>91120116300738701X</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>税务处理决定书</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>920146.9399999999</v>
-      </c>
-      <c r="S9" s="3" t="n"/>
-      <c r="T9" s="3" t="n"/>
-      <c r="U9" s="3" t="n"/>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
-        </is>
-      </c>
-      <c r="W9" s="4" t="n"/>
-      <c r="X9" s="4" t="n"/>
-      <c r="Y9" s="4" t="n"/>
-      <c r="Z9" s="4" t="n">
-        <v>46230</v>
-      </c>
-      <c r="AA9" s="4" t="n">
-        <v>46239</v>
-      </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>完整文书</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD9" s="2" t="inlineStr">
-        <is>
-          <t>待核验</t>
-        </is>
-      </c>
-      <c r="AE9" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF9" s="2" t="inlineStr"/>
-      <c r="AG9" s="2" t="inlineStr"/>
-      <c r="AH9" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
-        </is>
-      </c>
-      <c r="AI9" s="2" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="AJ9" s="2" t="inlineStr">
-        <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>CASE-7e3d4a321440d6a7</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>DOC-388bd01c01bbb789</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>天津市</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>天津市</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>天津展达科技有限公司</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>91120116300738701X</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>税务行政处罚决定书</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="n"/>
-      <c r="S10" s="3" t="n"/>
-      <c r="T10" s="3" t="n">
-        <v>131368.5</v>
-      </c>
-      <c r="U10" s="3" t="n"/>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
-        </is>
-      </c>
-      <c r="W10" s="4" t="n"/>
-      <c r="X10" s="4" t="n"/>
-      <c r="Y10" s="4" t="n"/>
-      <c r="Z10" s="4" t="n">
-        <v>46230</v>
-      </c>
-      <c r="AA10" s="4" t="n">
-        <v>46239</v>
-      </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>完整文书</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD10" s="2" t="inlineStr">
-        <is>
-          <t>待核验</t>
-        </is>
-      </c>
-      <c r="AE10" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF10" s="2" t="inlineStr"/>
-      <c r="AG10" s="2" t="inlineStr"/>
-      <c r="AH10" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
-        </is>
-      </c>
-      <c r="AI10" s="2" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="AJ10" s="2" t="inlineStr">
         <is>
           <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ10"/>
-  <conditionalFormatting sqref="AD2:AD10">
+  <autoFilter ref="A1:AJ8"/>
+  <conditionalFormatting sqref="AD2:AD8">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AD2="待核验"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI2:AI10">
+  <conditionalFormatting sqref="AI2:AI8">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>AND($AI2&lt;&gt;"正常",$AI2&lt;&gt;"附件正常")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AD2:AD10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AD2:AD8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"已核验,待核验,人工复核完成"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12693,13 +12409,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF4" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE5" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF5" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE6" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF6" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE9" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -13327,7 +13039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14601,8 +14313,204 @@
         </is>
       </c>
     </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:11:39+08:00</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 至 2026-08-05</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://guangxi.chinatax.gov.cn/nanning/xxgk/swjcgg: RetryError: HTTPConnectionPool(host='127.0.0.1', port=7897): Max retries exceeded with url: http://guangxi.chinatax.gov.cn:8000/nanning/xxgk/swjcgg/ (Caused by ResponseError('too many 502 error responses'))</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>本次检索未发现符合收录标准的新文书。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:13:04+08:00</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 至 2026-08-05</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://guangxi.chinatax.gov.cn/nanning/xxgk/swjcgg: RetryError: HTTPConnectionPool(host='127.0.0.1', port=7897): Max retries exceeded with url: http://guangxi.chinatax.gov.cn:8000/nanning/xxgk/swjcgg/ (Caused by ResponseError('too many 502 error responses'))</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>本次检索未发现符合收录标准的新文书。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:18:21+08:00</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 至 2026-08-05</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/qzsswj/xxgk/sjxxgk/qtgg_23603/: HTTPError: 412 Client Error: Precondition Failed for url: https://fujian.chinatax.gov.cn/qzsswj/xxgk/sjxxgk/qtgg_23603/ | discover_official_index: https://guangxi.chinatax.gov.cn/nanning/xxgk/swjcgg: RetryErro...</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>本次检索未发现符合收录标准的新文书。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:32:30+08:00</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 至 2026-08-05</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/qzsswj/xxgk/sjxxgk/qtgg_23603/: HTTPError: 412 Client Error: Precondition Failed for url: https://fujian.chinatax.gov.cn/qzsswj/xxgk/sjxxgk/qtgg_23603/ | discover_official_index: https://guangxi.chinatax.gov.cn/nanning/xxgk/swjcgg: RetryErro...</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>本次检索未发现符合收录标准的新文书。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M26"/>
+  <autoFilter ref="A1:M30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -13039,7 +13039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14509,8 +14509,57 @@
         </is>
       </c>
     </row>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:39:25+08:00</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 至 2026-08-05</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/smsswj/xxgk/sjxxgk/qtgg/: ConnectionError: HTTPSConnectionPool(host='fujian.chinatax.gov.cn', port=443): Max retries exceeded with url: /smsswj/xxgk/sjxxgk/qtgg/ (Caused by NewConnectionError("HTTPSConnection(host='fujian.chinatax.gov.cn', p...</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>本次检索未发现符合收录标准的新文书。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M30"/>
+  <autoFilter ref="A1:M31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -13039,7 +13039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14558,8 +14558,57 @@
         </is>
       </c>
     </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:06:43+08:00</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 至 2026-08-05</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinatax.gov.cn', port=443): Max retries exceeded with url: /fzsswj/xxgk/gsgg/qtl/ (Caused by NewConnectionError("HTTPSConnection(host='fujian.chinatax.gov.cn', port=44...</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>本次检索未发现符合收录标准的新文书。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M31"/>
+  <autoFilter ref="A1:M32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -13039,7 +13039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14607,8 +14607,57 @@
         </is>
       </c>
     </row>
+    <row r="33" ht="54" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:20:19+08:00</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 至 2026-08-05</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinatax.gov.cn', port=443): Max retries exceeded with url: /fzsswj/xxgk/gsgg/qtl/ (Caused by NewConnectionError("HTTPSConnection(host='fujian.chinatax.gov.cn', port=44...</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>本次检索未发现符合收录标准的新文书。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M32"/>
+  <autoFilter ref="A1:M33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -15,12 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日运行日志" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文书汇总'!$A$1:$AJ$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'完整文书'!$A$1:$AJ$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文书汇总'!$A$1:$AJ$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'完整文书'!$A$1:$AJ$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ40"/>
+  <dimension ref="A1:AJ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -705,47 +705,47 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CASE-ef382edddd0f50f8</t>
+          <t>CASE-2799cf13d16e48fa</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>DOC-f80d567b9343411c</t>
+          <t>DOC-4a944414e51221f4</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>泉州市</t>
+          <t>北海市</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局</t>
+          <t>国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局稽查局</t>
+          <t>国家税务总局北海市税务局稽查局</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>泉州平媛贸易有限公司</t>
+          <t>北海市丰赢商贸有限公司</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>91350503597867511E</t>
+          <t>91450500MAEULQHG42</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
@@ -756,44 +756,48 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>泉税稽处〔2026〕29号</t>
+          <t>北市税稽处〔2026〕16号</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>泉税稽处〔2026〕29号</t>
+          <t>北市税稽处〔2026〕16号</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>进行了检查,违法事实及处理决定如下: 经查,2013年1月25日至2013年1月28日期间,你公司将4900万元资金贷与庄彬阳使用,你公司未就该项贷款业务申报缴纳企业所得税、营业税及附加税费。</t>
+          <t>况进行了检查,违法事实及处理决定如下: 行,无法核实你公司资金流情况,你公司存在虚开风险。 经查实,根据《国家税务总局关于纳税人虚开增值税专用发 经查实,根据《中华人民共和国城市维护建设税暂行条例》 经查实,根据《征收教育费附加的暂行规定》(国发〔1986〕 经查实,根据《广西壮族自治区人民政府关于印发广西壮 你公司所属期 2025 年 8 月未进行纳税申报,不缴或者少缴 三条第一款规定,对上述行为定性为偷税,向你公司追缴少缴的 对你公司少缴的税款从税款滞纳之日起至实际缴纳税款之日止 公司向下游企业虚开 9 份增值税电子专用发票(发票号码: 况进行了检查,违法事实及处理决定如下: 行,无法核实你公司资金流情况,你公司存在虚开风险。 经查实,根据《国家税务总局关于纳税人虚开增值税专用发 经查实,根据《中华人民共和国城市维护建设税暂行条例》 经查实,根据《征收教育费附加的暂行规定》(国发〔1986〕 经查实,根据《广西壮族自治区人民政府关于印发广西壮 你公司所属期 2025 年 8 月未进行纳税申报,不缴或者少缴 三条第一款规定,对上述行为定性为偷税,向你公司追缴少缴的 对你公司少缴的税款从税款滞纳之日起至实际缴纳税款之日止 公司向下游企业虚开 9 份增值税电子专用发票(发票号码:</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>企业所得税</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="n"/>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>512334.96</v>
+      </c>
       <c r="S2" s="3" t="n"/>
       <c r="T2" s="3" t="n"/>
       <c r="U2" s="3" t="n"/>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满30日,即视为送达。</t>
-        </is>
-      </c>
-      <c r="W2" s="4" t="n"/>
+          <t>你公司所属期2025 年 8 月应补缴增值税465759.06 元。 司所属期2025 年 8 月应补缴纳城市维护建设税32603.13 元。 公司所属期 2025 年8 月应补缴纳教育费附加 13972.77 元。 第三条的规定,你公司所属期2025 年 8 月应补缴纳地方教育附 你公司所属期2025 年 8 月应补缴增值税465759.06 元。 司所属期2025 年 8 月应补缴纳城市维护建设税32603.13 元。 公司所属期 2025 年8 月应补缴纳教育费附加 13972.77 元。 第三条的规定,你公司所属期2025 年 8 月应补缴纳地方教育附</t>
+        </is>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>46237</v>
+      </c>
       <c r="X2" s="4" t="n">
         <v>46238</v>
       </c>
       <c r="Y2" s="4" t="n"/>
       <c r="Z2" s="4" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -815,69 +819,67 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr"/>
+      <c r="AF2" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG2" s="2" t="inlineStr"/>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>关于对泉州平媛贸易有限公司《税务处理决定书》送达的公告 _
- 其他公告 _
- 国家税务总局泉州市税务局</t>
+          <t>【市稽查】国家税务总局北海市税务局稽查局税务文书送达公告(北海市丰赢商贸有限公司)_国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="AI2" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="AJ2" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
+          <t>附件正常</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CASE-119dcfa5a7c6b239</t>
+          <t>CASE-ef382edddd0f50f8</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>DOC-1a423a3cbfed9f3f</t>
+          <t>DOC-f80d567b9343411c</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>南宁市</t>
+          <t>泉州市</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第三稽查局</t>
+          <t>国家税务总局泉州市税务局</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第三稽查局</t>
+          <t>国家税务总局泉州市税务局稽查局</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>广西威曼能源科技有限公司</t>
+          <t>泉州平媛贸易有限公司</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>91450103MA5NJYGEXM</t>
+          <t>91350503597867511E</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
@@ -888,40 +890,48 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽处〔2026〕19号</t>
+          <t>泉税稽处〔2026〕29号</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽处〔2026〕19号</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>南市税三稽罚〔2026〕10号</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
+          <t>泉税稽处〔2026〕29号</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>进行了检查,违法事实及处理决定如下: 经查,2013年1月25日至2013年1月28日期间,你公司将4900万元资金贷与庄彬阳使用,你公司未就该项贷款业务申报缴纳企业所得税、营业税及附加税费。</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>企业所得税</t>
+        </is>
+      </c>
       <c r="R3" s="3" t="n"/>
       <c r="S3" s="3" t="n"/>
       <c r="T3" s="3" t="n"/>
       <c r="U3" s="3" t="n"/>
-      <c r="V3" s="2" t="inlineStr"/>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满30日,即视为送达。</t>
+        </is>
+      </c>
       <c r="W3" s="4" t="n"/>
       <c r="X3" s="4" t="n">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="Y3" s="4" t="n"/>
       <c r="Z3" s="4" t="n">
-        <v>46236</v>
+        <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -939,20 +949,18 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF3" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF3" s="2" t="inlineStr"/>
       <c r="AG3" s="2" t="inlineStr"/>
       <c r="AH3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第三稽查局 税务文书送达公告_国家税务总局南宁市税务局</t>
+          <t>关于对泉州平媛贸易有限公司《税务处理决定书》送达的公告 _
+ 其他公告 _
+ 国家税务总局泉州市税务局</t>
         </is>
       </c>
       <c r="AI3" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ3" s="2" t="inlineStr">
@@ -963,7 +971,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -972,7 +980,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>DOC-f8499a65abd851d8</t>
+          <t>DOC-1a423a3cbfed9f3f</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1009,12 +1017,12 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽罚〔2026〕10号</t>
+          <t>南市税三稽处〔2026〕19号</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1043,7 +1051,7 @@
         <v>46236</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1089,16 +1097,16 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CASE-c48b4ac9b3677385</t>
+          <t>CASE-119dcfa5a7c6b239</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>DOC-d3324d06254a350f</t>
+          <t>DOC-f8499a65abd851d8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1124,33 +1132,33 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>广西松柏建筑装饰设计有限公司</t>
+          <t>广西威曼能源科技有限公司</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>91450108MA5P1DL467</t>
+          <t>91450103MA5NJYGEXM</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽处〔2026〕18号</t>
+          <t>南市税三稽罚〔2026〕10号</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽处〔2026〕18号</t>
+          <t>南市税三稽处〔2026〕19号</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽罚〔2026〕9号</t>
+          <t>南市税三稽罚〔2026〕10号</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr"/>
@@ -1166,10 +1174,10 @@
       </c>
       <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n">
-        <v>46238</v>
+        <v>46236</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1215,7 +1223,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -1224,7 +1232,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>DOC-c40aad0bbe60707b</t>
+          <t>DOC-d3324d06254a350f</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1261,12 +1269,12 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽罚〔2026〕9号</t>
+          <t>南市税三稽处〔2026〕18号</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1295,7 +1303,7 @@
         <v>46238</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1341,47 +1349,47 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CASE-f7f5d80ec431a14d</t>
+          <t>CASE-c48b4ac9b3677385</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>DOC-3a61d3452c421a37</t>
+          <t>DOC-c40aad0bbe60707b</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>福州市</t>
+          <t>南宁市</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局南宁市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局南宁市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>福州吉伦多德贸易有限公司</t>
+          <t>广西松柏建筑装饰设计有限公司</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>91350102MA33G4RD13</t>
+          <t>91450108MA5P1DL467</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
@@ -1392,25 +1400,21 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽罚〔2026〕39号</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>南市税三稽罚〔2026〕9号</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>南市税三稽处〔2026〕18号</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽罚〔2026〕39号</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>经我局于2022年5月20日起对你公司[地址:福建省福州市鼓楼区温泉街道东城边街39号(原东城边街东侧与温泉支路交叉处)恒宇国际2#楼5层10商务办公-1]2019年1月1日至2022年12月31日期间的涉税情况进行检查,你公司存在违法事实及处罚决定如下: 你公司假报出口骗取国家出口退税款4064566.77元。 你公司取得的已证实虚开发票、出口退税数据、报关单证资料比对结果等证据。</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>增值税、企业所得税、消费税</t>
-        </is>
-      </c>
+          <t>南市税三稽罚〔2026〕9号</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
       <c r="R7" s="3" t="n"/>
       <c r="S7" s="3" t="n"/>
       <c r="T7" s="3" t="n"/>
@@ -1425,11 +1429,11 @@
         <v>46238</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1447,18 +1451,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AF7" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG7" s="2" t="inlineStr"/>
       <c r="AH7" s="2" t="inlineStr">
         <is>
-          <t>关于送达福州吉伦多德贸易有限公司《税务行政处罚决定书》的公告 _
- 其他类 _
- 国家税务总局福州市税务局</t>
+          <t>国家税务总局南宁市税务局第三稽查局 税务文书送达公告_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI7" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr">
@@ -1469,93 +1475,91 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CASE-89fc66bfc8dad80d</t>
+          <t>CASE-f7f5d80ec431a14d</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DOC-6e5b966cd65a4366</t>
+          <t>DOC-3a61d3452c421a37</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>北海市</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>银海区</t>
-        </is>
-      </c>
+          <t>福州市</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局北海市税务局</t>
+          <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局北海市税务局稽查局</t>
+          <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>广西耿仁建材有限公司</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr"/>
+          <t>福州吉伦多德贸易有限公司</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>91350102MA33G4RD13</t>
+        </is>
+      </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>北市税稽处〔2026〕14号</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>北市税稽处〔2026〕14号</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr"/>
+          <t>榕税一稽罚〔2026〕39号</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>榕税一稽罚〔2026〕39号</t>
+        </is>
+      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>我局于2026年2月11日至2026年7月15日对你公司(地址:北海市银海区新世纪大道15号辰宸花园3幢二单元0901号)2026年1月1日至2026年1月31日期间的涉税情况进行了检查,违法事实及处理决定如下: (2)短时间开具大量大额发票且未申报 你公司未进行纳税申报,不缴或者少缴2026年1月增值税194612.47元,2026年1月城市维护建设税13622.87元,合计208235.34元。 根据《中华人民共和国税收征收管理法》第六十三条第一款规定,对上述行为定性为偷税,向你公司追缴少缴的2026年增值税194612.47元,城市维护建设税13622.87元,合计208235.34元。 1.根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)的规定,对你公司少缴所属期2026年1月的教育费附加5838.37元,予以追缴。 2.根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条的规定,对你公司少缴所属期2026年1月地方教育附加3892.25元,予以追缴。 根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司少缴的税款从税款滞纳之日起至实际缴纳税款之日止按日加收滞纳税款万分之五的滞纳金,滞纳金由金三系统自动计算加收。 (四)你公司无法联系且实地核查无实际生产地址、无生产能力、查无下落,短期开票金额大,无法核实资金流,未进行纳税申报,根据《国家税务总局关于走逃(失联)企业开具增值税专用发票认定处理有关问题的公告》(国家税务总局公告2016年第76号),将你公司按走逃(失联)处理,根据《中华人民共和国发票管理办法》(国函〔1993〕174号)第二十一条第(一)项,你公司无生产能力,却为他人开具与实际经营业务情况不符的发票,属于虚开发票的行为。</t>
+          <t>经我局于2022年5月20日起对你公司[地址:福建省福州市鼓楼区温泉街道东城边街39号(原东城边街东侧与温泉支路交叉处)恒宇国际2#楼5层10商务办公-1]2019年1月1日至2022年12月31日期间的涉税情况进行检查,你公司存在违法事实及处罚决定如下: 你公司假报出口骗取国家出口退税款4064566.77元。 你公司取得的已证实虚开发票、出口退税数据、报关单证资料比对结果等证据。</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>208235.34</v>
-      </c>
+          <t>增值税、企业所得税、消费税</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="n"/>
       <c r="S8" s="3" t="n"/>
       <c r="T8" s="3" t="n"/>
       <c r="U8" s="3" t="n"/>
       <c r="V8" s="2" t="inlineStr"/>
       <c r="W8" s="4" t="n"/>
       <c r="X8" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="Y8" s="4" t="n"/>
       <c r="Z8" s="4" t="n">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1581,7 +1585,9 @@
       <c r="AG8" s="2" t="inlineStr"/>
       <c r="AH8" s="2" t="inlineStr">
         <is>
-          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕14号)_国家税务总局北海市税务局</t>
+          <t>关于送达福州吉伦多德贸易有限公司《税务行政处罚决定书》的公告 _
+ 其他类 _
+ 国家税务总局福州市税务局</t>
         </is>
       </c>
       <c r="AI8" s="2" t="inlineStr">
@@ -1597,16 +1603,16 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>CASE-eb9cfd5295d501e5</t>
+          <t>CASE-89fc66bfc8dad80d</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DOC-4a8cf53b445afc63</t>
+          <t>DOC-6e5b966cd65a4366</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1621,7 +1627,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>海城区</t>
+          <t>银海区</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1636,14 +1642,10 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>广西轩易科技有限公司</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>91450500MAK3N9UJ2T</t>
-        </is>
-      </c>
+          <t>广西耿仁建材有限公司</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
@@ -1652,18 +1654,18 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>北市税稽处〔2026〕6号</t>
+          <t>北市税稽处〔2026〕14号</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>北市税稽处〔2026〕6号</t>
+          <t>北市税稽处〔2026〕14号</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>我局于2026年1月23日起对你公司(地址:北海市海城区北部湾东路“金宝小区”B幢B804号20北海汇算账商务秘书有限公司托管)2025年12月11日至2025年12月31日期间的涉税情况进行了检查,发现你公司存在税收违法行为,原《税务处理决定书》(北市税稽处〔2026〕6号)认定的违法事实有误,经重新调查核实,违法事实及处理决定如下: 经查询,你公司2026年1月20日通过网络方式零申报所属期2025年10月1日-2025年12月31日的增值税、城市维护建设税及附加,入库税款0元,申报金额与实际不符,存在虚假申报的情况。 你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 (一)根据《中华人民共和国发票管理办法》(财政部令第6号发布,经国务院令第587号、第709号、第764号修订)第二十一条第二款第(一)项的规定,认定你公司为他人开具与实际经营业务情况不符的前述13份增值税普通电子发票为虚开发票(金额合计571550.49元,税额合计5715.51元,价税合计577266.00元)。 根据《中华人民共和国税收征收管理法》第三十二条、第六十三条第一款、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,已构成偷税,向你公司追缴少缴的税款合计5915.56元,并从滞纳税款之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
+          <t>我局于2026年2月11日至2026年7月15日对你公司(地址:北海市银海区新世纪大道15号辰宸花园3幢二单元0901号)2026年1月1日至2026年1月31日期间的涉税情况进行了检查,违法事实及处理决定如下: (2)短时间开具大量大额发票且未申报 你公司未进行纳税申报,不缴或者少缴2026年1月增值税194612.47元,2026年1月城市维护建设税13622.87元,合计208235.34元。 根据《中华人民共和国税收征收管理法》第六十三条第一款规定,对上述行为定性为偷税,向你公司追缴少缴的2026年增值税194612.47元,城市维护建设税13622.87元,合计208235.34元。 1.根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)的规定,对你公司少缴所属期2026年1月的教育费附加5838.37元,予以追缴。 2.根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条的规定,对你公司少缴所属期2026年1月地方教育附加3892.25元,予以追缴。 根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司少缴的税款从税款滞纳之日起至实际缴纳税款之日止按日加收滞纳税款万分之五的滞纳金,滞纳金由金三系统自动计算加收。 (四)你公司无法联系且实地核查无实际生产地址、无生产能力、查无下落,短期开票金额大,无法核实资金流,未进行纳税申报,根据《国家税务总局关于走逃(失联)企业开具增值税专用发票认定处理有关问题的公告》(国家税务总局公告2016年第76号),将你公司按走逃(失联)处理,根据《中华人民共和国发票管理办法》(国函〔1993〕174号)第二十一条第(一)项,你公司无生产能力,却为他人开具与实际经营业务情况不符的发票,属于虚开发票的行为。</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1672,26 +1674,22 @@
         </is>
       </c>
       <c r="R9" s="3" t="n">
-        <v>6058.46</v>
+        <v>208235.34</v>
       </c>
       <c r="S9" s="3" t="n"/>
       <c r="T9" s="3" t="n"/>
       <c r="U9" s="3" t="n"/>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《中华人民共和国城市维护建设税法》(中华人民共和国主席令第五十一号)第一条、第二条、第四条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×7%×50%=200.05元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)、《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×3%×50%=85.74元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳地方教育附加5715.51×2%×50%=57.16元。</t>
-        </is>
-      </c>
+      <c r="V9" s="2" t="inlineStr"/>
       <c r="W9" s="4" t="n"/>
       <c r="X9" s="4" t="n">
         <v>46232</v>
       </c>
       <c r="Y9" s="4" t="n"/>
       <c r="Z9" s="4" t="n">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1717,7 +1715,7 @@
       <c r="AG9" s="2" t="inlineStr"/>
       <c r="AH9" s="2" t="inlineStr">
         <is>
-          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕13号)_国家税务总局北海市税务局</t>
+          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕14号)_国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="AI9" s="2" t="inlineStr">
@@ -1727,22 +1725,22 @@
       </c>
       <c r="AJ9" s="2" t="inlineStr">
         <is>
-          <t>字段“决定书文号”存在冲突:保留原值“北市税稽处〔2026〕6号”,新值“北市税稽处〔2026〕13号”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CASE-6e854d911c44fb48</t>
+          <t>CASE-eb9cfd5295d501e5</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DOC-4bf991cc37f1a595</t>
+          <t>DOC-4a8cf53b445afc63</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1752,28 +1750,32 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>南宁市</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
+          <t>北海市</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>海城区</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第四稽查局</t>
+          <t>国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第四稽查局</t>
+          <t>国家税务总局北海市税务局稽查局</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>南宁敏顺睿商务服务有限公司</t>
+          <t>广西轩易科技有限公司</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>91450128MAA79KD08F</t>
+          <t>91450500MAK3N9UJ2T</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
@@ -1784,36 +1786,50 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>南市税四稽处〔2025〕4号</t>
+          <t>北市税稽处〔2026〕6号</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>南市税四稽处〔2025〕4号</t>
+          <t>北市税稽处〔2026〕6号</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="3" t="n"/>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>我局于2026年1月23日起对你公司(地址:北海市海城区北部湾东路“金宝小区”B幢B804号20北海汇算账商务秘书有限公司托管)2025年12月11日至2025年12月31日期间的涉税情况进行了检查,发现你公司存在税收违法行为,原《税务处理决定书》(北市税稽处〔2026〕6号)认定的违法事实有误,经重新调查核实,违法事实及处理决定如下: 经查询,你公司2026年1月20日通过网络方式零申报所属期2025年10月1日-2025年12月31日的增值税、城市维护建设税及附加,入库税款0元,申报金额与实际不符,存在虚假申报的情况。 你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 (一)根据《中华人民共和国发票管理办法》(财政部令第6号发布,经国务院令第587号、第709号、第764号修订)第二十一条第二款第(一)项的规定,认定你公司为他人开具与实际经营业务情况不符的前述13份增值税普通电子发票为虚开发票(金额合计571550.49元,税额合计5715.51元,价税合计577266.00元)。 根据《中华人民共和国税收征收管理法》第三十二条、第六十三条第一款、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,已构成偷税,向你公司追缴少缴的税款合计5915.56元,并从滞纳税款之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>6058.46</v>
+      </c>
       <c r="S10" s="3" t="n"/>
       <c r="T10" s="3" t="n"/>
       <c r="U10" s="3" t="n"/>
-      <c r="V10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《中华人民共和国城市维护建设税法》(中华人民共和国主席令第五十一号)第一条、第二条、第四条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×7%×50%=200.05元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)、《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×3%×50%=85.74元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳地方教育附加5715.51×2%×50%=57.16元。</t>
+        </is>
+      </c>
       <c r="W10" s="4" t="n"/>
       <c r="X10" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="Y10" s="4" t="n"/>
       <c r="Z10" s="4" t="n">
-        <v>46238</v>
+        <v>46234</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1823,7 +1839,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE10" s="5" t="inlineStr">
@@ -1835,32 +1851,32 @@
       <c r="AG10" s="2" t="inlineStr"/>
       <c r="AH10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第四稽查局公告更正告知书(南宁敏顺睿商务服务有限公司)_国家税务总局南宁市税务局</t>
+          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕13号)_国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="AI10" s="2" t="inlineStr">
         <is>
-          <t>内容不匹配</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ10" s="2" t="inlineStr">
         <is>
-          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>字段“决定书文号”存在冲突:保留原值“北市税稽处〔2026〕6号”,新值“北市税稽处〔2026〕13号”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>CASE-85fda8617056d119</t>
+          <t>CASE-6e854d911c44fb48</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>DOC-9057f0b6746c97de</t>
+          <t>DOC-4bf991cc37f1a595</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1897,20 +1913,20 @@
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>南市税四稽罚〔2026〕4号</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>南市税四稽罚〔2026〕4号</t>
-        </is>
-      </c>
+          <t>南市税四稽处〔2025〕4号</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>南市税四稽处〔2025〕4号</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
       <c r="R11" s="3" t="n"/>
@@ -1927,7 +1943,7 @@
         <v>46238</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -1969,91 +1985,73 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CASE-97651030667b6c98</t>
+          <t>CASE-85fda8617056d119</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>DOC-f9817c8cadf0fc74</t>
+          <t>DOC-9057f0b6746c97de</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>福州市</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>仓山区</t>
-        </is>
-      </c>
+          <t>南宁市</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局南宁市税务局第四稽查局</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局南宁市税务局第四稽查局</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>福州盛广弘贸易有限公司</t>
+          <t>南宁敏顺睿商务服务有限公司</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>91350104MA34D5PT77</t>
+          <t>91450128MAA79KD08F</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽处〔2025〕233号</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>榕税一稽处〔2025〕233号</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>我局于2023年12月25日起对你公司(地址:福建省福州市仓山区信平路6号二层41室)2022年1月1日至2023年11月30日期间的涉税情况进行检查,违法事实及处理决定如下: (二)你公司于2022年至2023年取得新余伟宏服装有限公司已证实虚开的254份正常状态增值税专用发票(金额合计24261915.72元,税额合计3154049.38元,价税合计27415965.10元)用于出口退税,通过假报出口或者其他欺骗手段骗取国家出口退税款3154049.14元。 (三)你公司于2022年至2023年取得宜春润悟服饰有限公司已证实虚开的220份正常状态增值税专用发票(金额合计20853824.88元,税额合计2710997.42元,价税合计23564822.30元),上述发票你公司均用于申报出口退税,取得已退税额2710997.41元。 (一)根据《中华人民共和国税收征收管理法》第六十六条规定,认定你公司取得新余伟宏服装有限公司已证实虚开的增值税专用发票254份(金额合计24261915.72元,税额合计3154049.38元,价税合计27415965.10元,取得退税款3154049.14元)并用于出口退税的属于骗取国家出口退税。 追缴你公司骗取的出口退税款3154049.14元,具体明细如下(单位:元): (二)根据《财政部 国家税务总局关于出口货物劳务增值税和消费税政策的通知》(财税〔2012〕39号)第七条第(一)项第5目、第九条第(二)项第5目、《国家税务总局关于&lt;出口货物劳务增值税和消费税管理办法&gt;有关问题的公告》(国家税务总局公告2013年第12号)第五条第(九)项第1目规定,你公司取得宜春润悟服饰有限公司已证实虚开的220份增值税专用发票(金额合计20853824.88元,税额合计2710997.42元,价税合计23564822.30元),申报出口退税并取得退税款2710997.41元,适用增值税征税政策,追缴已退税款2710997.41元,具体明细如下(单位:元):</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="n">
-        <v>2710997.41</v>
-      </c>
+          <t>南市税四稽罚〔2026〕4号</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>南市税四稽罚〔2026〕4号</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="3" t="n"/>
       <c r="S12" s="3" t="n"/>
       <c r="T12" s="3" t="n"/>
       <c r="U12" s="3" t="n"/>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《征收教育费附加的暂行规定》第二条、第三条、《福建省人民政府关于调整地方教育附加征收标准有关问题的通知》(闽政文〔2011〕230号)第一条、第二条、《财政部 税务总局关于进一步实施小微企业“六税两费”减免政策的公告》(财政部 税务总局公告2022年第10号)第一条规定,你公司应补缴相应属期城市维护建设税合计83631.38元、教育费附加合计35842.03元、地方教育附加合计23894.68元,具体明细如下(单位:元):</t>
-        </is>
-      </c>
+      <c r="V12" s="2" t="inlineStr"/>
       <c r="W12" s="4" t="n"/>
       <c r="X12" s="4" t="n">
         <v>46231</v>
@@ -2063,11 +2061,11 @@
         <v>46238</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2077,7 +2075,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE12" s="5" t="inlineStr">
@@ -2089,133 +2087,147 @@
       <c r="AG12" s="2" t="inlineStr"/>
       <c r="AH12" s="2" t="inlineStr">
         <is>
+          <t>国家税务总局南宁市税务局第四稽查局公告更正告知书(南宁敏顺睿商务服务有限公司)_国家税务总局南宁市税务局</t>
+        </is>
+      </c>
+      <c r="AI12" s="2" t="inlineStr">
+        <is>
+          <t>内容不匹配</t>
+        </is>
+      </c>
+      <c r="AJ12" s="2" t="inlineStr">
+        <is>
+          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>CASE-97651030667b6c98</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>DOC-f9817c8cadf0fc74</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>福建省</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>福州市</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>仓山区</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局福州市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局福州市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>福州盛广弘贸易有限公司</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>91350104MA34D5PT77</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>榕税一稽处〔2025〕233号</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>榕税一稽处〔2025〕233号</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>我局于2023年12月25日起对你公司(地址:福建省福州市仓山区信平路6号二层41室)2022年1月1日至2023年11月30日期间的涉税情况进行检查,违法事实及处理决定如下: (二)你公司于2022年至2023年取得新余伟宏服装有限公司已证实虚开的254份正常状态增值税专用发票(金额合计24261915.72元,税额合计3154049.38元,价税合计27415965.10元)用于出口退税,通过假报出口或者其他欺骗手段骗取国家出口退税款3154049.14元。 (三)你公司于2022年至2023年取得宜春润悟服饰有限公司已证实虚开的220份正常状态增值税专用发票(金额合计20853824.88元,税额合计2710997.42元,价税合计23564822.30元),上述发票你公司均用于申报出口退税,取得已退税额2710997.41元。 (一)根据《中华人民共和国税收征收管理法》第六十六条规定,认定你公司取得新余伟宏服装有限公司已证实虚开的增值税专用发票254份(金额合计24261915.72元,税额合计3154049.38元,价税合计27415965.10元,取得退税款3154049.14元)并用于出口退税的属于骗取国家出口退税。 追缴你公司骗取的出口退税款3154049.14元,具体明细如下(单位:元): (二)根据《财政部 国家税务总局关于出口货物劳务增值税和消费税政策的通知》(财税〔2012〕39号)第七条第(一)项第5目、第九条第(二)项第5目、《国家税务总局关于&lt;出口货物劳务增值税和消费税管理办法&gt;有关问题的公告》(国家税务总局公告2013年第12号)第五条第(九)项第1目规定,你公司取得宜春润悟服饰有限公司已证实虚开的220份增值税专用发票(金额合计20853824.88元,税额合计2710997.42元,价税合计23564822.30元),申报出口退税并取得退税款2710997.41元,适用增值税征税政策,追缴已退税款2710997.41元,具体明细如下(单位:元):</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>2710997.41</v>
+      </c>
+      <c r="S13" s="3" t="n"/>
+      <c r="T13" s="3" t="n"/>
+      <c r="U13" s="3" t="n"/>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《征收教育费附加的暂行规定》第二条、第三条、《福建省人民政府关于调整地方教育附加征收标准有关问题的通知》(闽政文〔2011〕230号)第一条、第二条、《财政部 税务总局关于进一步实施小微企业“六税两费”减免政策的公告》(财政部 税务总局公告2022年第10号)第一条规定,你公司应补缴相应属期城市维护建设税合计83631.38元、教育费附加合计35842.03元、地方教育附加合计23894.68元,具体明细如下(单位:元):</t>
+        </is>
+      </c>
+      <c r="W13" s="4" t="n"/>
+      <c r="X13" s="4" t="n">
+        <v>46231</v>
+      </c>
+      <c r="Y13" s="4" t="n"/>
+      <c r="Z13" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="AA13" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD13" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AE13" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr">
+        <is>
           <t>关于送达福州盛广弘贸易有限公司《税务处理决定书》的公告 _
  其他类 _
  国家税务总局福州市税务局</t>
         </is>
       </c>
-      <c r="AI12" s="2" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="AJ12" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>CASE-3e050a699b29b0d0</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>DOC-96a3089a0e2b37cd</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>河南省</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>平顶山市</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局平顶山市税务局第一稽查局</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局平顶山市税务局第一稽查局</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>汝州泰隆实业有限公司</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>91410482MA40K4KA3B</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>税务处理决定书</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>平税稽一局处〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>平税稽一局处〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>增值税、个人所得税</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="n"/>
-      <c r="S13" s="3" t="n"/>
-      <c r="T13" s="3" t="n"/>
-      <c r="U13" s="3" t="n"/>
-      <c r="V13" s="2" t="inlineStr"/>
-      <c r="W13" s="4" t="n"/>
-      <c r="X13" s="4" t="n">
-        <v>46227</v>
-      </c>
-      <c r="Y13" s="4" t="n"/>
-      <c r="Z13" s="4" t="n">
-        <v>46229</v>
-      </c>
-      <c r="AA13" s="4" t="n">
-        <v>46239</v>
-      </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>仅公告送达/仅文号线索</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD13" s="2" t="inlineStr">
-        <is>
-          <t>已核验</t>
-        </is>
-      </c>
-      <c r="AE13" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF13" s="2" t="inlineStr"/>
-      <c r="AG13" s="2" t="inlineStr"/>
-      <c r="AH13" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局平顶山市税务局第一稽查局关于送达汝州泰隆实业有限公司《税务处理决定书》的公告 - 国家税务总局平顶山市税务局</t>
-        </is>
-      </c>
       <c r="AI13" s="2" t="inlineStr">
         <is>
           <t>正常</t>
@@ -2229,47 +2241,47 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASE-365e8a924cf64611</t>
+          <t>CASE-3e050a699b29b0d0</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DOC-4d14eba16f9aa8a0</t>
+          <t>DOC-96a3089a0e2b37cd</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>平顶山市</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局平顶山市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局平顶山市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>贵州博泰工贸有限公司</t>
+          <t>汝州泰隆实业有限公司</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>91520115587255589F</t>
+          <t>91410482MA40K4KA3B</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
@@ -2280,17 +2292,21 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕38号</t>
+          <t>平税稽一局处〔2026〕1号</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕38号</t>
+          <t>平税稽一局处〔2026〕1号</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>增值税、个人所得税</t>
+        </is>
+      </c>
       <c r="R14" s="3" t="n"/>
       <c r="S14" s="3" t="n"/>
       <c r="T14" s="3" t="n"/>
@@ -2298,14 +2314,14 @@
       <c r="V14" s="2" t="inlineStr"/>
       <c r="W14" s="4" t="n"/>
       <c r="X14" s="4" t="n">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="Y14" s="4" t="n"/>
       <c r="Z14" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -2331,7 +2347,7 @@
       <c r="AG14" s="2" t="inlineStr"/>
       <c r="AH14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书、税务行政处罚决定书的公告</t>
+          <t>国家税务总局平顶山市税务局第一稽查局关于送达汝州泰隆实业有限公司《税务处理决定书》的公告 - 国家税务总局平顶山市税务局</t>
         </is>
       </c>
       <c r="AI14" s="2" t="inlineStr">
@@ -2347,47 +2363,47 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CASE-7b9a26f2ac401107</t>
+          <t>CASE-365e8a924cf64611</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>DOC-f6c6ea472b2ca04a</t>
+          <t>DOC-4d14eba16f9aa8a0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>三明市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局三明市税务局第一稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局三明市税务局第一稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>三明众祥房地产开发有限公司</t>
+          <t>贵州博泰工贸有限公司</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>91350400678473231W</t>
+          <t>91520115587255589F</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
@@ -2398,50 +2414,36 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>明税一稽处〔2026〕20号</t>
+          <t>筑税三稽处〔2026〕38号</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>明税一稽处〔2026〕20号</t>
+          <t>筑税三稽处〔2026〕38号</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2016年期间,在没有真实业务情况下,取得重庆市博海建设工程(集团)有限公司、福建九九建设有限公司三明分公司开具的不符合规定的发票,发票金额400252379元,在企业所得税税前扣除,造成少缴纳企业所得税100063094.75元,该行为违反《中华人民共和国税收征收管理法》(2015年4月24日主席令第二十三号修改)第六十三条第一款 纳税人伪造、变造、隐匿、擅自销毁账簿、记账凭证,或者在账簿上多列支出或者不列、少列收入,或者经税务机关通知申报而拒不申报或者进行虚假的纳税申报,不缴或者少缴应纳税款的,是偷税。 对纳税人偷税的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款; 之规定,对你公司在账上多列支出,造成少缴企业所得税100063094.75元的行为认定为偷税。 之规定,对你公司少缴的企业所得税从滞纳之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>企业所得税</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="n">
-        <v>100063094.75</v>
-      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="3" t="n"/>
       <c r="S15" s="3" t="n"/>
       <c r="T15" s="3" t="n"/>
       <c r="U15" s="3" t="n"/>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>据《中华人民共和国税收征收管理法实施细则》第106条规定,将该文书予以公告送达,自公告之日起满30日视为送达。</t>
-        </is>
-      </c>
+      <c r="V15" s="2" t="inlineStr"/>
       <c r="W15" s="4" t="n"/>
       <c r="X15" s="4" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="Y15" s="4" t="n"/>
       <c r="Z15" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2463,9 +2465,7 @@
       <c r="AG15" s="2" t="inlineStr"/>
       <c r="AH15" s="2" t="inlineStr">
         <is>
-          <t>关于送达三明众祥房地产开发有限公司 《税务处理决定书》的公告 _
- 其他公告 _
- 国家税务总局三明市税务局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书、税务行政处罚决定书的公告</t>
         </is>
       </c>
       <c r="AI15" s="2" t="inlineStr">
@@ -2481,16 +2481,16 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CASE-31e4a827dfd253f2</t>
+          <t>CASE-7b9a26f2ac401107</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>DOC-3ec54358fce2350d</t>
+          <t>DOC-f6c6ea472b2ca04a</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2500,28 +2500,28 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>福州市</t>
+          <t>三明市</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局三明市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局三明市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>福州顺路汽车运输有限公司</t>
+          <t>三明众祥房地产开发有限公司</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>91350102MA31MF6611</t>
+          <t>91350400678473231W</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
@@ -2532,46 +2532,46 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽处〔2026〕137号</t>
+          <t>明税一稽处〔2026〕20号</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽处〔2026〕137号</t>
+          <t>明税一稽处〔2026〕20号</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>我局于2025年7月10日起对你公司(地址:福建省闽侯县青口镇祥宏南路922号)2023年1月1日至2024年12月31日期间的发票涉税情况进行检查,违法事实及处理决定如下: (二)你公司取得毕节七星关区辰楚汽车服务部(个人独资)、毕节七星关锦悦汽车服务部(个人独资)、贵州杨亭汽车销售有限公司、贵州楠鑫汽车销售有限公司已证实虚开的35份机动车发票。 (二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 (三)根据《中华人民共和国企业所得税法》第五条、第八条、《企业所得税税前扣除凭证管理办法》(国家税务总局公告2018年第28号发布)第四条、第十二条的规定,你公司取得上述虚开的发票不得作为税前扣除凭证。</t>
+          <t>情况进行了检查,违法事实及处理决定如下: 2016年期间,在没有真实业务情况下,取得重庆市博海建设工程(集团)有限公司、福建九九建设有限公司三明分公司开具的不符合规定的发票,发票金额400252379元,在企业所得税税前扣除,造成少缴纳企业所得税100063094.75元,该行为违反《中华人民共和国税收征收管理法》(2015年4月24日主席令第二十三号修改)第六十三条第一款 纳税人伪造、变造、隐匿、擅自销毁账簿、记账凭证,或者在账簿上多列支出或者不列、少列收入,或者经税务机关通知申报而拒不申报或者进行虚假的纳税申报,不缴或者少缴应纳税款的,是偷税。 对纳税人偷税的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款; 之规定,对你公司在账上多列支出,造成少缴企业所得税100063094.75元的行为认定为偷税。 之规定,对你公司少缴的企业所得税从滞纳之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
+          <t>企业所得税</t>
         </is>
       </c>
       <c r="R16" s="3" t="n">
-        <v>3778.22</v>
+        <v>100063094.75</v>
       </c>
       <c r="S16" s="3" t="n"/>
       <c r="T16" s="3" t="n"/>
       <c r="U16" s="3" t="n"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>(二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期城市维护建设税124.75元。 根据《征收教育费附加的暂行规定》第二条、第三条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期教育费附加53.47元。 根据《福建省人民政府关于调整地方教育附加征收标准等有关问题的通知》(闽政文〔2011〕230号)第一条、第二条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期地方教育附加35.64元。</t>
+          <t>据《中华人民共和国税收征收管理法实施细则》第106条规定,将该文书予以公告送达,自公告之日起满30日视为送达。</t>
         </is>
       </c>
       <c r="W16" s="4" t="n"/>
       <c r="X16" s="4" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="Y16" s="4" t="n"/>
       <c r="Z16" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -2597,140 +2597,148 @@
       <c r="AG16" s="2" t="inlineStr"/>
       <c r="AH16" s="2" t="inlineStr">
         <is>
+          <t>关于送达三明众祥房地产开发有限公司 《税务处理决定书》的公告 _
+ 其他公告 _
+ 国家税务总局三明市税务局</t>
+        </is>
+      </c>
+      <c r="AI16" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ16" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>CASE-31e4a827dfd253f2</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>DOC-3ec54358fce2350d</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>福建省</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>福州市</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局福州市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局福州市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>福州顺路汽车运输有限公司</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>91350102MA31MF6611</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>榕税一稽处〔2026〕137号</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>榕税一稽处〔2026〕137号</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>我局于2025年7月10日起对你公司(地址:福建省闽侯县青口镇祥宏南路922号)2023年1月1日至2024年12月31日期间的发票涉税情况进行检查,违法事实及处理决定如下: (二)你公司取得毕节七星关区辰楚汽车服务部(个人独资)、毕节七星关锦悦汽车服务部(个人独资)、贵州杨亭汽车销售有限公司、贵州楠鑫汽车销售有限公司已证实虚开的35份机动车发票。 (二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 (三)根据《中华人民共和国企业所得税法》第五条、第八条、《企业所得税税前扣除凭证管理办法》(国家税务总局公告2018年第28号发布)第四条、第十二条的规定,你公司取得上述虚开的发票不得作为税前扣除凭证。</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>3778.22</v>
+      </c>
+      <c r="S17" s="3" t="n"/>
+      <c r="T17" s="3" t="n"/>
+      <c r="U17" s="3" t="n"/>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>(二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期城市维护建设税124.75元。 根据《征收教育费附加的暂行规定》第二条、第三条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期教育费附加53.47元。 根据《福建省人民政府关于调整地方教育附加征收标准等有关问题的通知》(闽政文〔2011〕230号)第一条、第二条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期地方教育附加35.64元。</t>
+        </is>
+      </c>
+      <c r="W17" s="4" t="n"/>
+      <c r="X17" s="4" t="n">
+        <v>46218</v>
+      </c>
+      <c r="Y17" s="4" t="n"/>
+      <c r="Z17" s="4" t="n">
+        <v>46229</v>
+      </c>
+      <c r="AA17" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD17" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AE17" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr">
+        <is>
           <t>关于送达福州顺路汽车运输有限公司《税务处理决定书》的公告 _
  其他类 _
  国家税务总局福州市税务局</t>
         </is>
       </c>
-      <c r="AI16" s="2" t="inlineStr">
+      <c r="AI17" s="2" t="inlineStr">
         <is>
           <t>正常</t>
-        </is>
-      </c>
-      <c r="AJ16" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>CASE-089a3b9692e76ac4</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>DOC-d21cdc5988b1e304</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>江苏省</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>淮安市</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局江苏省税务局</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局淮安市税务局稽查局</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>淮安市百亦金商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>91320804MA1WEH7Y3U</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>税务处理决定书</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽处〔2026〕26号</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽处〔2026〕26号</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽罚〔2026〕6号</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="3" t="n"/>
-      <c r="S17" s="3" t="n"/>
-      <c r="T17" s="3" t="n"/>
-      <c r="U17" s="3" t="n"/>
-      <c r="V17" s="2" t="inlineStr"/>
-      <c r="W17" s="4" t="n"/>
-      <c r="X17" s="4" t="n">
-        <v>46216</v>
-      </c>
-      <c r="Y17" s="4" t="n"/>
-      <c r="Z17" s="4" t="n">
-        <v>46229</v>
-      </c>
-      <c r="AA17" s="4" t="n">
-        <v>46239</v>
-      </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>仅公告送达/仅文号线索</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD17" s="2" t="inlineStr">
-        <is>
-          <t>已核验</t>
-        </is>
-      </c>
-      <c r="AE17" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF17" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
-      <c r="AG17" s="2" t="inlineStr"/>
-      <c r="AH17" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
-        </is>
-      </c>
-      <c r="AI17" s="2" t="inlineStr">
-        <is>
-          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ17" s="2" t="inlineStr">
@@ -2741,7 +2749,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
@@ -2750,7 +2758,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>DOC-9f8e8958d8ff89b6</t>
+          <t>DOC-d21cdc5988b1e304</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2787,12 +2795,12 @@
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>淮税稽罚〔2026〕6号</t>
+          <t>淮税稽处〔2026〕26号</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2821,7 +2829,7 @@
         <v>46229</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -2867,99 +2875,91 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CASE-3f564fd9992b1ae3</t>
+          <t>CASE-089a3b9692e76ac4</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>DOC-c34e1d13286aafe2</t>
+          <t>DOC-9f8e8958d8ff89b6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>泉州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局第二稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局第二稽查局</t>
+          <t>国家税务总局淮安市税务局稽查局</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>泉州隆鸿服装制造有限公司</t>
+          <t>淮安市百亦金商贸有限公司</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>91350525MA8U3U963L</t>
+          <t>91320804MA1WEH7Y3U</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>泉税二稽处〔2026〕107号</t>
+          <t>淮税稽罚〔2026〕6号</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>泉税二稽处〔2026〕107号</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>日对你公司税收违法事实依法作出《税务处理决定书》(泉税二稽处〔 涉税情况进行了检查,查明违法事实及处理决定如下: 年你公司在无真实货物交易的情况下,取得河南中弘纺织有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 年期间,你公司在无真实货物交易的情况下,取得开封兴旺纺织品有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 上述违法事实有检查人员实地检查资料、电话拨打记录、邮寄退回函件、《已证实虚开通知单》等相关受托协查资料、主管税务机关出具的《已抵扣证明》、《情况说明》和你公司的申报纳税资料、银行账户流水等 号第三次修订)第二十一条第二款第二项之规定,认定你公司让他人为自己虚开 号第二次修订)第九条和《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告〔 号)之规定,对你公司取得上述已证实虚开的 之规定,决定向你公司追缴少缴的城市维护建设税-增值税附征 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 规定,决定向你公司追缴少缴的教育费附加-增值税附征 规定,决定向你公司追缴少缴的地方教育附加-增值税附征</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
+          <t>淮税稽处〔2026〕26号</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>淮税稽罚〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
       <c r="R19" s="3" t="n"/>
       <c r="S19" s="3" t="n"/>
       <c r="T19" s="3" t="n"/>
       <c r="U19" s="3" t="n"/>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>由于你公司走逃失联、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 (五)根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司上述应补缴税款按税款所属时间从税款滞纳之日起按日加收万分之五滞纳金</t>
-        </is>
-      </c>
+      <c r="V19" s="2" t="inlineStr"/>
       <c r="W19" s="4" t="n"/>
       <c r="X19" s="4" t="n">
-        <v>46202</v>
+        <v>46216</v>
       </c>
       <c r="Y19" s="4" t="n"/>
       <c r="Z19" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2977,18 +2977,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AF19" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG19" s="2" t="inlineStr"/>
       <c r="AH19" s="2" t="inlineStr">
         <is>
-          <t>关于对泉州隆鸿服装制造有限公司《税务处理决定书》送达的公告 _
- 其他公告 _
- 国家税务总局泉州市税务局</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
         </is>
       </c>
       <c r="AI19" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ19" s="2" t="inlineStr">
@@ -2999,91 +3001,99 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CASE-717dfe3250926214</t>
+          <t>CASE-3f564fd9992b1ae3</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>DOC-7df9c075e55777a1</t>
+          <t>DOC-c34e1d13286aafe2</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>泰州市</t>
+          <t>泉州市</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泰州市税务局第一稽查局</t>
+          <t>国家税务总局泉州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泰州市税务局第一稽查局</t>
+          <t>国家税务总局泉州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>靖江市长凌金属材料有限公司</t>
+          <t>泉州隆鸿服装制造有限公司</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>91321282742461893K</t>
+          <t>91350525MA8U3U963L</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>泰税一稽罚〔2025〕54号</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>泰税一稽罚〔2025〕54号</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
+          <t>泉税二稽处〔2026〕107号</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>泉税二稽处〔2026〕107号</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>日对你公司税收违法事实依法作出《税务处理决定书》(泉税二稽处〔 涉税情况进行了检查,查明违法事实及处理决定如下: 年你公司在无真实货物交易的情况下,取得河南中弘纺织有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 年期间,你公司在无真实货物交易的情况下,取得开封兴旺纺织品有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 上述违法事实有检查人员实地检查资料、电话拨打记录、邮寄退回函件、《已证实虚开通知单》等相关受托协查资料、主管税务机关出具的《已抵扣证明》、《情况说明》和你公司的申报纳税资料、银行账户流水等 号第三次修订)第二十一条第二款第二项之规定,认定你公司让他人为自己虚开 号第二次修订)第九条和《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告〔 号)之规定,对你公司取得上述已证实虚开的 之规定,决定向你公司追缴少缴的城市维护建设税-增值税附征 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 规定,决定向你公司追缴少缴的教育费附加-增值税附征 规定,决定向你公司追缴少缴的地方教育附加-增值税附征</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
       <c r="R20" s="3" t="n"/>
       <c r="S20" s="3" t="n"/>
       <c r="T20" s="3" t="n"/>
       <c r="U20" s="3" t="n"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>接上级通知,经我局研究决定,撤销上述《税务行政处罚决定书》。</t>
+          <t>由于你公司走逃失联、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 (五)根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司上述应补缴税款按税款所属时间从税款滞纳之日起按日加收万分之五滞纳金</t>
         </is>
       </c>
       <c r="W20" s="4" t="n"/>
       <c r="X20" s="4" t="n">
-        <v>46191</v>
+        <v>46202</v>
       </c>
       <c r="Y20" s="4" t="n"/>
       <c r="Z20" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -3105,7 +3115,9 @@
       <c r="AG20" s="2" t="inlineStr"/>
       <c r="AH20" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 关于撤销《税务行政处罚决定书》的公告</t>
+          <t>关于对泉州隆鸿服装制造有限公司《税务处理决定书》送达的公告 _
+ 其他公告 _
+ 国家税务总局泉州市税务局</t>
         </is>
       </c>
       <c r="AI20" s="2" t="inlineStr">
@@ -3115,101 +3127,97 @@
       </c>
       <c r="AJ20" s="2" t="inlineStr">
         <is>
-          <t>官方页面显示该决定书已被撤销。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CASE-a62e569c195adc3c</t>
+          <t>CASE-717dfe3250926214</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>DOC-b1dda915d4e6117d</t>
+          <t>DOC-7df9c075e55777a1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>遵义市</t>
+          <t>泰州市</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局泰州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局泰州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>贵州服格定商贸有限公司</t>
+          <t>靖江市长凌金属材料有限公司</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>91520302MABUEHN034</t>
+          <t>91321282742461893K</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>遵税一稽处〔2026〕30号</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>遵税一稽处〔2026〕30号</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>增值税</t>
-        </is>
-      </c>
+          <t>泰税一稽罚〔2025〕54号</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>泰税一稽罚〔2025〕54号</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
       <c r="R21" s="3" t="n"/>
       <c r="S21" s="3" t="n"/>
       <c r="T21" s="3" t="n"/>
       <c r="U21" s="3" t="n"/>
-      <c r="V21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>接上级通知,经我局研究决定,撤销上述《税务行政处罚决定书》。</t>
+        </is>
+      </c>
       <c r="W21" s="4" t="n"/>
       <c r="X21" s="4" t="n">
-        <v>46185</v>
+        <v>46191</v>
       </c>
       <c r="Y21" s="4" t="n"/>
       <c r="Z21" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3231,7 +3239,7 @@
       <c r="AG21" s="2" t="inlineStr"/>
       <c r="AH21" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 关于撤销《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI21" s="2" t="inlineStr">
@@ -3241,51 +3249,55 @@
       </c>
       <c r="AJ21" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>官方页面显示该决定书已被撤销。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CASE-13a8aac51595155a</t>
+          <t>CASE-a62e569c195adc3c</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>DOC-7189c9a2cee8e8ce</t>
+          <t>DOC-b1dda915d4e6117d</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>温州市</t>
+          <t>遵义市</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局遵义市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局遵义市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>温作潘</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr"/>
+          <t>贵州服格定商贸有限公司</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>91520302MABUEHN034</t>
+        </is>
+      </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
@@ -3294,21 +3306,25 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>温税三稽处〔2026〕100号</t>
+          <t>遵税一稽处〔2026〕30号</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>温税三稽处〔2026〕100号</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>温税三稽罚〔2026〕65号</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr"/>
-      <c r="Q22" s="2" t="inlineStr"/>
+          <t>遵税一稽处〔2026〕30号</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>增值税</t>
+        </is>
+      </c>
       <c r="R22" s="3" t="n"/>
       <c r="S22" s="3" t="n"/>
       <c r="T22" s="3" t="n"/>
@@ -3316,18 +3332,18 @@
       <c r="V22" s="2" t="inlineStr"/>
       <c r="W22" s="4" t="n"/>
       <c r="X22" s="4" t="n">
-        <v>46175</v>
+        <v>46185</v>
       </c>
       <c r="Y22" s="4" t="n"/>
       <c r="Z22" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3345,20 +3361,16 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF22" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF22" s="2" t="inlineStr"/>
       <c r="AG22" s="2" t="inlineStr"/>
       <c r="AH22" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
+          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
         </is>
       </c>
       <c r="AI22" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ22" s="2" t="inlineStr">
@@ -3369,7 +3381,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
@@ -3378,7 +3390,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>DOC-02fc2468fd0396a6</t>
+          <t>DOC-7189c9a2cee8e8ce</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3411,12 +3423,12 @@
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>温税三稽罚〔2026〕65号</t>
+          <t>温税三稽处〔2026〕100号</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3445,7 +3457,7 @@
         <v>46229</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
@@ -3491,66 +3503,66 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CASE-f8625e66b291a216</t>
+          <t>CASE-13a8aac51595155a</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>DOC-7970511393924720</t>
+          <t>DOC-02fc2468fd0396a6</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>温州市</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>贵州翰缤商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>91520114MAAK1C546F</t>
-        </is>
-      </c>
+          <t>温作潘</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>筑税二稽处〔2026〕27号</t>
+          <t>温税三稽罚〔2026〕65号</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>筑税二稽处〔2026〕27号</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr"/>
+          <t>温税三稽处〔2026〕100号</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>温税三稽罚〔2026〕65号</t>
+        </is>
+      </c>
       <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr"/>
       <c r="R24" s="3" t="n"/>
@@ -3560,14 +3572,14 @@
       <c r="V24" s="2" t="inlineStr"/>
       <c r="W24" s="4" t="n"/>
       <c r="X24" s="4" t="n">
-        <v>46156</v>
+        <v>46175</v>
       </c>
       <c r="Y24" s="4" t="n"/>
       <c r="Z24" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
@@ -3589,16 +3601,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF24" s="2" t="inlineStr"/>
+      <c r="AF24" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG24" s="2" t="inlineStr"/>
       <c r="AH24" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局关于送达《税务处理决定书》的公告</t>
+          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
         </is>
       </c>
       <c r="AI24" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ24" s="2" t="inlineStr">
@@ -3609,16 +3625,16 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CASE-0f4867f7b70d12f3</t>
+          <t>CASE-f8625e66b291a216</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>DOC-6f25d6b79e123d03</t>
+          <t>DOC-7970511393924720</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3634,22 +3650,22 @@
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局贵阳市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局贵阳市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>贵州铂朗物流有限公司</t>
+          <t>贵州翰缤商贸有限公司</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>91520115MAAK0DB335</t>
+          <t>91520114MAAK1C546F</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
@@ -3660,19 +3676,15 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
+          <t>筑税二稽处〔2026〕27号</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>筑税三稽罚〔2026〕22号</t>
-        </is>
-      </c>
+          <t>筑税二稽处〔2026〕27号</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr"/>
       <c r="R25" s="3" t="n"/>
@@ -3682,14 +3694,14 @@
       <c r="V25" s="2" t="inlineStr"/>
       <c r="W25" s="4" t="n"/>
       <c r="X25" s="4" t="n">
-        <v>46122</v>
+        <v>46156</v>
       </c>
       <c r="Y25" s="4" t="n"/>
       <c r="Z25" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
@@ -3715,7 +3727,7 @@
       <c r="AG25" s="2" t="inlineStr"/>
       <c r="AH25" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
+          <t>国家税务总局贵阳市税务局第二稽查局关于送达《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI25" s="2" t="inlineStr">
@@ -3731,7 +3743,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
@@ -3740,7 +3752,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>DOC-e8233eb0e06b6e3e</t>
+          <t>DOC-6f25d6b79e123d03</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3777,12 +3789,12 @@
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽罚〔2026〕22号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3811,7 +3823,7 @@
         <v>46229</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
@@ -3853,68 +3865,68 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CASE-136615addd5d0c0e</t>
+          <t>CASE-0f4867f7b70d12f3</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>DOC-551df7dc5c028b27</t>
+          <t>DOC-e8233eb0e06b6e3e</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>来宾市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>广西欣瑞木业有限公司</t>
+          <t>贵州铂朗物流有限公司</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>91451322MAD89XWX07</t>
+          <t>91520115MAAK0DB335</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr"/>
@@ -3926,14 +3938,14 @@
       <c r="V27" s="2" t="inlineStr"/>
       <c r="W27" s="4" t="n"/>
       <c r="X27" s="4" t="n">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="Y27" s="4" t="n"/>
       <c r="Z27" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
@@ -3959,7 +3971,7 @@
       <c r="AG27" s="2" t="inlineStr"/>
       <c r="AH27" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
         </is>
       </c>
       <c r="AI27" s="2" t="inlineStr">
@@ -3975,7 +3987,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
@@ -3984,7 +3996,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>DOC-21f0193b66d5c3e9</t>
+          <t>DOC-551df7dc5c028b27</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -4021,12 +4033,12 @@
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>来市税二稽处〔2026〕6号</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -4055,7 +4067,7 @@
         <v>46229</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
@@ -4097,47 +4109,47 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CASE-393a878d93a22709</t>
+          <t>CASE-136615addd5d0c0e</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>DOC-cda8cba853896b18</t>
+          <t>DOC-21f0193b66d5c3e9</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>广州市</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>番禺区</t>
-        </is>
-      </c>
+          <t>来宾市</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
+        </is>
+      </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>广州赞荣服装有限公司</t>
+          <t>广西欣瑞木业有限公司</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>91440113MA59AJFJ1J</t>
+          <t>91451322MAD89XWX07</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
@@ -4148,13 +4160,17 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>穗番税退罚字〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>来市税二稽罚〔2026〕4号</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>来市税二稽处〔2026〕6号</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>穗番税退罚字〔2026〕1号</t>
+          <t>来市税二稽罚〔2026〕4号</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr"/>
@@ -4166,14 +4182,14 @@
       <c r="V29" s="2" t="inlineStr"/>
       <c r="W29" s="4" t="n"/>
       <c r="X29" s="4" t="n">
-        <v>46091</v>
+        <v>46119</v>
       </c>
       <c r="Y29" s="4" t="n"/>
       <c r="Z29" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
@@ -4187,7 +4203,7 @@
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE29" s="5" t="inlineStr">
@@ -4195,131 +4211,107 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF29" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF29" s="2" t="inlineStr"/>
       <c r="AG29" s="2" t="inlineStr"/>
       <c r="AH29" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
+          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
         </is>
       </c>
       <c r="AI29" s="2" t="inlineStr">
         <is>
-          <t>内容不匹配</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ29" s="2" t="inlineStr">
         <is>
-          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CASE-f94bf08964abff5a</t>
+          <t>CASE-393a878d93a22709</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>DOC-4574b1aadef8f30d</t>
+          <t>DOC-cda8cba853896b18</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>广东省</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr"/>
+          <t>广州市</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>番禺区</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局常州市税务局稽查局</t>
-        </is>
-      </c>
+          <t>国家税务总局广州市番禺区税务局</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>常州市文杰车辆配件厂</t>
+          <t>广州赞荣服装有限公司</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>91320411799075280A</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>朱某</t>
-        </is>
-      </c>
+          <t>91440113MA59AJFJ1J</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕73号</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>常税稽处〔2026〕73号</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr"/>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公 月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R30" s="3" t="n">
-        <v>179137.12</v>
-      </c>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="3" t="n"/>
       <c r="S30" s="3" t="n"/>
       <c r="T30" s="3" t="n"/>
       <c r="U30" s="3" t="n"/>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市 份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元,</t>
-        </is>
-      </c>
-      <c r="W30" s="4" t="n">
-        <v>46044</v>
-      </c>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="4" t="n"/>
       <c r="X30" s="4" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="Y30" s="4" t="n"/>
       <c r="Z30" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4329,7 +4321,7 @@
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE30" s="5" t="inlineStr">
@@ -4345,32 +4337,32 @@
       <c r="AG30" s="2" t="inlineStr"/>
       <c r="AH30" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
+          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
         </is>
       </c>
       <c r="AI30" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>内容不匹配</t>
         </is>
       </c>
       <c r="AJ30" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CASE-0b4a4519ba4f5ad9</t>
+          <t>CASE-f94bf08964abff5a</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>DOC-5376b9bae81cfc82</t>
+          <t>DOC-4574b1aadef8f30d</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4396,15 +4388,19 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>常州好佳车辆配件有限公司</t>
+          <t>常州市文杰车辆配件厂</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>91320411094264460B</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
+          <t>91320411799075280A</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>朱某</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
           <t>税务处理决定书</t>
@@ -4412,36 +4408,52 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕71号</t>
+          <t>常税稽处〔2026〕73号</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕71号</t>
+          <t>常税稽处〔2026〕73号</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr"/>
-      <c r="P31" s="2" t="inlineStr"/>
-      <c r="Q31" s="2" t="inlineStr"/>
-      <c r="R31" s="3" t="n"/>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公 月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>179137.12</v>
+      </c>
       <c r="S31" s="3" t="n"/>
       <c r="T31" s="3" t="n"/>
       <c r="U31" s="3" t="n"/>
-      <c r="V31" s="2" t="inlineStr"/>
-      <c r="W31" s="4" t="n"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市 份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元,</t>
+        </is>
+      </c>
+      <c r="W31" s="4" t="n">
+        <v>46044</v>
+      </c>
       <c r="X31" s="4" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="Y31" s="4" t="n"/>
       <c r="Z31" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4467,7 +4479,7 @@
       <c r="AG31" s="2" t="inlineStr"/>
       <c r="AH31" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州好佳车辆配件有限公司《税务处理决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI31" s="2" t="inlineStr">
@@ -4483,16 +4495,16 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CASE-61b9b55a9d3357c7</t>
+          <t>CASE-0b4a4519ba4f5ad9</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>DOC-1228a9c92b2b0632</t>
+          <t>DOC-5376b9bae81cfc82</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4508,22 +4520,22 @@
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局常州市税务局稽查局</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>常州市三鹏机械有限公司</t>
+          <t>常州好佳车辆配件有限公司</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>91320404732260748Q</t>
+          <t>91320411094264460B</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
@@ -4534,50 +4546,36 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
+          <t>常税稽处〔2026〕71号</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>常税稽一罚〔2026〕14号</t>
-        </is>
-      </c>
+          <t>常税稽处〔2026〕71号</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr"/>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>63464.09</v>
-      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="3" t="n"/>
       <c r="S32" s="3" t="n"/>
       <c r="T32" s="3" t="n"/>
       <c r="U32" s="3" t="n"/>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
-        </is>
-      </c>
+      <c r="V32" s="2" t="inlineStr"/>
       <c r="W32" s="4" t="n"/>
       <c r="X32" s="4" t="n">
-        <v>46066</v>
+        <v>46087</v>
       </c>
       <c r="Y32" s="4" t="n"/>
       <c r="Z32" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA32" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4595,16 +4593,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF32" s="2" t="inlineStr"/>
+      <c r="AF32" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG32" s="2" t="inlineStr"/>
       <c r="AH32" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州好佳车辆配件有限公司《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI32" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ32" s="2" t="inlineStr">
@@ -4615,7 +4617,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
@@ -4624,7 +4626,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>DOC-b97456a64b153f67</t>
+          <t>DOC-1228a9c92b2b0632</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4661,12 +4663,12 @@
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>常税稽一罚〔2026〕14号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4685,11 +4687,11 @@
           <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R33" s="3" t="n"/>
+      <c r="R33" s="3" t="n">
+        <v>63464.09</v>
+      </c>
       <c r="S33" s="3" t="n"/>
-      <c r="T33" s="3" t="n">
-        <v>20000</v>
-      </c>
+      <c r="T33" s="3" t="n"/>
       <c r="U33" s="3" t="n"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
@@ -4705,7 +4707,7 @@
         <v>46229</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
@@ -4747,103 +4749,97 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CASE-f78ec1a594442165</t>
+          <t>CASE-61b9b55a9d3357c7</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>DOC-fbbe4a664b14f54b</t>
+          <t>DOC-b97456a64b153f67</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>安顺市</t>
+          <t>常州市</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
+          <t>常州市三鹏机械有限公司</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>91520423MA6DLH799Q</t>
+          <t>91320404732260748Q</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一罚〔2026〕14号</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
-        </is>
-      </c>
+          <t>常税稽一罚〔2026〕14号</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr"/>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R34" s="3" t="n">
-        <v>64884.41</v>
-      </c>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="n"/>
       <c r="S34" s="3" t="n"/>
-      <c r="T34" s="3" t="n"/>
+      <c r="T34" s="3" t="n">
+        <v>20000</v>
+      </c>
       <c r="U34" s="3" t="n"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
-      <c r="W34" s="4" t="n">
-        <v>45898</v>
-      </c>
+          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
+        </is>
+      </c>
+      <c r="W34" s="4" t="n"/>
       <c r="X34" s="4" t="n">
-        <v>46043</v>
+        <v>46066</v>
       </c>
       <c r="Y34" s="4" t="n"/>
       <c r="Z34" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
@@ -4865,31 +4861,27 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF34" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF34" s="2" t="inlineStr"/>
       <c r="AG34" s="2" t="inlineStr"/>
       <c r="AH34" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI34" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ34" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。 字段“主要违法事实”存在冲突:保留原值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”,新值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
@@ -4898,7 +4890,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>DOC-9a828a6048b54b6c</t>
+          <t>DOC-fbbe4a664b14f54b</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4935,24 +4927,24 @@
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
           <t>安市税稽罚〔2026〕1号</t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>安市税稽处〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
           <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
@@ -4963,11 +4955,11 @@
           <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R35" s="3" t="n"/>
+      <c r="R35" s="3" t="n">
+        <v>64884.41</v>
+      </c>
       <c r="S35" s="3" t="n"/>
-      <c r="T35" s="3" t="n">
-        <v>200000</v>
-      </c>
+      <c r="T35" s="3" t="n"/>
       <c r="U35" s="3" t="n"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
@@ -4985,7 +4977,7 @@
         <v>46229</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
@@ -5025,97 +5017,109 @@
       </c>
       <c r="AJ35" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。 字段“主要违法事实”存在冲突:保留原值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”,新值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CASE-fe959d4c6c52d910</t>
+          <t>CASE-f78ec1a594442165</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>DOC-f2643f2a0719d8d1</t>
+          <t>DOC-9a828a6048b54b6c</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>南宁市</t>
+          <t>安顺市</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局稽查局</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>南宁洪谦金贸易有限公司</t>
+          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>91450103MA5K9WHY7U</t>
+          <t>91520423MA6DLH799Q</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>南市税一稽处〔2026〕2号</t>
+          <t>安市税稽罚〔2026〕1号</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>南市税一稽处〔2026〕2号</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr"/>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽罚〔2026〕1号</t>
+        </is>
+      </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>经我局2025年10月29日至2025年12月8日对你公司(地址:南宁市青秀区云景路11号春晖花园C区3栋2单元1606号)2015年12月2日至2016年12月31日期间的涉税情况进行了检查,你(单位)存在以下违法事实: 经查询你公司向税务机关报备的银行账号:广西北部湾银行南宁市财富国际支行800099398800015,经函询广西北部湾银行南宁市财富国际支行,存在以下问题: 上述行为属于开具与实际经营业务情况不符的增值税发票,违反了《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第587号修改)第二十二条第一款、第二款第(一)项的规定,属于虚开发票行为。</t>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
+          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R36" s="3" t="n"/>
       <c r="S36" s="3" t="n"/>
-      <c r="T36" s="3" t="n"/>
+      <c r="T36" s="3" t="n">
+        <v>200000</v>
+      </c>
       <c r="U36" s="3" t="n"/>
-      <c r="V36" s="2" t="inlineStr"/>
-      <c r="W36" s="4" t="n"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="W36" s="4" t="n">
+        <v>45898</v>
+      </c>
       <c r="X36" s="4" t="n">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="Y36" s="4" t="n"/>
       <c r="Z36" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA36" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
@@ -5145,7 +5149,7 @@
       <c r="AG36" s="2" t="inlineStr"/>
       <c r="AH36" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局税务文书送达公告_国家税务总局南宁市税务局</t>
+          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI36" s="2" t="inlineStr">
@@ -5155,51 +5159,55 @@
       </c>
       <c r="AJ36" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CASE-1983d97878508732</t>
+          <t>CASE-fe959d4c6c52d910</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>DOC-f9760895b4f08cc2</t>
+          <t>DOC-f2643f2a0719d8d1</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>二连浩特市</t>
+          <t>南宁市</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局</t>
+          <t>国家税务总局南宁市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局稽查局</t>
+          <t>国家税务总局南宁市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>二连市坤益腾金属有限公司</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr"/>
+          <t>南宁洪谦金贸易有限公司</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>91450103MA5K9WHY7U</t>
+        </is>
+      </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
@@ -5208,18 +5216,18 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
+          <t>南市税一稽处〔2026〕2号</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
+          <t>南市税一稽处〔2026〕2号</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
+          <t>经我局2025年10月29日至2025年12月8日对你公司(地址:南宁市青秀区云景路11号春晖花园C区3栋2单元1606号)2015年12月2日至2016年12月31日期间的涉税情况进行了检查,你(单位)存在以下违法事实: 经查询你公司向税务机关报备的银行账号:广西北部湾银行南宁市财富国际支行800099398800015,经函询广西北部湾银行南宁市财富国际支行,存在以下问题: 上述行为属于开具与实际经营业务情况不符的增值税发票,违反了《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第587号修改)第二十二条第一款、第二款第(一)项的规定,属于虚开发票行为。</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5231,19 +5239,17 @@
       <c r="S37" s="3" t="n"/>
       <c r="T37" s="3" t="n"/>
       <c r="U37" s="3" t="n"/>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
-        </is>
-      </c>
+      <c r="V37" s="2" t="inlineStr"/>
       <c r="W37" s="4" t="n"/>
-      <c r="X37" s="4" t="n"/>
+      <c r="X37" s="4" t="n">
+        <v>46031</v>
+      </c>
       <c r="Y37" s="4" t="n"/>
       <c r="Z37" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
@@ -5257,7 +5263,7 @@
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE37" s="5" t="inlineStr">
@@ -5265,36 +5271,40 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF37" s="2" t="inlineStr"/>
+      <c r="AF37" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG37" s="2" t="inlineStr"/>
       <c r="AH37" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>国家税务总局南宁市税务局第一稽查局税务文书送达公告_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI37" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ37" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>CASE-d4b6986f3f97cd28</t>
+          <t>CASE-1983d97878508732</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>DOC-442cf3d9a5280c12</t>
+          <t>DOC-f9760895b4f08cc2</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -5304,19 +5314,23 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>鄂尔多斯市</t>
+          <t>二连浩特市</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局二连浩特市税务局</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>第二稽查局</t>
+          <t>国家税务总局二连浩特市税务局稽查局</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>廖礼平</t>
+          <t>二连市坤益腾金属有限公司</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -5328,36 +5342,32 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
+          <t>二税稽处〔2025〕1号</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
+          <t>二税稽处〔2025〕1号</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
+          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>个人所得税、印花税</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="n">
-        <v>15072487.5</v>
-      </c>
-      <c r="S38" s="3" t="n">
-        <v>1046925</v>
-      </c>
+          <t>增值税</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="n"/>
+      <c r="S38" s="3" t="n"/>
       <c r="T38" s="3" t="n"/>
       <c r="U38" s="3" t="n"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
+          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
         </is>
       </c>
       <c r="W38" s="4" t="n"/>
@@ -5367,7 +5377,7 @@
         <v>46229</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
@@ -5403,55 +5413,47 @@
       </c>
       <c r="AJ38" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
+          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>CASE-7e3d4a321440d6a7</t>
+          <t>CASE-d4b6986f3f97cd28</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>DOC-bed9330343ed06af</t>
+          <t>DOC-442cf3d9a5280c12</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>鄂尔多斯市</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
-        </is>
-      </c>
+      <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
+          <t>第二稽查局</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>天津展达科技有限公司</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>91120116300738701X</t>
-        </is>
-      </c>
+          <t>廖礼平</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
@@ -5460,48 +5462,46 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
+          <t>鄂税二稽处〔2023〕29号</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
+          <t>鄂税二稽处〔2023〕29号</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+          <t>个人所得税、印花税</t>
         </is>
       </c>
       <c r="R39" s="3" t="n">
-        <v>920146.9399999999</v>
-      </c>
-      <c r="S39" s="3" t="n"/>
+        <v>15072487.5</v>
+      </c>
+      <c r="S39" s="3" t="n">
+        <v>1046925</v>
+      </c>
       <c r="T39" s="3" t="n"/>
       <c r="U39" s="3" t="n"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
         </is>
       </c>
       <c r="W39" s="4" t="n"/>
       <c r="X39" s="4" t="n"/>
       <c r="Y39" s="4" t="n"/>
       <c r="Z39" s="4" t="n">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
       <c r="AG39" s="2" t="inlineStr"/>
       <c r="AH39" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="AI39" s="2" t="inlineStr">
@@ -5537,13 +5537,13 @@
       </c>
       <c r="AJ39" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>DOC-388bd01c01bbb789</t>
+          <t>DOC-bed9330343ed06af</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5589,24 +5589,24 @@
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
           <t>津税一稽罚〔2023〕21号</t>
         </is>
       </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
           <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
@@ -5617,11 +5617,11 @@
           <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R40" s="3" t="n"/>
+      <c r="R40" s="3" t="n">
+        <v>920146.9399999999</v>
+      </c>
       <c r="S40" s="3" t="n"/>
-      <c r="T40" s="3" t="n">
-        <v>131368.5</v>
-      </c>
+      <c r="T40" s="3" t="n"/>
       <c r="U40" s="3" t="n"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>46230</v>
       </c>
       <c r="AA40" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
@@ -5675,27 +5675,161 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7e3d4a321440d6a7</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>DOC-388bd01c01bbb789</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>91120116300738701X</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>税务行政处罚决定书</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="n"/>
+      <c r="S41" s="3" t="n"/>
+      <c r="T41" s="3" t="n">
+        <v>131368.5</v>
+      </c>
+      <c r="U41" s="3" t="n"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W41" s="4" t="n"/>
+      <c r="X41" s="4" t="n"/>
+      <c r="Y41" s="4" t="n"/>
+      <c r="Z41" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AA41" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE41" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF41" s="2" t="inlineStr"/>
+      <c r="AG41" s="2" t="inlineStr"/>
+      <c r="AH41" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+        </is>
+      </c>
+      <c r="AI41" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ41" s="2" t="inlineStr">
+        <is>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ40"/>
-  <conditionalFormatting sqref="AD2:AD40">
+  <autoFilter ref="A1:AJ41"/>
+  <conditionalFormatting sqref="AD2:AD41">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AD2="待核验"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI2:AI40">
+  <conditionalFormatting sqref="AI2:AI41">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>AND($AI2&lt;&gt;"正常",$AI2&lt;&gt;"附件正常")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AD2:AD40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AD2:AD41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"已核验,待核验,人工复核完成"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE3" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF4" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE5" r:id="rId6"/>
@@ -5703,49 +5837,51 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE6" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF6" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE9" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE10" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE11" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE12" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE14" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE15" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE16" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE17" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF17" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE10" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE11" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE14" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE15" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE16" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE17" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE18" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF18" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE19" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE20" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE21" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE22" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF22" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF19" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE20" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE21" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE22" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE23" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF23" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE24" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE25" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE26" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE27" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE28" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE29" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF29" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF24" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE25" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE26" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE27" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE28" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE29" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE30" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF30" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE31" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF31" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE32" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE33" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE34" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF34" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF32" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE33" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE34" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE35" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF35" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE36" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF36" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE37" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE38" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE39" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE40" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF37" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE38" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE39" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE40" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE41" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -5758,7 +5894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ20"/>
+  <dimension ref="A1:AJ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5983,47 +6119,47 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CASE-ef382edddd0f50f8</t>
+          <t>CASE-2799cf13d16e48fa</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>DOC-f80d567b9343411c</t>
+          <t>DOC-4a944414e51221f4</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>泉州市</t>
+          <t>北海市</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局</t>
+          <t>国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局稽查局</t>
+          <t>国家税务总局北海市税务局稽查局</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>泉州平媛贸易有限公司</t>
+          <t>北海市丰赢商贸有限公司</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>91350503597867511E</t>
+          <t>91450500MAEULQHG42</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
@@ -6034,44 +6170,48 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>泉税稽处〔2026〕29号</t>
+          <t>北市税稽处〔2026〕16号</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>泉税稽处〔2026〕29号</t>
+          <t>北市税稽处〔2026〕16号</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>进行了检查,违法事实及处理决定如下: 经查,2013年1月25日至2013年1月28日期间,你公司将4900万元资金贷与庄彬阳使用,你公司未就该项贷款业务申报缴纳企业所得税、营业税及附加税费。</t>
+          <t>况进行了检查,违法事实及处理决定如下: 行,无法核实你公司资金流情况,你公司存在虚开风险。 经查实,根据《国家税务总局关于纳税人虚开增值税专用发 经查实,根据《中华人民共和国城市维护建设税暂行条例》 经查实,根据《征收教育费附加的暂行规定》(国发〔1986〕 经查实,根据《广西壮族自治区人民政府关于印发广西壮 你公司所属期 2025 年 8 月未进行纳税申报,不缴或者少缴 三条第一款规定,对上述行为定性为偷税,向你公司追缴少缴的 对你公司少缴的税款从税款滞纳之日起至实际缴纳税款之日止 公司向下游企业虚开 9 份增值税电子专用发票(发票号码: 况进行了检查,违法事实及处理决定如下: 行,无法核实你公司资金流情况,你公司存在虚开风险。 经查实,根据《国家税务总局关于纳税人虚开增值税专用发 经查实,根据《中华人民共和国城市维护建设税暂行条例》 经查实,根据《征收教育费附加的暂行规定》(国发〔1986〕 经查实,根据《广西壮族自治区人民政府关于印发广西壮 你公司所属期 2025 年 8 月未进行纳税申报,不缴或者少缴 三条第一款规定,对上述行为定性为偷税,向你公司追缴少缴的 对你公司少缴的税款从税款滞纳之日起至实际缴纳税款之日止 公司向下游企业虚开 9 份增值税电子专用发票(发票号码:</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>企业所得税</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="n"/>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>512334.96</v>
+      </c>
       <c r="S2" s="3" t="n"/>
       <c r="T2" s="3" t="n"/>
       <c r="U2" s="3" t="n"/>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满30日,即视为送达。</t>
-        </is>
-      </c>
-      <c r="W2" s="4" t="n"/>
+          <t>你公司所属期2025 年 8 月应补缴增值税465759.06 元。 司所属期2025 年 8 月应补缴纳城市维护建设税32603.13 元。 公司所属期 2025 年8 月应补缴纳教育费附加 13972.77 元。 第三条的规定,你公司所属期2025 年 8 月应补缴纳地方教育附 你公司所属期2025 年 8 月应补缴增值税465759.06 元。 司所属期2025 年 8 月应补缴纳城市维护建设税32603.13 元。 公司所属期 2025 年8 月应补缴纳教育费附加 13972.77 元。 第三条的规定,你公司所属期2025 年 8 月应补缴纳地方教育附</t>
+        </is>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>46237</v>
+      </c>
       <c r="X2" s="4" t="n">
         <v>46238</v>
       </c>
       <c r="Y2" s="4" t="n"/>
       <c r="Z2" s="4" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -6093,38 +6233,36 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr"/>
+      <c r="AF2" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG2" s="2" t="inlineStr"/>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>关于对泉州平媛贸易有限公司《税务处理决定书》送达的公告 _
- 其他公告 _
- 国家税务总局泉州市税务局</t>
+          <t>【市稽查】国家税务总局北海市税务局稽查局税务文书送达公告(北海市丰赢商贸有限公司)_国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="AI2" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="AJ2" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
+          <t>附件正常</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CASE-f7f5d80ec431a14d</t>
+          <t>CASE-ef382edddd0f50f8</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>DOC-3a61d3452c421a37</t>
+          <t>DOC-f80d567b9343411c</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -6134,72 +6272,76 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>福州市</t>
+          <t>泉州市</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局泉州市税务局</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局泉州市税务局稽查局</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>福州吉伦多德贸易有限公司</t>
+          <t>泉州平媛贸易有限公司</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>91350102MA33G4RD13</t>
+          <t>91350503597867511E</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽罚〔2026〕39号</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>榕税一稽罚〔2026〕39号</t>
-        </is>
-      </c>
+          <t>泉税稽处〔2026〕29号</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>泉税稽处〔2026〕29号</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>经我局于2022年5月20日起对你公司[地址:福建省福州市鼓楼区温泉街道东城边街39号(原东城边街东侧与温泉支路交叉处)恒宇国际2#楼5层10商务办公-1]2019年1月1日至2022年12月31日期间的涉税情况进行检查,你公司存在违法事实及处罚决定如下: 你公司假报出口骗取国家出口退税款4064566.77元。 你公司取得的已证实虚开发票、出口退税数据、报关单证资料比对结果等证据。</t>
+          <t>进行了检查,违法事实及处理决定如下: 经查,2013年1月25日至2013年1月28日期间,你公司将4900万元资金贷与庄彬阳使用,你公司未就该项贷款业务申报缴纳企业所得税、营业税及附加税费。</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税</t>
+          <t>企业所得税</t>
         </is>
       </c>
       <c r="R3" s="3" t="n"/>
       <c r="S3" s="3" t="n"/>
       <c r="T3" s="3" t="n"/>
       <c r="U3" s="3" t="n"/>
-      <c r="V3" s="2" t="inlineStr"/>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满30日,即视为送达。</t>
+        </is>
+      </c>
       <c r="W3" s="4" t="n"/>
       <c r="X3" s="4" t="n">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="Y3" s="4" t="n"/>
       <c r="Z3" s="4" t="n">
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -6225,9 +6367,9 @@
       <c r="AG3" s="2" t="inlineStr"/>
       <c r="AH3" s="2" t="inlineStr">
         <is>
-          <t>关于送达福州吉伦多德贸易有限公司《税务行政处罚决定书》的公告 _
- 其他类 _
- 国家税务总局福州市税务局</t>
+          <t>关于对泉州平媛贸易有限公司《税务处理决定书》送达的公告 _
+ 其他公告 _
+ 国家税务总局泉州市税务局</t>
         </is>
       </c>
       <c r="AI3" s="2" t="inlineStr">
@@ -6243,93 +6385,91 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CASE-89fc66bfc8dad80d</t>
+          <t>CASE-f7f5d80ec431a14d</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>DOC-6e5b966cd65a4366</t>
+          <t>DOC-3a61d3452c421a37</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>北海市</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>银海区</t>
-        </is>
-      </c>
+          <t>福州市</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局北海市税务局</t>
+          <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局北海市税务局稽查局</t>
+          <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>广西耿仁建材有限公司</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t>福州吉伦多德贸易有限公司</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>91350102MA33G4RD13</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>北市税稽处〔2026〕14号</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>北市税稽处〔2026〕14号</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr"/>
+          <t>榕税一稽罚〔2026〕39号</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>榕税一稽罚〔2026〕39号</t>
+        </is>
+      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>我局于2026年2月11日至2026年7月15日对你公司(地址:北海市银海区新世纪大道15号辰宸花园3幢二单元0901号)2026年1月1日至2026年1月31日期间的涉税情况进行了检查,违法事实及处理决定如下: (2)短时间开具大量大额发票且未申报 你公司未进行纳税申报,不缴或者少缴2026年1月增值税194612.47元,2026年1月城市维护建设税13622.87元,合计208235.34元。 根据《中华人民共和国税收征收管理法》第六十三条第一款规定,对上述行为定性为偷税,向你公司追缴少缴的2026年增值税194612.47元,城市维护建设税13622.87元,合计208235.34元。 1.根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)的规定,对你公司少缴所属期2026年1月的教育费附加5838.37元,予以追缴。 2.根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条的规定,对你公司少缴所属期2026年1月地方教育附加3892.25元,予以追缴。 根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司少缴的税款从税款滞纳之日起至实际缴纳税款之日止按日加收滞纳税款万分之五的滞纳金,滞纳金由金三系统自动计算加收。 (四)你公司无法联系且实地核查无实际生产地址、无生产能力、查无下落,短期开票金额大,无法核实资金流,未进行纳税申报,根据《国家税务总局关于走逃(失联)企业开具增值税专用发票认定处理有关问题的公告》(国家税务总局公告2016年第76号),将你公司按走逃(失联)处理,根据《中华人民共和国发票管理办法》(国函〔1993〕174号)第二十一条第(一)项,你公司无生产能力,却为他人开具与实际经营业务情况不符的发票,属于虚开发票的行为。</t>
+          <t>经我局于2022年5月20日起对你公司[地址:福建省福州市鼓楼区温泉街道东城边街39号(原东城边街东侧与温泉支路交叉处)恒宇国际2#楼5层10商务办公-1]2019年1月1日至2022年12月31日期间的涉税情况进行检查,你公司存在违法事实及处罚决定如下: 你公司假报出口骗取国家出口退税款4064566.77元。 你公司取得的已证实虚开发票、出口退税数据、报关单证资料比对结果等证据。</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>208235.34</v>
-      </c>
+          <t>增值税、企业所得税、消费税</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="n"/>
       <c r="S4" s="3" t="n"/>
       <c r="T4" s="3" t="n"/>
       <c r="U4" s="3" t="n"/>
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="4" t="n"/>
       <c r="X4" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="Y4" s="4" t="n"/>
       <c r="Z4" s="4" t="n">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -6355,7 +6495,9 @@
       <c r="AG4" s="2" t="inlineStr"/>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕14号)_国家税务总局北海市税务局</t>
+          <t>关于送达福州吉伦多德贸易有限公司《税务行政处罚决定书》的公告 _
+ 其他类 _
+ 国家税务总局福州市税务局</t>
         </is>
       </c>
       <c r="AI4" s="2" t="inlineStr">
@@ -6371,16 +6513,16 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CASE-eb9cfd5295d501e5</t>
+          <t>CASE-89fc66bfc8dad80d</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>DOC-4a8cf53b445afc63</t>
+          <t>DOC-6e5b966cd65a4366</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -6395,7 +6537,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>海城区</t>
+          <t>银海区</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6410,14 +6552,10 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>广西轩易科技有限公司</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>91450500MAK3N9UJ2T</t>
-        </is>
-      </c>
+          <t>广西耿仁建材有限公司</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -6426,18 +6564,18 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>北市税稽处〔2026〕6号</t>
+          <t>北市税稽处〔2026〕14号</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>北市税稽处〔2026〕6号</t>
+          <t>北市税稽处〔2026〕14号</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>我局于2026年1月23日起对你公司(地址:北海市海城区北部湾东路“金宝小区”B幢B804号20北海汇算账商务秘书有限公司托管)2025年12月11日至2025年12月31日期间的涉税情况进行了检查,发现你公司存在税收违法行为,原《税务处理决定书》(北市税稽处〔2026〕6号)认定的违法事实有误,经重新调查核实,违法事实及处理决定如下: 经查询,你公司2026年1月20日通过网络方式零申报所属期2025年10月1日-2025年12月31日的增值税、城市维护建设税及附加,入库税款0元,申报金额与实际不符,存在虚假申报的情况。 你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 (一)根据《中华人民共和国发票管理办法》(财政部令第6号发布,经国务院令第587号、第709号、第764号修订)第二十一条第二款第(一)项的规定,认定你公司为他人开具与实际经营业务情况不符的前述13份增值税普通电子发票为虚开发票(金额合计571550.49元,税额合计5715.51元,价税合计577266.00元)。 根据《中华人民共和国税收征收管理法》第三十二条、第六十三条第一款、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,已构成偷税,向你公司追缴少缴的税款合计5915.56元,并从滞纳税款之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
+          <t>我局于2026年2月11日至2026年7月15日对你公司(地址:北海市银海区新世纪大道15号辰宸花园3幢二单元0901号)2026年1月1日至2026年1月31日期间的涉税情况进行了检查,违法事实及处理决定如下: (2)短时间开具大量大额发票且未申报 你公司未进行纳税申报,不缴或者少缴2026年1月增值税194612.47元,2026年1月城市维护建设税13622.87元,合计208235.34元。 根据《中华人民共和国税收征收管理法》第六十三条第一款规定,对上述行为定性为偷税,向你公司追缴少缴的2026年增值税194612.47元,城市维护建设税13622.87元,合计208235.34元。 1.根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)的规定,对你公司少缴所属期2026年1月的教育费附加5838.37元,予以追缴。 2.根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条的规定,对你公司少缴所属期2026年1月地方教育附加3892.25元,予以追缴。 根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司少缴的税款从税款滞纳之日起至实际缴纳税款之日止按日加收滞纳税款万分之五的滞纳金,滞纳金由金三系统自动计算加收。 (四)你公司无法联系且实地核查无实际生产地址、无生产能力、查无下落,短期开票金额大,无法核实资金流,未进行纳税申报,根据《国家税务总局关于走逃(失联)企业开具增值税专用发票认定处理有关问题的公告》(国家税务总局公告2016年第76号),将你公司按走逃(失联)处理,根据《中华人民共和国发票管理办法》(国函〔1993〕174号)第二十一条第(一)项,你公司无生产能力,却为他人开具与实际经营业务情况不符的发票,属于虚开发票的行为。</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6446,26 +6584,22 @@
         </is>
       </c>
       <c r="R5" s="3" t="n">
-        <v>6058.46</v>
+        <v>208235.34</v>
       </c>
       <c r="S5" s="3" t="n"/>
       <c r="T5" s="3" t="n"/>
       <c r="U5" s="3" t="n"/>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《中华人民共和国城市维护建设税法》(中华人民共和国主席令第五十一号)第一条、第二条、第四条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×7%×50%=200.05元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)、《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×3%×50%=85.74元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳地方教育附加5715.51×2%×50%=57.16元。</t>
-        </is>
-      </c>
+      <c r="V5" s="2" t="inlineStr"/>
       <c r="W5" s="4" t="n"/>
       <c r="X5" s="4" t="n">
         <v>46232</v>
       </c>
       <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -6491,7 +6625,7 @@
       <c r="AG5" s="2" t="inlineStr"/>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕13号)_国家税务总局北海市税务局</t>
+          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕14号)_国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="AI5" s="2" t="inlineStr">
@@ -6501,57 +6635,57 @@
       </c>
       <c r="AJ5" s="2" t="inlineStr">
         <is>
-          <t>字段“决定书文号”存在冲突:保留原值“北市税稽处〔2026〕6号”,新值“北市税稽处〔2026〕13号”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>CASE-97651030667b6c98</t>
+          <t>CASE-eb9cfd5295d501e5</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>DOC-f9817c8cadf0fc74</t>
+          <t>DOC-4a8cf53b445afc63</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>福州市</t>
+          <t>北海市</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>仓山区</t>
+          <t>海城区</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局北海市税务局稽查局</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>福州盛广弘贸易有限公司</t>
+          <t>广西轩易科技有限公司</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>91350104MA34D5PT77</t>
+          <t>91450500MAK3N9UJ2T</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
@@ -6562,46 +6696,46 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽处〔2025〕233号</t>
+          <t>北市税稽处〔2026〕6号</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽处〔2025〕233号</t>
+          <t>北市税稽处〔2026〕6号</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>我局于2023年12月25日起对你公司(地址:福建省福州市仓山区信平路6号二层41室)2022年1月1日至2023年11月30日期间的涉税情况进行检查,违法事实及处理决定如下: (二)你公司于2022年至2023年取得新余伟宏服装有限公司已证实虚开的254份正常状态增值税专用发票(金额合计24261915.72元,税额合计3154049.38元,价税合计27415965.10元)用于出口退税,通过假报出口或者其他欺骗手段骗取国家出口退税款3154049.14元。 (三)你公司于2022年至2023年取得宜春润悟服饰有限公司已证实虚开的220份正常状态增值税专用发票(金额合计20853824.88元,税额合计2710997.42元,价税合计23564822.30元),上述发票你公司均用于申报出口退税,取得已退税额2710997.41元。 (一)根据《中华人民共和国税收征收管理法》第六十六条规定,认定你公司取得新余伟宏服装有限公司已证实虚开的增值税专用发票254份(金额合计24261915.72元,税额合计3154049.38元,价税合计27415965.10元,取得退税款3154049.14元)并用于出口退税的属于骗取国家出口退税。 追缴你公司骗取的出口退税款3154049.14元,具体明细如下(单位:元): (二)根据《财政部 国家税务总局关于出口货物劳务增值税和消费税政策的通知》(财税〔2012〕39号)第七条第(一)项第5目、第九条第(二)项第5目、《国家税务总局关于&lt;出口货物劳务增值税和消费税管理办法&gt;有关问题的公告》(国家税务总局公告2013年第12号)第五条第(九)项第1目规定,你公司取得宜春润悟服饰有限公司已证实虚开的220份增值税专用发票(金额合计20853824.88元,税额合计2710997.42元,价税合计23564822.30元),申报出口退税并取得退税款2710997.41元,适用增值税征税政策,追缴已退税款2710997.41元,具体明细如下(单位:元):</t>
+          <t>我局于2026年1月23日起对你公司(地址:北海市海城区北部湾东路“金宝小区”B幢B804号20北海汇算账商务秘书有限公司托管)2025年12月11日至2025年12月31日期间的涉税情况进行了检查,发现你公司存在税收违法行为,原《税务处理决定书》(北市税稽处〔2026〕6号)认定的违法事实有误,经重新调查核实,违法事实及处理决定如下: 经查询,你公司2026年1月20日通过网络方式零申报所属期2025年10月1日-2025年12月31日的增值税、城市维护建设税及附加,入库税款0元,申报金额与实际不符,存在虚假申报的情况。 你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 (一)根据《中华人民共和国发票管理办法》(财政部令第6号发布,经国务院令第587号、第709号、第764号修订)第二十一条第二款第(一)项的规定,认定你公司为他人开具与实际经营业务情况不符的前述13份增值税普通电子发票为虚开发票(金额合计571550.49元,税额合计5715.51元,价税合计577266.00元)。 根据《中华人民共和国税收征收管理法》第三十二条、第六十三条第一款、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,已构成偷税,向你公司追缴少缴的税款合计5915.56元,并从滞纳税款之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R6" s="3" t="n">
-        <v>2710997.41</v>
+        <v>6058.46</v>
       </c>
       <c r="S6" s="3" t="n"/>
       <c r="T6" s="3" t="n"/>
       <c r="U6" s="3" t="n"/>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《征收教育费附加的暂行规定》第二条、第三条、《福建省人民政府关于调整地方教育附加征收标准有关问题的通知》(闽政文〔2011〕230号)第一条、第二条、《财政部 税务总局关于进一步实施小微企业“六税两费”减免政策的公告》(财政部 税务总局公告2022年第10号)第一条规定,你公司应补缴相应属期城市维护建设税合计83631.38元、教育费附加合计35842.03元、地方教育附加合计23894.68元,具体明细如下(单位:元):</t>
+          <t>你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《中华人民共和国城市维护建设税法》(中华人民共和国主席令第五十一号)第一条、第二条、第四条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×7%×50%=200.05元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)、《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×3%×50%=85.74元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳地方教育附加5715.51×2%×50%=57.16元。</t>
         </is>
       </c>
       <c r="W6" s="4" t="n"/>
       <c r="X6" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="Y6" s="4" t="n"/>
       <c r="Z6" s="4" t="n">
-        <v>46238</v>
+        <v>46234</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -6627,9 +6761,7 @@
       <c r="AG6" s="2" t="inlineStr"/>
       <c r="AH6" s="2" t="inlineStr">
         <is>
-          <t>关于送达福州盛广弘贸易有限公司《税务处理决定书》的公告 _
- 其他类 _
- 国家税务总局福州市税务局</t>
+          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕13号)_国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="AI6" s="2" t="inlineStr">
@@ -6639,22 +6771,22 @@
       </c>
       <c r="AJ6" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>字段“决定书文号”存在冲突:保留原值“北市税稽处〔2026〕6号”,新值“北市税稽处〔2026〕13号”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CASE-7b9a26f2ac401107</t>
+          <t>CASE-97651030667b6c98</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>DOC-f6c6ea472b2ca04a</t>
+          <t>DOC-f9817c8cadf0fc74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -6664,28 +6796,32 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>三明市</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
+          <t>福州市</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>仓山区</t>
+        </is>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局三明市税务局第一稽查局</t>
+          <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局三明市税务局第一稽查局</t>
+          <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>三明众祥房地产开发有限公司</t>
+          <t>福州盛广弘贸易有限公司</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>91350400678473231W</t>
+          <t>91350104MA34D5PT77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
@@ -6696,46 +6832,46 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>明税一稽处〔2026〕20号</t>
+          <t>榕税一稽处〔2025〕233号</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>明税一稽处〔2026〕20号</t>
+          <t>榕税一稽处〔2025〕233号</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2016年期间,在没有真实业务情况下,取得重庆市博海建设工程(集团)有限公司、福建九九建设有限公司三明分公司开具的不符合规定的发票,发票金额400252379元,在企业所得税税前扣除,造成少缴纳企业所得税100063094.75元,该行为违反《中华人民共和国税收征收管理法》(2015年4月24日主席令第二十三号修改)第六十三条第一款 纳税人伪造、变造、隐匿、擅自销毁账簿、记账凭证,或者在账簿上多列支出或者不列、少列收入,或者经税务机关通知申报而拒不申报或者进行虚假的纳税申报,不缴或者少缴应纳税款的,是偷税。 对纳税人偷税的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款; 之规定,对你公司在账上多列支出,造成少缴企业所得税100063094.75元的行为认定为偷税。 之规定,对你公司少缴的企业所得税从滞纳之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
+          <t>我局于2023年12月25日起对你公司(地址:福建省福州市仓山区信平路6号二层41室)2022年1月1日至2023年11月30日期间的涉税情况进行检查,违法事实及处理决定如下: (二)你公司于2022年至2023年取得新余伟宏服装有限公司已证实虚开的254份正常状态增值税专用发票(金额合计24261915.72元,税额合计3154049.38元,价税合计27415965.10元)用于出口退税,通过假报出口或者其他欺骗手段骗取国家出口退税款3154049.14元。 (三)你公司于2022年至2023年取得宜春润悟服饰有限公司已证实虚开的220份正常状态增值税专用发票(金额合计20853824.88元,税额合计2710997.42元,价税合计23564822.30元),上述发票你公司均用于申报出口退税,取得已退税额2710997.41元。 (一)根据《中华人民共和国税收征收管理法》第六十六条规定,认定你公司取得新余伟宏服装有限公司已证实虚开的增值税专用发票254份(金额合计24261915.72元,税额合计3154049.38元,价税合计27415965.10元,取得退税款3154049.14元)并用于出口退税的属于骗取国家出口退税。 追缴你公司骗取的出口退税款3154049.14元,具体明细如下(单位:元): (二)根据《财政部 国家税务总局关于出口货物劳务增值税和消费税政策的通知》(财税〔2012〕39号)第七条第(一)项第5目、第九条第(二)项第5目、《国家税务总局关于&lt;出口货物劳务增值税和消费税管理办法&gt;有关问题的公告》(国家税务总局公告2013年第12号)第五条第(九)项第1目规定,你公司取得宜春润悟服饰有限公司已证实虚开的220份增值税专用发票(金额合计20853824.88元,税额合计2710997.42元,价税合计23564822.30元),申报出口退税并取得退税款2710997.41元,适用增值税征税政策,追缴已退税款2710997.41元,具体明细如下(单位:元):</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>企业所得税</t>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R7" s="3" t="n">
-        <v>100063094.75</v>
+        <v>2710997.41</v>
       </c>
       <c r="S7" s="3" t="n"/>
       <c r="T7" s="3" t="n"/>
       <c r="U7" s="3" t="n"/>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>据《中华人民共和国税收征收管理法实施细则》第106条规定,将该文书予以公告送达,自公告之日起满30日视为送达。</t>
+          <t>根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《征收教育费附加的暂行规定》第二条、第三条、《福建省人民政府关于调整地方教育附加征收标准有关问题的通知》(闽政文〔2011〕230号)第一条、第二条、《财政部 税务总局关于进一步实施小微企业“六税两费”减免政策的公告》(财政部 税务总局公告2022年第10号)第一条规定,你公司应补缴相应属期城市维护建设税合计83631.38元、教育费附加合计35842.03元、地方教育附加合计23894.68元,具体明细如下(单位:元):</t>
         </is>
       </c>
       <c r="W7" s="4" t="n"/>
       <c r="X7" s="4" t="n">
-        <v>46223</v>
+        <v>46231</v>
       </c>
       <c r="Y7" s="4" t="n"/>
       <c r="Z7" s="4" t="n">
-        <v>46229</v>
+        <v>46238</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -6761,9 +6897,9 @@
       <c r="AG7" s="2" t="inlineStr"/>
       <c r="AH7" s="2" t="inlineStr">
         <is>
-          <t>关于送达三明众祥房地产开发有限公司 《税务处理决定书》的公告 _
- 其他公告 _
- 国家税务总局三明市税务局</t>
+          <t>关于送达福州盛广弘贸易有限公司《税务处理决定书》的公告 _
+ 其他类 _
+ 国家税务总局福州市税务局</t>
         </is>
       </c>
       <c r="AI7" s="2" t="inlineStr">
@@ -6779,16 +6915,16 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CASE-31e4a827dfd253f2</t>
+          <t>CASE-7b9a26f2ac401107</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DOC-3ec54358fce2350d</t>
+          <t>DOC-f6c6ea472b2ca04a</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -6798,28 +6934,28 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>福州市</t>
+          <t>三明市</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局三明市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局三明市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>福州顺路汽车运输有限公司</t>
+          <t>三明众祥房地产开发有限公司</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>91350102MA31MF6611</t>
+          <t>91350400678473231W</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
@@ -6830,46 +6966,46 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽处〔2026〕137号</t>
+          <t>明税一稽处〔2026〕20号</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽处〔2026〕137号</t>
+          <t>明税一稽处〔2026〕20号</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>我局于2025年7月10日起对你公司(地址:福建省闽侯县青口镇祥宏南路922号)2023年1月1日至2024年12月31日期间的发票涉税情况进行检查,违法事实及处理决定如下: (二)你公司取得毕节七星关区辰楚汽车服务部(个人独资)、毕节七星关锦悦汽车服务部(个人独资)、贵州杨亭汽车销售有限公司、贵州楠鑫汽车销售有限公司已证实虚开的35份机动车发票。 (二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 (三)根据《中华人民共和国企业所得税法》第五条、第八条、《企业所得税税前扣除凭证管理办法》(国家税务总局公告2018年第28号发布)第四条、第十二条的规定,你公司取得上述虚开的发票不得作为税前扣除凭证。</t>
+          <t>情况进行了检查,违法事实及处理决定如下: 2016年期间,在没有真实业务情况下,取得重庆市博海建设工程(集团)有限公司、福建九九建设有限公司三明分公司开具的不符合规定的发票,发票金额400252379元,在企业所得税税前扣除,造成少缴纳企业所得税100063094.75元,该行为违反《中华人民共和国税收征收管理法》(2015年4月24日主席令第二十三号修改)第六十三条第一款 纳税人伪造、变造、隐匿、擅自销毁账簿、记账凭证,或者在账簿上多列支出或者不列、少列收入,或者经税务机关通知申报而拒不申报或者进行虚假的纳税申报,不缴或者少缴应纳税款的,是偷税。 对纳税人偷税的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款; 之规定,对你公司在账上多列支出,造成少缴企业所得税100063094.75元的行为认定为偷税。 之规定,对你公司少缴的企业所得税从滞纳之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
+          <t>企业所得税</t>
         </is>
       </c>
       <c r="R8" s="3" t="n">
-        <v>3778.22</v>
+        <v>100063094.75</v>
       </c>
       <c r="S8" s="3" t="n"/>
       <c r="T8" s="3" t="n"/>
       <c r="U8" s="3" t="n"/>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>(二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期城市维护建设税124.75元。 根据《征收教育费附加的暂行规定》第二条、第三条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期教育费附加53.47元。 根据《福建省人民政府关于调整地方教育附加征收标准等有关问题的通知》(闽政文〔2011〕230号)第一条、第二条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期地方教育附加35.64元。</t>
+          <t>据《中华人民共和国税收征收管理法实施细则》第106条规定,将该文书予以公告送达,自公告之日起满30日视为送达。</t>
         </is>
       </c>
       <c r="W8" s="4" t="n"/>
       <c r="X8" s="4" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="Y8" s="4" t="n"/>
       <c r="Z8" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -6895,9 +7031,9 @@
       <c r="AG8" s="2" t="inlineStr"/>
       <c r="AH8" s="2" t="inlineStr">
         <is>
-          <t>关于送达福州顺路汽车运输有限公司《税务处理决定书》的公告 _
- 其他类 _
- 国家税务总局福州市税务局</t>
+          <t>关于送达三明众祥房地产开发有限公司 《税务处理决定书》的公告 _
+ 其他公告 _
+ 国家税务总局三明市税务局</t>
         </is>
       </c>
       <c r="AI8" s="2" t="inlineStr">
@@ -6913,16 +7049,16 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>CASE-3f564fd9992b1ae3</t>
+          <t>CASE-31e4a827dfd253f2</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DOC-c34e1d13286aafe2</t>
+          <t>DOC-3ec54358fce2350d</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -6932,28 +7068,28 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>泉州市</t>
+          <t>福州市</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局第二稽查局</t>
+          <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局第二稽查局</t>
+          <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>泉州隆鸿服装制造有限公司</t>
+          <t>福州顺路汽车运输有限公司</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91350525MA8U3U963L</t>
+          <t>91350102MA31MF6611</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -6964,18 +7100,18 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>泉税二稽处〔2026〕107号</t>
+          <t>榕税一稽处〔2026〕137号</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>泉税二稽处〔2026〕107号</t>
+          <t>榕税一稽处〔2026〕137号</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>日对你公司税收违法事实依法作出《税务处理决定书》(泉税二稽处〔 涉税情况进行了检查,查明违法事实及处理决定如下: 年你公司在无真实货物交易的情况下,取得河南中弘纺织有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 年期间,你公司在无真实货物交易的情况下,取得开封兴旺纺织品有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 上述违法事实有检查人员实地检查资料、电话拨打记录、邮寄退回函件、《已证实虚开通知单》等相关受托协查资料、主管税务机关出具的《已抵扣证明》、《情况说明》和你公司的申报纳税资料、银行账户流水等 号第三次修订)第二十一条第二款第二项之规定,认定你公司让他人为自己虚开 号第二次修订)第九条和《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告〔 号)之规定,对你公司取得上述已证实虚开的 之规定,决定向你公司追缴少缴的城市维护建设税-增值税附征 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 规定,决定向你公司追缴少缴的教育费附加-增值税附征 规定,决定向你公司追缴少缴的地方教育附加-增值税附征</t>
+          <t>我局于2025年7月10日起对你公司(地址:福建省闽侯县青口镇祥宏南路922号)2023年1月1日至2024年12月31日期间的发票涉税情况进行检查,违法事实及处理决定如下: (二)你公司取得毕节七星关区辰楚汽车服务部(个人独资)、毕节七星关锦悦汽车服务部(个人独资)、贵州杨亭汽车销售有限公司、贵州楠鑫汽车销售有限公司已证实虚开的35份机动车发票。 (二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 (三)根据《中华人民共和国企业所得税法》第五条、第八条、《企业所得税税前扣除凭证管理办法》(国家税务总局公告2018年第28号发布)第四条、第十二条的规定,你公司取得上述虚开的发票不得作为税前扣除凭证。</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6983,25 +7119,27 @@
           <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R9" s="3" t="n"/>
+      <c r="R9" s="3" t="n">
+        <v>3778.22</v>
+      </c>
       <c r="S9" s="3" t="n"/>
       <c r="T9" s="3" t="n"/>
       <c r="U9" s="3" t="n"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>由于你公司走逃失联、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 (五)根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司上述应补缴税款按税款所属时间从税款滞纳之日起按日加收万分之五滞纳金</t>
+          <t>(二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期城市维护建设税124.75元。 根据《征收教育费附加的暂行规定》第二条、第三条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期教育费附加53.47元。 根据《福建省人民政府关于调整地方教育附加征收标准等有关问题的通知》(闽政文〔2011〕230号)第一条、第二条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期地方教育附加35.64元。</t>
         </is>
       </c>
       <c r="W9" s="4" t="n"/>
       <c r="X9" s="4" t="n">
-        <v>46202</v>
+        <v>46218</v>
       </c>
       <c r="Y9" s="4" t="n"/>
       <c r="Z9" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -7027,9 +7165,9 @@
       <c r="AG9" s="2" t="inlineStr"/>
       <c r="AH9" s="2" t="inlineStr">
         <is>
-          <t>关于对泉州隆鸿服装制造有限公司《税务处理决定书》送达的公告 _
- 其他公告 _
- 国家税务总局泉州市税务局</t>
+          <t>关于送达福州顺路汽车运输有限公司《税务处理决定书》的公告 _
+ 其他类 _
+ 国家税务总局福州市税务局</t>
         </is>
       </c>
       <c r="AI9" s="2" t="inlineStr">
@@ -7045,47 +7183,47 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CASE-a62e569c195adc3c</t>
+          <t>CASE-3f564fd9992b1ae3</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DOC-b1dda915d4e6117d</t>
+          <t>DOC-c34e1d13286aafe2</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>遵义市</t>
+          <t>泉州市</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局泉州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局泉州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>贵州服格定商贸有限公司</t>
+          <t>泉州隆鸿服装制造有限公司</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>91520302MABUEHN034</t>
+          <t>91350525MA8U3U963L</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
@@ -7096,40 +7234,44 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>遵税一稽处〔2026〕30号</t>
+          <t>泉税二稽处〔2026〕107号</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>遵税一稽处〔2026〕30号</t>
+          <t>泉税二稽处〔2026〕107号</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
+          <t>日对你公司税收违法事实依法作出《税务处理决定书》(泉税二稽处〔 涉税情况进行了检查,查明违法事实及处理决定如下: 年你公司在无真实货物交易的情况下,取得河南中弘纺织有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 年期间,你公司在无真实货物交易的情况下,取得开封兴旺纺织品有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 上述违法事实有检查人员实地检查资料、电话拨打记录、邮寄退回函件、《已证实虚开通知单》等相关受托协查资料、主管税务机关出具的《已抵扣证明》、《情况说明》和你公司的申报纳税资料、银行账户流水等 号第三次修订)第二十一条第二款第二项之规定,认定你公司让他人为自己虚开 号第二次修订)第九条和《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告〔 号)之规定,对你公司取得上述已证实虚开的 之规定,决定向你公司追缴少缴的城市维护建设税-增值税附征 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 规定,决定向你公司追缴少缴的教育费附加-增值税附征 规定,决定向你公司追缴少缴的地方教育附加-增值税附征</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
+          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R10" s="3" t="n"/>
       <c r="S10" s="3" t="n"/>
       <c r="T10" s="3" t="n"/>
       <c r="U10" s="3" t="n"/>
-      <c r="V10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>由于你公司走逃失联、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 (五)根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司上述应补缴税款按税款所属时间从税款滞纳之日起按日加收万分之五滞纳金</t>
+        </is>
+      </c>
       <c r="W10" s="4" t="n"/>
       <c r="X10" s="4" t="n">
-        <v>46185</v>
+        <v>46202</v>
       </c>
       <c r="Y10" s="4" t="n"/>
       <c r="Z10" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -7155,7 +7297,9 @@
       <c r="AG10" s="2" t="inlineStr"/>
       <c r="AH10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
+          <t>关于对泉州隆鸿服装制造有限公司《税务处理决定书》送达的公告 _
+ 其他公告 _
+ 国家税务总局泉州市税务局</t>
         </is>
       </c>
       <c r="AI10" s="2" t="inlineStr">
@@ -7171,54 +7315,50 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>CASE-f94bf08964abff5a</t>
+          <t>CASE-a62e569c195adc3c</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>DOC-4574b1aadef8f30d</t>
+          <t>DOC-b1dda915d4e6117d</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
+          <t>遵义市</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
+          <t>国家税务总局遵义市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局稽查局</t>
+          <t>国家税务总局遵义市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>常州市文杰车辆配件厂</t>
+          <t>贵州服格定商贸有限公司</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91320411799075280A</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>朱某</t>
-        </is>
-      </c>
+          <t>91520302MABUEHN034</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t>税务处理决定书</t>
@@ -7226,48 +7366,40 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕73号</t>
+          <t>遵税一稽处〔2026〕30号</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕73号</t>
+          <t>遵税一稽处〔2026〕30号</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公 月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
+          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>179137.12</v>
-      </c>
+          <t>增值税</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="n"/>
       <c r="S11" s="3" t="n"/>
       <c r="T11" s="3" t="n"/>
       <c r="U11" s="3" t="n"/>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市 份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元,</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="n">
-        <v>46044</v>
-      </c>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="4" t="n"/>
       <c r="X11" s="4" t="n">
-        <v>46090</v>
+        <v>46185</v>
       </c>
       <c r="Y11" s="4" t="n"/>
       <c r="Z11" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -7289,20 +7421,16 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF11" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF11" s="2" t="inlineStr"/>
       <c r="AG11" s="2" t="inlineStr"/>
       <c r="AH11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
+          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
         </is>
       </c>
       <c r="AI11" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ11" s="2" t="inlineStr">
@@ -7313,16 +7441,16 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CASE-61b9b55a9d3357c7</t>
+          <t>CASE-f94bf08964abff5a</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>DOC-1228a9c92b2b0632</t>
+          <t>DOC-4574b1aadef8f30d</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -7338,25 +7466,29 @@
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局常州市税务局稽查局</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>常州市三鹏机械有限公司</t>
+          <t>常州市文杰车辆配件厂</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>91320404732260748Q</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr"/>
+          <t>91320411799075280A</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>朱某</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
           <t>税务处理决定书</t>
@@ -7364,46 +7496,48 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
+          <t>常税稽处〔2026〕73号</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>常税稽一罚〔2026〕14号</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
+          <t>常税稽处〔2026〕73号</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公 月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
+        </is>
+      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R12" s="3" t="n">
-        <v>63464.09</v>
+        <v>179137.12</v>
       </c>
       <c r="S12" s="3" t="n"/>
       <c r="T12" s="3" t="n"/>
       <c r="U12" s="3" t="n"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
-        </is>
-      </c>
-      <c r="W12" s="4" t="n"/>
+          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市 份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元,</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="n">
+        <v>46044</v>
+      </c>
       <c r="X12" s="4" t="n">
-        <v>46066</v>
+        <v>46090</v>
       </c>
       <c r="Y12" s="4" t="n"/>
       <c r="Z12" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -7425,16 +7559,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AF12" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG12" s="2" t="inlineStr"/>
       <c r="AH12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI12" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ12" s="2" t="inlineStr">
@@ -7445,7 +7583,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
@@ -7454,7 +7592,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>DOC-b97456a64b153f67</t>
+          <t>DOC-1228a9c92b2b0632</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -7491,12 +7629,12 @@
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>常税稽一罚〔2026〕14号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7515,11 +7653,11 @@
           <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R13" s="3" t="n"/>
+      <c r="R13" s="3" t="n">
+        <v>63464.09</v>
+      </c>
       <c r="S13" s="3" t="n"/>
-      <c r="T13" s="3" t="n">
-        <v>20000</v>
-      </c>
+      <c r="T13" s="3" t="n"/>
       <c r="U13" s="3" t="n"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
@@ -7535,7 +7673,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -7577,103 +7715,97 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASE-f78ec1a594442165</t>
+          <t>CASE-61b9b55a9d3357c7</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DOC-fbbe4a664b14f54b</t>
+          <t>DOC-b97456a64b153f67</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>安顺市</t>
+          <t>常州市</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
+          <t>常州市三鹏机械有限公司</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>91520423MA6DLH799Q</t>
+          <t>91320404732260748Q</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一罚〔2026〕14号</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
-        </is>
-      </c>
+          <t>常税稽一罚〔2026〕14号</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>64884.41</v>
-      </c>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="n"/>
       <c r="S14" s="3" t="n"/>
-      <c r="T14" s="3" t="n"/>
+      <c r="T14" s="3" t="n">
+        <v>20000</v>
+      </c>
       <c r="U14" s="3" t="n"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
-      <c r="W14" s="4" t="n">
-        <v>45898</v>
-      </c>
+          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="n"/>
       <c r="X14" s="4" t="n">
-        <v>46043</v>
+        <v>46066</v>
       </c>
       <c r="Y14" s="4" t="n"/>
       <c r="Z14" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -7695,31 +7827,27 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF14" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF14" s="2" t="inlineStr"/>
       <c r="AG14" s="2" t="inlineStr"/>
       <c r="AH14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI14" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ14" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。 字段“主要违法事实”存在冲突:保留原值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”,新值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
@@ -7728,7 +7856,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>DOC-9a828a6048b54b6c</t>
+          <t>DOC-fbbe4a664b14f54b</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -7765,24 +7893,24 @@
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
           <t>安市税稽罚〔2026〕1号</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>安市税稽处〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
           <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
@@ -7793,11 +7921,11 @@
           <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R15" s="3" t="n"/>
+      <c r="R15" s="3" t="n">
+        <v>64884.41</v>
+      </c>
       <c r="S15" s="3" t="n"/>
-      <c r="T15" s="3" t="n">
-        <v>200000</v>
-      </c>
+      <c r="T15" s="3" t="n"/>
       <c r="U15" s="3" t="n"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
@@ -7815,7 +7943,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -7855,97 +7983,109 @@
       </c>
       <c r="AJ15" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。 字段“主要违法事实”存在冲突:保留原值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”,新值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CASE-fe959d4c6c52d910</t>
+          <t>CASE-f78ec1a594442165</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>DOC-f2643f2a0719d8d1</t>
+          <t>DOC-9a828a6048b54b6c</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>南宁市</t>
+          <t>安顺市</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局稽查局</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>南宁洪谦金贸易有限公司</t>
+          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>91450103MA5K9WHY7U</t>
+          <t>91520423MA6DLH799Q</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>南市税一稽处〔2026〕2号</t>
+          <t>安市税稽罚〔2026〕1号</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>南市税一稽处〔2026〕2号</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr"/>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽罚〔2026〕1号</t>
+        </is>
+      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>经我局2025年10月29日至2025年12月8日对你公司(地址:南宁市青秀区云景路11号春晖花园C区3栋2单元1606号)2015年12月2日至2016年12月31日期间的涉税情况进行了检查,你(单位)存在以下违法事实: 经查询你公司向税务机关报备的银行账号:广西北部湾银行南宁市财富国际支行800099398800015,经函询广西北部湾银行南宁市财富国际支行,存在以下问题: 上述行为属于开具与实际经营业务情况不符的增值税发票,违反了《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第587号修改)第二十二条第一款、第二款第(一)项的规定,属于虚开发票行为。</t>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
+          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R16" s="3" t="n"/>
       <c r="S16" s="3" t="n"/>
-      <c r="T16" s="3" t="n"/>
+      <c r="T16" s="3" t="n">
+        <v>200000</v>
+      </c>
       <c r="U16" s="3" t="n"/>
-      <c r="V16" s="2" t="inlineStr"/>
-      <c r="W16" s="4" t="n"/>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="W16" s="4" t="n">
+        <v>45898</v>
+      </c>
       <c r="X16" s="4" t="n">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="Y16" s="4" t="n"/>
       <c r="Z16" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -7975,7 +8115,7 @@
       <c r="AG16" s="2" t="inlineStr"/>
       <c r="AH16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局税务文书送达公告_国家税务总局南宁市税务局</t>
+          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI16" s="2" t="inlineStr">
@@ -7985,51 +8125,55 @@
       </c>
       <c r="AJ16" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CASE-1983d97878508732</t>
+          <t>CASE-fe959d4c6c52d910</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>DOC-f9760895b4f08cc2</t>
+          <t>DOC-f2643f2a0719d8d1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>二连浩特市</t>
+          <t>南宁市</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局</t>
+          <t>国家税务总局南宁市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局稽查局</t>
+          <t>国家税务总局南宁市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>二连市坤益腾金属有限公司</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr"/>
+          <t>南宁洪谦金贸易有限公司</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>91450103MA5K9WHY7U</t>
+        </is>
+      </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
@@ -8038,18 +8182,18 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
+          <t>南市税一稽处〔2026〕2号</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
+          <t>南市税一稽处〔2026〕2号</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
+          <t>经我局2025年10月29日至2025年12月8日对你公司(地址:南宁市青秀区云景路11号春晖花园C区3栋2单元1606号)2015年12月2日至2016年12月31日期间的涉税情况进行了检查,你(单位)存在以下违法事实: 经查询你公司向税务机关报备的银行账号:广西北部湾银行南宁市财富国际支行800099398800015,经函询广西北部湾银行南宁市财富国际支行,存在以下问题: 上述行为属于开具与实际经营业务情况不符的增值税发票,违反了《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第587号修改)第二十二条第一款、第二款第(一)项的规定,属于虚开发票行为。</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8061,19 +8205,17 @@
       <c r="S17" s="3" t="n"/>
       <c r="T17" s="3" t="n"/>
       <c r="U17" s="3" t="n"/>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
-        </is>
-      </c>
+      <c r="V17" s="2" t="inlineStr"/>
       <c r="W17" s="4" t="n"/>
-      <c r="X17" s="4" t="n"/>
+      <c r="X17" s="4" t="n">
+        <v>46031</v>
+      </c>
       <c r="Y17" s="4" t="n"/>
       <c r="Z17" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -8087,7 +8229,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE17" s="5" t="inlineStr">
@@ -8095,36 +8237,40 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AF17" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG17" s="2" t="inlineStr"/>
       <c r="AH17" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>国家税务总局南宁市税务局第一稽查局税务文书送达公告_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI17" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ17" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CASE-d4b6986f3f97cd28</t>
+          <t>CASE-1983d97878508732</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>DOC-442cf3d9a5280c12</t>
+          <t>DOC-f9760895b4f08cc2</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -8134,19 +8280,23 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>鄂尔多斯市</t>
+          <t>二连浩特市</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局二连浩特市税务局</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>第二稽查局</t>
+          <t>国家税务总局二连浩特市税务局稽查局</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>廖礼平</t>
+          <t>二连市坤益腾金属有限公司</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -8158,36 +8308,32 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
+          <t>二税稽处〔2025〕1号</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
+          <t>二税稽处〔2025〕1号</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
+          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>个人所得税、印花税</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>15072487.5</v>
-      </c>
-      <c r="S18" s="3" t="n">
-        <v>1046925</v>
-      </c>
+          <t>增值税</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="n"/>
+      <c r="S18" s="3" t="n"/>
       <c r="T18" s="3" t="n"/>
       <c r="U18" s="3" t="n"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
+          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
         </is>
       </c>
       <c r="W18" s="4" t="n"/>
@@ -8197,7 +8343,7 @@
         <v>46229</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -8233,55 +8379,47 @@
       </c>
       <c r="AJ18" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
+          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CASE-7e3d4a321440d6a7</t>
+          <t>CASE-d4b6986f3f97cd28</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>DOC-bed9330343ed06af</t>
+          <t>DOC-442cf3d9a5280c12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>鄂尔多斯市</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
-        </is>
-      </c>
+      <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
+          <t>第二稽查局</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>天津展达科技有限公司</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>91120116300738701X</t>
-        </is>
-      </c>
+          <t>廖礼平</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
@@ -8290,48 +8428,46 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
+          <t>鄂税二稽处〔2023〕29号</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
+          <t>鄂税二稽处〔2023〕29号</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+          <t>个人所得税、印花税</t>
         </is>
       </c>
       <c r="R19" s="3" t="n">
-        <v>920146.9399999999</v>
-      </c>
-      <c r="S19" s="3" t="n"/>
+        <v>15072487.5</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>1046925</v>
+      </c>
       <c r="T19" s="3" t="n"/>
       <c r="U19" s="3" t="n"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
         </is>
       </c>
       <c r="W19" s="4" t="n"/>
       <c r="X19" s="4" t="n"/>
       <c r="Y19" s="4" t="n"/>
       <c r="Z19" s="4" t="n">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -8357,7 +8493,7 @@
       <c r="AG19" s="2" t="inlineStr"/>
       <c r="AH19" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="AI19" s="2" t="inlineStr">
@@ -8367,13 +8503,13 @@
       </c>
       <c r="AJ19" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
@@ -8382,7 +8518,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>DOC-388bd01c01bbb789</t>
+          <t>DOC-bed9330343ed06af</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -8419,24 +8555,24 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
           <t>津税一稽罚〔2023〕21号</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
           <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
@@ -8447,11 +8583,11 @@
           <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R20" s="3" t="n"/>
+      <c r="R20" s="3" t="n">
+        <v>920146.9399999999</v>
+      </c>
       <c r="S20" s="3" t="n"/>
-      <c r="T20" s="3" t="n">
-        <v>131368.5</v>
-      </c>
+      <c r="T20" s="3" t="n"/>
       <c r="U20" s="3" t="n"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
@@ -8465,7 +8601,7 @@
         <v>46230</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -8505,47 +8641,183 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7e3d4a321440d6a7</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>DOC-388bd01c01bbb789</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>91120116300738701X</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>税务行政处罚决定书</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="n"/>
+      <c r="S21" s="3" t="n"/>
+      <c r="T21" s="3" t="n">
+        <v>131368.5</v>
+      </c>
+      <c r="U21" s="3" t="n"/>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W21" s="4" t="n"/>
+      <c r="X21" s="4" t="n"/>
+      <c r="Y21" s="4" t="n"/>
+      <c r="Z21" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AA21" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD21" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE21" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AG21" s="2" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+        </is>
+      </c>
+      <c r="AI21" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ21" s="2" t="inlineStr">
+        <is>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ20"/>
-  <conditionalFormatting sqref="AD2:AD20">
+  <autoFilter ref="A1:AJ21"/>
+  <conditionalFormatting sqref="AD2:AD21">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AD2="待核验"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI2:AI20">
+  <conditionalFormatting sqref="AI2:AI21">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>AND($AI2&lt;&gt;"正常",$AI2&lt;&gt;"附件正常")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AD2:AD20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AD2:AD21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"已核验,待核验,人工复核完成"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE10" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE11" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE12" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE14" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF14" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF12" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE14" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE15" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF15" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE16" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF16" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE17" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE18" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE19" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE20" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF17" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE18" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE19" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE20" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE21" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -8863,7 +9135,7 @@
         <v>46236</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -8989,7 +9261,7 @@
         <v>46236</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -9115,7 +9387,7 @@
         <v>46238</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -9241,7 +9513,7 @@
         <v>46238</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -9363,7 +9635,7 @@
         <v>46238</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -9481,7 +9753,7 @@
         <v>46238</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -9603,7 +9875,7 @@
         <v>46229</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -9721,7 +9993,7 @@
         <v>46229</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -9843,7 +10115,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -9969,7 +10241,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -10095,7 +10367,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -10213,7 +10485,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -10335,7 +10607,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -10457,7 +10729,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -10579,7 +10851,7 @@
         <v>46229</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -10701,7 +10973,7 @@
         <v>46229</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -10823,7 +11095,7 @@
         <v>46229</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -10945,7 +11217,7 @@
         <v>46229</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -11063,7 +11335,7 @@
         <v>46229</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -11185,7 +11457,7 @@
         <v>46229</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -11590,7 +11862,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -11708,7 +11980,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -11826,7 +12098,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -11954,7 +12226,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -12078,7 +12350,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -12212,7 +12484,7 @@
         <v>46230</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -12346,7 +12618,7 @@
         <v>46230</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -12725,7 +12997,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -12843,7 +13115,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -12961,7 +13233,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -13039,7 +13311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14656,8 +14928,61 @@
         </is>
       </c>
     </row>
+    <row r="34" ht="54" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T14:42:00+08:00</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 至 2026-08-06</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>北海市丰赢商贸有限公司</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinatax.gov.cn', port=443): Max retries exceeded with url: /fzsswj/xxgk/gsgg/qtl/ (Caused by NewConnectionError("HTTPSConnection(host='fujian.chinatax.gov.cn', port=44...</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>已完成候选发现、逐条访问核验、去重、关联和历史数据增量写入。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M33"/>
+  <autoFilter ref="A1:M34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -15,12 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日运行日志" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文书汇总'!$A$1:$AJ$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'完整文书'!$A$1:$AJ$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文书汇总'!$A$1:$AJ$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'完整文书'!$A$1:$AJ$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ41"/>
+  <dimension ref="A1:AJ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -835,7 +835,11 @@
           <t>附件正常</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -2363,47 +2367,47 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CASE-365e8a924cf64611</t>
+          <t>CASE-1a685b98e7b293c8</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>DOC-4d14eba16f9aa8a0</t>
+          <t>DOC-9b5fab8065382bd9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>辽宁省</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>铁岭市</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局铁岭市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局铁岭市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>贵州博泰工贸有限公司</t>
+          <t>辽宁恒慧专用车箱有限公司</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>91520115587255589F</t>
+          <t>91211200683741982W</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
@@ -2414,36 +2418,56 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕38号</t>
+          <t>铁税一稽处〔2026〕35号</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕38号</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="3" t="n"/>
+          <t>铁税一稽处〔2026〕35号</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>铁税一稽罚〔2026〕17号</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>查属期内违法行为均定性偷税, 需要对原处罚决定中的罚款数额 以变更,你(单位)存在违法事实及处罚决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 〔2022〕59号) 第一条、 第三条之规定, 你单位存在少缴属期2010 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。 月属期申报数据,用于证明你单位未申报缴纳印花税。 报,不缴或者少缴应纳税款的,是偷税。 务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴 内首次因偷税被税务机关处罚,并能够配合税务机关检查的,处 不缴或者少缴的税款百分之五十的罚款”之规定,对你单位城镇 土地使用税和印花税处不缴或者少缴的税款50%的罚款。 你单位印花税偷税违法行为发生于2009年11月26日,至立案 位检查属期内违法行为均定性偷税, 需要对原处理决定中的查补 情况进行了检查,违法事实及处理决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 定, 你单位存在少缴属期2010年1月至2022年6月城镇土地使 用税5,710,765.50元的违法事实。 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 该地块未缴纳契税,你单位存在少缴契税509,984.64元的违法 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>增值税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、契税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44269.5</v>
+      </c>
       <c r="S15" s="3" t="n"/>
       <c r="T15" s="3" t="n"/>
       <c r="U15" s="3" t="n"/>
-      <c r="V15" s="2" t="inlineStr"/>
-      <c r="W15" s="4" t="n"/>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>定,每日按罚款数额的百分之三加处罚款。 日”之规定,你单位每月应补缴城镇土地使用税44,269.50元 征收城镇土地使用税, 自2010年1月至2022年6月应补缴城镇 所载金额的万分之五,你单位应补缴2009年11月26日印花税 日”之规定,你单位每月应补缴城镇土地使用税44,269.50元 征收城镇土地使用税, 自2010年1月至2022年6月应补缴城镇 所载金额的万分之五,你单位应补缴2009年11月26日印花税</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="n">
+        <v>46183</v>
+      </c>
       <c r="X15" s="4" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="Y15" s="4" t="n"/>
       <c r="Z15" s="4" t="n">
-        <v>46229</v>
+        <v>46240</v>
       </c>
       <c r="AA15" s="4" t="n">
         <v>46240</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2461,114 +2485,124 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AF15" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG15" s="2" t="inlineStr"/>
       <c r="AH15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书、税务行政处罚决定书的公告</t>
+          <t>国家税务总局辽宁省税务局 通知公告 国家税务总局铁岭市税务局税务文书送达公告</t>
         </is>
       </c>
       <c r="AI15" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ15" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>字段“决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处理决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处罚决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CASE-7b9a26f2ac401107</t>
+          <t>CASE-1a685b98e7b293c8</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>DOC-f6c6ea472b2ca04a</t>
+          <t>DOC-8fc89a4906937181</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>辽宁省</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>三明市</t>
+          <t>铁岭市</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局三明市税务局第一稽查局</t>
+          <t>国家税务总局铁岭市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局三明市税务局第一稽查局</t>
+          <t>国家税务总局铁岭市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>三明众祥房地产开发有限公司</t>
+          <t>辽宁恒慧专用车箱有限公司</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>91350400678473231W</t>
+          <t>91211200683741982W</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>明税一稽处〔2026〕20号</t>
+          <t>铁税一稽罚〔2026〕17号</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>明税一稽处〔2026〕20号</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr"/>
+          <t>铁税一稽处〔2026〕35号</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>铁税一稽罚〔2026〕17号</t>
+        </is>
+      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2016年期间,在没有真实业务情况下,取得重庆市博海建设工程(集团)有限公司、福建九九建设有限公司三明分公司开具的不符合规定的发票,发票金额400252379元,在企业所得税税前扣除,造成少缴纳企业所得税100063094.75元,该行为违反《中华人民共和国税收征收管理法》(2015年4月24日主席令第二十三号修改)第六十三条第一款 纳税人伪造、变造、隐匿、擅自销毁账簿、记账凭证,或者在账簿上多列支出或者不列、少列收入,或者经税务机关通知申报而拒不申报或者进行虚假的纳税申报,不缴或者少缴应纳税款的,是偷税。 对纳税人偷税的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款; 之规定,对你公司在账上多列支出,造成少缴企业所得税100063094.75元的行为认定为偷税。 之规定,对你公司少缴的企业所得税从滞纳之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
+          <t>查属期内违法行为均定性偷税, 需要对原处罚决定中的罚款数额 以变更,你(单位)存在违法事实及处罚决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 〔2022〕59号) 第一条、 第三条之规定, 你单位存在少缴属期2010 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。 月属期申报数据,用于证明你单位未申报缴纳印花税。 报,不缴或者少缴应纳税款的,是偷税。 务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴 内首次因偷税被税务机关处罚,并能够配合税务机关检查的,处 不缴或者少缴的税款百分之五十的罚款”之规定,对你单位城镇 土地使用税和印花税处不缴或者少缴的税款50%的罚款。 你单位印花税偷税违法行为发生于2009年11月26日,至立案 位检查属期内违法行为均定性偷税, 需要对原处理决定中的查补 情况进行了检查,违法事实及处理决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 定, 你单位存在少缴属期2010年1月至2022年6月城镇土地使 用税5,710,765.50元的违法事实。 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 该地块未缴纳契税,你单位存在少缴契税509,984.64元的违法 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>企业所得税</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>100063094.75</v>
-      </c>
+          <t>增值税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、契税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="n"/>
       <c r="S16" s="3" t="n"/>
-      <c r="T16" s="3" t="n"/>
+      <c r="T16" s="3" t="n">
+        <v>2855382.83</v>
+      </c>
       <c r="U16" s="3" t="n"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>据《中华人民共和国税收征收管理法实施细则》第106条规定,将该文书予以公告送达,自公告之日起满30日视为送达。</t>
-        </is>
-      </c>
-      <c r="W16" s="4" t="n"/>
+          <t>定,每日按罚款数额的百分之三加处罚款。 日”之规定,你单位每月应补缴城镇土地使用税44,269.50元 征收城镇土地使用税, 自2010年1月至2022年6月应补缴城镇 所载金额的万分之五,你单位应补缴2009年11月26日印花税 定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W16" s="4" t="n">
+        <v>46183</v>
+      </c>
       <c r="X16" s="4" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="Y16" s="4" t="n"/>
       <c r="Z16" s="4" t="n">
-        <v>46229</v>
+        <v>46240</v>
       </c>
       <c r="AA16" s="4" t="n">
         <v>46240</v>
@@ -2593,404 +2627,406 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AF16" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG16" s="2" t="inlineStr"/>
       <c r="AH16" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局辽宁省税务局 通知公告 国家税务总局铁岭市税务局税务文书送达公告</t>
+        </is>
+      </c>
+      <c r="AI16" s="2" t="inlineStr">
+        <is>
+          <t>附件正常</t>
+        </is>
+      </c>
+      <c r="AJ16" s="2" t="inlineStr">
+        <is>
+          <t>字段“决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。 字段“关联处理决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处罚决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>CASE-365e8a924cf64611</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>DOC-4d14eba16f9aa8a0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>贵州省</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>贵阳市</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>贵州博泰工贸有限公司</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>91520115587255589F</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>筑税三稽处〔2026〕38号</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>筑税三稽处〔2026〕38号</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="3" t="n"/>
+      <c r="S17" s="3" t="n"/>
+      <c r="T17" s="3" t="n"/>
+      <c r="U17" s="3" t="n"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="4" t="n"/>
+      <c r="X17" s="4" t="n">
+        <v>46224</v>
+      </c>
+      <c r="Y17" s="4" t="n"/>
+      <c r="Z17" s="4" t="n">
+        <v>46229</v>
+      </c>
+      <c r="AA17" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>仅公告送达/仅文号线索</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD17" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AE17" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书、税务行政处罚决定书的公告</t>
+        </is>
+      </c>
+      <c r="AI17" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ17" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7b9a26f2ac401107</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>DOC-f6c6ea472b2ca04a</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>福建省</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>三明市</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局三明市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局三明市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>三明众祥房地产开发有限公司</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>91350400678473231W</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>明税一稽处〔2026〕20号</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>明税一稽处〔2026〕20号</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>情况进行了检查,违法事实及处理决定如下: 2016年期间,在没有真实业务情况下,取得重庆市博海建设工程(集团)有限公司、福建九九建设有限公司三明分公司开具的不符合规定的发票,发票金额400252379元,在企业所得税税前扣除,造成少缴纳企业所得税100063094.75元,该行为违反《中华人民共和国税收征收管理法》(2015年4月24日主席令第二十三号修改)第六十三条第一款 纳税人伪造、变造、隐匿、擅自销毁账簿、记账凭证,或者在账簿上多列支出或者不列、少列收入,或者经税务机关通知申报而拒不申报或者进行虚假的纳税申报,不缴或者少缴应纳税款的,是偷税。 对纳税人偷税的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款; 之规定,对你公司在账上多列支出,造成少缴企业所得税100063094.75元的行为认定为偷税。 之规定,对你公司少缴的企业所得税从滞纳之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>企业所得税</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>100063094.75</v>
+      </c>
+      <c r="S18" s="3" t="n"/>
+      <c r="T18" s="3" t="n"/>
+      <c r="U18" s="3" t="n"/>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>据《中华人民共和国税收征收管理法实施细则》第106条规定,将该文书予以公告送达,自公告之日起满30日视为送达。</t>
+        </is>
+      </c>
+      <c r="W18" s="4" t="n"/>
+      <c r="X18" s="4" t="n">
+        <v>46223</v>
+      </c>
+      <c r="Y18" s="4" t="n"/>
+      <c r="Z18" s="4" t="n">
+        <v>46229</v>
+      </c>
+      <c r="AA18" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD18" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AE18" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr">
         <is>
           <t>关于送达三明众祥房地产开发有限公司 《税务处理决定书》的公告 _
  其他公告 _
  国家税务总局三明市税务局</t>
         </is>
       </c>
-      <c r="AI16" s="2" t="inlineStr">
+      <c r="AI18" s="2" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ16" s="2" t="inlineStr">
+      <c r="AJ18" s="2" t="inlineStr">
         <is>
           <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
+    <row r="19">
+      <c r="A19" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>CASE-31e4a827dfd253f2</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>DOC-3ec54358fce2350d</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>福建省</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>福州市</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>福州顺路汽车运输有限公司</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>91350102MA31MF6611</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>税务处理决定书</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>榕税一稽处〔2026〕137号</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>榕税一稽处〔2026〕137号</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>我局于2025年7月10日起对你公司(地址:福建省闽侯县青口镇祥宏南路922号)2023年1月1日至2024年12月31日期间的发票涉税情况进行检查,违法事实及处理决定如下: (二)你公司取得毕节七星关区辰楚汽车服务部(个人独资)、毕节七星关锦悦汽车服务部(个人独资)、贵州杨亭汽车销售有限公司、贵州楠鑫汽车销售有限公司已证实虚开的35份机动车发票。 (二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 (三)根据《中华人民共和国企业所得税法》第五条、第八条、《企业所得税税前扣除凭证管理办法》(国家税务总局公告2018年第28号发布)第四条、第十二条的规定,你公司取得上述虚开的发票不得作为税前扣除凭证。</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R19" s="3" t="n">
         <v>3778.22</v>
       </c>
-      <c r="S17" s="3" t="n"/>
-      <c r="T17" s="3" t="n"/>
-      <c r="U17" s="3" t="n"/>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="S19" s="3" t="n"/>
+      <c r="T19" s="3" t="n"/>
+      <c r="U19" s="3" t="n"/>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>(二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期城市维护建设税124.75元。 根据《征收教育费附加的暂行规定》第二条、第三条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期教育费附加53.47元。 根据《福建省人民政府关于调整地方教育附加征收标准等有关问题的通知》(闽政文〔2011〕230号)第一条、第二条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期地方教育附加35.64元。</t>
         </is>
       </c>
-      <c r="W17" s="4" t="n"/>
-      <c r="X17" s="4" t="n">
+      <c r="W19" s="4" t="n"/>
+      <c r="X19" s="4" t="n">
         <v>46218</v>
       </c>
-      <c r="Y17" s="4" t="n"/>
-      <c r="Z17" s="4" t="n">
+      <c r="Y19" s="4" t="n"/>
+      <c r="Z19" s="4" t="n">
         <v>46229</v>
       </c>
-      <c r="AA17" s="4" t="n">
+      <c r="AA19" s="4" t="n">
         <v>46240</v>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
+      <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>完整文书</t>
         </is>
       </c>
-      <c r="AC17" s="2" t="inlineStr">
+      <c r="AC19" s="2" t="inlineStr">
         <is>
           <t>税务机关官网</t>
         </is>
       </c>
-      <c r="AD17" s="2" t="inlineStr">
+      <c r="AD19" s="2" t="inlineStr">
         <is>
           <t>已核验</t>
         </is>
       </c>
-      <c r="AE17" s="5" t="inlineStr">
+      <c r="AE19" s="5" t="inlineStr">
         <is>
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF17" s="2" t="inlineStr"/>
-      <c r="AG17" s="2" t="inlineStr"/>
-      <c r="AH17" s="2" t="inlineStr">
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr">
         <is>
           <t>关于送达福州顺路汽车运输有限公司《税务处理决定书》的公告 _
  其他类 _
  国家税务总局福州市税务局</t>
         </is>
       </c>
-      <c r="AI17" s="2" t="inlineStr">
+      <c r="AI19" s="2" t="inlineStr">
         <is>
           <t>正常</t>
-        </is>
-      </c>
-      <c r="AJ17" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>CASE-089a3b9692e76ac4</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>DOC-d21cdc5988b1e304</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>江苏省</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>淮安市</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局江苏省税务局</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局淮安市税务局稽查局</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>淮安市百亦金商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>91320804MA1WEH7Y3U</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>税务处理决定书</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽处〔2026〕26号</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽处〔2026〕26号</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽罚〔2026〕6号</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
-      <c r="R18" s="3" t="n"/>
-      <c r="S18" s="3" t="n"/>
-      <c r="T18" s="3" t="n"/>
-      <c r="U18" s="3" t="n"/>
-      <c r="V18" s="2" t="inlineStr"/>
-      <c r="W18" s="4" t="n"/>
-      <c r="X18" s="4" t="n">
-        <v>46216</v>
-      </c>
-      <c r="Y18" s="4" t="n"/>
-      <c r="Z18" s="4" t="n">
-        <v>46229</v>
-      </c>
-      <c r="AA18" s="4" t="n">
-        <v>46240</v>
-      </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>仅公告送达/仅文号线索</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD18" s="2" t="inlineStr">
-        <is>
-          <t>已核验</t>
-        </is>
-      </c>
-      <c r="AE18" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF18" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
-      <c r="AG18" s="2" t="inlineStr"/>
-      <c r="AH18" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
-        </is>
-      </c>
-      <c r="AI18" s="2" t="inlineStr">
-        <is>
-          <t>附件正常</t>
-        </is>
-      </c>
-      <c r="AJ18" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>CASE-089a3b9692e76ac4</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>DOC-9f8e8958d8ff89b6</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>江苏省</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>淮安市</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局江苏省税务局</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局淮安市税务局稽查局</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>淮安市百亦金商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>91320804MA1WEH7Y3U</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>税务行政处罚决定书</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽罚〔2026〕6号</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽处〔2026〕26号</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽罚〔2026〕6号</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="3" t="n"/>
-      <c r="S19" s="3" t="n"/>
-      <c r="T19" s="3" t="n"/>
-      <c r="U19" s="3" t="n"/>
-      <c r="V19" s="2" t="inlineStr"/>
-      <c r="W19" s="4" t="n"/>
-      <c r="X19" s="4" t="n">
-        <v>46216</v>
-      </c>
-      <c r="Y19" s="4" t="n"/>
-      <c r="Z19" s="4" t="n">
-        <v>46229</v>
-      </c>
-      <c r="AA19" s="4" t="n">
-        <v>46240</v>
-      </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>仅公告送达/仅文号线索</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD19" s="2" t="inlineStr">
-        <is>
-          <t>已核验</t>
-        </is>
-      </c>
-      <c r="AE19" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF19" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
-      <c r="AG19" s="2" t="inlineStr"/>
-      <c r="AH19" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
-        </is>
-      </c>
-      <c r="AI19" s="2" t="inlineStr">
-        <is>
-          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ19" s="2" t="inlineStr">
@@ -3001,47 +3037,47 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CASE-3f564fd9992b1ae3</t>
+          <t>CASE-089a3b9692e76ac4</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>DOC-c34e1d13286aafe2</t>
+          <t>DOC-d21cdc5988b1e304</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>泉州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局第二稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局第二稽查局</t>
+          <t>国家税务总局淮安市税务局稽查局</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>泉州隆鸿服装制造有限公司</t>
+          <t>淮安市百亦金商贸有限公司</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>91350525MA8U3U963L</t>
+          <t>91320804MA1WEH7Y3U</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
@@ -3052,37 +3088,29 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>泉税二稽处〔2026〕107号</t>
+          <t>淮税稽处〔2026〕26号</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>泉税二稽处〔2026〕107号</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>日对你公司税收违法事实依法作出《税务处理决定书》(泉税二稽处〔 涉税情况进行了检查,查明违法事实及处理决定如下: 年你公司在无真实货物交易的情况下,取得河南中弘纺织有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 年期间,你公司在无真实货物交易的情况下,取得开封兴旺纺织品有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 上述违法事实有检查人员实地检查资料、电话拨打记录、邮寄退回函件、《已证实虚开通知单》等相关受托协查资料、主管税务机关出具的《已抵扣证明》、《情况说明》和你公司的申报纳税资料、银行账户流水等 号第三次修订)第二十一条第二款第二项之规定,认定你公司让他人为自己虚开 号第二次修订)第九条和《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告〔 号)之规定,对你公司取得上述已证实虚开的 之规定,决定向你公司追缴少缴的城市维护建设税-增值税附征 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 规定,决定向你公司追缴少缴的教育费附加-增值税附征 规定,决定向你公司追缴少缴的地方教育附加-增值税附征</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
+          <t>淮税稽处〔2026〕26号</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>淮税稽罚〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
       <c r="R20" s="3" t="n"/>
       <c r="S20" s="3" t="n"/>
       <c r="T20" s="3" t="n"/>
       <c r="U20" s="3" t="n"/>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>由于你公司走逃失联、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 (五)根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司上述应补缴税款按税款所属时间从税款滞纳之日起按日加收万分之五滞纳金</t>
-        </is>
-      </c>
+      <c r="V20" s="2" t="inlineStr"/>
       <c r="W20" s="4" t="n"/>
       <c r="X20" s="4" t="n">
-        <v>46202</v>
+        <v>46216</v>
       </c>
       <c r="Y20" s="4" t="n"/>
       <c r="Z20" s="4" t="n">
@@ -3093,7 +3121,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -3111,18 +3139,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF20" s="2" t="inlineStr"/>
+      <c r="AF20" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG20" s="2" t="inlineStr"/>
       <c r="AH20" s="2" t="inlineStr">
         <is>
-          <t>关于对泉州隆鸿服装制造有限公司《税务处理决定书》送达的公告 _
- 其他公告 _
- 国家税务总局泉州市税务局</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
         </is>
       </c>
       <c r="AI20" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ20" s="2" t="inlineStr">
@@ -3133,16 +3163,16 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CASE-717dfe3250926214</t>
+          <t>CASE-089a3b9692e76ac4</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>DOC-7df9c075e55777a1</t>
+          <t>DOC-9f8e8958d8ff89b6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3152,28 +3182,28 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>泰州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泰州市税务局第一稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泰州市税务局第一稽查局</t>
+          <t>国家税务总局淮安市税务局稽查局</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>靖江市长凌金属材料有限公司</t>
+          <t>淮安市百亦金商贸有限公司</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>91321282742461893K</t>
+          <t>91320804MA1WEH7Y3U</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
@@ -3184,13 +3214,17 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>泰税一稽罚〔2025〕54号</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr"/>
+          <t>淮税稽罚〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>淮税稽处〔2026〕26号</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>泰税一稽罚〔2025〕54号</t>
+          <t>淮税稽罚〔2026〕6号</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr"/>
@@ -3199,14 +3233,10 @@
       <c r="S21" s="3" t="n"/>
       <c r="T21" s="3" t="n"/>
       <c r="U21" s="3" t="n"/>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>接上级通知,经我局研究决定,撤销上述《税务行政处罚决定书》。</t>
-        </is>
-      </c>
+      <c r="V21" s="2" t="inlineStr"/>
       <c r="W21" s="4" t="n"/>
       <c r="X21" s="4" t="n">
-        <v>46191</v>
+        <v>46216</v>
       </c>
       <c r="Y21" s="4" t="n"/>
       <c r="Z21" s="4" t="n">
@@ -3235,67 +3265,71 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AF21" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG21" s="2" t="inlineStr"/>
       <c r="AH21" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 关于撤销《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
         </is>
       </c>
       <c r="AI21" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ21" s="2" t="inlineStr">
         <is>
-          <t>官方页面显示该决定书已被撤销。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CASE-a62e569c195adc3c</t>
+          <t>CASE-3f564fd9992b1ae3</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>DOC-b1dda915d4e6117d</t>
+          <t>DOC-c34e1d13286aafe2</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>遵义市</t>
+          <t>泉州市</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局泉州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局泉州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>贵州服格定商贸有限公司</t>
+          <t>泉州隆鸿服装制造有限公司</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>91520302MABUEHN034</t>
+          <t>91350525MA8U3U963L</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
@@ -3306,33 +3340,37 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>遵税一稽处〔2026〕30号</t>
+          <t>泉税二稽处〔2026〕107号</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>遵税一稽处〔2026〕30号</t>
+          <t>泉税二稽处〔2026〕107号</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
+          <t>日对你公司税收违法事实依法作出《税务处理决定书》(泉税二稽处〔 涉税情况进行了检查,查明违法事实及处理决定如下: 年你公司在无真实货物交易的情况下,取得河南中弘纺织有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 年期间,你公司在无真实货物交易的情况下,取得开封兴旺纺织品有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 上述违法事实有检查人员实地检查资料、电话拨打记录、邮寄退回函件、《已证实虚开通知单》等相关受托协查资料、主管税务机关出具的《已抵扣证明》、《情况说明》和你公司的申报纳税资料、银行账户流水等 号第三次修订)第二十一条第二款第二项之规定,认定你公司让他人为自己虚开 号第二次修订)第九条和《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告〔 号)之规定,对你公司取得上述已证实虚开的 之规定,决定向你公司追缴少缴的城市维护建设税-增值税附征 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 规定,决定向你公司追缴少缴的教育费附加-增值税附征 规定,决定向你公司追缴少缴的地方教育附加-增值税附征</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
+          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R22" s="3" t="n"/>
       <c r="S22" s="3" t="n"/>
       <c r="T22" s="3" t="n"/>
       <c r="U22" s="3" t="n"/>
-      <c r="V22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>由于你公司走逃失联、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 (五)根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司上述应补缴税款按税款所属时间从税款滞纳之日起按日加收万分之五滞纳金</t>
+        </is>
+      </c>
       <c r="W22" s="4" t="n"/>
       <c r="X22" s="4" t="n">
-        <v>46185</v>
+        <v>46202</v>
       </c>
       <c r="Y22" s="4" t="n"/>
       <c r="Z22" s="4" t="n">
@@ -3365,7 +3403,9 @@
       <c r="AG22" s="2" t="inlineStr"/>
       <c r="AH22" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
+          <t>关于对泉州隆鸿服装制造有限公司《税务处理决定书》送达的公告 _
+ 其他公告 _
+ 国家税务总局泉州市税务局</t>
         </is>
       </c>
       <c r="AI22" s="2" t="inlineStr">
@@ -3381,64 +3421,64 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CASE-13a8aac51595155a</t>
+          <t>CASE-717dfe3250926214</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>DOC-7189c9a2cee8e8ce</t>
+          <t>DOC-7df9c075e55777a1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>温州市</t>
+          <t>泰州市</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局泰州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局泰州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>温作潘</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr"/>
+          <t>靖江市长凌金属材料有限公司</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>91321282742461893K</t>
+        </is>
+      </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>温税三稽处〔2026〕100号</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>温税三稽处〔2026〕100号</t>
-        </is>
-      </c>
+          <t>泰税一稽罚〔2025〕54号</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>温税三稽罚〔2026〕65号</t>
+          <t>泰税一稽罚〔2025〕54号</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr"/>
@@ -3447,10 +3487,14 @@
       <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="n"/>
       <c r="U23" s="3" t="n"/>
-      <c r="V23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>接上级通知,经我局研究决定,撤销上述《税务行政处罚决定书》。</t>
+        </is>
+      </c>
       <c r="W23" s="4" t="n"/>
       <c r="X23" s="4" t="n">
-        <v>46175</v>
+        <v>46191</v>
       </c>
       <c r="Y23" s="4" t="n"/>
       <c r="Z23" s="4" t="n">
@@ -3479,92 +3523,96 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF23" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF23" s="2" t="inlineStr"/>
       <c r="AG23" s="2" t="inlineStr"/>
       <c r="AH23" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 关于撤销《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI23" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ23" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>官方页面显示该决定书已被撤销。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CASE-13a8aac51595155a</t>
+          <t>CASE-a62e569c195adc3c</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>DOC-02fc2468fd0396a6</t>
+          <t>DOC-b1dda915d4e6117d</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>温州市</t>
+          <t>遵义市</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局遵义市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局遵义市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>温作潘</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr"/>
+          <t>贵州服格定商贸有限公司</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>91520302MABUEHN034</t>
+        </is>
+      </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>温税三稽罚〔2026〕65号</t>
+          <t>遵税一稽处〔2026〕30号</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>温税三稽处〔2026〕100号</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>温税三稽罚〔2026〕65号</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr"/>
-      <c r="Q24" s="2" t="inlineStr"/>
+          <t>遵税一稽处〔2026〕30号</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>增值税</t>
+        </is>
+      </c>
       <c r="R24" s="3" t="n"/>
       <c r="S24" s="3" t="n"/>
       <c r="T24" s="3" t="n"/>
@@ -3572,7 +3620,7 @@
       <c r="V24" s="2" t="inlineStr"/>
       <c r="W24" s="4" t="n"/>
       <c r="X24" s="4" t="n">
-        <v>46175</v>
+        <v>46185</v>
       </c>
       <c r="Y24" s="4" t="n"/>
       <c r="Z24" s="4" t="n">
@@ -3583,7 +3631,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3601,20 +3649,16 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF24" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF24" s="2" t="inlineStr"/>
       <c r="AG24" s="2" t="inlineStr"/>
       <c r="AH24" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
+          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
         </is>
       </c>
       <c r="AI24" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ24" s="2" t="inlineStr">
@@ -3625,49 +3669,45 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CASE-f8625e66b291a216</t>
+          <t>CASE-13a8aac51595155a</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>DOC-7970511393924720</t>
+          <t>DOC-7189c9a2cee8e8ce</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>温州市</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>贵州翰缤商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>91520114MAAK1C546F</t>
-        </is>
-      </c>
+          <t>温作潘</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
@@ -3676,15 +3716,19 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>筑税二稽处〔2026〕27号</t>
+          <t>温税三稽处〔2026〕100号</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>筑税二稽处〔2026〕27号</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr"/>
+          <t>温税三稽处〔2026〕100号</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>温税三稽罚〔2026〕65号</t>
+        </is>
+      </c>
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr"/>
       <c r="R25" s="3" t="n"/>
@@ -3694,7 +3738,7 @@
       <c r="V25" s="2" t="inlineStr"/>
       <c r="W25" s="4" t="n"/>
       <c r="X25" s="4" t="n">
-        <v>46156</v>
+        <v>46175</v>
       </c>
       <c r="Y25" s="4" t="n"/>
       <c r="Z25" s="4" t="n">
@@ -3723,16 +3767,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF25" s="2" t="inlineStr"/>
+      <c r="AF25" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG25" s="2" t="inlineStr"/>
       <c r="AH25" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局关于送达《税务处理决定书》的公告</t>
+          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
         </is>
       </c>
       <c r="AI25" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ25" s="2" t="inlineStr">
@@ -3743,68 +3791,64 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CASE-0f4867f7b70d12f3</t>
+          <t>CASE-13a8aac51595155a</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>DOC-6f25d6b79e123d03</t>
+          <t>DOC-02fc2468fd0396a6</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>温州市</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>贵州铂朗物流有限公司</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>91520115MAAK0DB335</t>
-        </is>
-      </c>
+          <t>温作潘</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
+          <t>温税三稽罚〔2026〕65号</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
+          <t>温税三稽处〔2026〕100号</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽罚〔2026〕22号</t>
+          <t>温税三稽罚〔2026〕65号</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr"/>
@@ -3816,7 +3860,7 @@
       <c r="V26" s="2" t="inlineStr"/>
       <c r="W26" s="4" t="n"/>
       <c r="X26" s="4" t="n">
-        <v>46122</v>
+        <v>46175</v>
       </c>
       <c r="Y26" s="4" t="n"/>
       <c r="Z26" s="4" t="n">
@@ -3845,16 +3889,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF26" s="2" t="inlineStr"/>
+      <c r="AF26" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG26" s="2" t="inlineStr"/>
       <c r="AH26" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
+          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
         </is>
       </c>
       <c r="AI26" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ26" s="2" t="inlineStr">
@@ -3865,16 +3913,16 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CASE-0f4867f7b70d12f3</t>
+          <t>CASE-f8625e66b291a216</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>DOC-e8233eb0e06b6e3e</t>
+          <t>DOC-7970511393924720</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3890,45 +3938,41 @@
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局贵阳市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局贵阳市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>贵州铂朗物流有限公司</t>
+          <t>贵州翰缤商贸有限公司</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>91520115MAAK0DB335</t>
+          <t>91520114MAAK1C546F</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽罚〔2026〕22号</t>
+          <t>筑税二稽处〔2026〕27号</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>筑税三稽罚〔2026〕22号</t>
-        </is>
-      </c>
+          <t>筑税二稽处〔2026〕27号</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr"/>
       <c r="Q27" s="2" t="inlineStr"/>
       <c r="R27" s="3" t="n"/>
@@ -3938,7 +3982,7 @@
       <c r="V27" s="2" t="inlineStr"/>
       <c r="W27" s="4" t="n"/>
       <c r="X27" s="4" t="n">
-        <v>46122</v>
+        <v>46156</v>
       </c>
       <c r="Y27" s="4" t="n"/>
       <c r="Z27" s="4" t="n">
@@ -3971,7 +4015,7 @@
       <c r="AG27" s="2" t="inlineStr"/>
       <c r="AH27" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
+          <t>国家税务总局贵阳市税务局第二稽查局关于送达《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI27" s="2" t="inlineStr">
@@ -3987,47 +4031,47 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CASE-136615addd5d0c0e</t>
+          <t>CASE-0f4867f7b70d12f3</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>DOC-551df7dc5c028b27</t>
+          <t>DOC-6f25d6b79e123d03</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>来宾市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>广西欣瑞木业有限公司</t>
+          <t>贵州铂朗物流有限公司</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>91451322MAD89XWX07</t>
+          <t>91520115MAAK0DB335</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
@@ -4038,17 +4082,17 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr"/>
@@ -4060,7 +4104,7 @@
       <c r="V28" s="2" t="inlineStr"/>
       <c r="W28" s="4" t="n"/>
       <c r="X28" s="4" t="n">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="Y28" s="4" t="n"/>
       <c r="Z28" s="4" t="n">
@@ -4093,7 +4137,7 @@
       <c r="AG28" s="2" t="inlineStr"/>
       <c r="AH28" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
         </is>
       </c>
       <c r="AI28" s="2" t="inlineStr">
@@ -4109,47 +4153,47 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CASE-136615addd5d0c0e</t>
+          <t>CASE-0f4867f7b70d12f3</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>DOC-21f0193b66d5c3e9</t>
+          <t>DOC-e8233eb0e06b6e3e</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>来宾市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>广西欣瑞木业有限公司</t>
+          <t>贵州铂朗物流有限公司</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>91451322MAD89XWX07</t>
+          <t>91520115MAAK0DB335</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
@@ -4160,17 +4204,17 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr"/>
@@ -4182,7 +4226,7 @@
       <c r="V29" s="2" t="inlineStr"/>
       <c r="W29" s="4" t="n"/>
       <c r="X29" s="4" t="n">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="Y29" s="4" t="n"/>
       <c r="Z29" s="4" t="n">
@@ -4215,7 +4259,7 @@
       <c r="AG29" s="2" t="inlineStr"/>
       <c r="AH29" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
         </is>
       </c>
       <c r="AI29" s="2" t="inlineStr">
@@ -4231,64 +4275,68 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CASE-393a878d93a22709</t>
+          <t>CASE-136615addd5d0c0e</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>DOC-cda8cba853896b18</t>
+          <t>DOC-551df7dc5c028b27</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>广州市</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>番禺区</t>
-        </is>
-      </c>
+          <t>来宾市</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
+        </is>
+      </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>广州赞荣服装有限公司</t>
+          <t>广西欣瑞木业有限公司</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>91440113MA59AJFJ1J</t>
+          <t>91451322MAD89XWX07</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>穗番税退罚字〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr"/>
+          <t>来市税二稽处〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>来市税二稽处〔2026〕6号</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>穗番税退罚字〔2026〕1号</t>
+          <t>来市税二稽罚〔2026〕4号</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr"/>
@@ -4300,7 +4348,7 @@
       <c r="V30" s="2" t="inlineStr"/>
       <c r="W30" s="4" t="n"/>
       <c r="X30" s="4" t="n">
-        <v>46091</v>
+        <v>46119</v>
       </c>
       <c r="Y30" s="4" t="n"/>
       <c r="Z30" s="4" t="n">
@@ -4321,7 +4369,7 @@
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE30" s="5" t="inlineStr">
@@ -4329,120 +4377,100 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF30" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF30" s="2" t="inlineStr"/>
       <c r="AG30" s="2" t="inlineStr"/>
       <c r="AH30" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
+          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
         </is>
       </c>
       <c r="AI30" s="2" t="inlineStr">
         <is>
-          <t>内容不匹配</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ30" s="2" t="inlineStr">
         <is>
-          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CASE-f94bf08964abff5a</t>
+          <t>CASE-136615addd5d0c0e</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>DOC-4574b1aadef8f30d</t>
+          <t>DOC-21f0193b66d5c3e9</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
+          <t>来宾市</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局稽查局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>常州市文杰车辆配件厂</t>
+          <t>广西欣瑞木业有限公司</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>91320411799075280A</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>朱某</t>
-        </is>
-      </c>
+          <t>91451322MAD89XWX07</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕73号</t>
+          <t>来市税二稽罚〔2026〕4号</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕73号</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr"/>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公 月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>179137.12</v>
-      </c>
+          <t>来市税二稽处〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>来市税二稽罚〔2026〕4号</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="3" t="n"/>
       <c r="S31" s="3" t="n"/>
       <c r="T31" s="3" t="n"/>
       <c r="U31" s="3" t="n"/>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市 份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元,</t>
-        </is>
-      </c>
-      <c r="W31" s="4" t="n">
-        <v>46044</v>
-      </c>
+      <c r="V31" s="2" t="inlineStr"/>
+      <c r="W31" s="4" t="n"/>
       <c r="X31" s="4" t="n">
-        <v>46090</v>
+        <v>46119</v>
       </c>
       <c r="Y31" s="4" t="n"/>
       <c r="Z31" s="4" t="n">
@@ -4453,7 +4481,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4471,20 +4499,16 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF31" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF31" s="2" t="inlineStr"/>
       <c r="AG31" s="2" t="inlineStr"/>
       <c r="AH31" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
+          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
         </is>
       </c>
       <c r="AI31" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ31" s="2" t="inlineStr">
@@ -4495,66 +4519,66 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CASE-0b4a4519ba4f5ad9</t>
+          <t>CASE-393a878d93a22709</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>DOC-5376b9bae81cfc82</t>
+          <t>DOC-cda8cba853896b18</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>广东省</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr"/>
+          <t>广州市</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>番禺区</t>
+        </is>
+      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局常州市税务局稽查局</t>
-        </is>
-      </c>
+          <t>国家税务总局广州市番禺区税务局</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>常州好佳车辆配件有限公司</t>
+          <t>广州赞荣服装有限公司</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>91320411094264460B</t>
+          <t>91440113MA59AJFJ1J</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕71号</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>常税稽处〔2026〕71号</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr"/>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="2" t="inlineStr"/>
       <c r="R32" s="3" t="n"/>
@@ -4564,7 +4588,7 @@
       <c r="V32" s="2" t="inlineStr"/>
       <c r="W32" s="4" t="n"/>
       <c r="X32" s="4" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="Y32" s="4" t="n"/>
       <c r="Z32" s="4" t="n">
@@ -4585,7 +4609,7 @@
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE32" s="5" t="inlineStr">
@@ -4601,32 +4625,32 @@
       <c r="AG32" s="2" t="inlineStr"/>
       <c r="AH32" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州好佳车辆配件有限公司《税务处理决定书》的公告</t>
+          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
         </is>
       </c>
       <c r="AI32" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>内容不匹配</t>
         </is>
       </c>
       <c r="AJ32" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>CASE-61b9b55a9d3357c7</t>
+          <t>CASE-f94bf08964abff5a</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>DOC-1228a9c92b2b0632</t>
+          <t>DOC-4574b1aadef8f30d</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4642,25 +4666,29 @@
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局常州市税务局稽查局</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>常州市三鹏机械有限公司</t>
+          <t>常州市文杰车辆配件厂</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>91320404732260748Q</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr"/>
+          <t>91320411799075280A</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>朱某</t>
+        </is>
+      </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
           <t>税务处理决定书</t>
@@ -4668,39 +4696,41 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
+          <t>常税稽处〔2026〕73号</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>常税稽一罚〔2026〕14号</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr"/>
+          <t>常税稽处〔2026〕73号</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公 月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
+        </is>
+      </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
           <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R33" s="3" t="n">
-        <v>63464.09</v>
+        <v>179137.12</v>
       </c>
       <c r="S33" s="3" t="n"/>
       <c r="T33" s="3" t="n"/>
       <c r="U33" s="3" t="n"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
-        </is>
-      </c>
-      <c r="W33" s="4" t="n"/>
+          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市 份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元,</t>
+        </is>
+      </c>
+      <c r="W33" s="4" t="n">
+        <v>46044</v>
+      </c>
       <c r="X33" s="4" t="n">
-        <v>46066</v>
+        <v>46090</v>
       </c>
       <c r="Y33" s="4" t="n"/>
       <c r="Z33" s="4" t="n">
@@ -4729,16 +4759,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF33" s="2" t="inlineStr"/>
+      <c r="AF33" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG33" s="2" t="inlineStr"/>
       <c r="AH33" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI33" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ33" s="2" t="inlineStr">
@@ -4749,16 +4783,16 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CASE-61b9b55a9d3357c7</t>
+          <t>CASE-0b4a4519ba4f5ad9</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>DOC-b97456a64b153f67</t>
+          <t>DOC-5376b9bae81cfc82</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4774,65 +4808,51 @@
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局常州市税务局稽查局</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>常州市三鹏机械有限公司</t>
+          <t>常州好佳车辆配件有限公司</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>91320404732260748Q</t>
+          <t>91320411094264460B</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>常税稽一罚〔2026〕14号</t>
+          <t>常税稽处〔2026〕71号</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>常税稽一罚〔2026〕14号</t>
-        </is>
-      </c>
+          <t>常税稽处〔2026〕71号</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr"/>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
       <c r="R34" s="3" t="n"/>
       <c r="S34" s="3" t="n"/>
-      <c r="T34" s="3" t="n">
-        <v>20000</v>
-      </c>
+      <c r="T34" s="3" t="n"/>
       <c r="U34" s="3" t="n"/>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
-        </is>
-      </c>
+      <c r="V34" s="2" t="inlineStr"/>
       <c r="W34" s="4" t="n"/>
       <c r="X34" s="4" t="n">
-        <v>46066</v>
+        <v>46087</v>
       </c>
       <c r="Y34" s="4" t="n"/>
       <c r="Z34" s="4" t="n">
@@ -4843,7 +4863,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4861,16 +4881,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF34" s="2" t="inlineStr"/>
+      <c r="AF34" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG34" s="2" t="inlineStr"/>
       <c r="AH34" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州好佳车辆配件有限公司《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI34" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ34" s="2" t="inlineStr">
@@ -4881,47 +4905,47 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>CASE-f78ec1a594442165</t>
+          <t>CASE-61b9b55a9d3357c7</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>DOC-fbbe4a664b14f54b</t>
+          <t>DOC-1228a9c92b2b0632</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>安顺市</t>
+          <t>常州市</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
+          <t>常州市三鹏机械有限公司</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>91520423MA6DLH799Q</t>
+          <t>91320404732260748Q</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
@@ -4932,45 +4956,39 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
-        </is>
-      </c>
+          <t>常税稽一罚〔2026〕14号</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr"/>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R35" s="3" t="n">
-        <v>64884.41</v>
+        <v>63464.09</v>
       </c>
       <c r="S35" s="3" t="n"/>
       <c r="T35" s="3" t="n"/>
       <c r="U35" s="3" t="n"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
-      <c r="W35" s="4" t="n">
-        <v>45898</v>
-      </c>
+          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
+        </is>
+      </c>
+      <c r="W35" s="4" t="n"/>
       <c r="X35" s="4" t="n">
-        <v>46043</v>
+        <v>46066</v>
       </c>
       <c r="Y35" s="4" t="n"/>
       <c r="Z35" s="4" t="n">
@@ -4999,71 +5017,67 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF35" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF35" s="2" t="inlineStr"/>
       <c r="AG35" s="2" t="inlineStr"/>
       <c r="AH35" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI35" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ35" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。 字段“主要违法事实”存在冲突:保留原值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”,新值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CASE-f78ec1a594442165</t>
+          <t>CASE-61b9b55a9d3357c7</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>DOC-9a828a6048b54b6c</t>
+          <t>DOC-b97456a64b153f67</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>安顺市</t>
+          <t>常州市</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
+          <t>常州市三鹏机械有限公司</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>91520423MA6DLH799Q</t>
+          <t>91320404732260748Q</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
@@ -5074,45 +5088,39 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>安市税稽罚〔2026〕1号</t>
+          <t>常税稽一罚〔2026〕14号</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
-        </is>
-      </c>
+          <t>常税稽一罚〔2026〕14号</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr"/>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R36" s="3" t="n"/>
       <c r="S36" s="3" t="n"/>
       <c r="T36" s="3" t="n">
-        <v>200000</v>
+        <v>20000</v>
       </c>
       <c r="U36" s="3" t="n"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
-      <c r="W36" s="4" t="n">
-        <v>45898</v>
-      </c>
+          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
+        </is>
+      </c>
+      <c r="W36" s="4" t="n"/>
       <c r="X36" s="4" t="n">
-        <v>46043</v>
+        <v>46066</v>
       </c>
       <c r="Y36" s="4" t="n"/>
       <c r="Z36" s="4" t="n">
@@ -5141,71 +5149,67 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF36" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF36" s="2" t="inlineStr"/>
       <c r="AG36" s="2" t="inlineStr"/>
       <c r="AH36" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI36" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ36" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CASE-fe959d4c6c52d910</t>
+          <t>CASE-f78ec1a594442165</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>DOC-f2643f2a0719d8d1</t>
+          <t>DOC-fbbe4a664b14f54b</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>南宁市</t>
+          <t>安顺市</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局稽查局</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>南宁洪谦金贸易有限公司</t>
+          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>91450103MA5K9WHY7U</t>
+          <t>91520423MA6DLH799Q</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
@@ -5216,33 +5220,45 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>南市税一稽处〔2026〕2号</t>
+          <t>安市税稽处〔2026〕1号</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>南市税一稽处〔2026〕2号</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr"/>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽罚〔2026〕1号</t>
+        </is>
+      </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>经我局2025年10月29日至2025年12月8日对你公司(地址:南宁市青秀区云景路11号春晖花园C区3栋2单元1606号)2015年12月2日至2016年12月31日期间的涉税情况进行了检查,你(单位)存在以下违法事实: 经查询你公司向税务机关报备的银行账号:广西北部湾银行南宁市财富国际支行800099398800015,经函询广西北部湾银行南宁市财富国际支行,存在以下问题: 上述行为属于开具与实际经营业务情况不符的增值税发票,违反了《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第587号修改)第二十二条第一款、第二款第(一)项的规定,属于虚开发票行为。</t>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
-        </is>
-      </c>
-      <c r="R37" s="3" t="n"/>
+          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>64884.41</v>
+      </c>
       <c r="S37" s="3" t="n"/>
       <c r="T37" s="3" t="n"/>
       <c r="U37" s="3" t="n"/>
-      <c r="V37" s="2" t="inlineStr"/>
-      <c r="W37" s="4" t="n"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="W37" s="4" t="n">
+        <v>45898</v>
+      </c>
       <c r="X37" s="4" t="n">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="Y37" s="4" t="n"/>
       <c r="Z37" s="4" t="n">
@@ -5279,7 +5295,7 @@
       <c r="AG37" s="2" t="inlineStr"/>
       <c r="AH37" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局税务文书送达公告_国家税务总局南宁市税务局</t>
+          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI37" s="2" t="inlineStr">
@@ -5289,89 +5305,103 @@
       </c>
       <c r="AJ37" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。 字段“主要违法事实”存在冲突:保留原值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”,新值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>CASE-1983d97878508732</t>
+          <t>CASE-f78ec1a594442165</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>DOC-f9760895b4f08cc2</t>
+          <t>DOC-9a828a6048b54b6c</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>二连浩特市</t>
+          <t>安顺市</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局</t>
+          <t>国家税务总局安顺市税务局</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局稽查局</t>
+          <t>国家税务总局安顺市税务局稽查局</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>二连市坤益腾金属有限公司</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr"/>
+          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>91520423MA6DLH799Q</t>
+        </is>
+      </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
+          <t>安市税稽罚〔2026〕1号</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr"/>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽罚〔2026〕1号</t>
+        </is>
+      </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
+          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R38" s="3" t="n"/>
       <c r="S38" s="3" t="n"/>
-      <c r="T38" s="3" t="n"/>
+      <c r="T38" s="3" t="n">
+        <v>200000</v>
+      </c>
       <c r="U38" s="3" t="n"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
-        </is>
-      </c>
-      <c r="W38" s="4" t="n"/>
-      <c r="X38" s="4" t="n"/>
+          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="W38" s="4" t="n">
+        <v>45898</v>
+      </c>
+      <c r="X38" s="4" t="n">
+        <v>46043</v>
+      </c>
       <c r="Y38" s="4" t="n"/>
       <c r="Z38" s="4" t="n">
         <v>46229</v>
@@ -5391,7 +5421,7 @@
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE38" s="5" t="inlineStr">
@@ -5399,61 +5429,73 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF38" s="2" t="inlineStr"/>
+      <c r="AF38" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG38" s="2" t="inlineStr"/>
       <c r="AH38" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI38" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ38" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>CASE-d4b6986f3f97cd28</t>
+          <t>CASE-fe959d4c6c52d910</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>DOC-442cf3d9a5280c12</t>
+          <t>DOC-f2643f2a0719d8d1</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>鄂尔多斯市</t>
+          <t>南宁市</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局南宁市税务局第一稽查局</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>第二稽查局</t>
+          <t>国家税务总局南宁市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>廖礼平</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr"/>
+          <t>南宁洪谦金贸易有限公司</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>91450103MA5K9WHY7U</t>
+        </is>
+      </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
@@ -5462,40 +5504,34 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
+          <t>南市税一稽处〔2026〕2号</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
+          <t>南市税一稽处〔2026〕2号</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
+          <t>经我局2025年10月29日至2025年12月8日对你公司(地址:南宁市青秀区云景路11号春晖花园C区3栋2单元1606号)2015年12月2日至2016年12月31日期间的涉税情况进行了检查,你(单位)存在以下违法事实: 经查询你公司向税务机关报备的银行账号:广西北部湾银行南宁市财富国际支行800099398800015,经函询广西北部湾银行南宁市财富国际支行,存在以下问题: 上述行为属于开具与实际经营业务情况不符的增值税发票,违反了《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第587号修改)第二十二条第一款、第二款第(一)项的规定,属于虚开发票行为。</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>个人所得税、印花税</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="n">
-        <v>15072487.5</v>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>1046925</v>
-      </c>
+          <t>增值税</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="n"/>
+      <c r="S39" s="3" t="n"/>
       <c r="T39" s="3" t="n"/>
       <c r="U39" s="3" t="n"/>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
-        </is>
-      </c>
+      <c r="V39" s="2" t="inlineStr"/>
       <c r="W39" s="4" t="n"/>
-      <c r="X39" s="4" t="n"/>
+      <c r="X39" s="4" t="n">
+        <v>46031</v>
+      </c>
       <c r="Y39" s="4" t="n"/>
       <c r="Z39" s="4" t="n">
         <v>46229</v>
@@ -5515,7 +5551,7 @@
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE39" s="5" t="inlineStr">
@@ -5523,69 +5559,69 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF39" s="2" t="inlineStr"/>
+      <c r="AF39" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG39" s="2" t="inlineStr"/>
       <c r="AH39" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>国家税务总局南宁市税务局第一稽查局税务文书送达公告_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI39" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ39" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>CASE-7e3d4a321440d6a7</t>
+          <t>CASE-1983d97878508732</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>DOC-bed9330343ed06af</t>
+          <t>DOC-f9760895b4f08cc2</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>二连浩特市</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
+          <t>国家税务总局二连浩特市税务局</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
+          <t>国家税务总局二连浩特市税务局稽查局</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>天津展达科技有限公司</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>91120116300738701X</t>
-        </is>
-      </c>
+          <t>二连市坤益腾金属有限公司</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
@@ -5594,45 +5630,39 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
+          <t>二税稽处〔2025〕1号</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
+          <t>二税稽处〔2025〕1号</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>920146.9399999999</v>
-      </c>
+          <t>增值税</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="n"/>
       <c r="S40" s="3" t="n"/>
       <c r="T40" s="3" t="n"/>
       <c r="U40" s="3" t="n"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
         </is>
       </c>
       <c r="W40" s="4" t="n"/>
       <c r="X40" s="4" t="n"/>
       <c r="Y40" s="4" t="n"/>
       <c r="Z40" s="4" t="n">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="AA40" s="4" t="n">
         <v>46240</v>
@@ -5661,7 +5691,7 @@
       <c r="AG40" s="2" t="inlineStr"/>
       <c r="AH40" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="AI40" s="2" t="inlineStr">
@@ -5671,102 +5701,92 @@
       </c>
       <c r="AJ40" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>CASE-7e3d4a321440d6a7</t>
+          <t>CASE-d4b6986f3f97cd28</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>DOC-388bd01c01bbb789</t>
+          <t>DOC-442cf3d9a5280c12</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>鄂尔多斯市</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
-        </is>
-      </c>
+      <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
+          <t>第二稽查局</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>天津展达科技有限公司</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>91120116300738701X</t>
-        </is>
-      </c>
+          <t>廖礼平</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>津税一稽罚〔2023〕21号</t>
+          <t>鄂税二稽处〔2023〕29号</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
+          <t>鄂税二稽处〔2023〕29号</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="n"/>
-      <c r="S41" s="3" t="n"/>
-      <c r="T41" s="3" t="n">
-        <v>131368.5</v>
-      </c>
+          <t>个人所得税、印花税</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>15072487.5</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>1046925</v>
+      </c>
+      <c r="T41" s="3" t="n"/>
       <c r="U41" s="3" t="n"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
         </is>
       </c>
       <c r="W41" s="4" t="n"/>
       <c r="X41" s="4" t="n"/>
       <c r="Y41" s="4" t="n"/>
       <c r="Z41" s="4" t="n">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="AA41" s="4" t="n">
         <v>46240</v>
@@ -5795,34 +5815,302 @@
       <c r="AG41" s="2" t="inlineStr"/>
       <c r="AH41" s="2" t="inlineStr">
         <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="AI41" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ41" s="2" t="inlineStr">
+        <is>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7e3d4a321440d6a7</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>DOC-bed9330343ed06af</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>91120116300738701X</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>920146.9399999999</v>
+      </c>
+      <c r="S42" s="3" t="n"/>
+      <c r="T42" s="3" t="n"/>
+      <c r="U42" s="3" t="n"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W42" s="4" t="n"/>
+      <c r="X42" s="4" t="n"/>
+      <c r="Y42" s="4" t="n"/>
+      <c r="Z42" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AA42" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE42" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF42" s="2" t="inlineStr"/>
+      <c r="AG42" s="2" t="inlineStr"/>
+      <c r="AH42" s="2" t="inlineStr">
+        <is>
           <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
-      <c r="AI41" s="2" t="inlineStr">
+      <c r="AI42" s="2" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ41" s="2" t="inlineStr">
+      <c r="AJ42" s="2" t="inlineStr">
+        <is>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7e3d4a321440d6a7</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>DOC-388bd01c01bbb789</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>91120116300738701X</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>税务行政处罚决定书</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="n"/>
+      <c r="S43" s="3" t="n"/>
+      <c r="T43" s="3" t="n">
+        <v>131368.5</v>
+      </c>
+      <c r="U43" s="3" t="n"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W43" s="4" t="n"/>
+      <c r="X43" s="4" t="n"/>
+      <c r="Y43" s="4" t="n"/>
+      <c r="Z43" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AA43" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE43" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF43" s="2" t="inlineStr"/>
+      <c r="AG43" s="2" t="inlineStr"/>
+      <c r="AH43" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+        </is>
+      </c>
+      <c r="AI43" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ43" s="2" t="inlineStr">
         <is>
           <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ41"/>
-  <conditionalFormatting sqref="AD2:AD41">
+  <autoFilter ref="A1:AJ43"/>
+  <conditionalFormatting sqref="AD2:AD43">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AD2="待核验"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI2:AI41">
+  <conditionalFormatting sqref="AI2:AI43">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>AND($AI2&lt;&gt;"正常",$AI2&lt;&gt;"附件正常")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AD2:AD41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AD2:AD43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"已核验,待核验,人工复核完成"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5846,42 +6134,46 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE14" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE15" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE16" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE17" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE18" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF18" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE19" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF19" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF15" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE16" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF16" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE17" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE18" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE19" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE20" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE21" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE22" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE23" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF23" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE24" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF24" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF20" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE21" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF21" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE22" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE23" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE24" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE25" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE26" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE27" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE28" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE29" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE30" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF30" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE31" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF31" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF25" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE26" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF26" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE27" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE28" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE29" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE30" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE31" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE32" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF32" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE33" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE34" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE35" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF35" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE36" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF36" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF33" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE34" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF34" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE35" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE36" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE37" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF37" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE38" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE39" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE40" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE41" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF38" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE39" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF39" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE40" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE41" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE42" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE43" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -5894,7 +6186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ21"/>
+  <dimension ref="A1:AJ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6249,7 +6541,11 @@
           <t>附件正常</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -6915,47 +7211,47 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CASE-7b9a26f2ac401107</t>
+          <t>CASE-1a685b98e7b293c8</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DOC-f6c6ea472b2ca04a</t>
+          <t>DOC-9b5fab8065382bd9</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>辽宁省</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>三明市</t>
+          <t>铁岭市</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局三明市税务局第一稽查局</t>
+          <t>国家税务总局铁岭市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局三明市税务局第一稽查局</t>
+          <t>国家税务总局铁岭市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>三明众祥房地产开发有限公司</t>
+          <t>辽宁恒慧专用车箱有限公司</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>91350400678473231W</t>
+          <t>91211200683741982W</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
@@ -6966,43 +7262,49 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>明税一稽处〔2026〕20号</t>
+          <t>铁税一稽处〔2026〕35号</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>明税一稽处〔2026〕20号</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr"/>
+          <t>铁税一稽处〔2026〕35号</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>铁税一稽罚〔2026〕17号</t>
+        </is>
+      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2016年期间,在没有真实业务情况下,取得重庆市博海建设工程(集团)有限公司、福建九九建设有限公司三明分公司开具的不符合规定的发票,发票金额400252379元,在企业所得税税前扣除,造成少缴纳企业所得税100063094.75元,该行为违反《中华人民共和国税收征收管理法》(2015年4月24日主席令第二十三号修改)第六十三条第一款 纳税人伪造、变造、隐匿、擅自销毁账簿、记账凭证,或者在账簿上多列支出或者不列、少列收入,或者经税务机关通知申报而拒不申报或者进行虚假的纳税申报,不缴或者少缴应纳税款的,是偷税。 对纳税人偷税的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款; 之规定,对你公司在账上多列支出,造成少缴企业所得税100063094.75元的行为认定为偷税。 之规定,对你公司少缴的企业所得税从滞纳之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
+          <t>查属期内违法行为均定性偷税, 需要对原处罚决定中的罚款数额 以变更,你(单位)存在违法事实及处罚决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 〔2022〕59号) 第一条、 第三条之规定, 你单位存在少缴属期2010 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。 月属期申报数据,用于证明你单位未申报缴纳印花税。 报,不缴或者少缴应纳税款的,是偷税。 务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴 内首次因偷税被税务机关处罚,并能够配合税务机关检查的,处 不缴或者少缴的税款百分之五十的罚款”之规定,对你单位城镇 土地使用税和印花税处不缴或者少缴的税款50%的罚款。 你单位印花税偷税违法行为发生于2009年11月26日,至立案 位检查属期内违法行为均定性偷税, 需要对原处理决定中的查补 情况进行了检查,违法事实及处理决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 定, 你单位存在少缴属期2010年1月至2022年6月城镇土地使 用税5,710,765.50元的违法事实。 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 该地块未缴纳契税,你单位存在少缴契税509,984.64元的违法 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>企业所得税</t>
+          <t>增值税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、契税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R8" s="3" t="n">
-        <v>100063094.75</v>
+        <v>44269.5</v>
       </c>
       <c r="S8" s="3" t="n"/>
       <c r="T8" s="3" t="n"/>
       <c r="U8" s="3" t="n"/>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>据《中华人民共和国税收征收管理法实施细则》第106条规定,将该文书予以公告送达,自公告之日起满30日视为送达。</t>
-        </is>
-      </c>
-      <c r="W8" s="4" t="n"/>
+          <t>定,每日按罚款数额的百分之三加处罚款。 日”之规定,你单位每月应补缴城镇土地使用税44,269.50元 征收城镇土地使用税, 自2010年1月至2022年6月应补缴城镇 所载金额的万分之五,你单位应补缴2009年11月26日印花税 日”之规定,你单位每月应补缴城镇土地使用税44,269.50元 征收城镇土地使用税, 自2010年1月至2022年6月应补缴城镇 所载金额的万分之五,你单位应补缴2009年11月26日印花税</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="n">
+        <v>46183</v>
+      </c>
       <c r="X8" s="4" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="Y8" s="4" t="n"/>
       <c r="Z8" s="4" t="n">
-        <v>46229</v>
+        <v>46240</v>
       </c>
       <c r="AA8" s="4" t="n">
         <v>46240</v>
@@ -7027,116 +7329,124 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AF8" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG8" s="2" t="inlineStr"/>
       <c r="AH8" s="2" t="inlineStr">
         <is>
-          <t>关于送达三明众祥房地产开发有限公司 《税务处理决定书》的公告 _
- 其他公告 _
- 国家税务总局三明市税务局</t>
+          <t>国家税务总局辽宁省税务局 通知公告 国家税务总局铁岭市税务局税务文书送达公告</t>
         </is>
       </c>
       <c r="AI8" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>字段“决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处理决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处罚决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>CASE-31e4a827dfd253f2</t>
+          <t>CASE-1a685b98e7b293c8</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DOC-3ec54358fce2350d</t>
+          <t>DOC-8fc89a4906937181</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>辽宁省</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>福州市</t>
+          <t>铁岭市</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局铁岭市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局铁岭市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>福州顺路汽车运输有限公司</t>
+          <t>辽宁恒慧专用车箱有限公司</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91350102MA31MF6611</t>
+          <t>91211200683741982W</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽处〔2026〕137号</t>
+          <t>铁税一稽罚〔2026〕17号</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽处〔2026〕137号</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
+          <t>铁税一稽处〔2026〕35号</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>铁税一稽罚〔2026〕17号</t>
+        </is>
+      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>我局于2025年7月10日起对你公司(地址:福建省闽侯县青口镇祥宏南路922号)2023年1月1日至2024年12月31日期间的发票涉税情况进行检查,违法事实及处理决定如下: (二)你公司取得毕节七星关区辰楚汽车服务部(个人独资)、毕节七星关锦悦汽车服务部(个人独资)、贵州杨亭汽车销售有限公司、贵州楠鑫汽车销售有限公司已证实虚开的35份机动车发票。 (二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 (三)根据《中华人民共和国企业所得税法》第五条、第八条、《企业所得税税前扣除凭证管理办法》(国家税务总局公告2018年第28号发布)第四条、第十二条的规定,你公司取得上述虚开的发票不得作为税前扣除凭证。</t>
+          <t>查属期内违法行为均定性偷税, 需要对原处罚决定中的罚款数额 以变更,你(单位)存在违法事实及处罚决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 〔2022〕59号) 第一条、 第三条之规定, 你单位存在少缴属期2010 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。 月属期申报数据,用于证明你单位未申报缴纳印花税。 报,不缴或者少缴应纳税款的,是偷税。 务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴 内首次因偷税被税务机关处罚,并能够配合税务机关检查的,处 不缴或者少缴的税款百分之五十的罚款”之规定,对你单位城镇 土地使用税和印花税处不缴或者少缴的税款50%的罚款。 你单位印花税偷税违法行为发生于2009年11月26日,至立案 位检查属期内违法行为均定性偷税, 需要对原处理决定中的查补 情况进行了检查,违法事实及处理决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 定, 你单位存在少缴属期2010年1月至2022年6月城镇土地使 用税5,710,765.50元的违法事实。 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 该地块未缴纳契税,你单位存在少缴契税509,984.64元的违法 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>3778.22</v>
-      </c>
+          <t>增值税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、契税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="n"/>
       <c r="S9" s="3" t="n"/>
-      <c r="T9" s="3" t="n"/>
+      <c r="T9" s="3" t="n">
+        <v>2855382.83</v>
+      </c>
       <c r="U9" s="3" t="n"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>(二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期城市维护建设税124.75元。 根据《征收教育费附加的暂行规定》第二条、第三条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期教育费附加53.47元。 根据《福建省人民政府关于调整地方教育附加征收标准等有关问题的通知》(闽政文〔2011〕230号)第一条、第二条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期地方教育附加35.64元。</t>
-        </is>
-      </c>
-      <c r="W9" s="4" t="n"/>
+          <t>定,每日按罚款数额的百分之三加处罚款。 日”之规定,你单位每月应补缴城镇土地使用税44,269.50元 征收城镇土地使用税, 自2010年1月至2022年6月应补缴城镇 所载金额的万分之五,你单位应补缴2009年11月26日印花税 定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="n">
+        <v>46183</v>
+      </c>
       <c r="X9" s="4" t="n">
-        <v>46218</v>
+        <v>46225</v>
       </c>
       <c r="Y9" s="4" t="n"/>
       <c r="Z9" s="4" t="n">
-        <v>46229</v>
+        <v>46240</v>
       </c>
       <c r="AA9" s="4" t="n">
         <v>46240</v>
@@ -7161,38 +7471,40 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AF9" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG9" s="2" t="inlineStr"/>
       <c r="AH9" s="2" t="inlineStr">
         <is>
-          <t>关于送达福州顺路汽车运输有限公司《税务处理决定书》的公告 _
- 其他类 _
- 国家税务总局福州市税务局</t>
+          <t>国家税务总局辽宁省税务局 通知公告 国家税务总局铁岭市税务局税务文书送达公告</t>
         </is>
       </c>
       <c r="AI9" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>字段“决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。 字段“关联处理决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处罚决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CASE-3f564fd9992b1ae3</t>
+          <t>CASE-7b9a26f2ac401107</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DOC-c34e1d13286aafe2</t>
+          <t>DOC-f6c6ea472b2ca04a</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -7202,28 +7514,28 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>泉州市</t>
+          <t>三明市</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局第二稽查局</t>
+          <t>国家税务总局三明市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局第二稽查局</t>
+          <t>国家税务总局三明市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>泉州隆鸿服装制造有限公司</t>
+          <t>三明众祥房地产开发有限公司</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>91350525MA8U3U963L</t>
+          <t>91350400678473231W</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
@@ -7234,37 +7546,39 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>泉税二稽处〔2026〕107号</t>
+          <t>明税一稽处〔2026〕20号</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>泉税二稽处〔2026〕107号</t>
+          <t>明税一稽处〔2026〕20号</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>日对你公司税收违法事实依法作出《税务处理决定书》(泉税二稽处〔 涉税情况进行了检查,查明违法事实及处理决定如下: 年你公司在无真实货物交易的情况下,取得河南中弘纺织有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 年期间,你公司在无真实货物交易的情况下,取得开封兴旺纺织品有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 上述违法事实有检查人员实地检查资料、电话拨打记录、邮寄退回函件、《已证实虚开通知单》等相关受托协查资料、主管税务机关出具的《已抵扣证明》、《情况说明》和你公司的申报纳税资料、银行账户流水等 号第三次修订)第二十一条第二款第二项之规定,认定你公司让他人为自己虚开 号第二次修订)第九条和《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告〔 号)之规定,对你公司取得上述已证实虚开的 之规定,决定向你公司追缴少缴的城市维护建设税-增值税附征 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 规定,决定向你公司追缴少缴的教育费附加-增值税附征 规定,决定向你公司追缴少缴的地方教育附加-增值税附征</t>
+          <t>情况进行了检查,违法事实及处理决定如下: 2016年期间,在没有真实业务情况下,取得重庆市博海建设工程(集团)有限公司、福建九九建设有限公司三明分公司开具的不符合规定的发票,发票金额400252379元,在企业所得税税前扣除,造成少缴纳企业所得税100063094.75元,该行为违反《中华人民共和国税收征收管理法》(2015年4月24日主席令第二十三号修改)第六十三条第一款 纳税人伪造、变造、隐匿、擅自销毁账簿、记账凭证,或者在账簿上多列支出或者不列、少列收入,或者经税务机关通知申报而拒不申报或者进行虚假的纳税申报,不缴或者少缴应纳税款的,是偷税。 对纳税人偷税的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款; 之规定,对你公司在账上多列支出,造成少缴企业所得税100063094.75元的行为认定为偷税。 之规定,对你公司少缴的企业所得税从滞纳之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="n"/>
+          <t>企业所得税</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>100063094.75</v>
+      </c>
       <c r="S10" s="3" t="n"/>
       <c r="T10" s="3" t="n"/>
       <c r="U10" s="3" t="n"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>由于你公司走逃失联、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 (五)根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司上述应补缴税款按税款所属时间从税款滞纳之日起按日加收万分之五滞纳金</t>
+          <t>据《中华人民共和国税收征收管理法实施细则》第106条规定,将该文书予以公告送达,自公告之日起满30日视为送达。</t>
         </is>
       </c>
       <c r="W10" s="4" t="n"/>
       <c r="X10" s="4" t="n">
-        <v>46202</v>
+        <v>46223</v>
       </c>
       <c r="Y10" s="4" t="n"/>
       <c r="Z10" s="4" t="n">
@@ -7297,9 +7611,9 @@
       <c r="AG10" s="2" t="inlineStr"/>
       <c r="AH10" s="2" t="inlineStr">
         <is>
-          <t>关于对泉州隆鸿服装制造有限公司《税务处理决定书》送达的公告 _
+          <t>关于送达三明众祥房地产开发有限公司 《税务处理决定书》的公告 _
  其他公告 _
- 国家税务总局泉州市税务局</t>
+ 国家税务总局三明市税务局</t>
         </is>
       </c>
       <c r="AI10" s="2" t="inlineStr">
@@ -7315,47 +7629,47 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>CASE-a62e569c195adc3c</t>
+          <t>CASE-31e4a827dfd253f2</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>DOC-b1dda915d4e6117d</t>
+          <t>DOC-3ec54358fce2350d</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>遵义市</t>
+          <t>福州市</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>贵州服格定商贸有限公司</t>
+          <t>福州顺路汽车运输有限公司</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91520302MABUEHN034</t>
+          <t>91350102MA31MF6611</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
@@ -7366,33 +7680,39 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>遵税一稽处〔2026〕30号</t>
+          <t>榕税一稽处〔2026〕137号</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>遵税一稽处〔2026〕30号</t>
+          <t>榕税一稽处〔2026〕137号</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
+          <t>我局于2025年7月10日起对你公司(地址:福建省闽侯县青口镇祥宏南路922号)2023年1月1日至2024年12月31日期间的发票涉税情况进行检查,违法事实及处理决定如下: (二)你公司取得毕节七星关区辰楚汽车服务部(个人独资)、毕节七星关锦悦汽车服务部(个人独资)、贵州杨亭汽车销售有限公司、贵州楠鑫汽车销售有限公司已证实虚开的35份机动车发票。 (二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 (三)根据《中华人民共和国企业所得税法》第五条、第八条、《企业所得税税前扣除凭证管理办法》(国家税务总局公告2018年第28号发布)第四条、第十二条的规定,你公司取得上述虚开的发票不得作为税前扣除凭证。</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="n"/>
+          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>3778.22</v>
+      </c>
       <c r="S11" s="3" t="n"/>
       <c r="T11" s="3" t="n"/>
       <c r="U11" s="3" t="n"/>
-      <c r="V11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>(二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期城市维护建设税124.75元。 根据《征收教育费附加的暂行规定》第二条、第三条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期教育费附加53.47元。 根据《福建省人民政府关于调整地方教育附加征收标准等有关问题的通知》(闽政文〔2011〕230号)第一条、第二条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期地方教育附加35.64元。</t>
+        </is>
+      </c>
       <c r="W11" s="4" t="n"/>
       <c r="X11" s="4" t="n">
-        <v>46185</v>
+        <v>46218</v>
       </c>
       <c r="Y11" s="4" t="n"/>
       <c r="Z11" s="4" t="n">
@@ -7425,7 +7745,9 @@
       <c r="AG11" s="2" t="inlineStr"/>
       <c r="AH11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
+          <t>关于送达福州顺路汽车运输有限公司《税务处理决定书》的公告 _
+ 其他类 _
+ 国家税务总局福州市税务局</t>
         </is>
       </c>
       <c r="AI11" s="2" t="inlineStr">
@@ -7441,54 +7763,50 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CASE-f94bf08964abff5a</t>
+          <t>CASE-3f564fd9992b1ae3</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>DOC-4574b1aadef8f30d</t>
+          <t>DOC-c34e1d13286aafe2</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
+          <t>泉州市</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
+          <t>国家税务总局泉州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局稽查局</t>
+          <t>国家税务总局泉州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>常州市文杰车辆配件厂</t>
+          <t>泉州隆鸿服装制造有限公司</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>91320411799075280A</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>朱某</t>
-        </is>
-      </c>
+          <t>91350525MA8U3U963L</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
           <t>税务处理决定书</t>
@@ -7496,41 +7814,37 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕73号</t>
+          <t>泉税二稽处〔2026〕107号</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕73号</t>
+          <t>泉税二稽处〔2026〕107号</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公 月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
+          <t>日对你公司税收违法事实依法作出《税务处理决定书》(泉税二稽处〔 涉税情况进行了检查,查明违法事实及处理决定如下: 年你公司在无真实货物交易的情况下,取得河南中弘纺织有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 年期间,你公司在无真实货物交易的情况下,取得开封兴旺纺织品有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 上述违法事实有检查人员实地检查资料、电话拨打记录、邮寄退回函件、《已证实虚开通知单》等相关受托协查资料、主管税务机关出具的《已抵扣证明》、《情况说明》和你公司的申报纳税资料、银行账户流水等 号第三次修订)第二十一条第二款第二项之规定,认定你公司让他人为自己虚开 号第二次修订)第九条和《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告〔 号)之规定,对你公司取得上述已证实虚开的 之规定,决定向你公司追缴少缴的城市维护建设税-增值税附征 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 规定,决定向你公司追缴少缴的教育费附加-增值税附征 规定,决定向你公司追缴少缴的地方教育附加-增值税附征</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="n">
-        <v>179137.12</v>
-      </c>
+          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="n"/>
       <c r="S12" s="3" t="n"/>
       <c r="T12" s="3" t="n"/>
       <c r="U12" s="3" t="n"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市 份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元,</t>
-        </is>
-      </c>
-      <c r="W12" s="4" t="n">
-        <v>46044</v>
-      </c>
+          <t>由于你公司走逃失联、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 (五)根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司上述应补缴税款按税款所属时间从税款滞纳之日起按日加收万分之五滞纳金</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="n"/>
       <c r="X12" s="4" t="n">
-        <v>46090</v>
+        <v>46202</v>
       </c>
       <c r="Y12" s="4" t="n"/>
       <c r="Z12" s="4" t="n">
@@ -7559,20 +7873,18 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF12" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF12" s="2" t="inlineStr"/>
       <c r="AG12" s="2" t="inlineStr"/>
       <c r="AH12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
+          <t>关于对泉州隆鸿服装制造有限公司《税务处理决定书》送达的公告 _
+ 其他公告 _
+ 国家税务总局泉州市税务局</t>
         </is>
       </c>
       <c r="AI12" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ12" s="2" t="inlineStr">
@@ -7583,47 +7895,47 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CASE-61b9b55a9d3357c7</t>
+          <t>CASE-a62e569c195adc3c</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>DOC-1228a9c92b2b0632</t>
+          <t>DOC-b1dda915d4e6117d</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
+          <t>遵义市</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局遵义市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局遵义市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>常州市三鹏机械有限公司</t>
+          <t>贵州服格定商贸有限公司</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>91320404732260748Q</t>
+          <t>91520302MABUEHN034</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
@@ -7634,39 +7946,33 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
+          <t>遵税一稽处〔2026〕30号</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>常税稽一罚〔2026〕14号</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
+          <t>遵税一稽处〔2026〕30号</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
+        </is>
+      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="n">
-        <v>63464.09</v>
-      </c>
+          <t>增值税</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="n"/>
       <c r="S13" s="3" t="n"/>
       <c r="T13" s="3" t="n"/>
       <c r="U13" s="3" t="n"/>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
-        </is>
-      </c>
+      <c r="V13" s="2" t="inlineStr"/>
       <c r="W13" s="4" t="n"/>
       <c r="X13" s="4" t="n">
-        <v>46066</v>
+        <v>46185</v>
       </c>
       <c r="Y13" s="4" t="n"/>
       <c r="Z13" s="4" t="n">
@@ -7699,7 +8005,7 @@
       <c r="AG13" s="2" t="inlineStr"/>
       <c r="AH13" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
         </is>
       </c>
       <c r="AI13" s="2" t="inlineStr">
@@ -7715,16 +8021,16 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASE-61b9b55a9d3357c7</t>
+          <t>CASE-f94bf08964abff5a</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DOC-b97456a64b153f67</t>
+          <t>DOC-4574b1aadef8f30d</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -7740,65 +8046,71 @@
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局常州市税务局稽查局</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>常州市三鹏机械有限公司</t>
+          <t>常州市文杰车辆配件厂</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>91320404732260748Q</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
+          <t>91320411799075280A</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>朱某</t>
+        </is>
+      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>常税稽一罚〔2026〕14号</t>
+          <t>常税稽处〔2026〕73号</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>常税稽一罚〔2026〕14号</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr"/>
+          <t>常税稽处〔2026〕73号</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公 月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
+        </is>
+      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R14" s="3" t="n"/>
+      <c r="R14" s="3" t="n">
+        <v>179137.12</v>
+      </c>
       <c r="S14" s="3" t="n"/>
-      <c r="T14" s="3" t="n">
-        <v>20000</v>
-      </c>
+      <c r="T14" s="3" t="n"/>
       <c r="U14" s="3" t="n"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
-        </is>
-      </c>
-      <c r="W14" s="4" t="n"/>
+          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市 份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元,</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="n">
+        <v>46044</v>
+      </c>
       <c r="X14" s="4" t="n">
-        <v>46066</v>
+        <v>46090</v>
       </c>
       <c r="Y14" s="4" t="n"/>
       <c r="Z14" s="4" t="n">
@@ -7827,16 +8139,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AF14" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG14" s="2" t="inlineStr"/>
       <c r="AH14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI14" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ14" s="2" t="inlineStr">
@@ -7847,47 +8163,47 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CASE-f78ec1a594442165</t>
+          <t>CASE-61b9b55a9d3357c7</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>DOC-fbbe4a664b14f54b</t>
+          <t>DOC-1228a9c92b2b0632</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>安顺市</t>
+          <t>常州市</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
+          <t>常州市三鹏机械有限公司</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>91520423MA6DLH799Q</t>
+          <t>91320404732260748Q</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
@@ -7898,45 +8214,39 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
-        </is>
-      </c>
+          <t>常税稽一罚〔2026〕14号</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R15" s="3" t="n">
-        <v>64884.41</v>
+        <v>63464.09</v>
       </c>
       <c r="S15" s="3" t="n"/>
       <c r="T15" s="3" t="n"/>
       <c r="U15" s="3" t="n"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
-      <c r="W15" s="4" t="n">
-        <v>45898</v>
-      </c>
+          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="n"/>
       <c r="X15" s="4" t="n">
-        <v>46043</v>
+        <v>46066</v>
       </c>
       <c r="Y15" s="4" t="n"/>
       <c r="Z15" s="4" t="n">
@@ -7965,71 +8275,67 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF15" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF15" s="2" t="inlineStr"/>
       <c r="AG15" s="2" t="inlineStr"/>
       <c r="AH15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI15" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ15" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。 字段“主要违法事实”存在冲突:保留原值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”,新值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CASE-f78ec1a594442165</t>
+          <t>CASE-61b9b55a9d3357c7</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>DOC-9a828a6048b54b6c</t>
+          <t>DOC-b97456a64b153f67</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>安顺市</t>
+          <t>常州市</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
+          <t>常州市三鹏机械有限公司</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>91520423MA6DLH799Q</t>
+          <t>91320404732260748Q</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
@@ -8040,45 +8346,39 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>安市税稽罚〔2026〕1号</t>
+          <t>常税稽一罚〔2026〕14号</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
-        </is>
-      </c>
+          <t>常税稽一罚〔2026〕14号</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R16" s="3" t="n"/>
       <c r="S16" s="3" t="n"/>
       <c r="T16" s="3" t="n">
-        <v>200000</v>
+        <v>20000</v>
       </c>
       <c r="U16" s="3" t="n"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
-      <c r="W16" s="4" t="n">
-        <v>45898</v>
-      </c>
+          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
+        </is>
+      </c>
+      <c r="W16" s="4" t="n"/>
       <c r="X16" s="4" t="n">
-        <v>46043</v>
+        <v>46066</v>
       </c>
       <c r="Y16" s="4" t="n"/>
       <c r="Z16" s="4" t="n">
@@ -8107,71 +8407,67 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF16" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF16" s="2" t="inlineStr"/>
       <c r="AG16" s="2" t="inlineStr"/>
       <c r="AH16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI16" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ16" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CASE-fe959d4c6c52d910</t>
+          <t>CASE-f78ec1a594442165</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>DOC-f2643f2a0719d8d1</t>
+          <t>DOC-fbbe4a664b14f54b</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>南宁市</t>
+          <t>安顺市</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局稽查局</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>南宁洪谦金贸易有限公司</t>
+          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>91450103MA5K9WHY7U</t>
+          <t>91520423MA6DLH799Q</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
@@ -8182,33 +8478,45 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>南市税一稽处〔2026〕2号</t>
+          <t>安市税稽处〔2026〕1号</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>南市税一稽处〔2026〕2号</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr"/>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽罚〔2026〕1号</t>
+        </is>
+      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>经我局2025年10月29日至2025年12月8日对你公司(地址:南宁市青秀区云景路11号春晖花园C区3栋2单元1606号)2015年12月2日至2016年12月31日期间的涉税情况进行了检查,你(单位)存在以下违法事实: 经查询你公司向税务机关报备的银行账号:广西北部湾银行南宁市财富国际支行800099398800015,经函询广西北部湾银行南宁市财富国际支行,存在以下问题: 上述行为属于开具与实际经营业务情况不符的增值税发票,违反了《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第587号修改)第二十二条第一款、第二款第(一)项的规定,属于虚开发票行为。</t>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="n"/>
+          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>64884.41</v>
+      </c>
       <c r="S17" s="3" t="n"/>
       <c r="T17" s="3" t="n"/>
       <c r="U17" s="3" t="n"/>
-      <c r="V17" s="2" t="inlineStr"/>
-      <c r="W17" s="4" t="n"/>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="W17" s="4" t="n">
+        <v>45898</v>
+      </c>
       <c r="X17" s="4" t="n">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="Y17" s="4" t="n"/>
       <c r="Z17" s="4" t="n">
@@ -8245,7 +8553,7 @@
       <c r="AG17" s="2" t="inlineStr"/>
       <c r="AH17" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局税务文书送达公告_国家税务总局南宁市税务局</t>
+          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI17" s="2" t="inlineStr">
@@ -8255,89 +8563,103 @@
       </c>
       <c r="AJ17" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。 字段“主要违法事实”存在冲突:保留原值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”,新值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CASE-1983d97878508732</t>
+          <t>CASE-f78ec1a594442165</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>DOC-f9760895b4f08cc2</t>
+          <t>DOC-9a828a6048b54b6c</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>二连浩特市</t>
+          <t>安顺市</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局</t>
+          <t>国家税务总局安顺市税务局</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局稽查局</t>
+          <t>国家税务总局安顺市税务局稽查局</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>二连市坤益腾金属有限公司</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr"/>
+          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>91520423MA6DLH799Q</t>
+        </is>
+      </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
+          <t>安市税稽罚〔2026〕1号</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr"/>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽罚〔2026〕1号</t>
+        </is>
+      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
+          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R18" s="3" t="n"/>
       <c r="S18" s="3" t="n"/>
-      <c r="T18" s="3" t="n"/>
+      <c r="T18" s="3" t="n">
+        <v>200000</v>
+      </c>
       <c r="U18" s="3" t="n"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
-        </is>
-      </c>
-      <c r="W18" s="4" t="n"/>
-      <c r="X18" s="4" t="n"/>
+          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="W18" s="4" t="n">
+        <v>45898</v>
+      </c>
+      <c r="X18" s="4" t="n">
+        <v>46043</v>
+      </c>
       <c r="Y18" s="4" t="n"/>
       <c r="Z18" s="4" t="n">
         <v>46229</v>
@@ -8357,7 +8679,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE18" s="5" t="inlineStr">
@@ -8365,61 +8687,73 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AF18" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG18" s="2" t="inlineStr"/>
       <c r="AH18" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI18" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ18" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CASE-d4b6986f3f97cd28</t>
+          <t>CASE-fe959d4c6c52d910</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>DOC-442cf3d9a5280c12</t>
+          <t>DOC-f2643f2a0719d8d1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>鄂尔多斯市</t>
+          <t>南宁市</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局南宁市税务局第一稽查局</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>第二稽查局</t>
+          <t>国家税务总局南宁市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>廖礼平</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr"/>
+          <t>南宁洪谦金贸易有限公司</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>91450103MA5K9WHY7U</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
@@ -8428,40 +8762,34 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
+          <t>南市税一稽处〔2026〕2号</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
+          <t>南市税一稽处〔2026〕2号</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
+          <t>经我局2025年10月29日至2025年12月8日对你公司(地址:南宁市青秀区云景路11号春晖花园C区3栋2单元1606号)2015年12月2日至2016年12月31日期间的涉税情况进行了检查,你(单位)存在以下违法事实: 经查询你公司向税务机关报备的银行账号:广西北部湾银行南宁市财富国际支行800099398800015,经函询广西北部湾银行南宁市财富国际支行,存在以下问题: 上述行为属于开具与实际经营业务情况不符的增值税发票,违反了《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第587号修改)第二十二条第一款、第二款第(一)项的规定,属于虚开发票行为。</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>个人所得税、印花税</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>15072487.5</v>
-      </c>
-      <c r="S19" s="3" t="n">
-        <v>1046925</v>
-      </c>
+          <t>增值税</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="n"/>
+      <c r="S19" s="3" t="n"/>
       <c r="T19" s="3" t="n"/>
       <c r="U19" s="3" t="n"/>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
-        </is>
-      </c>
+      <c r="V19" s="2" t="inlineStr"/>
       <c r="W19" s="4" t="n"/>
-      <c r="X19" s="4" t="n"/>
+      <c r="X19" s="4" t="n">
+        <v>46031</v>
+      </c>
       <c r="Y19" s="4" t="n"/>
       <c r="Z19" s="4" t="n">
         <v>46229</v>
@@ -8481,7 +8809,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE19" s="5" t="inlineStr">
@@ -8489,69 +8817,69 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AF19" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG19" s="2" t="inlineStr"/>
       <c r="AH19" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>国家税务总局南宁市税务局第一稽查局税务文书送达公告_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI19" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ19" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CASE-7e3d4a321440d6a7</t>
+          <t>CASE-1983d97878508732</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>DOC-bed9330343ed06af</t>
+          <t>DOC-f9760895b4f08cc2</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>二连浩特市</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
+          <t>国家税务总局二连浩特市税务局</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
+          <t>国家税务总局二连浩特市税务局稽查局</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>天津展达科技有限公司</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>91120116300738701X</t>
-        </is>
-      </c>
+          <t>二连市坤益腾金属有限公司</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
@@ -8560,45 +8888,39 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
+          <t>二税稽处〔2025〕1号</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
+          <t>二税稽处〔2025〕1号</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R20" s="3" t="n">
-        <v>920146.9399999999</v>
-      </c>
+          <t>增值税</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="n"/>
       <c r="S20" s="3" t="n"/>
       <c r="T20" s="3" t="n"/>
       <c r="U20" s="3" t="n"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
         </is>
       </c>
       <c r="W20" s="4" t="n"/>
       <c r="X20" s="4" t="n"/>
       <c r="Y20" s="4" t="n"/>
       <c r="Z20" s="4" t="n">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="AA20" s="4" t="n">
         <v>46240</v>
@@ -8627,7 +8949,7 @@
       <c r="AG20" s="2" t="inlineStr"/>
       <c r="AH20" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="AI20" s="2" t="inlineStr">
@@ -8637,102 +8959,92 @@
       </c>
       <c r="AJ20" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CASE-7e3d4a321440d6a7</t>
+          <t>CASE-d4b6986f3f97cd28</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>DOC-388bd01c01bbb789</t>
+          <t>DOC-442cf3d9a5280c12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>鄂尔多斯市</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
-        </is>
-      </c>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
+          <t>第二稽查局</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>天津展达科技有限公司</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>91120116300738701X</t>
-        </is>
-      </c>
+          <t>廖礼平</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>津税一稽罚〔2023〕21号</t>
+          <t>鄂税二稽处〔2023〕29号</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
+          <t>鄂税二稽处〔2023〕29号</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="n"/>
-      <c r="S21" s="3" t="n"/>
-      <c r="T21" s="3" t="n">
-        <v>131368.5</v>
-      </c>
+          <t>个人所得税、印花税</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>15072487.5</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>1046925</v>
+      </c>
+      <c r="T21" s="3" t="n"/>
       <c r="U21" s="3" t="n"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
         </is>
       </c>
       <c r="W21" s="4" t="n"/>
       <c r="X21" s="4" t="n"/>
       <c r="Y21" s="4" t="n"/>
       <c r="Z21" s="4" t="n">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="AA21" s="4" t="n">
         <v>46240</v>
@@ -8761,34 +9073,302 @@
       <c r="AG21" s="2" t="inlineStr"/>
       <c r="AH21" s="2" t="inlineStr">
         <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="AI21" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ21" s="2" t="inlineStr">
+        <is>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7e3d4a321440d6a7</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>DOC-bed9330343ed06af</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>91120116300738701X</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>920146.9399999999</v>
+      </c>
+      <c r="S22" s="3" t="n"/>
+      <c r="T22" s="3" t="n"/>
+      <c r="U22" s="3" t="n"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W22" s="4" t="n"/>
+      <c r="X22" s="4" t="n"/>
+      <c r="Y22" s="4" t="n"/>
+      <c r="Z22" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AA22" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE22" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AG22" s="2" t="inlineStr"/>
+      <c r="AH22" s="2" t="inlineStr">
+        <is>
           <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
-      <c r="AI21" s="2" t="inlineStr">
+      <c r="AI22" s="2" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ21" s="2" t="inlineStr">
+      <c r="AJ22" s="2" t="inlineStr">
+        <is>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7e3d4a321440d6a7</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>DOC-388bd01c01bbb789</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>91120116300738701X</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>税务行政处罚决定书</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="n"/>
+      <c r="S23" s="3" t="n"/>
+      <c r="T23" s="3" t="n">
+        <v>131368.5</v>
+      </c>
+      <c r="U23" s="3" t="n"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W23" s="4" t="n"/>
+      <c r="X23" s="4" t="n"/>
+      <c r="Y23" s="4" t="n"/>
+      <c r="Z23" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AA23" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE23" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF23" s="2" t="inlineStr"/>
+      <c r="AG23" s="2" t="inlineStr"/>
+      <c r="AH23" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+        </is>
+      </c>
+      <c r="AI23" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ23" s="2" t="inlineStr">
         <is>
           <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ21"/>
-  <conditionalFormatting sqref="AD2:AD21">
+  <autoFilter ref="A1:AJ23"/>
+  <conditionalFormatting sqref="AD2:AD23">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AD2="待核验"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI2:AI21">
+  <conditionalFormatting sqref="AI2:AI23">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>AND($AI2&lt;&gt;"正常",$AI2&lt;&gt;"附件正常")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AD2:AD21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AD2:AD23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"已核验,待核验,人工复核完成"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8801,23 +9381,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE6" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE10" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE11" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE12" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF12" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE14" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE15" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF15" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE16" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF16" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE12" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE14" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF14" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE15" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE16" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE17" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF17" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE18" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE19" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE20" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE21" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF18" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE19" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF19" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE20" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE21" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE22" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE23" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -13311,7 +13895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14981,8 +15565,61 @@
         </is>
       </c>
     </row>
+    <row r="35" ht="54" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:19:59+08:00</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 至 2026-08-06</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>辽宁恒慧专用车箱有限公司</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinatax.gov.cn', port=443): Max retries exceeded with url: /fzsswj/xxgk/gsgg/qtl/ (Caused by NewConnectionError("HTTPSConnection(host='fujian.chinatax.gov.cn', port=44...</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>已完成候选发现、逐条访问核验、去重、关联和历史数据增量写入。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M34"/>
+  <autoFilter ref="A1:M35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -15,12 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日运行日志" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文书汇总'!$A$1:$AJ$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文书汇总'!$A$1:$AJ$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'完整文书'!$A$1:$AJ$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ43"/>
+  <dimension ref="A1:AJ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -705,16 +705,16 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CASE-2799cf13d16e48fa</t>
+          <t>CASE-183c0161a86cb188</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>DOC-4a944414e51221f4</t>
+          <t>DOC-b42ca490d19e80f1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -724,28 +724,28 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>北海市</t>
+          <t>来宾市</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局北海市税务局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局北海市税务局稽查局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>北海市丰赢商贸有限公司</t>
+          <t>广西侯珏酒店有限公司</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>91450500MAEULQHG42</t>
+          <t>91451323MAK6QBE777</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
@@ -756,52 +756,40 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>北市税稽处〔2026〕16号</t>
+          <t>来市税二稽处〔2026〕8号</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>北市税稽处〔2026〕16号</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>况进行了检查,违法事实及处理决定如下: 行,无法核实你公司资金流情况,你公司存在虚开风险。 经查实,根据《国家税务总局关于纳税人虚开增值税专用发 经查实,根据《中华人民共和国城市维护建设税暂行条例》 经查实,根据《征收教育费附加的暂行规定》(国发〔1986〕 经查实,根据《广西壮族自治区人民政府关于印发广西壮 你公司所属期 2025 年 8 月未进行纳税申报,不缴或者少缴 三条第一款规定,对上述行为定性为偷税,向你公司追缴少缴的 对你公司少缴的税款从税款滞纳之日起至实际缴纳税款之日止 公司向下游企业虚开 9 份增值税电子专用发票(发票号码: 况进行了检查,违法事实及处理决定如下: 行,无法核实你公司资金流情况,你公司存在虚开风险。 经查实,根据《国家税务总局关于纳税人虚开增值税专用发 经查实,根据《中华人民共和国城市维护建设税暂行条例》 经查实,根据《征收教育费附加的暂行规定》(国发〔1986〕 经查实,根据《广西壮族自治区人民政府关于印发广西壮 你公司所属期 2025 年 8 月未进行纳税申报,不缴或者少缴 三条第一款规定,对上述行为定性为偷税,向你公司追缴少缴的 对你公司少缴的税款从税款滞纳之日起至实际缴纳税款之日止 公司向下游企业虚开 9 份增值税电子专用发票(发票号码:</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>512334.96</v>
-      </c>
+          <t>来市税二稽处〔2026〕8号</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>来市税二稽罚〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="3" t="n"/>
       <c r="S2" s="3" t="n"/>
       <c r="T2" s="3" t="n"/>
       <c r="U2" s="3" t="n"/>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>你公司所属期2025 年 8 月应补缴增值税465759.06 元。 司所属期2025 年 8 月应补缴纳城市维护建设税32603.13 元。 公司所属期 2025 年8 月应补缴纳教育费附加 13972.77 元。 第三条的规定,你公司所属期2025 年 8 月应补缴纳地方教育附 你公司所属期2025 年 8 月应补缴增值税465759.06 元。 司所属期2025 年 8 月应补缴纳城市维护建设税32603.13 元。 公司所属期 2025 年8 月应补缴纳教育费附加 13972.77 元。 第三条的规定,你公司所属期2025 年 8 月应补缴纳地方教育附</t>
-        </is>
-      </c>
-      <c r="W2" s="4" t="n">
-        <v>46237</v>
-      </c>
+      <c r="V2" s="2" t="inlineStr"/>
+      <c r="W2" s="4" t="n"/>
       <c r="X2" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="Y2" s="4" t="n"/>
       <c r="Z2" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -819,123 +807,107 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF2" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF2" s="2" t="inlineStr"/>
       <c r="AG2" s="2" t="inlineStr"/>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>【市稽查】国家税务总局北海市税务局稽查局税务文书送达公告(北海市丰赢商贸有限公司)_国家税务总局北海市税务局</t>
+          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
         </is>
       </c>
       <c r="AI2" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
-        </is>
-      </c>
-      <c r="AJ2" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CASE-ef382edddd0f50f8</t>
+          <t>CASE-183c0161a86cb188</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>DOC-f80d567b9343411c</t>
+          <t>DOC-d238efe5d5ba0f2d</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>泉州市</t>
+          <t>来宾市</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局稽查局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>泉州平媛贸易有限公司</t>
+          <t>广西侯珏酒店有限公司</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>91350503597867511E</t>
+          <t>91451323MAK6QBE777</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>泉税稽处〔2026〕29号</t>
+          <t>来市税二稽罚〔2026〕6号</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>泉税稽处〔2026〕29号</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>进行了检查,违法事实及处理决定如下: 经查,2013年1月25日至2013年1月28日期间,你公司将4900万元资金贷与庄彬阳使用,你公司未就该项贷款业务申报缴纳企业所得税、营业税及附加税费。</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>企业所得税</t>
-        </is>
-      </c>
+          <t>来市税二稽处〔2026〕8号</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>来市税二稽罚〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
       <c r="R3" s="3" t="n"/>
       <c r="S3" s="3" t="n"/>
       <c r="T3" s="3" t="n"/>
       <c r="U3" s="3" t="n"/>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满30日,即视为送达。</t>
-        </is>
-      </c>
+      <c r="V3" s="2" t="inlineStr"/>
       <c r="W3" s="4" t="n"/>
       <c r="X3" s="4" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="Y3" s="4" t="n"/>
       <c r="Z3" s="4" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -957,9 +929,7 @@
       <c r="AG3" s="2" t="inlineStr"/>
       <c r="AH3" s="2" t="inlineStr">
         <is>
-          <t>关于对泉州平媛贸易有限公司《税务处理决定书》送达的公告 _
- 其他公告 _
- 国家税务总局泉州市税务局</t>
+          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
         </is>
       </c>
       <c r="AI3" s="2" t="inlineStr">
@@ -967,24 +937,20 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ3" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
+      <c r="AJ3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CASE-119dcfa5a7c6b239</t>
+          <t>CASE-2799cf13d16e48fa</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>DOC-1a423a3cbfed9f3f</t>
+          <t>DOC-4a944414e51221f4</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -994,28 +960,28 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>南宁市</t>
+          <t>北海市</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第三稽查局</t>
+          <t>国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第三稽查局</t>
+          <t>国家税务总局北海市税务局稽查局</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>广西威曼能源科技有限公司</t>
+          <t>北海市丰赢商贸有限公司</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>91450103MA5NJYGEXM</t>
+          <t>91450500MAEULQHG42</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
@@ -1026,40 +992,52 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽处〔2026〕19号</t>
+          <t>北市税稽处〔2026〕16号</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽处〔2026〕19号</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>南市税三稽罚〔2026〕10号</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="3" t="n"/>
+          <t>北市税稽处〔2026〕16号</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>况进行了检查,违法事实及处理决定如下: 行,无法核实你公司资金流情况,你公司存在虚开风险。 经查实,根据《国家税务总局关于纳税人虚开增值税专用发 经查实,根据《中华人民共和国城市维护建设税暂行条例》 经查实,根据《征收教育费附加的暂行规定》(国发〔1986〕 经查实,根据《广西壮族自治区人民政府关于印发广西壮 你公司所属期 2025 年 8 月未进行纳税申报,不缴或者少缴 三条第一款规定,对上述行为定性为偷税,向你公司追缴少缴的 对你公司少缴的税款从税款滞纳之日起至实际缴纳税款之日止 公司向下游企业虚开 9 份增值税电子专用发票(发票号码: 况进行了检查,违法事实及处理决定如下: 行,无法核实你公司资金流情况,你公司存在虚开风险。 经查实,根据《国家税务总局关于纳税人虚开增值税专用发 经查实,根据《中华人民共和国城市维护建设税暂行条例》 经查实,根据《征收教育费附加的暂行规定》(国发〔1986〕 经查实,根据《广西壮族自治区人民政府关于印发广西壮 你公司所属期 2025 年 8 月未进行纳税申报,不缴或者少缴 三条第一款规定,对上述行为定性为偷税,向你公司追缴少缴的 对你公司少缴的税款从税款滞纳之日起至实际缴纳税款之日止 公司向下游企业虚开 9 份增值税电子专用发票(发票号码:</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>512334.96</v>
+      </c>
       <c r="S4" s="3" t="n"/>
       <c r="T4" s="3" t="n"/>
       <c r="U4" s="3" t="n"/>
-      <c r="V4" s="2" t="inlineStr"/>
-      <c r="W4" s="4" t="n"/>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>你公司所属期2025 年 8 月应补缴增值税465759.06 元。 司所属期2025 年 8 月应补缴纳城市维护建设税32603.13 元。 公司所属期 2025 年8 月应补缴纳教育费附加 13972.77 元。 第三条的规定,你公司所属期2025 年 8 月应补缴纳地方教育附 你公司所属期2025 年 8 月应补缴增值税465759.06 元。 司所属期2025 年 8 月应补缴纳城市维护建设税32603.13 元。 公司所属期 2025 年8 月应补缴纳教育费附加 13972.77 元。 第三条的规定,你公司所属期2025 年 8 月应补缴纳地方教育附</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>46237</v>
+      </c>
       <c r="X4" s="4" t="n">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="Y4" s="4" t="n"/>
       <c r="Z4" s="4" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1085,7 +1063,7 @@
       <c r="AG4" s="2" t="inlineStr"/>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第三稽查局 税务文书送达公告_国家税务总局南宁市税务局</t>
+          <t>【市稽查】国家税务总局北海市税务局稽查局税务文书送达公告(北海市丰赢商贸有限公司)_国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="AI4" s="2" t="inlineStr">
@@ -1101,91 +1079,99 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CASE-119dcfa5a7c6b239</t>
+          <t>CASE-ef382edddd0f50f8</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>DOC-f8499a65abd851d8</t>
+          <t>DOC-f80d567b9343411c</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>南宁市</t>
+          <t>泉州市</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第三稽查局</t>
+          <t>国家税务总局泉州市税务局</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第三稽查局</t>
+          <t>国家税务总局泉州市税务局稽查局</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>广西威曼能源科技有限公司</t>
+          <t>泉州平媛贸易有限公司</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>91450103MA5NJYGEXM</t>
+          <t>91350503597867511E</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽罚〔2026〕10号</t>
+          <t>泉税稽处〔2026〕29号</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽处〔2026〕19号</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>南市税三稽罚〔2026〕10号</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
+          <t>泉税稽处〔2026〕29号</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>进行了检查,违法事实及处理决定如下: 经查,2013年1月25日至2013年1月28日期间,你公司将4900万元资金贷与庄彬阳使用,你公司未就该项贷款业务申报缴纳企业所得税、营业税及附加税费。</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>企业所得税</t>
+        </is>
+      </c>
       <c r="R5" s="3" t="n"/>
       <c r="S5" s="3" t="n"/>
       <c r="T5" s="3" t="n"/>
       <c r="U5" s="3" t="n"/>
-      <c r="V5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满30日,即视为送达。</t>
+        </is>
+      </c>
       <c r="W5" s="4" t="n"/>
       <c r="X5" s="4" t="n">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n">
-        <v>46236</v>
+        <v>46238</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1203,20 +1189,18 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF5" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF5" s="2" t="inlineStr"/>
       <c r="AG5" s="2" t="inlineStr"/>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第三稽查局 税务文书送达公告_国家税务总局南宁市税务局</t>
+          <t>关于对泉州平媛贸易有限公司《税务处理决定书》送达的公告 _
+ 其他公告 _
+ 国家税务总局泉州市税务局</t>
         </is>
       </c>
       <c r="AI5" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr">
@@ -1227,16 +1211,16 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>CASE-c48b4ac9b3677385</t>
+          <t>CASE-119dcfa5a7c6b239</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>DOC-d3324d06254a350f</t>
+          <t>DOC-1a423a3cbfed9f3f</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1262,12 +1246,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>广西松柏建筑装饰设计有限公司</t>
+          <t>广西威曼能源科技有限公司</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>91450108MA5P1DL467</t>
+          <t>91450103MA5NJYGEXM</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
@@ -1278,17 +1262,17 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽处〔2026〕18号</t>
+          <t>南市税三稽处〔2026〕19号</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽处〔2026〕18号</t>
+          <t>南市税三稽处〔2026〕19号</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽罚〔2026〕9号</t>
+          <t>南市税三稽罚〔2026〕10号</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr"/>
@@ -1304,10 +1288,10 @@
       </c>
       <c r="Y6" s="4" t="n"/>
       <c r="Z6" s="4" t="n">
-        <v>46238</v>
+        <v>46236</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1353,16 +1337,16 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CASE-c48b4ac9b3677385</t>
+          <t>CASE-119dcfa5a7c6b239</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>DOC-c40aad0bbe60707b</t>
+          <t>DOC-f8499a65abd851d8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1388,12 +1372,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>广西松柏建筑装饰设计有限公司</t>
+          <t>广西威曼能源科技有限公司</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>91450108MA5P1DL467</t>
+          <t>91450103MA5NJYGEXM</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
@@ -1404,17 +1388,17 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽罚〔2026〕9号</t>
+          <t>南市税三稽罚〔2026〕10号</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽处〔2026〕18号</t>
+          <t>南市税三稽处〔2026〕19号</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽罚〔2026〕9号</t>
+          <t>南市税三稽罚〔2026〕10号</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr"/>
@@ -1430,10 +1414,10 @@
       </c>
       <c r="Y7" s="4" t="n"/>
       <c r="Z7" s="4" t="n">
-        <v>46238</v>
+        <v>46236</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1479,76 +1463,72 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CASE-f7f5d80ec431a14d</t>
+          <t>CASE-c48b4ac9b3677385</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DOC-3a61d3452c421a37</t>
+          <t>DOC-d3324d06254a350f</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>福州市</t>
+          <t>南宁市</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局南宁市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局南宁市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>福州吉伦多德贸易有限公司</t>
+          <t>广西松柏建筑装饰设计有限公司</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>91350102MA33G4RD13</t>
+          <t>91450108MA5P1DL467</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽罚〔2026〕39号</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>南市税三稽处〔2026〕18号</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>南市税三稽处〔2026〕18号</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽罚〔2026〕39号</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>经我局于2022年5月20日起对你公司[地址:福建省福州市鼓楼区温泉街道东城边街39号(原东城边街东侧与温泉支路交叉处)恒宇国际2#楼5层10商务办公-1]2019年1月1日至2022年12月31日期间的涉税情况进行检查,你公司存在违法事实及处罚决定如下: 你公司假报出口骗取国家出口退税款4064566.77元。 你公司取得的已证实虚开发票、出口退税数据、报关单证资料比对结果等证据。</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>增值税、企业所得税、消费税</t>
-        </is>
-      </c>
+          <t>南市税三稽罚〔2026〕9号</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
       <c r="R8" s="3" t="n"/>
       <c r="S8" s="3" t="n"/>
       <c r="T8" s="3" t="n"/>
@@ -1563,11 +1543,11 @@
         <v>46238</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1585,18 +1565,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AF8" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG8" s="2" t="inlineStr"/>
       <c r="AH8" s="2" t="inlineStr">
         <is>
-          <t>关于送达福州吉伦多德贸易有限公司《税务行政处罚决定书》的公告 _
- 其他类 _
- 国家税务总局福州市税务局</t>
+          <t>国家税务总局南宁市税务局第三稽查局 税务文书送达公告_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI8" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="inlineStr">
@@ -1607,16 +1589,16 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>CASE-89fc66bfc8dad80d</t>
+          <t>CASE-c48b4ac9b3677385</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DOC-6e5b966cd65a4366</t>
+          <t>DOC-c40aad0bbe60707b</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1626,78 +1608,72 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>北海市</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>银海区</t>
-        </is>
-      </c>
+          <t>南宁市</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局北海市税务局</t>
+          <t>国家税务总局南宁市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局北海市税务局稽查局</t>
+          <t>国家税务总局南宁市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>广西耿仁建材有限公司</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr"/>
+          <t>广西松柏建筑装饰设计有限公司</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>91450108MA5P1DL467</t>
+        </is>
+      </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>北市税稽处〔2026〕14号</t>
+          <t>南市税三稽罚〔2026〕9号</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>北市税稽处〔2026〕14号</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>我局于2026年2月11日至2026年7月15日对你公司(地址:北海市银海区新世纪大道15号辰宸花园3幢二单元0901号)2026年1月1日至2026年1月31日期间的涉税情况进行了检查,违法事实及处理决定如下: (2)短时间开具大量大额发票且未申报 你公司未进行纳税申报,不缴或者少缴2026年1月增值税194612.47元,2026年1月城市维护建设税13622.87元,合计208235.34元。 根据《中华人民共和国税收征收管理法》第六十三条第一款规定,对上述行为定性为偷税,向你公司追缴少缴的2026年增值税194612.47元,城市维护建设税13622.87元,合计208235.34元。 1.根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)的规定,对你公司少缴所属期2026年1月的教育费附加5838.37元,予以追缴。 2.根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条的规定,对你公司少缴所属期2026年1月地方教育附加3892.25元,予以追缴。 根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司少缴的税款从税款滞纳之日起至实际缴纳税款之日止按日加收滞纳税款万分之五的滞纳金,滞纳金由金三系统自动计算加收。 (四)你公司无法联系且实地核查无实际生产地址、无生产能力、查无下落,短期开票金额大,无法核实资金流,未进行纳税申报,根据《国家税务总局关于走逃(失联)企业开具增值税专用发票认定处理有关问题的公告》(国家税务总局公告2016年第76号),将你公司按走逃(失联)处理,根据《中华人民共和国发票管理办法》(国函〔1993〕174号)第二十一条第(一)项,你公司无生产能力,却为他人开具与实际经营业务情况不符的发票,属于虚开发票的行为。</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>208235.34</v>
-      </c>
+          <t>南市税三稽处〔2026〕18号</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>南市税三稽罚〔2026〕9号</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="3" t="n"/>
       <c r="S9" s="3" t="n"/>
       <c r="T9" s="3" t="n"/>
       <c r="U9" s="3" t="n"/>
       <c r="V9" s="2" t="inlineStr"/>
       <c r="W9" s="4" t="n"/>
       <c r="X9" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="Y9" s="4" t="n"/>
       <c r="Z9" s="4" t="n">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1715,16 +1691,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AF9" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG9" s="2" t="inlineStr"/>
       <c r="AH9" s="2" t="inlineStr">
         <is>
-          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕14号)_国家税务总局北海市税务局</t>
+          <t>国家税务总局南宁市税务局第三稽查局 税务文书送达公告_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI9" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr">
@@ -1735,101 +1715,91 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CASE-eb9cfd5295d501e5</t>
+          <t>CASE-f7f5d80ec431a14d</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DOC-4a8cf53b445afc63</t>
+          <t>DOC-3a61d3452c421a37</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>北海市</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>海城区</t>
-        </is>
-      </c>
+          <t>福州市</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局北海市税务局</t>
+          <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局北海市税务局稽查局</t>
+          <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>广西轩易科技有限公司</t>
+          <t>福州吉伦多德贸易有限公司</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>91450500MAK3N9UJ2T</t>
+          <t>91350102MA33G4RD13</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>北市税稽处〔2026〕6号</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>北市税稽处〔2026〕6号</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr"/>
+          <t>榕税一稽罚〔2026〕39号</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>榕税一稽罚〔2026〕39号</t>
+        </is>
+      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>我局于2026年1月23日起对你公司(地址:北海市海城区北部湾东路“金宝小区”B幢B804号20北海汇算账商务秘书有限公司托管)2025年12月11日至2025年12月31日期间的涉税情况进行了检查,发现你公司存在税收违法行为,原《税务处理决定书》(北市税稽处〔2026〕6号)认定的违法事实有误,经重新调查核实,违法事实及处理决定如下: 经查询,你公司2026年1月20日通过网络方式零申报所属期2025年10月1日-2025年12月31日的增值税、城市维护建设税及附加,入库税款0元,申报金额与实际不符,存在虚假申报的情况。 你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 (一)根据《中华人民共和国发票管理办法》(财政部令第6号发布,经国务院令第587号、第709号、第764号修订)第二十一条第二款第(一)项的规定,认定你公司为他人开具与实际经营业务情况不符的前述13份增值税普通电子发票为虚开发票(金额合计571550.49元,税额合计5715.51元,价税合计577266.00元)。 根据《中华人民共和国税收征收管理法》第三十二条、第六十三条第一款、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,已构成偷税,向你公司追缴少缴的税款合计5915.56元,并从滞纳税款之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
+          <t>经我局于2022年5月20日起对你公司[地址:福建省福州市鼓楼区温泉街道东城边街39号(原东城边街东侧与温泉支路交叉处)恒宇国际2#楼5层10商务办公-1]2019年1月1日至2022年12月31日期间的涉税情况进行检查,你公司存在违法事实及处罚决定如下: 你公司假报出口骗取国家出口退税款4064566.77元。 你公司取得的已证实虚开发票、出口退税数据、报关单证资料比对结果等证据。</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>6058.46</v>
-      </c>
+          <t>增值税、企业所得税、消费税</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="n"/>
       <c r="S10" s="3" t="n"/>
       <c r="T10" s="3" t="n"/>
       <c r="U10" s="3" t="n"/>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《中华人民共和国城市维护建设税法》(中华人民共和国主席令第五十一号)第一条、第二条、第四条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×7%×50%=200.05元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)、《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×3%×50%=85.74元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳地方教育附加5715.51×2%×50%=57.16元。</t>
-        </is>
-      </c>
+      <c r="V10" s="2" t="inlineStr"/>
       <c r="W10" s="4" t="n"/>
       <c r="X10" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="Y10" s="4" t="n"/>
       <c r="Z10" s="4" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1855,7 +1825,9 @@
       <c r="AG10" s="2" t="inlineStr"/>
       <c r="AH10" s="2" t="inlineStr">
         <is>
-          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕13号)_国家税务总局北海市税务局</t>
+          <t>关于送达福州吉伦多德贸易有限公司《税务行政处罚决定书》的公告 _
+ 其他类 _
+ 国家税务总局福州市税务局</t>
         </is>
       </c>
       <c r="AI10" s="2" t="inlineStr">
@@ -1865,22 +1837,22 @@
       </c>
       <c r="AJ10" s="2" t="inlineStr">
         <is>
-          <t>字段“决定书文号”存在冲突:保留原值“北市税稽处〔2026〕6号”,新值“北市税稽处〔2026〕13号”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>CASE-6e854d911c44fb48</t>
+          <t>CASE-89fc66bfc8dad80d</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>DOC-4bf991cc37f1a595</t>
+          <t>DOC-6e5b966cd65a4366</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1890,30 +1862,30 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>南宁市</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr"/>
+          <t>北海市</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>银海区</t>
+        </is>
+      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第四稽查局</t>
+          <t>国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第四稽查局</t>
+          <t>国家税务总局北海市税务局稽查局</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>南宁敏顺睿商务服务有限公司</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>91450128MAA79KD08F</t>
-        </is>
-      </c>
+          <t>广西耿仁建材有限公司</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1922,36 +1894,46 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>南市税四稽处〔2025〕4号</t>
+          <t>北市税稽处〔2026〕14号</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>南市税四稽处〔2025〕4号</t>
+          <t>北市税稽处〔2026〕14号</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="3" t="n"/>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>我局于2026年2月11日至2026年7月15日对你公司(地址:北海市银海区新世纪大道15号辰宸花园3幢二单元0901号)2026年1月1日至2026年1月31日期间的涉税情况进行了检查,违法事实及处理决定如下: (2)短时间开具大量大额发票且未申报 你公司未进行纳税申报,不缴或者少缴2026年1月增值税194612.47元,2026年1月城市维护建设税13622.87元,合计208235.34元。 根据《中华人民共和国税收征收管理法》第六十三条第一款规定,对上述行为定性为偷税,向你公司追缴少缴的2026年增值税194612.47元,城市维护建设税13622.87元,合计208235.34元。 1.根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)的规定,对你公司少缴所属期2026年1月的教育费附加5838.37元,予以追缴。 2.根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条的规定,对你公司少缴所属期2026年1月地方教育附加3892.25元,予以追缴。 根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司少缴的税款从税款滞纳之日起至实际缴纳税款之日止按日加收滞纳税款万分之五的滞纳金,滞纳金由金三系统自动计算加收。 (四)你公司无法联系且实地核查无实际生产地址、无生产能力、查无下落,短期开票金额大,无法核实资金流,未进行纳税申报,根据《国家税务总局关于走逃(失联)企业开具增值税专用发票认定处理有关问题的公告》(国家税务总局公告2016年第76号),将你公司按走逃(失联)处理,根据《中华人民共和国发票管理办法》(国函〔1993〕174号)第二十一条第(一)项,你公司无生产能力,却为他人开具与实际经营业务情况不符的发票,属于虚开发票的行为。</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>208235.34</v>
+      </c>
       <c r="S11" s="3" t="n"/>
       <c r="T11" s="3" t="n"/>
       <c r="U11" s="3" t="n"/>
       <c r="V11" s="2" t="inlineStr"/>
       <c r="W11" s="4" t="n"/>
       <c r="X11" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="Y11" s="4" t="n"/>
       <c r="Z11" s="4" t="n">
-        <v>46238</v>
+        <v>46233</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1961,7 +1943,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE11" s="5" t="inlineStr">
@@ -1973,32 +1955,32 @@
       <c r="AG11" s="2" t="inlineStr"/>
       <c r="AH11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第四稽查局公告更正告知书(南宁敏顺睿商务服务有限公司)_国家税务总局南宁市税务局</t>
+          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕14号)_国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="AI11" s="2" t="inlineStr">
         <is>
-          <t>内容不匹配</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ11" s="2" t="inlineStr">
         <is>
-          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CASE-85fda8617056d119</t>
+          <t>CASE-eb9cfd5295d501e5</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>DOC-9057f0b6746c97de</t>
+          <t>DOC-4a8cf53b445afc63</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2008,68 +1990,86 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>南宁市</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
+          <t>北海市</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>海城区</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第四稽查局</t>
+          <t>国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第四稽查局</t>
+          <t>国家税务总局北海市税务局稽查局</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>南宁敏顺睿商务服务有限公司</t>
+          <t>广西轩易科技有限公司</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>91450128MAA79KD08F</t>
+          <t>91450500MAK3N9UJ2T</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>南市税四稽罚〔2026〕4号</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>南市税四稽罚〔2026〕4号</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="3" t="n"/>
+          <t>北市税稽处〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>北市税稽处〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>我局于2026年1月23日起对你公司(地址:北海市海城区北部湾东路“金宝小区”B幢B804号20北海汇算账商务秘书有限公司托管)2025年12月11日至2025年12月31日期间的涉税情况进行了检查,发现你公司存在税收违法行为,原《税务处理决定书》(北市税稽处〔2026〕6号)认定的违法事实有误,经重新调查核实,违法事实及处理决定如下: 经查询,你公司2026年1月20日通过网络方式零申报所属期2025年10月1日-2025年12月31日的增值税、城市维护建设税及附加,入库税款0元,申报金额与实际不符,存在虚假申报的情况。 你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 (一)根据《中华人民共和国发票管理办法》(财政部令第6号发布,经国务院令第587号、第709号、第764号修订)第二十一条第二款第(一)项的规定,认定你公司为他人开具与实际经营业务情况不符的前述13份增值税普通电子发票为虚开发票(金额合计571550.49元,税额合计5715.51元,价税合计577266.00元)。 根据《中华人民共和国税收征收管理法》第三十二条、第六十三条第一款、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,已构成偷税,向你公司追缴少缴的税款合计5915.56元,并从滞纳税款之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>6058.46</v>
+      </c>
       <c r="S12" s="3" t="n"/>
       <c r="T12" s="3" t="n"/>
       <c r="U12" s="3" t="n"/>
-      <c r="V12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《中华人民共和国城市维护建设税法》(中华人民共和国主席令第五十一号)第一条、第二条、第四条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×7%×50%=200.05元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)、《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×3%×50%=85.74元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳地方教育附加5715.51×2%×50%=57.16元。</t>
+        </is>
+      </c>
       <c r="W12" s="4" t="n"/>
       <c r="X12" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="Y12" s="4" t="n"/>
       <c r="Z12" s="4" t="n">
-        <v>46238</v>
+        <v>46234</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE12" s="5" t="inlineStr">
@@ -2091,67 +2091,63 @@
       <c r="AG12" s="2" t="inlineStr"/>
       <c r="AH12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第四稽查局公告更正告知书(南宁敏顺睿商务服务有限公司)_国家税务总局南宁市税务局</t>
+          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕13号)_国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="AI12" s="2" t="inlineStr">
         <is>
-          <t>内容不匹配</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ12" s="2" t="inlineStr">
         <is>
-          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>字段“决定书文号”存在冲突:保留原值“北市税稽处〔2026〕6号”,新值“北市税稽处〔2026〕13号”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CASE-97651030667b6c98</t>
+          <t>CASE-6e854d911c44fb48</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>DOC-f9817c8cadf0fc74</t>
+          <t>DOC-4bf991cc37f1a595</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>福州市</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>仓山区</t>
-        </is>
-      </c>
+          <t>南宁市</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局南宁市税务局第四稽查局</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局南宁市税务局第四稽查局</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>福州盛广弘贸易有限公司</t>
+          <t>南宁敏顺睿商务服务有限公司</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>91350104MA34D5PT77</t>
+          <t>91450128MAA79KD08F</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
@@ -2162,36 +2158,22 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽处〔2025〕233号</t>
+          <t>南市税四稽处〔2025〕4号</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽处〔2025〕233号</t>
+          <t>南市税四稽处〔2025〕4号</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>我局于2023年12月25日起对你公司(地址:福建省福州市仓山区信平路6号二层41室)2022年1月1日至2023年11月30日期间的涉税情况进行检查,违法事实及处理决定如下: (二)你公司于2022年至2023年取得新余伟宏服装有限公司已证实虚开的254份正常状态增值税专用发票(金额合计24261915.72元,税额合计3154049.38元,价税合计27415965.10元)用于出口退税,通过假报出口或者其他欺骗手段骗取国家出口退税款3154049.14元。 (三)你公司于2022年至2023年取得宜春润悟服饰有限公司已证实虚开的220份正常状态增值税专用发票(金额合计20853824.88元,税额合计2710997.42元,价税合计23564822.30元),上述发票你公司均用于申报出口退税,取得已退税额2710997.41元。 (一)根据《中华人民共和国税收征收管理法》第六十六条规定,认定你公司取得新余伟宏服装有限公司已证实虚开的增值税专用发票254份(金额合计24261915.72元,税额合计3154049.38元,价税合计27415965.10元,取得退税款3154049.14元)并用于出口退税的属于骗取国家出口退税。 追缴你公司骗取的出口退税款3154049.14元,具体明细如下(单位:元): (二)根据《财政部 国家税务总局关于出口货物劳务增值税和消费税政策的通知》(财税〔2012〕39号)第七条第(一)项第5目、第九条第(二)项第5目、《国家税务总局关于&lt;出口货物劳务增值税和消费税管理办法&gt;有关问题的公告》(国家税务总局公告2013年第12号)第五条第(九)项第1目规定,你公司取得宜春润悟服饰有限公司已证实虚开的220份增值税专用发票(金额合计20853824.88元,税额合计2710997.42元,价税合计23564822.30元),申报出口退税并取得退税款2710997.41元,适用增值税征税政策,追缴已退税款2710997.41元,具体明细如下(单位:元):</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="n">
-        <v>2710997.41</v>
-      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="3" t="n"/>
       <c r="S13" s="3" t="n"/>
       <c r="T13" s="3" t="n"/>
       <c r="U13" s="3" t="n"/>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《征收教育费附加的暂行规定》第二条、第三条、《福建省人民政府关于调整地方教育附加征收标准有关问题的通知》(闽政文〔2011〕230号)第一条、第二条、《财政部 税务总局关于进一步实施小微企业“六税两费”减免政策的公告》(财政部 税务总局公告2022年第10号)第一条规定,你公司应补缴相应属期城市维护建设税合计83631.38元、教育费附加合计35842.03元、地方教育附加合计23894.68元,具体明细如下(单位:元):</t>
-        </is>
-      </c>
+      <c r="V13" s="2" t="inlineStr"/>
       <c r="W13" s="4" t="n"/>
       <c r="X13" s="4" t="n">
         <v>46231</v>
@@ -2201,11 +2183,11 @@
         <v>46238</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2215,7 +2197,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE13" s="5" t="inlineStr">
@@ -2227,90 +2209,84 @@
       <c r="AG13" s="2" t="inlineStr"/>
       <c r="AH13" s="2" t="inlineStr">
         <is>
-          <t>关于送达福州盛广弘贸易有限公司《税务处理决定书》的公告 _
- 其他类 _
- 国家税务总局福州市税务局</t>
+          <t>国家税务总局南宁市税务局第四稽查局公告更正告知书(南宁敏顺睿商务服务有限公司)_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI13" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>内容不匹配</t>
         </is>
       </c>
       <c r="AJ13" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASE-3e050a699b29b0d0</t>
+          <t>CASE-85fda8617056d119</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DOC-96a3089a0e2b37cd</t>
+          <t>DOC-9057f0b6746c97de</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>河南省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>平顶山市</t>
+          <t>南宁市</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局平顶山市税务局第一稽查局</t>
+          <t>国家税务总局南宁市税务局第四稽查局</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局平顶山市税务局第一稽查局</t>
+          <t>国家税务总局南宁市税务局第四稽查局</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>汝州泰隆实业有限公司</t>
+          <t>南宁敏顺睿商务服务有限公司</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>91410482MA40K4KA3B</t>
+          <t>91450128MAA79KD08F</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>平税稽一局处〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>平税稽一局处〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr"/>
+          <t>南市税四稽罚〔2026〕4号</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>南市税四稽罚〔2026〕4号</t>
+        </is>
+      </c>
       <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>增值税、个人所得税</t>
-        </is>
-      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
       <c r="R14" s="3" t="n"/>
       <c r="S14" s="3" t="n"/>
       <c r="T14" s="3" t="n"/>
@@ -2318,14 +2294,14 @@
       <c r="V14" s="2" t="inlineStr"/>
       <c r="W14" s="4" t="n"/>
       <c r="X14" s="4" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="Y14" s="4" t="n"/>
       <c r="Z14" s="4" t="n">
-        <v>46229</v>
+        <v>46238</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -2339,7 +2315,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE14" s="5" t="inlineStr">
@@ -2351,63 +2327,67 @@
       <c r="AG14" s="2" t="inlineStr"/>
       <c r="AH14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局平顶山市税务局第一稽查局关于送达汝州泰隆实业有限公司《税务处理决定书》的公告 - 国家税务总局平顶山市税务局</t>
+          <t>国家税务总局南宁市税务局第四稽查局公告更正告知书(南宁敏顺睿商务服务有限公司)_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI14" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>内容不匹配</t>
         </is>
       </c>
       <c r="AJ14" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CASE-1a685b98e7b293c8</t>
+          <t>CASE-97651030667b6c98</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>DOC-9b5fab8065382bd9</t>
+          <t>DOC-f9817c8cadf0fc74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>辽宁省</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>铁岭市</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr"/>
+          <t>福州市</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>仓山区</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局铁岭市税务局第一稽查局</t>
+          <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局铁岭市税务局第一稽查局</t>
+          <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>辽宁恒慧专用车箱有限公司</t>
+          <t>福州盛广弘贸易有限公司</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>91211200683741982W</t>
+          <t>91350104MA34D5PT77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
@@ -2418,52 +2398,46 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>铁税一稽处〔2026〕35号</t>
+          <t>榕税一稽处〔2025〕233号</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>铁税一稽处〔2026〕35号</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>铁税一稽罚〔2026〕17号</t>
-        </is>
-      </c>
+          <t>榕税一稽处〔2025〕233号</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>查属期内违法行为均定性偷税, 需要对原处罚决定中的罚款数额 以变更,你(单位)存在违法事实及处罚决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 〔2022〕59号) 第一条、 第三条之规定, 你单位存在少缴属期2010 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。 月属期申报数据,用于证明你单位未申报缴纳印花税。 报,不缴或者少缴应纳税款的,是偷税。 务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴 内首次因偷税被税务机关处罚,并能够配合税务机关检查的,处 不缴或者少缴的税款百分之五十的罚款”之规定,对你单位城镇 土地使用税和印花税处不缴或者少缴的税款50%的罚款。 你单位印花税偷税违法行为发生于2009年11月26日,至立案 位检查属期内违法行为均定性偷税, 需要对原处理决定中的查补 情况进行了检查,违法事实及处理决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 定, 你单位存在少缴属期2010年1月至2022年6月城镇土地使 用税5,710,765.50元的违法事实。 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 该地块未缴纳契税,你单位存在少缴契税509,984.64元的违法 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。</t>
+          <t>我局于2023年12月25日起对你公司(地址:福建省福州市仓山区信平路6号二层41室)2022年1月1日至2023年11月30日期间的涉税情况进行检查,违法事实及处理决定如下: (二)你公司于2022年至2023年取得新余伟宏服装有限公司已证实虚开的254份正常状态增值税专用发票(金额合计24261915.72元,税额合计3154049.38元,价税合计27415965.10元)用于出口退税,通过假报出口或者其他欺骗手段骗取国家出口退税款3154049.14元。 (三)你公司于2022年至2023年取得宜春润悟服饰有限公司已证实虚开的220份正常状态增值税专用发票(金额合计20853824.88元,税额合计2710997.42元,价税合计23564822.30元),上述发票你公司均用于申报出口退税,取得已退税额2710997.41元。 (一)根据《中华人民共和国税收征收管理法》第六十六条规定,认定你公司取得新余伟宏服装有限公司已证实虚开的增值税专用发票254份(金额合计24261915.72元,税额合计3154049.38元,价税合计27415965.10元,取得退税款3154049.14元)并用于出口退税的属于骗取国家出口退税。 追缴你公司骗取的出口退税款3154049.14元,具体明细如下(单位:元): (二)根据《财政部 国家税务总局关于出口货物劳务增值税和消费税政策的通知》(财税〔2012〕39号)第七条第(一)项第5目、第九条第(二)项第5目、《国家税务总局关于&lt;出口货物劳务增值税和消费税管理办法&gt;有关问题的公告》(国家税务总局公告2013年第12号)第五条第(九)项第1目规定,你公司取得宜春润悟服饰有限公司已证实虚开的220份增值税专用发票(金额合计20853824.88元,税额合计2710997.42元,价税合计23564822.30元),申报出口退税并取得退税款2710997.41元,适用增值税征税政策,追缴已退税款2710997.41元,具体明细如下(单位:元):</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>增值税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、契税、教育费附加、地方教育附加</t>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R15" s="3" t="n">
-        <v>44269.5</v>
+        <v>2710997.41</v>
       </c>
       <c r="S15" s="3" t="n"/>
       <c r="T15" s="3" t="n"/>
       <c r="U15" s="3" t="n"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>定,每日按罚款数额的百分之三加处罚款。 日”之规定,你单位每月应补缴城镇土地使用税44,269.50元 征收城镇土地使用税, 自2010年1月至2022年6月应补缴城镇 所载金额的万分之五,你单位应补缴2009年11月26日印花税 日”之规定,你单位每月应补缴城镇土地使用税44,269.50元 征收城镇土地使用税, 自2010年1月至2022年6月应补缴城镇 所载金额的万分之五,你单位应补缴2009年11月26日印花税</t>
-        </is>
-      </c>
-      <c r="W15" s="4" t="n">
-        <v>46183</v>
-      </c>
+          <t>根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《征收教育费附加的暂行规定》第二条、第三条、《福建省人民政府关于调整地方教育附加征收标准有关问题的通知》(闽政文〔2011〕230号)第一条、第二条、《财政部 税务总局关于进一步实施小微企业“六税两费”减免政策的公告》(财政部 税务总局公告2022年第10号)第一条规定,你公司应补缴相应属期城市维护建设税合计83631.38元、教育费附加合计35842.03元、地方教育附加合计23894.68元,具体明细如下(单位:元):</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="n"/>
       <c r="X15" s="4" t="n">
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="Y15" s="4" t="n"/>
       <c r="Z15" s="4" t="n">
-        <v>46240</v>
+        <v>46238</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -2485,131 +2459,113 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF15" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF15" s="2" t="inlineStr"/>
       <c r="AG15" s="2" t="inlineStr"/>
       <c r="AH15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局辽宁省税务局 通知公告 国家税务总局铁岭市税务局税务文书送达公告</t>
+          <t>关于送达福州盛广弘贸易有限公司《税务处理决定书》的公告 _
+ 其他类 _
+ 国家税务总局福州市税务局</t>
         </is>
       </c>
       <c r="AI15" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ15" s="2" t="inlineStr">
         <is>
-          <t>字段“决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处理决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处罚决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CASE-1a685b98e7b293c8</t>
+          <t>CASE-3e050a699b29b0d0</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>DOC-8fc89a4906937181</t>
+          <t>DOC-96a3089a0e2b37cd</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>辽宁省</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>铁岭市</t>
+          <t>平顶山市</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局铁岭市税务局第一稽查局</t>
+          <t>国家税务总局平顶山市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局铁岭市税务局第一稽查局</t>
+          <t>国家税务总局平顶山市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>辽宁恒慧专用车箱有限公司</t>
+          <t>汝州泰隆实业有限公司</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>91211200683741982W</t>
+          <t>91410482MA40K4KA3B</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>铁税一稽罚〔2026〕17号</t>
+          <t>平税稽一局处〔2026〕1号</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>铁税一稽处〔2026〕35号</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>铁税一稽罚〔2026〕17号</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>查属期内违法行为均定性偷税, 需要对原处罚决定中的罚款数额 以变更,你(单位)存在违法事实及处罚决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 〔2022〕59号) 第一条、 第三条之规定, 你单位存在少缴属期2010 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。 月属期申报数据,用于证明你单位未申报缴纳印花税。 报,不缴或者少缴应纳税款的,是偷税。 务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴 内首次因偷税被税务机关处罚,并能够配合税务机关检查的,处 不缴或者少缴的税款百分之五十的罚款”之规定,对你单位城镇 土地使用税和印花税处不缴或者少缴的税款50%的罚款。 你单位印花税偷税违法行为发生于2009年11月26日,至立案 位检查属期内违法行为均定性偷税, 需要对原处理决定中的查补 情况进行了检查,违法事实及处理决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 定, 你单位存在少缴属期2010年1月至2022年6月城镇土地使 用税5,710,765.50元的违法事实。 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 该地块未缴纳契税,你单位存在少缴契税509,984.64元的违法 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。</t>
-        </is>
-      </c>
+          <t>平税稽一局处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>增值税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、契税、教育费附加、地方教育附加</t>
+          <t>增值税、个人所得税</t>
         </is>
       </c>
       <c r="R16" s="3" t="n"/>
       <c r="S16" s="3" t="n"/>
-      <c r="T16" s="3" t="n">
-        <v>2855382.83</v>
-      </c>
+      <c r="T16" s="3" t="n"/>
       <c r="U16" s="3" t="n"/>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>定,每日按罚款数额的百分之三加处罚款。 日”之规定,你单位每月应补缴城镇土地使用税44,269.50元 征收城镇土地使用税, 自2010年1月至2022年6月应补缴城镇 所载金额的万分之五,你单位应补缴2009年11月26日印花税 定,每日按罚款数额的百分之三加处罚款。</t>
-        </is>
-      </c>
-      <c r="W16" s="4" t="n">
-        <v>46183</v>
-      </c>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="4" t="n"/>
       <c r="X16" s="4" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="Y16" s="4" t="n"/>
       <c r="Z16" s="4" t="n">
-        <v>46240</v>
+        <v>46229</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2627,71 +2583,67 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF16" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF16" s="2" t="inlineStr"/>
       <c r="AG16" s="2" t="inlineStr"/>
       <c r="AH16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局辽宁省税务局 通知公告 国家税务总局铁岭市税务局税务文书送达公告</t>
+          <t>国家税务总局平顶山市税务局第一稽查局关于送达汝州泰隆实业有限公司《税务处理决定书》的公告 - 国家税务总局平顶山市税务局</t>
         </is>
       </c>
       <c r="AI16" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ16" s="2" t="inlineStr">
         <is>
-          <t>字段“决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。 字段“关联处理决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处罚决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CASE-365e8a924cf64611</t>
+          <t>CASE-1a685b98e7b293c8</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>DOC-4d14eba16f9aa8a0</t>
+          <t>DOC-9b5fab8065382bd9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>辽宁省</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>铁岭市</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局铁岭市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局铁岭市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>贵州博泰工贸有限公司</t>
+          <t>辽宁恒慧专用车箱有限公司</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>91520115587255589F</t>
+          <t>91211200683741982W</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
@@ -2702,36 +2654,56 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕38号</t>
+          <t>铁税一稽处〔2026〕35号</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕38号</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="3" t="n"/>
+          <t>铁税一稽处〔2026〕35号</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>铁税一稽罚〔2026〕17号</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>查属期内违法行为均定性偷税, 需要对原处罚决定中的罚款数额 以变更,你(单位)存在违法事实及处罚决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 〔2022〕59号) 第一条、 第三条之规定, 你单位存在少缴属期2010 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。 月属期申报数据,用于证明你单位未申报缴纳印花税。 报,不缴或者少缴应纳税款的,是偷税。 务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴 内首次因偷税被税务机关处罚,并能够配合税务机关检查的,处 不缴或者少缴的税款百分之五十的罚款”之规定,对你单位城镇 土地使用税和印花税处不缴或者少缴的税款50%的罚款。 你单位印花税偷税违法行为发生于2009年11月26日,至立案 位检查属期内违法行为均定性偷税, 需要对原处理决定中的查补 情况进行了检查,违法事实及处理决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 定, 你单位存在少缴属期2010年1月至2022年6月城镇土地使 用税5,710,765.50元的违法事实。 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 该地块未缴纳契税,你单位存在少缴契税509,984.64元的违法 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>增值税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、契税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44269.5</v>
+      </c>
       <c r="S17" s="3" t="n"/>
       <c r="T17" s="3" t="n"/>
       <c r="U17" s="3" t="n"/>
-      <c r="V17" s="2" t="inlineStr"/>
-      <c r="W17" s="4" t="n"/>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>定,每日按罚款数额的百分之三加处罚款。 日”之规定,你单位每月应补缴城镇土地使用税44,269.50元 征收城镇土地使用税, 自2010年1月至2022年6月应补缴城镇 所载金额的万分之五,你单位应补缴2009年11月26日印花税 日”之规定,你单位每月应补缴城镇土地使用税44,269.50元 征收城镇土地使用税, 自2010年1月至2022年6月应补缴城镇 所载金额的万分之五,你单位应补缴2009年11月26日印花税</t>
+        </is>
+      </c>
+      <c r="W17" s="4" t="n">
+        <v>46183</v>
+      </c>
       <c r="X17" s="4" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="Y17" s="4" t="n"/>
       <c r="Z17" s="4" t="n">
-        <v>46229</v>
+        <v>46240</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2749,117 +2721,127 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AF17" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG17" s="2" t="inlineStr"/>
       <c r="AH17" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书、税务行政处罚决定书的公告</t>
+          <t>国家税务总局辽宁省税务局 通知公告 国家税务总局铁岭市税务局税务文书送达公告</t>
         </is>
       </c>
       <c r="AI17" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ17" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>字段“决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处理决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处罚决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CASE-7b9a26f2ac401107</t>
+          <t>CASE-1a685b98e7b293c8</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>DOC-f6c6ea472b2ca04a</t>
+          <t>DOC-8fc89a4906937181</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>辽宁省</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>三明市</t>
+          <t>铁岭市</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局三明市税务局第一稽查局</t>
+          <t>国家税务总局铁岭市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局三明市税务局第一稽查局</t>
+          <t>国家税务总局铁岭市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>三明众祥房地产开发有限公司</t>
+          <t>辽宁恒慧专用车箱有限公司</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>91350400678473231W</t>
+          <t>91211200683741982W</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>明税一稽处〔2026〕20号</t>
+          <t>铁税一稽罚〔2026〕17号</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>明税一稽处〔2026〕20号</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr"/>
+          <t>铁税一稽处〔2026〕35号</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>铁税一稽罚〔2026〕17号</t>
+        </is>
+      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2016年期间,在没有真实业务情况下,取得重庆市博海建设工程(集团)有限公司、福建九九建设有限公司三明分公司开具的不符合规定的发票,发票金额400252379元,在企业所得税税前扣除,造成少缴纳企业所得税100063094.75元,该行为违反《中华人民共和国税收征收管理法》(2015年4月24日主席令第二十三号修改)第六十三条第一款 纳税人伪造、变造、隐匿、擅自销毁账簿、记账凭证,或者在账簿上多列支出或者不列、少列收入,或者经税务机关通知申报而拒不申报或者进行虚假的纳税申报,不缴或者少缴应纳税款的,是偷税。 对纳税人偷税的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款; 之规定,对你公司在账上多列支出,造成少缴企业所得税100063094.75元的行为认定为偷税。 之规定,对你公司少缴的企业所得税从滞纳之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
+          <t>查属期内违法行为均定性偷税, 需要对原处罚决定中的罚款数额 以变更,你(单位)存在违法事实及处罚决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 〔2022〕59号) 第一条、 第三条之规定, 你单位存在少缴属期2010 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。 月属期申报数据,用于证明你单位未申报缴纳印花税。 报,不缴或者少缴应纳税款的,是偷税。 务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴 内首次因偷税被税务机关处罚,并能够配合税务机关检查的,处 不缴或者少缴的税款百分之五十的罚款”之规定,对你单位城镇 土地使用税和印花税处不缴或者少缴的税款50%的罚款。 你单位印花税偷税违法行为发生于2009年11月26日,至立案 位检查属期内违法行为均定性偷税, 需要对原处理决定中的查补 情况进行了检查,违法事实及处理决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 定, 你单位存在少缴属期2010年1月至2022年6月城镇土地使 用税5,710,765.50元的违法事实。 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 该地块未缴纳契税,你单位存在少缴契税509,984.64元的违法 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>企业所得税</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>100063094.75</v>
-      </c>
+          <t>增值税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、契税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="n"/>
       <c r="S18" s="3" t="n"/>
-      <c r="T18" s="3" t="n"/>
+      <c r="T18" s="3" t="n">
+        <v>2855382.83</v>
+      </c>
       <c r="U18" s="3" t="n"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>据《中华人民共和国税收征收管理法实施细则》第106条规定,将该文书予以公告送达,自公告之日起满30日视为送达。</t>
-        </is>
-      </c>
-      <c r="W18" s="4" t="n"/>
+          <t>定,每日按罚款数额的百分之三加处罚款。 日”之规定,你单位每月应补缴城镇土地使用税44,269.50元 征收城镇土地使用税, 自2010年1月至2022年6月应补缴城镇 所载金额的万分之五,你单位应补缴2009年11月26日印花税 定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W18" s="4" t="n">
+        <v>46183</v>
+      </c>
       <c r="X18" s="4" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="Y18" s="4" t="n"/>
       <c r="Z18" s="4" t="n">
-        <v>46229</v>
+        <v>46240</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -2881,404 +2863,406 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AF18" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG18" s="2" t="inlineStr"/>
       <c r="AH18" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局辽宁省税务局 通知公告 国家税务总局铁岭市税务局税务文书送达公告</t>
+        </is>
+      </c>
+      <c r="AI18" s="2" t="inlineStr">
+        <is>
+          <t>附件正常</t>
+        </is>
+      </c>
+      <c r="AJ18" s="2" t="inlineStr">
+        <is>
+          <t>字段“决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。 字段“关联处理决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处罚决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>CASE-365e8a924cf64611</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>DOC-4d14eba16f9aa8a0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>贵州省</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>贵阳市</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>贵州博泰工贸有限公司</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>91520115587255589F</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>筑税三稽处〔2026〕38号</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>筑税三稽处〔2026〕38号</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="3" t="n"/>
+      <c r="S19" s="3" t="n"/>
+      <c r="T19" s="3" t="n"/>
+      <c r="U19" s="3" t="n"/>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="4" t="n"/>
+      <c r="X19" s="4" t="n">
+        <v>46224</v>
+      </c>
+      <c r="Y19" s="4" t="n"/>
+      <c r="Z19" s="4" t="n">
+        <v>46229</v>
+      </c>
+      <c r="AA19" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>仅公告送达/仅文号线索</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD19" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AE19" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书、税务行政处罚决定书的公告</t>
+        </is>
+      </c>
+      <c r="AI19" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ19" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7b9a26f2ac401107</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>DOC-f6c6ea472b2ca04a</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>福建省</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>三明市</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局三明市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局三明市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>三明众祥房地产开发有限公司</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>91350400678473231W</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>明税一稽处〔2026〕20号</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>明税一稽处〔2026〕20号</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>情况进行了检查,违法事实及处理决定如下: 2016年期间,在没有真实业务情况下,取得重庆市博海建设工程(集团)有限公司、福建九九建设有限公司三明分公司开具的不符合规定的发票,发票金额400252379元,在企业所得税税前扣除,造成少缴纳企业所得税100063094.75元,该行为违反《中华人民共和国税收征收管理法》(2015年4月24日主席令第二十三号修改)第六十三条第一款 纳税人伪造、变造、隐匿、擅自销毁账簿、记账凭证,或者在账簿上多列支出或者不列、少列收入,或者经税务机关通知申报而拒不申报或者进行虚假的纳税申报,不缴或者少缴应纳税款的,是偷税。 对纳税人偷税的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款; 之规定,对你公司在账上多列支出,造成少缴企业所得税100063094.75元的行为认定为偷税。 之规定,对你公司少缴的企业所得税从滞纳之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>企业所得税</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>100063094.75</v>
+      </c>
+      <c r="S20" s="3" t="n"/>
+      <c r="T20" s="3" t="n"/>
+      <c r="U20" s="3" t="n"/>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>据《中华人民共和国税收征收管理法实施细则》第106条规定,将该文书予以公告送达,自公告之日起满30日视为送达。</t>
+        </is>
+      </c>
+      <c r="W20" s="4" t="n"/>
+      <c r="X20" s="4" t="n">
+        <v>46223</v>
+      </c>
+      <c r="Y20" s="4" t="n"/>
+      <c r="Z20" s="4" t="n">
+        <v>46229</v>
+      </c>
+      <c r="AA20" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD20" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AE20" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF20" s="2" t="inlineStr"/>
+      <c r="AG20" s="2" t="inlineStr"/>
+      <c r="AH20" s="2" t="inlineStr">
         <is>
           <t>关于送达三明众祥房地产开发有限公司 《税务处理决定书》的公告 _
  其他公告 _
  国家税务总局三明市税务局</t>
         </is>
       </c>
-      <c r="AI18" s="2" t="inlineStr">
+      <c r="AI20" s="2" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ18" s="2" t="inlineStr">
+      <c r="AJ20" s="2" t="inlineStr">
         <is>
           <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
+    <row r="21">
+      <c r="A21" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>CASE-31e4a827dfd253f2</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>DOC-3ec54358fce2350d</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>福建省</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>福州市</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>福州顺路汽车运输有限公司</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>91350102MA31MF6611</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>税务处理决定书</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>榕税一稽处〔2026〕137号</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>榕税一稽处〔2026〕137号</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>我局于2025年7月10日起对你公司(地址:福建省闽侯县青口镇祥宏南路922号)2023年1月1日至2024年12月31日期间的发票涉税情况进行检查,违法事实及处理决定如下: (二)你公司取得毕节七星关区辰楚汽车服务部(个人独资)、毕节七星关锦悦汽车服务部(个人独资)、贵州杨亭汽车销售有限公司、贵州楠鑫汽车销售有限公司已证实虚开的35份机动车发票。 (二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 (三)根据《中华人民共和国企业所得税法》第五条、第八条、《企业所得税税前扣除凭证管理办法》(国家税务总局公告2018年第28号发布)第四条、第十二条的规定,你公司取得上述虚开的发票不得作为税前扣除凭证。</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R21" s="3" t="n">
         <v>3778.22</v>
       </c>
-      <c r="S19" s="3" t="n"/>
-      <c r="T19" s="3" t="n"/>
-      <c r="U19" s="3" t="n"/>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="S21" s="3" t="n"/>
+      <c r="T21" s="3" t="n"/>
+      <c r="U21" s="3" t="n"/>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>(二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期城市维护建设税124.75元。 根据《征收教育费附加的暂行规定》第二条、第三条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期教育费附加53.47元。 根据《福建省人民政府关于调整地方教育附加征收标准等有关问题的通知》(闽政文〔2011〕230号)第一条、第二条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期地方教育附加35.64元。</t>
         </is>
       </c>
-      <c r="W19" s="4" t="n"/>
-      <c r="X19" s="4" t="n">
+      <c r="W21" s="4" t="n"/>
+      <c r="X21" s="4" t="n">
         <v>46218</v>
       </c>
-      <c r="Y19" s="4" t="n"/>
-      <c r="Z19" s="4" t="n">
+      <c r="Y21" s="4" t="n"/>
+      <c r="Z21" s="4" t="n">
         <v>46229</v>
       </c>
-      <c r="AA19" s="4" t="n">
-        <v>46240</v>
-      </c>
-      <c r="AB19" s="2" t="inlineStr">
+      <c r="AA21" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>完整文书</t>
         </is>
       </c>
-      <c r="AC19" s="2" t="inlineStr">
+      <c r="AC21" s="2" t="inlineStr">
         <is>
           <t>税务机关官网</t>
         </is>
       </c>
-      <c r="AD19" s="2" t="inlineStr">
+      <c r="AD21" s="2" t="inlineStr">
         <is>
           <t>已核验</t>
         </is>
       </c>
-      <c r="AE19" s="5" t="inlineStr">
+      <c r="AE21" s="5" t="inlineStr">
         <is>
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF19" s="2" t="inlineStr"/>
-      <c r="AG19" s="2" t="inlineStr"/>
-      <c r="AH19" s="2" t="inlineStr">
+      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AG21" s="2" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr">
         <is>
           <t>关于送达福州顺路汽车运输有限公司《税务处理决定书》的公告 _
  其他类 _
  国家税务总局福州市税务局</t>
         </is>
       </c>
-      <c r="AI19" s="2" t="inlineStr">
+      <c r="AI21" s="2" t="inlineStr">
         <is>
           <t>正常</t>
-        </is>
-      </c>
-      <c r="AJ19" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>CASE-089a3b9692e76ac4</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>DOC-d21cdc5988b1e304</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>江苏省</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>淮安市</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局江苏省税务局</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局淮安市税务局稽查局</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>淮安市百亦金商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>91320804MA1WEH7Y3U</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>税务处理决定书</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽处〔2026〕26号</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽处〔2026〕26号</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽罚〔2026〕6号</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="3" t="n"/>
-      <c r="S20" s="3" t="n"/>
-      <c r="T20" s="3" t="n"/>
-      <c r="U20" s="3" t="n"/>
-      <c r="V20" s="2" t="inlineStr"/>
-      <c r="W20" s="4" t="n"/>
-      <c r="X20" s="4" t="n">
-        <v>46216</v>
-      </c>
-      <c r="Y20" s="4" t="n"/>
-      <c r="Z20" s="4" t="n">
-        <v>46229</v>
-      </c>
-      <c r="AA20" s="4" t="n">
-        <v>46240</v>
-      </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>仅公告送达/仅文号线索</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD20" s="2" t="inlineStr">
-        <is>
-          <t>已核验</t>
-        </is>
-      </c>
-      <c r="AE20" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF20" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
-      <c r="AG20" s="2" t="inlineStr"/>
-      <c r="AH20" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
-        </is>
-      </c>
-      <c r="AI20" s="2" t="inlineStr">
-        <is>
-          <t>附件正常</t>
-        </is>
-      </c>
-      <c r="AJ20" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>CASE-089a3b9692e76ac4</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>DOC-9f8e8958d8ff89b6</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>江苏省</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>淮安市</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局江苏省税务局</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局淮安市税务局稽查局</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>淮安市百亦金商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>91320804MA1WEH7Y3U</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>税务行政处罚决定书</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽罚〔2026〕6号</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽处〔2026〕26号</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽罚〔2026〕6号</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="3" t="n"/>
-      <c r="S21" s="3" t="n"/>
-      <c r="T21" s="3" t="n"/>
-      <c r="U21" s="3" t="n"/>
-      <c r="V21" s="2" t="inlineStr"/>
-      <c r="W21" s="4" t="n"/>
-      <c r="X21" s="4" t="n">
-        <v>46216</v>
-      </c>
-      <c r="Y21" s="4" t="n"/>
-      <c r="Z21" s="4" t="n">
-        <v>46229</v>
-      </c>
-      <c r="AA21" s="4" t="n">
-        <v>46240</v>
-      </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>仅公告送达/仅文号线索</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD21" s="2" t="inlineStr">
-        <is>
-          <t>已核验</t>
-        </is>
-      </c>
-      <c r="AE21" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF21" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
-      <c r="AG21" s="2" t="inlineStr"/>
-      <c r="AH21" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
-        </is>
-      </c>
-      <c r="AI21" s="2" t="inlineStr">
-        <is>
-          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ21" s="2" t="inlineStr">
@@ -3289,47 +3273,47 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CASE-3f564fd9992b1ae3</t>
+          <t>CASE-089a3b9692e76ac4</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>DOC-c34e1d13286aafe2</t>
+          <t>DOC-d21cdc5988b1e304</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>泉州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局第二稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局第二稽查局</t>
+          <t>国家税务总局淮安市税务局稽查局</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>泉州隆鸿服装制造有限公司</t>
+          <t>淮安市百亦金商贸有限公司</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>91350525MA8U3U963L</t>
+          <t>91320804MA1WEH7Y3U</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
@@ -3340,48 +3324,40 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>泉税二稽处〔2026〕107号</t>
+          <t>淮税稽处〔2026〕26号</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>泉税二稽处〔2026〕107号</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr"/>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>日对你公司税收违法事实依法作出《税务处理决定书》(泉税二稽处〔 涉税情况进行了检查,查明违法事实及处理决定如下: 年你公司在无真实货物交易的情况下,取得河南中弘纺织有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 年期间,你公司在无真实货物交易的情况下,取得开封兴旺纺织品有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 上述违法事实有检查人员实地检查资料、电话拨打记录、邮寄退回函件、《已证实虚开通知单》等相关受托协查资料、主管税务机关出具的《已抵扣证明》、《情况说明》和你公司的申报纳税资料、银行账户流水等 号第三次修订)第二十一条第二款第二项之规定,认定你公司让他人为自己虚开 号第二次修订)第九条和《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告〔 号)之规定,对你公司取得上述已证实虚开的 之规定,决定向你公司追缴少缴的城市维护建设税-增值税附征 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 规定,决定向你公司追缴少缴的教育费附加-增值税附征 规定,决定向你公司追缴少缴的地方教育附加-增值税附征</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
+          <t>淮税稽处〔2026〕26号</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>淮税稽罚〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr"/>
       <c r="R22" s="3" t="n"/>
       <c r="S22" s="3" t="n"/>
       <c r="T22" s="3" t="n"/>
       <c r="U22" s="3" t="n"/>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>由于你公司走逃失联、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 (五)根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司上述应补缴税款按税款所属时间从税款滞纳之日起按日加收万分之五滞纳金</t>
-        </is>
-      </c>
+      <c r="V22" s="2" t="inlineStr"/>
       <c r="W22" s="4" t="n"/>
       <c r="X22" s="4" t="n">
-        <v>46202</v>
+        <v>46216</v>
       </c>
       <c r="Y22" s="4" t="n"/>
       <c r="Z22" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3399,18 +3375,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AF22" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG22" s="2" t="inlineStr"/>
       <c r="AH22" s="2" t="inlineStr">
         <is>
-          <t>关于对泉州隆鸿服装制造有限公司《税务处理决定书》送达的公告 _
- 其他公告 _
- 国家税务总局泉州市税务局</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
         </is>
       </c>
       <c r="AI22" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ22" s="2" t="inlineStr">
@@ -3421,16 +3399,16 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CASE-717dfe3250926214</t>
+          <t>CASE-089a3b9692e76ac4</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>DOC-7df9c075e55777a1</t>
+          <t>DOC-9f8e8958d8ff89b6</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3440,28 +3418,28 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>泰州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泰州市税务局第一稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泰州市税务局第一稽查局</t>
+          <t>国家税务总局淮安市税务局稽查局</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>靖江市长凌金属材料有限公司</t>
+          <t>淮安市百亦金商贸有限公司</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>91321282742461893K</t>
+          <t>91320804MA1WEH7Y3U</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
@@ -3472,13 +3450,17 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>泰税一稽罚〔2025〕54号</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr"/>
+          <t>淮税稽罚〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>淮税稽处〔2026〕26号</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>泰税一稽罚〔2025〕54号</t>
+          <t>淮税稽罚〔2026〕6号</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr"/>
@@ -3487,21 +3469,17 @@
       <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="n"/>
       <c r="U23" s="3" t="n"/>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>接上级通知,经我局研究决定,撤销上述《税务行政处罚决定书》。</t>
-        </is>
-      </c>
+      <c r="V23" s="2" t="inlineStr"/>
       <c r="W23" s="4" t="n"/>
       <c r="X23" s="4" t="n">
-        <v>46191</v>
+        <v>46216</v>
       </c>
       <c r="Y23" s="4" t="n"/>
       <c r="Z23" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
@@ -3523,67 +3501,71 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF23" s="2" t="inlineStr"/>
+      <c r="AF23" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG23" s="2" t="inlineStr"/>
       <c r="AH23" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 关于撤销《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
         </is>
       </c>
       <c r="AI23" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ23" s="2" t="inlineStr">
         <is>
-          <t>官方页面显示该决定书已被撤销。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CASE-a62e569c195adc3c</t>
+          <t>CASE-3f564fd9992b1ae3</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>DOC-b1dda915d4e6117d</t>
+          <t>DOC-c34e1d13286aafe2</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>遵义市</t>
+          <t>泉州市</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局泉州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局泉州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>贵州服格定商贸有限公司</t>
+          <t>泉州隆鸿服装制造有限公司</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>91520302MABUEHN034</t>
+          <t>91350525MA8U3U963L</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
@@ -3594,40 +3576,44 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>遵税一稽处〔2026〕30号</t>
+          <t>泉税二稽处〔2026〕107号</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>遵税一稽处〔2026〕30号</t>
+          <t>泉税二稽处〔2026〕107号</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
+          <t>日对你公司税收违法事实依法作出《税务处理决定书》(泉税二稽处〔 涉税情况进行了检查,查明违法事实及处理决定如下: 年你公司在无真实货物交易的情况下,取得河南中弘纺织有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 年期间,你公司在无真实货物交易的情况下,取得开封兴旺纺织品有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 上述违法事实有检查人员实地检查资料、电话拨打记录、邮寄退回函件、《已证实虚开通知单》等相关受托协查资料、主管税务机关出具的《已抵扣证明》、《情况说明》和你公司的申报纳税资料、银行账户流水等 号第三次修订)第二十一条第二款第二项之规定,认定你公司让他人为自己虚开 号第二次修订)第九条和《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告〔 号)之规定,对你公司取得上述已证实虚开的 之规定,决定向你公司追缴少缴的城市维护建设税-增值税附征 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 规定,决定向你公司追缴少缴的教育费附加-增值税附征 规定,决定向你公司追缴少缴的地方教育附加-增值税附征</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
+          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R24" s="3" t="n"/>
       <c r="S24" s="3" t="n"/>
       <c r="T24" s="3" t="n"/>
       <c r="U24" s="3" t="n"/>
-      <c r="V24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>由于你公司走逃失联、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 (五)根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司上述应补缴税款按税款所属时间从税款滞纳之日起按日加收万分之五滞纳金</t>
+        </is>
+      </c>
       <c r="W24" s="4" t="n"/>
       <c r="X24" s="4" t="n">
-        <v>46185</v>
+        <v>46202</v>
       </c>
       <c r="Y24" s="4" t="n"/>
       <c r="Z24" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
@@ -3653,7 +3639,9 @@
       <c r="AG24" s="2" t="inlineStr"/>
       <c r="AH24" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
+          <t>关于对泉州隆鸿服装制造有限公司《税务处理决定书》送达的公告 _
+ 其他公告 _
+ 国家税务总局泉州市税务局</t>
         </is>
       </c>
       <c r="AI24" s="2" t="inlineStr">
@@ -3669,64 +3657,64 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CASE-13a8aac51595155a</t>
+          <t>CASE-717dfe3250926214</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>DOC-7189c9a2cee8e8ce</t>
+          <t>DOC-7df9c075e55777a1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>温州市</t>
+          <t>泰州市</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局泰州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局泰州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>温作潘</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr"/>
+          <t>靖江市长凌金属材料有限公司</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>91321282742461893K</t>
+        </is>
+      </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>温税三稽处〔2026〕100号</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>温税三稽处〔2026〕100号</t>
-        </is>
-      </c>
+          <t>泰税一稽罚〔2025〕54号</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>温税三稽罚〔2026〕65号</t>
+          <t>泰税一稽罚〔2025〕54号</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr"/>
@@ -3735,17 +3723,21 @@
       <c r="S25" s="3" t="n"/>
       <c r="T25" s="3" t="n"/>
       <c r="U25" s="3" t="n"/>
-      <c r="V25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>接上级通知,经我局研究决定,撤销上述《税务行政处罚决定书》。</t>
+        </is>
+      </c>
       <c r="W25" s="4" t="n"/>
       <c r="X25" s="4" t="n">
-        <v>46175</v>
+        <v>46191</v>
       </c>
       <c r="Y25" s="4" t="n"/>
       <c r="Z25" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
@@ -3767,92 +3759,96 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF25" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF25" s="2" t="inlineStr"/>
       <c r="AG25" s="2" t="inlineStr"/>
       <c r="AH25" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 关于撤销《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI25" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ25" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>官方页面显示该决定书已被撤销。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CASE-13a8aac51595155a</t>
+          <t>CASE-a62e569c195adc3c</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>DOC-02fc2468fd0396a6</t>
+          <t>DOC-b1dda915d4e6117d</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>温州市</t>
+          <t>遵义市</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局遵义市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局遵义市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>温作潘</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr"/>
+          <t>贵州服格定商贸有限公司</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>91520302MABUEHN034</t>
+        </is>
+      </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>温税三稽罚〔2026〕65号</t>
+          <t>遵税一稽处〔2026〕30号</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>温税三稽处〔2026〕100号</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>温税三稽罚〔2026〕65号</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr"/>
-      <c r="Q26" s="2" t="inlineStr"/>
+          <t>遵税一稽处〔2026〕30号</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>增值税</t>
+        </is>
+      </c>
       <c r="R26" s="3" t="n"/>
       <c r="S26" s="3" t="n"/>
       <c r="T26" s="3" t="n"/>
@@ -3860,18 +3856,18 @@
       <c r="V26" s="2" t="inlineStr"/>
       <c r="W26" s="4" t="n"/>
       <c r="X26" s="4" t="n">
-        <v>46175</v>
+        <v>46185</v>
       </c>
       <c r="Y26" s="4" t="n"/>
       <c r="Z26" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3889,20 +3885,16 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF26" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF26" s="2" t="inlineStr"/>
       <c r="AG26" s="2" t="inlineStr"/>
       <c r="AH26" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
+          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
         </is>
       </c>
       <c r="AI26" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ26" s="2" t="inlineStr">
@@ -3913,49 +3905,45 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CASE-f8625e66b291a216</t>
+          <t>CASE-13a8aac51595155a</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>DOC-7970511393924720</t>
+          <t>DOC-7189c9a2cee8e8ce</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>温州市</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>贵州翰缤商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>91520114MAAK1C546F</t>
-        </is>
-      </c>
+          <t>温作潘</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
@@ -3964,15 +3952,19 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>筑税二稽处〔2026〕27号</t>
+          <t>温税三稽处〔2026〕100号</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>筑税二稽处〔2026〕27号</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr"/>
+          <t>温税三稽处〔2026〕100号</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>温税三稽罚〔2026〕65号</t>
+        </is>
+      </c>
       <c r="P27" s="2" t="inlineStr"/>
       <c r="Q27" s="2" t="inlineStr"/>
       <c r="R27" s="3" t="n"/>
@@ -3982,14 +3974,14 @@
       <c r="V27" s="2" t="inlineStr"/>
       <c r="W27" s="4" t="n"/>
       <c r="X27" s="4" t="n">
-        <v>46156</v>
+        <v>46175</v>
       </c>
       <c r="Y27" s="4" t="n"/>
       <c r="Z27" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
@@ -4011,16 +4003,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF27" s="2" t="inlineStr"/>
+      <c r="AF27" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG27" s="2" t="inlineStr"/>
       <c r="AH27" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局关于送达《税务处理决定书》的公告</t>
+          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
         </is>
       </c>
       <c r="AI27" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ27" s="2" t="inlineStr">
@@ -4031,68 +4027,64 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CASE-0f4867f7b70d12f3</t>
+          <t>CASE-13a8aac51595155a</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>DOC-6f25d6b79e123d03</t>
+          <t>DOC-02fc2468fd0396a6</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>温州市</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>贵州铂朗物流有限公司</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>91520115MAAK0DB335</t>
-        </is>
-      </c>
+          <t>温作潘</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
+          <t>温税三稽罚〔2026〕65号</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
+          <t>温税三稽处〔2026〕100号</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽罚〔2026〕22号</t>
+          <t>温税三稽罚〔2026〕65号</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr"/>
@@ -4104,14 +4096,14 @@
       <c r="V28" s="2" t="inlineStr"/>
       <c r="W28" s="4" t="n"/>
       <c r="X28" s="4" t="n">
-        <v>46122</v>
+        <v>46175</v>
       </c>
       <c r="Y28" s="4" t="n"/>
       <c r="Z28" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
@@ -4133,16 +4125,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF28" s="2" t="inlineStr"/>
+      <c r="AF28" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG28" s="2" t="inlineStr"/>
       <c r="AH28" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
+          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
         </is>
       </c>
       <c r="AI28" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ28" s="2" t="inlineStr">
@@ -4153,16 +4149,16 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CASE-0f4867f7b70d12f3</t>
+          <t>CASE-f8625e66b291a216</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>DOC-e8233eb0e06b6e3e</t>
+          <t>DOC-7970511393924720</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -4178,45 +4174,41 @@
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局贵阳市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局贵阳市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>贵州铂朗物流有限公司</t>
+          <t>贵州翰缤商贸有限公司</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>91520115MAAK0DB335</t>
+          <t>91520114MAAK1C546F</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽罚〔2026〕22号</t>
+          <t>筑税二稽处〔2026〕27号</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>筑税三稽罚〔2026〕22号</t>
-        </is>
-      </c>
+          <t>筑税二稽处〔2026〕27号</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr"/>
       <c r="Q29" s="2" t="inlineStr"/>
       <c r="R29" s="3" t="n"/>
@@ -4226,14 +4218,14 @@
       <c r="V29" s="2" t="inlineStr"/>
       <c r="W29" s="4" t="n"/>
       <c r="X29" s="4" t="n">
-        <v>46122</v>
+        <v>46156</v>
       </c>
       <c r="Y29" s="4" t="n"/>
       <c r="Z29" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
@@ -4259,7 +4251,7 @@
       <c r="AG29" s="2" t="inlineStr"/>
       <c r="AH29" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
+          <t>国家税务总局贵阳市税务局第二稽查局关于送达《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI29" s="2" t="inlineStr">
@@ -4275,47 +4267,47 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CASE-136615addd5d0c0e</t>
+          <t>CASE-0f4867f7b70d12f3</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>DOC-551df7dc5c028b27</t>
+          <t>DOC-6f25d6b79e123d03</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>来宾市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>广西欣瑞木业有限公司</t>
+          <t>贵州铂朗物流有限公司</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>91451322MAD89XWX07</t>
+          <t>91520115MAAK0DB335</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
@@ -4326,17 +4318,17 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr"/>
@@ -4348,14 +4340,14 @@
       <c r="V30" s="2" t="inlineStr"/>
       <c r="W30" s="4" t="n"/>
       <c r="X30" s="4" t="n">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="Y30" s="4" t="n"/>
       <c r="Z30" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
@@ -4381,7 +4373,7 @@
       <c r="AG30" s="2" t="inlineStr"/>
       <c r="AH30" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
         </is>
       </c>
       <c r="AI30" s="2" t="inlineStr">
@@ -4397,47 +4389,47 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CASE-136615addd5d0c0e</t>
+          <t>CASE-0f4867f7b70d12f3</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>DOC-21f0193b66d5c3e9</t>
+          <t>DOC-e8233eb0e06b6e3e</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>来宾市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>广西欣瑞木业有限公司</t>
+          <t>贵州铂朗物流有限公司</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>91451322MAD89XWX07</t>
+          <t>91520115MAAK0DB335</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
@@ -4448,17 +4440,17 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr"/>
@@ -4470,14 +4462,14 @@
       <c r="V31" s="2" t="inlineStr"/>
       <c r="W31" s="4" t="n"/>
       <c r="X31" s="4" t="n">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="Y31" s="4" t="n"/>
       <c r="Z31" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
@@ -4503,7 +4495,7 @@
       <c r="AG31" s="2" t="inlineStr"/>
       <c r="AH31" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
         </is>
       </c>
       <c r="AI31" s="2" t="inlineStr">
@@ -4519,64 +4511,68 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CASE-393a878d93a22709</t>
+          <t>CASE-136615addd5d0c0e</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>DOC-cda8cba853896b18</t>
+          <t>DOC-551df7dc5c028b27</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>广州市</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>番禺区</t>
-        </is>
-      </c>
+          <t>来宾市</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
+        </is>
+      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>广州赞荣服装有限公司</t>
+          <t>广西欣瑞木业有限公司</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>91440113MA59AJFJ1J</t>
+          <t>91451322MAD89XWX07</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>穗番税退罚字〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>来市税二稽处〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>来市税二稽处〔2026〕6号</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>穗番税退罚字〔2026〕1号</t>
+          <t>来市税二稽罚〔2026〕4号</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr"/>
@@ -4588,14 +4584,14 @@
       <c r="V32" s="2" t="inlineStr"/>
       <c r="W32" s="4" t="n"/>
       <c r="X32" s="4" t="n">
-        <v>46091</v>
+        <v>46119</v>
       </c>
       <c r="Y32" s="4" t="n"/>
       <c r="Z32" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA32" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
@@ -4609,7 +4605,7 @@
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE32" s="5" t="inlineStr">
@@ -4617,131 +4613,111 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF32" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF32" s="2" t="inlineStr"/>
       <c r="AG32" s="2" t="inlineStr"/>
       <c r="AH32" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
+          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
         </is>
       </c>
       <c r="AI32" s="2" t="inlineStr">
         <is>
-          <t>内容不匹配</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ32" s="2" t="inlineStr">
         <is>
-          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>CASE-f94bf08964abff5a</t>
+          <t>CASE-136615addd5d0c0e</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>DOC-4574b1aadef8f30d</t>
+          <t>DOC-21f0193b66d5c3e9</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
+          <t>来宾市</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局稽查局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>常州市文杰车辆配件厂</t>
+          <t>广西欣瑞木业有限公司</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>91320411799075280A</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>朱某</t>
-        </is>
-      </c>
+          <t>91451322MAD89XWX07</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕73号</t>
+          <t>来市税二稽罚〔2026〕4号</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕73号</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr"/>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公 月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="n">
-        <v>179137.12</v>
-      </c>
+          <t>来市税二稽处〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>来市税二稽罚〔2026〕4号</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="3" t="n"/>
       <c r="S33" s="3" t="n"/>
       <c r="T33" s="3" t="n"/>
       <c r="U33" s="3" t="n"/>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市 份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元,</t>
-        </is>
-      </c>
-      <c r="W33" s="4" t="n">
-        <v>46044</v>
-      </c>
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="4" t="n"/>
       <c r="X33" s="4" t="n">
-        <v>46090</v>
+        <v>46119</v>
       </c>
       <c r="Y33" s="4" t="n"/>
       <c r="Z33" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4759,20 +4735,16 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF33" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF33" s="2" t="inlineStr"/>
       <c r="AG33" s="2" t="inlineStr"/>
       <c r="AH33" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
+          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
         </is>
       </c>
       <c r="AI33" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ33" s="2" t="inlineStr">
@@ -4783,66 +4755,66 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CASE-0b4a4519ba4f5ad9</t>
+          <t>CASE-393a878d93a22709</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>DOC-5376b9bae81cfc82</t>
+          <t>DOC-cda8cba853896b18</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>广东省</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr"/>
+          <t>广州市</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>番禺区</t>
+        </is>
+      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局常州市税务局稽查局</t>
-        </is>
-      </c>
+          <t>国家税务总局广州市番禺区税务局</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>常州好佳车辆配件有限公司</t>
+          <t>广州赞荣服装有限公司</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>91320411094264460B</t>
+          <t>91440113MA59AJFJ1J</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕71号</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>常税稽处〔2026〕71号</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr"/>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
       <c r="P34" s="2" t="inlineStr"/>
       <c r="Q34" s="2" t="inlineStr"/>
       <c r="R34" s="3" t="n"/>
@@ -4852,14 +4824,14 @@
       <c r="V34" s="2" t="inlineStr"/>
       <c r="W34" s="4" t="n"/>
       <c r="X34" s="4" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="Y34" s="4" t="n"/>
       <c r="Z34" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
@@ -4873,7 +4845,7 @@
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE34" s="5" t="inlineStr">
@@ -4889,32 +4861,32 @@
       <c r="AG34" s="2" t="inlineStr"/>
       <c r="AH34" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州好佳车辆配件有限公司《税务处理决定书》的公告</t>
+          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
         </is>
       </c>
       <c r="AI34" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>内容不匹配</t>
         </is>
       </c>
       <c r="AJ34" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>CASE-61b9b55a9d3357c7</t>
+          <t>CASE-f94bf08964abff5a</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>DOC-1228a9c92b2b0632</t>
+          <t>DOC-4574b1aadef8f30d</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4930,25 +4902,29 @@
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局常州市税务局稽查局</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>常州市三鹏机械有限公司</t>
+          <t>常州市文杰车辆配件厂</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>91320404732260748Q</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr"/>
+          <t>91320411799075280A</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>朱某</t>
+        </is>
+      </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
           <t>税务处理决定书</t>
@@ -4956,46 +4932,48 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
+          <t>常税稽处〔2026〕73号</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>常税稽一罚〔2026〕14号</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr"/>
+          <t>常税稽处〔2026〕73号</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公 月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
+        </is>
+      </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R35" s="3" t="n">
-        <v>63464.09</v>
+        <v>179137.12</v>
       </c>
       <c r="S35" s="3" t="n"/>
       <c r="T35" s="3" t="n"/>
       <c r="U35" s="3" t="n"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
-        </is>
-      </c>
-      <c r="W35" s="4" t="n"/>
+          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市 份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元,</t>
+        </is>
+      </c>
+      <c r="W35" s="4" t="n">
+        <v>46044</v>
+      </c>
       <c r="X35" s="4" t="n">
-        <v>46066</v>
+        <v>46090</v>
       </c>
       <c r="Y35" s="4" t="n"/>
       <c r="Z35" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
@@ -5017,16 +4995,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF35" s="2" t="inlineStr"/>
+      <c r="AF35" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG35" s="2" t="inlineStr"/>
       <c r="AH35" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI35" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ35" s="2" t="inlineStr">
@@ -5037,16 +5019,16 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CASE-61b9b55a9d3357c7</t>
+          <t>CASE-0b4a4519ba4f5ad9</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>DOC-b97456a64b153f67</t>
+          <t>DOC-5376b9bae81cfc82</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -5062,76 +5044,62 @@
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局常州市税务局稽查局</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>常州市三鹏机械有限公司</t>
+          <t>常州好佳车辆配件有限公司</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>91320404732260748Q</t>
+          <t>91320411094264460B</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>常税稽一罚〔2026〕14号</t>
+          <t>常税稽处〔2026〕71号</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>常税稽一罚〔2026〕14号</t>
-        </is>
-      </c>
+          <t>常税稽处〔2026〕71号</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr"/>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
       <c r="R36" s="3" t="n"/>
       <c r="S36" s="3" t="n"/>
-      <c r="T36" s="3" t="n">
-        <v>20000</v>
-      </c>
+      <c r="T36" s="3" t="n"/>
       <c r="U36" s="3" t="n"/>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
-        </is>
-      </c>
+      <c r="V36" s="2" t="inlineStr"/>
       <c r="W36" s="4" t="n"/>
       <c r="X36" s="4" t="n">
-        <v>46066</v>
+        <v>46087</v>
       </c>
       <c r="Y36" s="4" t="n"/>
       <c r="Z36" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA36" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -5149,16 +5117,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF36" s="2" t="inlineStr"/>
+      <c r="AF36" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG36" s="2" t="inlineStr"/>
       <c r="AH36" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州好佳车辆配件有限公司《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI36" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ36" s="2" t="inlineStr">
@@ -5169,47 +5141,47 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CASE-f78ec1a594442165</t>
+          <t>CASE-61b9b55a9d3357c7</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>DOC-fbbe4a664b14f54b</t>
+          <t>DOC-1228a9c92b2b0632</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>安顺市</t>
+          <t>常州市</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
+          <t>常州市三鹏机械有限公司</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>91520423MA6DLH799Q</t>
+          <t>91320404732260748Q</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
@@ -5220,52 +5192,46 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
-        </is>
-      </c>
+          <t>常税稽一罚〔2026〕14号</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr"/>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R37" s="3" t="n">
-        <v>64884.41</v>
+        <v>63464.09</v>
       </c>
       <c r="S37" s="3" t="n"/>
       <c r="T37" s="3" t="n"/>
       <c r="U37" s="3" t="n"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
-      <c r="W37" s="4" t="n">
-        <v>45898</v>
-      </c>
+          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
+        </is>
+      </c>
+      <c r="W37" s="4" t="n"/>
       <c r="X37" s="4" t="n">
-        <v>46043</v>
+        <v>46066</v>
       </c>
       <c r="Y37" s="4" t="n"/>
       <c r="Z37" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
@@ -5287,71 +5253,67 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF37" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF37" s="2" t="inlineStr"/>
       <c r="AG37" s="2" t="inlineStr"/>
       <c r="AH37" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI37" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ37" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。 字段“主要违法事实”存在冲突:保留原值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”,新值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>CASE-f78ec1a594442165</t>
+          <t>CASE-61b9b55a9d3357c7</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>DOC-9a828a6048b54b6c</t>
+          <t>DOC-b97456a64b153f67</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>安顺市</t>
+          <t>常州市</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
+          <t>常州市三鹏机械有限公司</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>91520423MA6DLH799Q</t>
+          <t>91320404732260748Q</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
@@ -5362,52 +5324,46 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>安市税稽罚〔2026〕1号</t>
+          <t>常税稽一罚〔2026〕14号</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
-        </is>
-      </c>
+          <t>常税稽一罚〔2026〕14号</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr"/>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R38" s="3" t="n"/>
       <c r="S38" s="3" t="n"/>
       <c r="T38" s="3" t="n">
-        <v>200000</v>
+        <v>20000</v>
       </c>
       <c r="U38" s="3" t="n"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
-      <c r="W38" s="4" t="n">
-        <v>45898</v>
-      </c>
+          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
+        </is>
+      </c>
+      <c r="W38" s="4" t="n"/>
       <c r="X38" s="4" t="n">
-        <v>46043</v>
+        <v>46066</v>
       </c>
       <c r="Y38" s="4" t="n"/>
       <c r="Z38" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
@@ -5429,71 +5385,67 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF38" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF38" s="2" t="inlineStr"/>
       <c r="AG38" s="2" t="inlineStr"/>
       <c r="AH38" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI38" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ38" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>CASE-fe959d4c6c52d910</t>
+          <t>CASE-f78ec1a594442165</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>DOC-f2643f2a0719d8d1</t>
+          <t>DOC-fbbe4a664b14f54b</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>南宁市</t>
+          <t>安顺市</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局稽查局</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>南宁洪谦金贸易有限公司</t>
+          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>91450103MA5K9WHY7U</t>
+          <t>91520423MA6DLH799Q</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
@@ -5504,40 +5456,52 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>南市税一稽处〔2026〕2号</t>
+          <t>安市税稽处〔2026〕1号</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>南市税一稽处〔2026〕2号</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr"/>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽罚〔2026〕1号</t>
+        </is>
+      </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>经我局2025年10月29日至2025年12月8日对你公司(地址:南宁市青秀区云景路11号春晖花园C区3栋2单元1606号)2015年12月2日至2016年12月31日期间的涉税情况进行了检查,你(单位)存在以下违法事实: 经查询你公司向税务机关报备的银行账号:广西北部湾银行南宁市财富国际支行800099398800015,经函询广西北部湾银行南宁市财富国际支行,存在以下问题: 上述行为属于开具与实际经营业务情况不符的增值税发票,违反了《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第587号修改)第二十二条第一款、第二款第(一)项的规定,属于虚开发票行为。</t>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="n"/>
+          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>64884.41</v>
+      </c>
       <c r="S39" s="3" t="n"/>
       <c r="T39" s="3" t="n"/>
       <c r="U39" s="3" t="n"/>
-      <c r="V39" s="2" t="inlineStr"/>
-      <c r="W39" s="4" t="n"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="W39" s="4" t="n">
+        <v>45898</v>
+      </c>
       <c r="X39" s="4" t="n">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="Y39" s="4" t="n"/>
       <c r="Z39" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
@@ -5567,7 +5531,7 @@
       <c r="AG39" s="2" t="inlineStr"/>
       <c r="AH39" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局税务文书送达公告_国家税务总局南宁市税务局</t>
+          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI39" s="2" t="inlineStr">
@@ -5577,95 +5541,109 @@
       </c>
       <c r="AJ39" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636255688.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。 字段“主要违法事实”存在冲突:保留原值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”,新值“我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>CASE-1983d97878508732</t>
+          <t>CASE-f78ec1a594442165</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>DOC-f9760895b4f08cc2</t>
+          <t>DOC-9a828a6048b54b6c</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>二连浩特市</t>
+          <t>安顺市</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局</t>
+          <t>国家税务总局安顺市税务局</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局稽查局</t>
+          <t>国家税务总局安顺市税务局稽查局</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>二连市坤益腾金属有限公司</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr"/>
+          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>91520423MA6DLH799Q</t>
+        </is>
+      </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
+          <t>安市税稽罚〔2026〕1号</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr"/>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽罚〔2026〕1号</t>
+        </is>
+      </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
+          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R40" s="3" t="n"/>
       <c r="S40" s="3" t="n"/>
-      <c r="T40" s="3" t="n"/>
+      <c r="T40" s="3" t="n">
+        <v>200000</v>
+      </c>
       <c r="U40" s="3" t="n"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
-        </is>
-      </c>
-      <c r="W40" s="4" t="n"/>
-      <c r="X40" s="4" t="n"/>
+          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="W40" s="4" t="n">
+        <v>45898</v>
+      </c>
+      <c r="X40" s="4" t="n">
+        <v>46043</v>
+      </c>
       <c r="Y40" s="4" t="n"/>
       <c r="Z40" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA40" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
@@ -5679,7 +5657,7 @@
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE40" s="5" t="inlineStr">
@@ -5687,61 +5665,73 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF40" s="2" t="inlineStr"/>
+      <c r="AF40" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG40" s="2" t="inlineStr"/>
       <c r="AH40" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI40" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ40" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/t20260121_89320381.html”,新值“https://guizhou.chinatax.gov.cn/sjpd/ass/tzgg_59745/202601/P020260121598636222410.docx”未静默覆盖。 字段“处理或处罚结果”存在冲突:保留原值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。”,新值“你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。 你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>CASE-d4b6986f3f97cd28</t>
+          <t>CASE-fe959d4c6c52d910</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>DOC-442cf3d9a5280c12</t>
+          <t>DOC-f2643f2a0719d8d1</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>鄂尔多斯市</t>
+          <t>南宁市</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局南宁市税务局第一稽查局</t>
+        </is>
+      </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>第二稽查局</t>
+          <t>国家税务总局南宁市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>廖礼平</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr"/>
+          <t>南宁洪谦金贸易有限公司</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>91450103MA5K9WHY7U</t>
+        </is>
+      </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
@@ -5750,46 +5740,40 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
+          <t>南市税一稽处〔2026〕2号</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
+          <t>南市税一稽处〔2026〕2号</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
+          <t>经我局2025年10月29日至2025年12月8日对你公司(地址:南宁市青秀区云景路11号春晖花园C区3栋2单元1606号)2015年12月2日至2016年12月31日期间的涉税情况进行了检查,你(单位)存在以下违法事实: 经查询你公司向税务机关报备的银行账号:广西北部湾银行南宁市财富国际支行800099398800015,经函询广西北部湾银行南宁市财富国际支行,存在以下问题: 上述行为属于开具与实际经营业务情况不符的增值税发票,违反了《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第587号修改)第二十二条第一款、第二款第(一)项的规定,属于虚开发票行为。</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>个人所得税、印花税</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>15072487.5</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>1046925</v>
-      </c>
+          <t>增值税</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="n"/>
+      <c r="S41" s="3" t="n"/>
       <c r="T41" s="3" t="n"/>
       <c r="U41" s="3" t="n"/>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
-        </is>
-      </c>
+      <c r="V41" s="2" t="inlineStr"/>
       <c r="W41" s="4" t="n"/>
-      <c r="X41" s="4" t="n"/>
+      <c r="X41" s="4" t="n">
+        <v>46031</v>
+      </c>
       <c r="Y41" s="4" t="n"/>
       <c r="Z41" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA41" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
@@ -5803,7 +5787,7 @@
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE41" s="5" t="inlineStr">
@@ -5811,69 +5795,69 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF41" s="2" t="inlineStr"/>
+      <c r="AF41" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG41" s="2" t="inlineStr"/>
       <c r="AH41" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>国家税务总局南宁市税务局第一稽查局税务文书送达公告_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI41" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ41" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>CASE-7e3d4a321440d6a7</t>
+          <t>CASE-1983d97878508732</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>DOC-bed9330343ed06af</t>
+          <t>DOC-f9760895b4f08cc2</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>二连浩特市</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
+          <t>国家税务总局二连浩特市税务局</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
+          <t>国家税务总局二连浩特市税务局稽查局</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>天津展达科技有限公司</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>91120116300738701X</t>
-        </is>
-      </c>
+          <t>二连市坤益腾金属有限公司</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
@@ -5882,48 +5866,42 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
+          <t>二税稽处〔2025〕1号</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
+          <t>二税稽处〔2025〕1号</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="n">
-        <v>920146.9399999999</v>
-      </c>
+          <t>增值税</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="n"/>
       <c r="S42" s="3" t="n"/>
       <c r="T42" s="3" t="n"/>
       <c r="U42" s="3" t="n"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
         </is>
       </c>
       <c r="W42" s="4" t="n"/>
       <c r="X42" s="4" t="n"/>
       <c r="Y42" s="4" t="n"/>
       <c r="Z42" s="4" t="n">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="AA42" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
@@ -5949,7 +5927,7 @@
       <c r="AG42" s="2" t="inlineStr"/>
       <c r="AH42" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="AI42" s="2" t="inlineStr">
@@ -5959,105 +5937,95 @@
       </c>
       <c r="AJ42" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>CASE-7e3d4a321440d6a7</t>
+          <t>CASE-d4b6986f3f97cd28</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>DOC-388bd01c01bbb789</t>
+          <t>DOC-442cf3d9a5280c12</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>鄂尔多斯市</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
-        </is>
-      </c>
+      <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
+          <t>第二稽查局</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>天津展达科技有限公司</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>91120116300738701X</t>
-        </is>
-      </c>
+          <t>廖礼平</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>津税一稽罚〔2023〕21号</t>
+          <t>鄂税二稽处〔2023〕29号</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
+          <t>鄂税二稽处〔2023〕29号</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="n"/>
-      <c r="S43" s="3" t="n"/>
-      <c r="T43" s="3" t="n">
-        <v>131368.5</v>
-      </c>
+          <t>个人所得税、印花税</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>15072487.5</v>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>1046925</v>
+      </c>
+      <c r="T43" s="3" t="n"/>
       <c r="U43" s="3" t="n"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
         </is>
       </c>
       <c r="W43" s="4" t="n"/>
       <c r="X43" s="4" t="n"/>
       <c r="Y43" s="4" t="n"/>
       <c r="Z43" s="4" t="n">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="AA43" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
@@ -6083,97 +6051,367 @@
       <c r="AG43" s="2" t="inlineStr"/>
       <c r="AH43" s="2" t="inlineStr">
         <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="AI43" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ43" s="2" t="inlineStr">
+        <is>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7e3d4a321440d6a7</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>DOC-bed9330343ed06af</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>91120116300738701X</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>920146.9399999999</v>
+      </c>
+      <c r="S44" s="3" t="n"/>
+      <c r="T44" s="3" t="n"/>
+      <c r="U44" s="3" t="n"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W44" s="4" t="n"/>
+      <c r="X44" s="4" t="n"/>
+      <c r="Y44" s="4" t="n"/>
+      <c r="Z44" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AA44" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE44" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF44" s="2" t="inlineStr"/>
+      <c r="AG44" s="2" t="inlineStr"/>
+      <c r="AH44" s="2" t="inlineStr">
+        <is>
           <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
-      <c r="AI43" s="2" t="inlineStr">
+      <c r="AI44" s="2" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ43" s="2" t="inlineStr">
+      <c r="AJ44" s="2" t="inlineStr">
+        <is>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7e3d4a321440d6a7</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>DOC-388bd01c01bbb789</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>91120116300738701X</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>税务行政处罚决定书</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="n"/>
+      <c r="S45" s="3" t="n"/>
+      <c r="T45" s="3" t="n">
+        <v>131368.5</v>
+      </c>
+      <c r="U45" s="3" t="n"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W45" s="4" t="n"/>
+      <c r="X45" s="4" t="n"/>
+      <c r="Y45" s="4" t="n"/>
+      <c r="Z45" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AA45" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE45" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF45" s="2" t="inlineStr"/>
+      <c r="AG45" s="2" t="inlineStr"/>
+      <c r="AH45" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+        </is>
+      </c>
+      <c r="AI45" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ45" s="2" t="inlineStr">
         <is>
           <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ43"/>
-  <conditionalFormatting sqref="AD2:AD43">
+  <autoFilter ref="A1:AJ45"/>
+  <conditionalFormatting sqref="AD2:AD45">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AD2="待核验"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI2:AI43">
+  <conditionalFormatting sqref="AI2:AI45">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>AND($AI2&lt;&gt;"正常",$AI2&lt;&gt;"附件正常")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AD2:AD43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AD2:AD45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"已核验,待核验,人工复核完成"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE5" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE6" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF8" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE9" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF9" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE10" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE11" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE12" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE14" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE15" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF15" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE16" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF16" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE17" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE18" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE16" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE17" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF17" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE18" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF18" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE19" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE20" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF20" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE21" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF21" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE22" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE23" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE21" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE22" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF22" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE23" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF23" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE24" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE25" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF25" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE26" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF26" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE27" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE28" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE26" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE27" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF27" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE28" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF28" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE29" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE30" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE31" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE32" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF32" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE33" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF33" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE34" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF34" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE35" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE36" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE33" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE34" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF34" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE35" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF35" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE36" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF36" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE37" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF37" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE38" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF38" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE39" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF39" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE40" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE41" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE38" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE39" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF39" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE40" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF40" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE41" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF41" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE42" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE43" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE44" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE45" r:id="rId61"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -6503,7 +6741,7 @@
         <v>46240</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -6637,7 +6875,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -6765,7 +7003,7 @@
         <v>46238</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -6895,7 +7133,7 @@
         <v>46233</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -7031,7 +7269,7 @@
         <v>46234</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -7167,7 +7405,7 @@
         <v>46238</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -7307,7 +7545,7 @@
         <v>46240</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -7347,7 +7585,7 @@
       </c>
       <c r="AJ8" s="2" t="inlineStr">
         <is>
-          <t>字段“决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处理决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处罚决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。</t>
+          <t>字段“决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处理决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处罚决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -7449,7 +7687,7 @@
         <v>46240</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -7489,7 +7727,7 @@
       </c>
       <c r="AJ9" s="2" t="inlineStr">
         <is>
-          <t>字段“决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。 字段“关联处理决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处罚决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。</t>
+          <t>字段“决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。 字段“关联处理决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处罚决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7823,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -7719,7 +7957,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -7851,7 +8089,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -7979,7 +8217,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -8117,7 +8355,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -8253,7 +8491,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -8385,7 +8623,7 @@
         <v>46229</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -8523,7 +8761,7 @@
         <v>46229</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -8665,7 +8903,7 @@
         <v>46229</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -8795,7 +9033,7 @@
         <v>46229</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -8923,7 +9161,7 @@
         <v>46229</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -9047,7 +9285,7 @@
         <v>46229</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -9181,7 +9419,7 @@
         <v>46230</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
@@ -9315,7 +9553,7 @@
         <v>46230</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
@@ -9414,7 +9652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ21"/>
+  <dimension ref="A1:AJ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9639,16 +9877,16 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CASE-119dcfa5a7c6b239</t>
+          <t>CASE-183c0161a86cb188</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>DOC-1a423a3cbfed9f3f</t>
+          <t>DOC-b42ca490d19e80f1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -9658,28 +9896,28 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>南宁市</t>
+          <t>来宾市</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第三稽查局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第三稽查局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>广西威曼能源科技有限公司</t>
+          <t>广西侯珏酒店有限公司</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>91450103MA5NJYGEXM</t>
+          <t>91451323MAK6QBE777</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
@@ -9690,17 +9928,17 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽处〔2026〕19号</t>
+          <t>来市税二稽处〔2026〕8号</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽处〔2026〕19号</t>
+          <t>来市税二稽处〔2026〕8号</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽罚〔2026〕10号</t>
+          <t>来市税二稽罚〔2026〕6号</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr"/>
@@ -9712,14 +9950,14 @@
       <c r="V2" s="2" t="inlineStr"/>
       <c r="W2" s="4" t="n"/>
       <c r="X2" s="4" t="n">
-        <v>46233</v>
+        <v>46239</v>
       </c>
       <c r="Y2" s="4" t="n"/>
       <c r="Z2" s="4" t="n">
-        <v>46236</v>
+        <v>46241</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -9741,40 +9979,32 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF2" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF2" s="2" t="inlineStr"/>
       <c r="AG2" s="2" t="inlineStr"/>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第三稽查局 税务文书送达公告_国家税务总局南宁市税务局</t>
+          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
         </is>
       </c>
       <c r="AI2" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
-        </is>
-      </c>
-      <c r="AJ2" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CASE-119dcfa5a7c6b239</t>
+          <t>CASE-183c0161a86cb188</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>DOC-f8499a65abd851d8</t>
+          <t>DOC-d238efe5d5ba0f2d</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -9784,28 +10014,28 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>南宁市</t>
+          <t>来宾市</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第三稽查局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第三稽查局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>广西威曼能源科技有限公司</t>
+          <t>广西侯珏酒店有限公司</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>91450103MA5NJYGEXM</t>
+          <t>91451323MAK6QBE777</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
@@ -9816,17 +10046,17 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽罚〔2026〕10号</t>
+          <t>来市税二稽罚〔2026〕6号</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽处〔2026〕19号</t>
+          <t>来市税二稽处〔2026〕8号</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽罚〔2026〕10号</t>
+          <t>来市税二稽罚〔2026〕6号</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr"/>
@@ -9838,14 +10068,14 @@
       <c r="V3" s="2" t="inlineStr"/>
       <c r="W3" s="4" t="n"/>
       <c r="X3" s="4" t="n">
-        <v>46233</v>
+        <v>46239</v>
       </c>
       <c r="Y3" s="4" t="n"/>
       <c r="Z3" s="4" t="n">
-        <v>46236</v>
+        <v>46241</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -9867,40 +10097,32 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF3" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF3" s="2" t="inlineStr"/>
       <c r="AG3" s="2" t="inlineStr"/>
       <c r="AH3" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第三稽查局 税务文书送达公告_国家税务总局南宁市税务局</t>
+          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
         </is>
       </c>
       <c r="AI3" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
-        </is>
-      </c>
-      <c r="AJ3" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CASE-c48b4ac9b3677385</t>
+          <t>CASE-119dcfa5a7c6b239</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>DOC-d3324d06254a350f</t>
+          <t>DOC-1a423a3cbfed9f3f</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9926,12 +10148,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>广西松柏建筑装饰设计有限公司</t>
+          <t>广西威曼能源科技有限公司</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>91450108MA5P1DL467</t>
+          <t>91450103MA5NJYGEXM</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
@@ -9942,17 +10164,17 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽处〔2026〕18号</t>
+          <t>南市税三稽处〔2026〕19号</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽处〔2026〕18号</t>
+          <t>南市税三稽处〔2026〕19号</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽罚〔2026〕9号</t>
+          <t>南市税三稽罚〔2026〕10号</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr"/>
@@ -9968,10 +10190,10 @@
       </c>
       <c r="Y4" s="4" t="n"/>
       <c r="Z4" s="4" t="n">
-        <v>46238</v>
+        <v>46236</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -10017,16 +10239,16 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CASE-c48b4ac9b3677385</t>
+          <t>CASE-119dcfa5a7c6b239</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>DOC-c40aad0bbe60707b</t>
+          <t>DOC-f8499a65abd851d8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -10052,12 +10274,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>广西松柏建筑装饰设计有限公司</t>
+          <t>广西威曼能源科技有限公司</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>91450108MA5P1DL467</t>
+          <t>91450103MA5NJYGEXM</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
@@ -10068,17 +10290,17 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽罚〔2026〕9号</t>
+          <t>南市税三稽罚〔2026〕10号</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽处〔2026〕18号</t>
+          <t>南市税三稽处〔2026〕19号</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽罚〔2026〕9号</t>
+          <t>南市税三稽罚〔2026〕10号</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr"/>
@@ -10094,10 +10316,10 @@
       </c>
       <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n">
-        <v>46238</v>
+        <v>46236</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -10143,16 +10365,16 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>CASE-6e854d911c44fb48</t>
+          <t>CASE-c48b4ac9b3677385</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>DOC-4bf991cc37f1a595</t>
+          <t>DOC-d3324d06254a350f</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -10168,22 +10390,22 @@
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第四稽查局</t>
+          <t>国家税务总局南宁市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第四稽查局</t>
+          <t>国家税务总局南宁市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>南宁敏顺睿商务服务有限公司</t>
+          <t>广西松柏建筑装饰设计有限公司</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>91450128MAA79KD08F</t>
+          <t>91450108MA5P1DL467</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
@@ -10194,15 +10416,19 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>南市税四稽处〔2025〕4号</t>
+          <t>南市税三稽处〔2026〕18号</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>南市税四稽处〔2025〕4号</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr"/>
+          <t>南市税三稽处〔2026〕18号</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>南市税三稽罚〔2026〕9号</t>
+        </is>
+      </c>
       <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr"/>
       <c r="R6" s="3" t="n"/>
@@ -10212,14 +10438,14 @@
       <c r="V6" s="2" t="inlineStr"/>
       <c r="W6" s="4" t="n"/>
       <c r="X6" s="4" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="Y6" s="4" t="n"/>
       <c r="Z6" s="4" t="n">
         <v>46238</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -10233,7 +10459,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE6" s="5" t="inlineStr">
@@ -10241,36 +10467,40 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AF6" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG6" s="2" t="inlineStr"/>
       <c r="AH6" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第四稽查局公告更正告知书(南宁敏顺睿商务服务有限公司)_国家税务总局南宁市税务局</t>
+          <t>国家税务总局南宁市税务局第三稽查局 税务文书送达公告_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI6" s="2" t="inlineStr">
         <is>
-          <t>内容不匹配</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="inlineStr">
         <is>
-          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CASE-85fda8617056d119</t>
+          <t>CASE-c48b4ac9b3677385</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>DOC-9057f0b6746c97de</t>
+          <t>DOC-c40aad0bbe60707b</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -10286,22 +10516,22 @@
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第四稽查局</t>
+          <t>国家税务总局南宁市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第四稽查局</t>
+          <t>国家税务总局南宁市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>南宁敏顺睿商务服务有限公司</t>
+          <t>广西松柏建筑装饰设计有限公司</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>91450128MAA79KD08F</t>
+          <t>91450108MA5P1DL467</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
@@ -10312,13 +10542,17 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>南市税四稽罚〔2026〕4号</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>南市税三稽罚〔2026〕9号</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>南市税三稽处〔2026〕18号</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>南市税四稽罚〔2026〕4号</t>
+          <t>南市税三稽罚〔2026〕9号</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr"/>
@@ -10330,14 +10564,14 @@
       <c r="V7" s="2" t="inlineStr"/>
       <c r="W7" s="4" t="n"/>
       <c r="X7" s="4" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="Y7" s="4" t="n"/>
       <c r="Z7" s="4" t="n">
         <v>46238</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -10351,7 +10585,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE7" s="5" t="inlineStr">
@@ -10359,67 +10593,71 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AF7" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG7" s="2" t="inlineStr"/>
       <c r="AH7" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第四稽查局公告更正告知书(南宁敏顺睿商务服务有限公司)_国家税务总局南宁市税务局</t>
+          <t>国家税务总局南宁市税务局第三稽查局 税务文书送达公告_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI7" s="2" t="inlineStr">
         <is>
-          <t>内容不匹配</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr">
         <is>
-          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CASE-3e050a699b29b0d0</t>
+          <t>CASE-6e854d911c44fb48</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DOC-96a3089a0e2b37cd</t>
+          <t>DOC-4bf991cc37f1a595</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>河南省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>平顶山市</t>
+          <t>南宁市</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局平顶山市税务局第一稽查局</t>
+          <t>国家税务总局南宁市税务局第四稽查局</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局平顶山市税务局第一稽查局</t>
+          <t>国家税务总局南宁市税务局第四稽查局</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>汝州泰隆实业有限公司</t>
+          <t>南宁敏顺睿商务服务有限公司</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>91410482MA40K4KA3B</t>
+          <t>91450128MAA79KD08F</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
@@ -10430,21 +10668,17 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>平税稽一局处〔2026〕1号</t>
+          <t>南市税四稽处〔2025〕4号</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>平税稽一局处〔2026〕1号</t>
+          <t>南市税四稽处〔2025〕4号</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>增值税、个人所得税</t>
-        </is>
-      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
       <c r="R8" s="3" t="n"/>
       <c r="S8" s="3" t="n"/>
       <c r="T8" s="3" t="n"/>
@@ -10452,14 +10686,14 @@
       <c r="V8" s="2" t="inlineStr"/>
       <c r="W8" s="4" t="n"/>
       <c r="X8" s="4" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="Y8" s="4" t="n"/>
       <c r="Z8" s="4" t="n">
-        <v>46229</v>
+        <v>46238</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -10473,7 +10707,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE8" s="5" t="inlineStr">
@@ -10485,82 +10719,82 @@
       <c r="AG8" s="2" t="inlineStr"/>
       <c r="AH8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局平顶山市税务局第一稽查局关于送达汝州泰隆实业有限公司《税务处理决定书》的公告 - 国家税务总局平顶山市税务局</t>
+          <t>国家税务总局南宁市税务局第四稽查局公告更正告知书(南宁敏顺睿商务服务有限公司)_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI8" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>内容不匹配</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>CASE-365e8a924cf64611</t>
+          <t>CASE-85fda8617056d119</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DOC-4d14eba16f9aa8a0</t>
+          <t>DOC-9057f0b6746c97de</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>南宁市</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局南宁市税务局第四稽查局</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局南宁市税务局第四稽查局</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>贵州博泰工贸有限公司</t>
+          <t>南宁敏顺睿商务服务有限公司</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91520115587255589F</t>
+          <t>91450128MAA79KD08F</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕38号</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>筑税三稽处〔2026〕38号</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
+          <t>南市税四稽罚〔2026〕4号</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>南市税四稽罚〔2026〕4号</t>
+        </is>
+      </c>
       <c r="P9" s="2" t="inlineStr"/>
       <c r="Q9" s="2" t="inlineStr"/>
       <c r="R9" s="3" t="n"/>
@@ -10570,14 +10804,14 @@
       <c r="V9" s="2" t="inlineStr"/>
       <c r="W9" s="4" t="n"/>
       <c r="X9" s="4" t="n">
-        <v>46224</v>
+        <v>46231</v>
       </c>
       <c r="Y9" s="4" t="n"/>
       <c r="Z9" s="4" t="n">
-        <v>46229</v>
+        <v>46238</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -10591,7 +10825,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE9" s="5" t="inlineStr">
@@ -10603,63 +10837,63 @@
       <c r="AG9" s="2" t="inlineStr"/>
       <c r="AH9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书、税务行政处罚决定书的公告</t>
+          <t>国家税务总局南宁市税务局第四稽查局公告更正告知书(南宁敏顺睿商务服务有限公司)_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI9" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>内容不匹配</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CASE-089a3b9692e76ac4</t>
+          <t>CASE-3e050a699b29b0d0</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DOC-d21cdc5988b1e304</t>
+          <t>DOC-96a3089a0e2b37cd</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>淮安市</t>
+          <t>平顶山市</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
+          <t>国家税务总局平顶山市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局淮安市税务局稽查局</t>
+          <t>国家税务总局平顶山市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>淮安市百亦金商贸有限公司</t>
+          <t>汝州泰隆实业有限公司</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>91320804MA1WEH7Y3U</t>
+          <t>91410482MA40K4KA3B</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
@@ -10670,21 +10904,21 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>淮税稽处〔2026〕26号</t>
+          <t>平税稽一局处〔2026〕1号</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>淮税稽处〔2026〕26号</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽罚〔2026〕6号</t>
-        </is>
-      </c>
+          <t>平税稽一局处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>增值税、个人所得税</t>
+        </is>
+      </c>
       <c r="R10" s="3" t="n"/>
       <c r="S10" s="3" t="n"/>
       <c r="T10" s="3" t="n"/>
@@ -10692,14 +10926,14 @@
       <c r="V10" s="2" t="inlineStr"/>
       <c r="W10" s="4" t="n"/>
       <c r="X10" s="4" t="n">
-        <v>46216</v>
+        <v>46227</v>
       </c>
       <c r="Y10" s="4" t="n"/>
       <c r="Z10" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -10721,20 +10955,16 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF10" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF10" s="2" t="inlineStr"/>
       <c r="AG10" s="2" t="inlineStr"/>
       <c r="AH10" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
+          <t>国家税务总局平顶山市税务局第一稽查局关于送达汝州泰隆实业有限公司《税务处理决定书》的公告 - 国家税务总局平顶山市税务局</t>
         </is>
       </c>
       <c r="AI10" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ10" s="2" t="inlineStr">
@@ -10745,70 +10975,66 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>CASE-089a3b9692e76ac4</t>
+          <t>CASE-365e8a924cf64611</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>DOC-9f8e8958d8ff89b6</t>
+          <t>DOC-4d14eba16f9aa8a0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>淮安市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局淮安市税务局稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>淮安市百亦金商贸有限公司</t>
+          <t>贵州博泰工贸有限公司</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91320804MA1WEH7Y3U</t>
+          <t>91520115587255589F</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>淮税稽罚〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕38号</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>淮税稽处〔2026〕26号</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽罚〔2026〕6号</t>
-        </is>
-      </c>
+          <t>筑税三稽处〔2026〕38号</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
       <c r="R11" s="3" t="n"/>
@@ -10818,14 +11044,14 @@
       <c r="V11" s="2" t="inlineStr"/>
       <c r="W11" s="4" t="n"/>
       <c r="X11" s="4" t="n">
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="Y11" s="4" t="n"/>
       <c r="Z11" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -10847,20 +11073,16 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF11" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF11" s="2" t="inlineStr"/>
       <c r="AG11" s="2" t="inlineStr"/>
       <c r="AH11" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书、税务行政处罚决定书的公告</t>
         </is>
       </c>
       <c r="AI11" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ11" s="2" t="inlineStr">
@@ -10871,16 +11093,16 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CASE-717dfe3250926214</t>
+          <t>CASE-089a3b9692e76ac4</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>DOC-7df9c075e55777a1</t>
+          <t>DOC-d21cdc5988b1e304</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -10890,45 +11112,49 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>泰州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泰州市税务局第一稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泰州市税务局第一稽查局</t>
+          <t>国家税务总局淮安市税务局稽查局</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>靖江市长凌金属材料有限公司</t>
+          <t>淮安市百亦金商贸有限公司</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>91321282742461893K</t>
+          <t>91320804MA1WEH7Y3U</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>泰税一稽罚〔2025〕54号</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>淮税稽处〔2026〕26号</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>淮税稽处〔2026〕26号</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>泰税一稽罚〔2025〕54号</t>
+          <t>淮税稽罚〔2026〕6号</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr"/>
@@ -10937,21 +11163,17 @@
       <c r="S12" s="3" t="n"/>
       <c r="T12" s="3" t="n"/>
       <c r="U12" s="3" t="n"/>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>接上级通知,经我局研究决定,撤销上述《税务行政处罚决定书》。</t>
-        </is>
-      </c>
+      <c r="V12" s="2" t="inlineStr"/>
       <c r="W12" s="4" t="n"/>
       <c r="X12" s="4" t="n">
-        <v>46191</v>
+        <v>46216</v>
       </c>
       <c r="Y12" s="4" t="n"/>
       <c r="Z12" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -10973,84 +11195,92 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AF12" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG12" s="2" t="inlineStr"/>
       <c r="AH12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 关于撤销《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
         </is>
       </c>
       <c r="AI12" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ12" s="2" t="inlineStr">
         <is>
-          <t>官方页面显示该决定书已被撤销。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CASE-13a8aac51595155a</t>
+          <t>CASE-089a3b9692e76ac4</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>DOC-7189c9a2cee8e8ce</t>
+          <t>DOC-9f8e8958d8ff89b6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>温州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局淮安市税务局稽查局</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>温作潘</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr"/>
+          <t>淮安市百亦金商贸有限公司</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>91320804MA1WEH7Y3U</t>
+        </is>
+      </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>温税三稽处〔2026〕100号</t>
+          <t>淮税稽罚〔2026〕6号</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>温税三稽处〔2026〕100号</t>
+          <t>淮税稽处〔2026〕26号</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>温税三稽罚〔2026〕65号</t>
+          <t>淮税稽罚〔2026〕6号</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr"/>
@@ -11062,14 +11292,14 @@
       <c r="V13" s="2" t="inlineStr"/>
       <c r="W13" s="4" t="n"/>
       <c r="X13" s="4" t="n">
-        <v>46175</v>
+        <v>46216</v>
       </c>
       <c r="Y13" s="4" t="n"/>
       <c r="Z13" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -11099,7 +11329,7 @@
       <c r="AG13" s="2" t="inlineStr"/>
       <c r="AH13" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
         </is>
       </c>
       <c r="AI13" s="2" t="inlineStr">
@@ -11115,45 +11345,49 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASE-13a8aac51595155a</t>
+          <t>CASE-717dfe3250926214</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DOC-02fc2468fd0396a6</t>
+          <t>DOC-7df9c075e55777a1</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>温州市</t>
+          <t>泰州市</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局泰州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局泰州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>温作潘</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr"/>
+          <t>靖江市长凌金属材料有限公司</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>91321282742461893K</t>
+        </is>
+      </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -11162,17 +11396,13 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>温税三稽罚〔2026〕65号</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>温税三稽处〔2026〕100号</t>
-        </is>
-      </c>
+          <t>泰税一稽罚〔2025〕54号</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>温税三稽罚〔2026〕65号</t>
+          <t>泰税一稽罚〔2025〕54号</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr"/>
@@ -11181,17 +11411,21 @@
       <c r="S14" s="3" t="n"/>
       <c r="T14" s="3" t="n"/>
       <c r="U14" s="3" t="n"/>
-      <c r="V14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>接上级通知,经我局研究决定,撤销上述《税务行政处罚决定书》。</t>
+        </is>
+      </c>
       <c r="W14" s="4" t="n"/>
       <c r="X14" s="4" t="n">
-        <v>46175</v>
+        <v>46191</v>
       </c>
       <c r="Y14" s="4" t="n"/>
       <c r="Z14" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -11213,73 +11447,65 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF14" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF14" s="2" t="inlineStr"/>
       <c r="AG14" s="2" t="inlineStr"/>
       <c r="AH14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 关于撤销《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI14" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ14" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>官方页面显示该决定书已被撤销。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CASE-f8625e66b291a216</t>
+          <t>CASE-13a8aac51595155a</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>DOC-7970511393924720</t>
+          <t>DOC-7189c9a2cee8e8ce</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>温州市</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>贵州翰缤商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>91520114MAAK1C546F</t>
-        </is>
-      </c>
+          <t>温作潘</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -11288,15 +11514,19 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>筑税二稽处〔2026〕27号</t>
+          <t>温税三稽处〔2026〕100号</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>筑税二稽处〔2026〕27号</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
+          <t>温税三稽处〔2026〕100号</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>温税三稽罚〔2026〕65号</t>
+        </is>
+      </c>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr"/>
       <c r="R15" s="3" t="n"/>
@@ -11306,14 +11536,14 @@
       <c r="V15" s="2" t="inlineStr"/>
       <c r="W15" s="4" t="n"/>
       <c r="X15" s="4" t="n">
-        <v>46156</v>
+        <v>46175</v>
       </c>
       <c r="Y15" s="4" t="n"/>
       <c r="Z15" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -11335,16 +11565,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AF15" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG15" s="2" t="inlineStr"/>
       <c r="AH15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局关于送达《税务处理决定书》的公告</t>
+          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
         </is>
       </c>
       <c r="AI15" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ15" s="2" t="inlineStr">
@@ -11355,68 +11589,64 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CASE-0f4867f7b70d12f3</t>
+          <t>CASE-13a8aac51595155a</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>DOC-6f25d6b79e123d03</t>
+          <t>DOC-02fc2468fd0396a6</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>温州市</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>贵州铂朗物流有限公司</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>91520115MAAK0DB335</t>
-        </is>
-      </c>
+          <t>温作潘</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
+          <t>温税三稽罚〔2026〕65号</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
+          <t>温税三稽处〔2026〕100号</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽罚〔2026〕22号</t>
+          <t>温税三稽罚〔2026〕65号</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr"/>
@@ -11428,14 +11658,14 @@
       <c r="V16" s="2" t="inlineStr"/>
       <c r="W16" s="4" t="n"/>
       <c r="X16" s="4" t="n">
-        <v>46122</v>
+        <v>46175</v>
       </c>
       <c r="Y16" s="4" t="n"/>
       <c r="Z16" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -11457,16 +11687,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AF16" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG16" s="2" t="inlineStr"/>
       <c r="AH16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
+          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
         </is>
       </c>
       <c r="AI16" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ16" s="2" t="inlineStr">
@@ -11477,16 +11711,16 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CASE-0f4867f7b70d12f3</t>
+          <t>CASE-f8625e66b291a216</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>DOC-e8233eb0e06b6e3e</t>
+          <t>DOC-7970511393924720</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -11502,45 +11736,41 @@
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局贵阳市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局贵阳市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>贵州铂朗物流有限公司</t>
+          <t>贵州翰缤商贸有限公司</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>91520115MAAK0DB335</t>
+          <t>91520114MAAK1C546F</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽罚〔2026〕22号</t>
+          <t>筑税二稽处〔2026〕27号</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>筑税三稽罚〔2026〕22号</t>
-        </is>
-      </c>
+          <t>筑税二稽处〔2026〕27号</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr"/>
       <c r="R17" s="3" t="n"/>
@@ -11550,14 +11780,14 @@
       <c r="V17" s="2" t="inlineStr"/>
       <c r="W17" s="4" t="n"/>
       <c r="X17" s="4" t="n">
-        <v>46122</v>
+        <v>46156</v>
       </c>
       <c r="Y17" s="4" t="n"/>
       <c r="Z17" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -11583,7 +11813,7 @@
       <c r="AG17" s="2" t="inlineStr"/>
       <c r="AH17" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
+          <t>国家税务总局贵阳市税务局第二稽查局关于送达《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI17" s="2" t="inlineStr">
@@ -11599,47 +11829,47 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CASE-136615addd5d0c0e</t>
+          <t>CASE-0f4867f7b70d12f3</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>DOC-551df7dc5c028b27</t>
+          <t>DOC-6f25d6b79e123d03</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>来宾市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>广西欣瑞木业有限公司</t>
+          <t>贵州铂朗物流有限公司</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>91451322MAD89XWX07</t>
+          <t>91520115MAAK0DB335</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
@@ -11650,17 +11880,17 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr"/>
@@ -11672,14 +11902,14 @@
       <c r="V18" s="2" t="inlineStr"/>
       <c r="W18" s="4" t="n"/>
       <c r="X18" s="4" t="n">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="Y18" s="4" t="n"/>
       <c r="Z18" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -11705,7 +11935,7 @@
       <c r="AG18" s="2" t="inlineStr"/>
       <c r="AH18" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
         </is>
       </c>
       <c r="AI18" s="2" t="inlineStr">
@@ -11721,47 +11951,47 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CASE-136615addd5d0c0e</t>
+          <t>CASE-0f4867f7b70d12f3</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>DOC-21f0193b66d5c3e9</t>
+          <t>DOC-e8233eb0e06b6e3e</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>来宾市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>广西欣瑞木业有限公司</t>
+          <t>贵州铂朗物流有限公司</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>91451322MAD89XWX07</t>
+          <t>91520115MAAK0DB335</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
@@ -11772,17 +12002,17 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr"/>
@@ -11794,14 +12024,14 @@
       <c r="V19" s="2" t="inlineStr"/>
       <c r="W19" s="4" t="n"/>
       <c r="X19" s="4" t="n">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="Y19" s="4" t="n"/>
       <c r="Z19" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -11827,7 +12057,7 @@
       <c r="AG19" s="2" t="inlineStr"/>
       <c r="AH19" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
         </is>
       </c>
       <c r="AI19" s="2" t="inlineStr">
@@ -11843,64 +12073,68 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CASE-393a878d93a22709</t>
+          <t>CASE-136615addd5d0c0e</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>DOC-cda8cba853896b18</t>
+          <t>DOC-551df7dc5c028b27</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>广州市</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>番禺区</t>
-        </is>
-      </c>
+          <t>来宾市</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>广州赞荣服装有限公司</t>
+          <t>广西欣瑞木业有限公司</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>91440113MA59AJFJ1J</t>
+          <t>91451322MAD89XWX07</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>穗番税退罚字〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>来市税二稽处〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>来市税二稽处〔2026〕6号</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>穗番税退罚字〔2026〕1号</t>
+          <t>来市税二稽罚〔2026〕4号</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr"/>
@@ -11912,14 +12146,14 @@
       <c r="V20" s="2" t="inlineStr"/>
       <c r="W20" s="4" t="n"/>
       <c r="X20" s="4" t="n">
-        <v>46091</v>
+        <v>46119</v>
       </c>
       <c r="Y20" s="4" t="n"/>
       <c r="Z20" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -11933,7 +12167,7 @@
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE20" s="5" t="inlineStr">
@@ -11941,90 +12175,90 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF20" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF20" s="2" t="inlineStr"/>
       <c r="AG20" s="2" t="inlineStr"/>
       <c r="AH20" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
+          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
         </is>
       </c>
       <c r="AI20" s="2" t="inlineStr">
         <is>
-          <t>内容不匹配</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ20" s="2" t="inlineStr">
         <is>
-          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CASE-0b4a4519ba4f5ad9</t>
+          <t>CASE-136615addd5d0c0e</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>DOC-5376b9bae81cfc82</t>
+          <t>DOC-21f0193b66d5c3e9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
+          <t>来宾市</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局稽查局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>常州好佳车辆配件有限公司</t>
+          <t>广西欣瑞木业有限公司</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>91320411094264460B</t>
+          <t>91451322MAD89XWX07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕71号</t>
+          <t>来市税二稽罚〔2026〕4号</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕71号</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr"/>
+          <t>来市税二稽处〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>来市税二稽罚〔2026〕4号</t>
+        </is>
+      </c>
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr"/>
       <c r="R21" s="3" t="n"/>
@@ -12034,14 +12268,14 @@
       <c r="V21" s="2" t="inlineStr"/>
       <c r="W21" s="4" t="n"/>
       <c r="X21" s="4" t="n">
-        <v>46087</v>
+        <v>46119</v>
       </c>
       <c r="Y21" s="4" t="n"/>
       <c r="Z21" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -12063,76 +12297,318 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF21" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF21" s="2" t="inlineStr"/>
       <c r="AG21" s="2" t="inlineStr"/>
       <c r="AH21" s="2" t="inlineStr">
         <is>
+          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
+        </is>
+      </c>
+      <c r="AI21" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ21" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>CASE-393a878d93a22709</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>DOC-cda8cba853896b18</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>广州市</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>番禺区</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局广州市番禺区税务局</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>广州赞荣服装有限公司</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>91440113MA59AJFJ1J</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>税务行政处罚决定书</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="3" t="n"/>
+      <c r="S22" s="3" t="n"/>
+      <c r="T22" s="3" t="n"/>
+      <c r="U22" s="3" t="n"/>
+      <c r="V22" s="2" t="inlineStr"/>
+      <c r="W22" s="4" t="n"/>
+      <c r="X22" s="4" t="n">
+        <v>46091</v>
+      </c>
+      <c r="Y22" s="4" t="n"/>
+      <c r="Z22" s="4" t="n">
+        <v>46229</v>
+      </c>
+      <c r="AA22" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>仅公告送达/仅文号线索</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE22" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF22" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
+      <c r="AG22" s="2" t="inlineStr"/>
+      <c r="AH22" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
+        </is>
+      </c>
+      <c r="AI22" s="2" t="inlineStr">
+        <is>
+          <t>内容不匹配</t>
+        </is>
+      </c>
+      <c r="AJ22" s="2" t="inlineStr">
+        <is>
+          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>CASE-0b4a4519ba4f5ad9</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>DOC-5376b9bae81cfc82</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>江苏省</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>常州市</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局江苏省税务局</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局常州市税务局稽查局</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>常州好佳车辆配件有限公司</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>91320411094264460B</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>常税稽处〔2026〕71号</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>常税稽处〔2026〕71号</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="3" t="n"/>
+      <c r="S23" s="3" t="n"/>
+      <c r="T23" s="3" t="n"/>
+      <c r="U23" s="3" t="n"/>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="4" t="n"/>
+      <c r="X23" s="4" t="n">
+        <v>46087</v>
+      </c>
+      <c r="Y23" s="4" t="n"/>
+      <c r="Z23" s="4" t="n">
+        <v>46229</v>
+      </c>
+      <c r="AA23" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>仅公告送达/仅文号线索</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AE23" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF23" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
+      <c r="AG23" s="2" t="inlineStr"/>
+      <c r="AH23" s="2" t="inlineStr">
+        <is>
           <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州好佳车辆配件有限公司《税务处理决定书》的公告</t>
         </is>
       </c>
-      <c r="AI21" s="2" t="inlineStr">
+      <c r="AI23" s="2" t="inlineStr">
         <is>
           <t>附件正常</t>
         </is>
       </c>
-      <c r="AJ21" s="2" t="inlineStr">
+      <c r="AJ23" s="2" t="inlineStr">
         <is>
           <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ21"/>
-  <conditionalFormatting sqref="AD2:AD21">
+  <autoFilter ref="A1:AJ23"/>
+  <conditionalFormatting sqref="AD2:AD23">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AD2="待核验"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI2:AI21">
+  <conditionalFormatting sqref="AI2:AI23">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>AND($AI2&lt;&gt;"正常",$AI2&lt;&gt;"附件正常")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AD2:AD21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AD2:AD23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"已核验,待核验,人工复核完成"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF7" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE9" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE10" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF10" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE11" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF11" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE12" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF13" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE14" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF14" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE15" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE16" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE12" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE14" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE15" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE16" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF16" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE17" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE18" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE19" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE20" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF20" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE21" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF21" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE21" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE22" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF22" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE23" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF23" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -12446,7 +12922,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -12564,7 +13040,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -12682,7 +13158,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -12810,7 +13286,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -12934,7 +13410,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -13068,7 +13544,7 @@
         <v>46230</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -13202,7 +13678,7 @@
         <v>46230</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -13581,7 +14057,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -13699,7 +14175,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -13817,7 +14293,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -13895,7 +14371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -15618,8 +16094,61 @@
         </is>
       </c>
     </row>
+    <row r="36" ht="54" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:48:20+08:00</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31 至 2026-08-07</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>广西侯珏酒店有限公司</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/qzsswj/xxgk/sjxxgk/qtgg_23603/: ConnectionError: HTTPSConnectionPool(host='fujian.chinatax.gov.cn', port=443): Max retries exceeded with url: /qzsswj/xxgk/sjxxgk/qtgg_23603/ (Caused by NewConnectionError("HTTPSConnection(host='fujian.chinata...</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>已完成候选发现、逐条访问核验、去重、关联和历史数据增量写入。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M35"/>
+  <autoFilter ref="A1:M36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -819,7 +819,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -937,7 +941,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -9991,7 +9999,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -10109,7 +10121,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -14371,7 +14387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -16147,8 +16163,57 @@
         </is>
       </c>
     </row>
+    <row r="37" ht="54" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T14:05:45+08:00</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31 至 2026-08-07</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinatax.gov.cn', port=443): Max retries exceeded with url: /fzsswj/xxgk/gsgg/qtl/ (Caused by NewConnectionError("HTTPSConnection(host='fujian.chinatax.gov.cn', port=44...</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>本次检索未发现符合收录标准的新文书。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M36"/>
+  <autoFilter ref="A1:M37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -785,7 +785,7 @@
         <v>46241</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>46241</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46240</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>46238</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>46236</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>46236</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>46238</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>46238</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>46238</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>46233</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>46234</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>46238</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>46238</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>46238</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>46229</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>46240</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>46240</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>46229</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>46229</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>46229</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>46229</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>46229</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>46229</v>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>46229</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>46229</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>46229</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>46229</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>46229</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>46229</v>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>46229</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>46229</v>
       </c>
       <c r="AA32" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>46229</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>46229</v>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>46229</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>46229</v>
       </c>
       <c r="AA36" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>46229</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>46229</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>46229</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>46229</v>
       </c>
       <c r="AA40" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>46229</v>
       </c>
       <c r="AA41" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>46229</v>
       </c>
       <c r="AA42" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>46229</v>
       </c>
       <c r="AA43" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>46230</v>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>46230</v>
       </c>
       <c r="AA45" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>46240</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>46238</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>46233</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>46234</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>46238</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>46240</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>46240</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>46229</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>46229</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>46229</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>46229</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>46229</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>46229</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>46230</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>46230</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
@@ -9965,7 +9965,7 @@
         <v>46241</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>46241</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>46236</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>46236</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>46238</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>46238</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>46238</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>46238</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>46229</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>46229</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>46229</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         <v>46229</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>46229</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>46229</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>46229</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>46229</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>46229</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>46229</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>46229</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>46229</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>46229</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>46229</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>46229</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>46230</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>46230</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -16212,8 +16212,57 @@
         </is>
       </c>
     </row>
+    <row r="38" ht="54" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T13:07:28+08:00</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01 至 2026-08-08</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinatax.gov.cn', port=443): Max retries exceeded with url: /fzsswj/xxgk/gsgg/qtl/ (Caused by NewConnectionError("HTTPSConnection(host='fujian.chinatax.gov.cn', port=44...</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>本次检索未发现符合收录标准的新文书。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M37"/>
+  <autoFilter ref="A1:M38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/public/downloads/全国税务处理及行政处罚决定书汇总.xlsx
@@ -15,12 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日运行日志" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文书汇总'!$A$1:$AJ$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文书汇总'!$A$1:$AJ$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'完整文书'!$A$1:$AJ$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ47"/>
+  <dimension ref="A1:AJ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -799,7 +799,7 @@
         <v>46242</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -837,7 +837,11 @@
           <t>附件正常</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“主要违法事实”存在冲突:保留原值“经我局于2026年3月24日至2026年5月15日对你公司(地址:河池市金城江区明月路21号幸福嘉园6栋2-108号)2026年01月26日至2026年02月28日期间涉税情况进行检查,你公司存在违法事实及处理决定如下: 你公司存续时间短,开具发票后,直接走逃失踪不进行纳税申报:通过金税三期税收管理系统、增值税发票电子底账系统、广西税务局大数据分析应用集成平台查询,你公司的“申报明细”信息数为“0”,“未申报信息”信息数为“17”,“税款入库信息”信息数为“0”,即:你公司未进行任何纳税申报,无任何税款入库信息。 综合以上调查情况,你公司无实际办公经营场所、无真实货物购进,未向税务机关报备银行存款账号,未进行纳税申报,相关工作人员均无法联系,经公告送达文书后亦无人向税务机关反馈,参照《国家税务总局关于走逃(失联)企业开具增值税专用发票认定处理有关问题的公告》(国家税务总局公告2016年第76号)、《国家税务总局关于走逃(失联)企业涉嫌虚开增值税专用发票检查问题的通知》(税总发〔2016〕172号)规定,认定你公司为走逃失联企业,且无真实办公场所,无真实经营业务。 经核查,你公司已走逃失联,经公告送达文书后亦无公司相关人员联系配合调查,注册地址无实际经营场所,无货物购进发票,开票后已连续多月未进行纳税申报,根据《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第764号修订)第二十一条第二款第(一)项、《中华人民共和国发票管理办法实施细则》(国家税务总局令第56号)第二十九条第(一)项、参照《国家税务总局关于走逃(失联)企业涉嫌虚开增值税专用发票检查问题的通知》(税总发〔2016〕172号)规定,认定你公司开具的上述53份增值税电子普通发票为虚开。”,新值“经我局于2026年3月24日至2026年5月15日对你公司(地址:河池市金城江区明月路21号幸福嘉园6栋2-108号)2026年01月26日至2026年02月28日期间涉税情况进行检查,你公司存在违法事实及处罚决定如下: 你公司存续时间短,开具发票后,直接走逃失踪不进行纳税申报:通过金税三期税收管理系统、增值税发票电子底账系统、广西税务局大数据分析应用集成平台查询,你公司的“申报明细”信息数为“0”,“未申报信息”信息数为“17”,“税款入库信息”信息数为“0”,即:你公司未进行任何纳税申报,无任何税款入库信息。 综合以上调查情况,你公司无实际办公经营场所、无真实货物购进,未向税务机关报备银行存款账号,未进行纳税申报,相关工作人员均无法联系,经公告送达文书后亦无人向税务机关反馈,参照《国家税务总局关于走逃(失联)企业开具增值税专用发票认定处理有关问题的公告》(国家税务总局公告2016年第76号)、《国家税务总局关于走逃(失联)企业涉嫌虚开增值税专用发票检查问题的通知》(税总发〔2016〕172号)规定,认定你公司为走逃失联企业,且无真实办公场所,无真实经营业务。 经核查,你公司已走逃失联,经公告送达文书后亦无公司相关人员联系配合调查,注册地址无实际经营场所,无货物购进发票,开票后已连续多月未进行纳税申报,根据《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第764号修订)第二十一条第二款第(一)项、《中华人民共和国发票管理办法实施细则》(国家税务总局令第56号)第二十九条第(一)项、参照《国家税务总局关于走逃(失联)企业涉嫌虚开增值税专用发票检查问题的通知》(税总发〔2016〕172号)规定,认定你公司开具的上述53份增值税电子普通发票为虚开。”未静默覆盖。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -935,7 +939,7 @@
         <v>46242</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -973,7 +977,11 @@
           <t>附件正常</t>
         </is>
       </c>
-      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“主要违法事实”存在冲突:保留原值“经我局于2026年3月24日至2026年5月15日对你公司(地址:河池市金城江区明月路21号幸福嘉园6栋2-108号)2026年01月26日至2026年02月28日期间涉税情况进行检查,你公司存在违法事实及处理决定如下: 你公司存续时间短,开具发票后,直接走逃失踪不进行纳税申报:通过金税三期税收管理系统、增值税发票电子底账系统、广西税务局大数据分析应用集成平台查询,你公司的“申报明细”信息数为“0”,“未申报信息”信息数为“17”,“税款入库信息”信息数为“0”,即:你公司未进行任何纳税申报,无任何税款入库信息。 综合以上调查情况,你公司无实际办公经营场所、无真实货物购进,未向税务机关报备银行存款账号,未进行纳税申报,相关工作人员均无法联系,经公告送达文书后亦无人向税务机关反馈,参照《国家税务总局关于走逃(失联)企业开具增值税专用发票认定处理有关问题的公告》(国家税务总局公告2016年第76号)、《国家税务总局关于走逃(失联)企业涉嫌虚开增值税专用发票检查问题的通知》(税总发〔2016〕172号)规定,认定你公司为走逃失联企业,且无真实办公场所,无真实经营业务。 经核查,你公司已走逃失联,经公告送达文书后亦无公司相关人员联系配合调查,注册地址无实际经营场所,无货物购进发票,开票后已连续多月未进行纳税申报,根据《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第764号修订)第二十一条第二款第(一)项、《中华人民共和国发票管理办法实施细则》(国家税务总局令第56号)第二十九条第(一)项、参照《国家税务总局关于走逃(失联)企业涉嫌虚开增值税专用发票检查问题的通知》(税总发〔2016〕172号)规定,认定你公司开具的上述53份增值税电子普通发票为虚开。”,新值“经我局于2026年3月24日至2026年5月15日对你公司(地址:河池市金城江区明月路21号幸福嘉园6栋2-108号)2026年01月26日至2026年02月28日期间涉税情况进行检查,你公司存在违法事实及处罚决定如下: 你公司存续时间短,开具发票后,直接走逃失踪不进行纳税申报:通过金税三期税收管理系统、增值税发票电子底账系统、广西税务局大数据分析应用集成平台查询,你公司的“申报明细”信息数为“0”,“未申报信息”信息数为“17”,“税款入库信息”信息数为“0”,即:你公司未进行任何纳税申报,无任何税款入库信息。 综合以上调查情况,你公司无实际办公经营场所、无真实货物购进,未向税务机关报备银行存款账号,未进行纳税申报,相关工作人员均无法联系,经公告送达文书后亦无人向税务机关反馈,参照《国家税务总局关于走逃(失联)企业开具增值税专用发票认定处理有关问题的公告》(国家税务总局公告2016年第76号)、《国家税务总局关于走逃(失联)企业涉嫌虚开增值税专用发票检查问题的通知》(税总发〔2016〕172号)规定,认定你公司为走逃失联企业,且无真实办公场所,无真实经营业务。 经核查,你公司已走逃失联,经公告送达文书后亦无公司相关人员联系配合调查,注册地址无实际经营场所,无货物购进发票,开票后已连续多月未进行纳税申报,根据《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第764号修订)第二十一条第二款第(一)项、《中华人民共和国发票管理办法实施细则》(国家税务总局令第56号)第二十九条第(一)项、参照《国家税务总局关于走逃(失联)企业涉嫌虚开增值税专用发票检查问题的通知》(税总发〔2016〕172号)规定,认定你公司开具的上述53份增值税电子普通发票为虚开。”未静默覆盖。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1057,7 +1065,7 @@
         <v>46241</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1179,7 +1187,7 @@
         <v>46241</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1313,7 +1321,7 @@
         <v>46240</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1359,47 +1367,47 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CASE-ef382edddd0f50f8</t>
+          <t>CASE-b86ef2eaf21a5a7c</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>DOC-f80d567b9343411c</t>
+          <t>DOC-ff40d7c55beb9efe</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>泉州市</t>
+          <t>河池市</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局</t>
+          <t>国家税务总局河池市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局稽查局</t>
+          <t>国家税务总局河池市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>泉州平媛贸易有限公司</t>
+          <t>广西槟咪科技有限公司</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>91350503597867511E</t>
+          <t>91451202MAK5F6YF55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
@@ -1410,32 +1418,28 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>泉税稽处〔2026〕29号</t>
+          <t>河市税二稽处〔2026〕13号</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>泉税稽处〔2026〕29号</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>进行了检查,违法事实及处理决定如下: 经查,2013年1月25日至2013年1月28日期间,你公司将4900万元资金贷与庄彬阳使用,你公司未就该项贷款业务申报缴纳企业所得税、营业税及附加税费。</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>企业所得税</t>
-        </is>
-      </c>
+          <t>河市税二稽处〔2026〕13号</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>河市税二稽罚〔2026〕5号</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
       <c r="R7" s="3" t="n"/>
       <c r="S7" s="3" t="n"/>
       <c r="T7" s="3" t="n"/>
       <c r="U7" s="3" t="n"/>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满30日,即视为送达。</t>
+          <t>2026〕13 号)、《国家税务总局河池市税务局第二稽查局税务行政处罚决定书》(河市税二稽罚〔2026〕5 号)予以公告送达。 2026〕13 号)、《国家税务总局河池市税务局第二稽查局税务行政处罚决定书》(河市税二稽罚〔2026〕5 号)予以公告送达。</t>
         </is>
       </c>
       <c r="W7" s="4" t="n"/>
@@ -1444,14 +1448,14 @@
       </c>
       <c r="Y7" s="4" t="n"/>
       <c r="Z7" s="4" t="n">
-        <v>46238</v>
+        <v>46243</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1469,38 +1473,36 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AF7" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG7" s="2" t="inlineStr"/>
       <c r="AH7" s="2" t="inlineStr">
         <is>
-          <t>关于对泉州平媛贸易有限公司《税务处理决定书》送达的公告 _
- 其他公告 _
- 国家税务总局泉州市税务局</t>
+          <t>国家税务总局河池市税务局第二稽查局税务文书送达公告(河市税二稽公告〔2026〕37号)_国家税务总局河池市税务局</t>
         </is>
       </c>
       <c r="AI7" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="AJ7" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
+          <t>附件正常</t>
+        </is>
+      </c>
+      <c r="AJ7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CASE-119dcfa5a7c6b239</t>
+          <t>CASE-b86ef2eaf21a5a7c</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DOC-1a423a3cbfed9f3f</t>
+          <t>DOC-fde4cc39ffbd9be3</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1510,49 +1512,49 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>南宁市</t>
+          <t>河池市</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第三稽查局</t>
+          <t>国家税务总局河池市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第三稽查局</t>
+          <t>国家税务总局河池市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>广西威曼能源科技有限公司</t>
+          <t>广西槟咪科技有限公司</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>91450103MA5NJYGEXM</t>
+          <t>91451202MAK5F6YF55</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽处〔2026〕19号</t>
+          <t>河市税二稽罚〔2026〕5号</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽处〔2026〕19号</t>
+          <t>河市税二稽处〔2026〕13号</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽罚〔2026〕10号</t>
+          <t>河市税二稽罚〔2026〕5号</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr"/>
@@ -1561,17 +1563,21 @@
       <c r="S8" s="3" t="n"/>
       <c r="T8" s="3" t="n"/>
       <c r="U8" s="3" t="n"/>
-      <c r="V8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>2026〕13 号)、《国家税务总局河池市税务局第二稽查局税务行政处罚决定书》(河市税二稽罚〔2026〕5 号)予以公告送达。 2026〕13 号)、《国家税务总局河池市税务局第二稽查局税务行政处罚决定书》(河市税二稽罚〔2026〕5 号)予以公告送达。</t>
+        </is>
+      </c>
       <c r="W8" s="4" t="n"/>
       <c r="X8" s="4" t="n">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="Y8" s="4" t="n"/>
       <c r="Z8" s="4" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1601,7 +1607,7 @@
       <c r="AG8" s="2" t="inlineStr"/>
       <c r="AH8" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第三稽查局 税务文书送达公告_国家税务总局南宁市税务局</t>
+          <t>国家税务总局河池市税务局第二稽查局税务文书送达公告(河市税二稽公告〔2026〕37号)_国家税务总局河池市税务局</t>
         </is>
       </c>
       <c r="AI8" s="2" t="inlineStr">
@@ -1609,99 +1615,103 @@
           <t>附件正常</t>
         </is>
       </c>
-      <c r="AJ8" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
+      <c r="AJ8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>CASE-119dcfa5a7c6b239</t>
+          <t>CASE-ef382edddd0f50f8</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DOC-f8499a65abd851d8</t>
+          <t>DOC-f80d567b9343411c</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>南宁市</t>
+          <t>泉州市</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第三稽查局</t>
+          <t>国家税务总局泉州市税务局</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第三稽查局</t>
+          <t>国家税务总局泉州市税务局稽查局</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>广西威曼能源科技有限公司</t>
+          <t>泉州平媛贸易有限公司</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91450103MA5NJYGEXM</t>
+          <t>91350503597867511E</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽罚〔2026〕10号</t>
+          <t>泉税稽处〔2026〕29号</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽处〔2026〕19号</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>南市税三稽罚〔2026〕10号</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
+          <t>泉税稽处〔2026〕29号</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>进行了检查,违法事实及处理决定如下: 经查,2013年1月25日至2013年1月28日期间,你公司将4900万元资金贷与庄彬阳使用,你公司未就该项贷款业务申报缴纳企业所得税、营业税及附加税费。</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>企业所得税</t>
+        </is>
+      </c>
       <c r="R9" s="3" t="n"/>
       <c r="S9" s="3" t="n"/>
       <c r="T9" s="3" t="n"/>
       <c r="U9" s="3" t="n"/>
-      <c r="V9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满30日,即视为送达。</t>
+        </is>
+      </c>
       <c r="W9" s="4" t="n"/>
       <c r="X9" s="4" t="n">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="Y9" s="4" t="n"/>
       <c r="Z9" s="4" t="n">
-        <v>46236</v>
+        <v>46238</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1719,20 +1729,18 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF9" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF9" s="2" t="inlineStr"/>
       <c r="AG9" s="2" t="inlineStr"/>
       <c r="AH9" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第三稽查局 税务文书送达公告_国家税务总局南宁市税务局</t>
+          <t>关于对泉州平媛贸易有限公司《税务处理决定书》送达的公告 _
+ 其他公告 _
+ 国家税务总局泉州市税务局</t>
         </is>
       </c>
       <c r="AI9" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr">
@@ -1743,16 +1751,16 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CASE-c48b4ac9b3677385</t>
+          <t>CASE-119dcfa5a7c6b239</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DOC-d3324d06254a350f</t>
+          <t>DOC-1a423a3cbfed9f3f</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1778,12 +1786,12 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>广西松柏建筑装饰设计有限公司</t>
+          <t>广西威曼能源科技有限公司</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>91450108MA5P1DL467</t>
+          <t>91450103MA5NJYGEXM</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
@@ -1794,17 +1802,17 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽处〔2026〕18号</t>
+          <t>南市税三稽处〔2026〕19号</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽处〔2026〕18号</t>
+          <t>南市税三稽处〔2026〕19号</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽罚〔2026〕9号</t>
+          <t>南市税三稽罚〔2026〕10号</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr"/>
@@ -1820,10 +1828,10 @@
       </c>
       <c r="Y10" s="4" t="n"/>
       <c r="Z10" s="4" t="n">
-        <v>46238</v>
+        <v>46236</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1869,16 +1877,16 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>CASE-c48b4ac9b3677385</t>
+          <t>CASE-119dcfa5a7c6b239</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>DOC-c40aad0bbe60707b</t>
+          <t>DOC-f8499a65abd851d8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1904,12 +1912,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>广西松柏建筑装饰设计有限公司</t>
+          <t>广西威曼能源科技有限公司</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91450108MA5P1DL467</t>
+          <t>91450103MA5NJYGEXM</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
@@ -1920,17 +1928,17 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽罚〔2026〕9号</t>
+          <t>南市税三稽罚〔2026〕10号</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽处〔2026〕18号</t>
+          <t>南市税三稽处〔2026〕19号</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>南市税三稽罚〔2026〕9号</t>
+          <t>南市税三稽罚〔2026〕10号</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr"/>
@@ -1946,10 +1954,10 @@
       </c>
       <c r="Y11" s="4" t="n"/>
       <c r="Z11" s="4" t="n">
-        <v>46238</v>
+        <v>46236</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -1995,76 +2003,72 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CASE-f7f5d80ec431a14d</t>
+          <t>CASE-c48b4ac9b3677385</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>DOC-3a61d3452c421a37</t>
+          <t>DOC-d3324d06254a350f</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>福州市</t>
+          <t>南宁市</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局南宁市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局南宁市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>福州吉伦多德贸易有限公司</t>
+          <t>广西松柏建筑装饰设计有限公司</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>91350102MA33G4RD13</t>
+          <t>91450108MA5P1DL467</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽罚〔2026〕39号</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>南市税三稽处〔2026〕18号</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>南市税三稽处〔2026〕18号</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽罚〔2026〕39号</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>经我局于2022年5月20日起对你公司[地址:福建省福州市鼓楼区温泉街道东城边街39号(原东城边街东侧与温泉支路交叉处)恒宇国际2#楼5层10商务办公-1]2019年1月1日至2022年12月31日期间的涉税情况进行检查,你公司存在违法事实及处罚决定如下: 你公司假报出口骗取国家出口退税款4064566.77元。 你公司取得的已证实虚开发票、出口退税数据、报关单证资料比对结果等证据。</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>增值税、企业所得税、消费税</t>
-        </is>
-      </c>
+          <t>南市税三稽罚〔2026〕9号</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
       <c r="R12" s="3" t="n"/>
       <c r="S12" s="3" t="n"/>
       <c r="T12" s="3" t="n"/>
@@ -2079,11 +2083,11 @@
         <v>46238</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2101,18 +2105,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AF12" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG12" s="2" t="inlineStr"/>
       <c r="AH12" s="2" t="inlineStr">
         <is>
-          <t>关于送达福州吉伦多德贸易有限公司《税务行政处罚决定书》的公告 _
- 其他类 _
- 国家税务总局福州市税务局</t>
+          <t>国家税务总局南宁市税务局第三稽查局 税务文书送达公告_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI12" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ12" s="2" t="inlineStr">
@@ -2123,16 +2129,16 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CASE-89fc66bfc8dad80d</t>
+          <t>CASE-c48b4ac9b3677385</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>DOC-6e5b966cd65a4366</t>
+          <t>DOC-c40aad0bbe60707b</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2142,78 +2148,72 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>北海市</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>银海区</t>
-        </is>
-      </c>
+          <t>南宁市</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局北海市税务局</t>
+          <t>国家税务总局南宁市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局北海市税务局稽查局</t>
+          <t>国家税务总局南宁市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>广西耿仁建材有限公司</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr"/>
+          <t>广西松柏建筑装饰设计有限公司</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>91450108MA5P1DL467</t>
+        </is>
+      </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>北市税稽处〔2026〕14号</t>
+          <t>南市税三稽罚〔2026〕9号</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>北市税稽处〔2026〕14号</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>我局于2026年2月11日至2026年7月15日对你公司(地址:北海市银海区新世纪大道15号辰宸花园3幢二单元0901号)2026年1月1日至2026年1月31日期间的涉税情况进行了检查,违法事实及处理决定如下: (2)短时间开具大量大额发票且未申报 你公司未进行纳税申报,不缴或者少缴2026年1月增值税194612.47元,2026年1月城市维护建设税13622.87元,合计208235.34元。 根据《中华人民共和国税收征收管理法》第六十三条第一款规定,对上述行为定性为偷税,向你公司追缴少缴的2026年增值税194612.47元,城市维护建设税13622.87元,合计208235.34元。 1.根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)的规定,对你公司少缴所属期2026年1月的教育费附加5838.37元,予以追缴。 2.根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条的规定,对你公司少缴所属期2026年1月地方教育附加3892.25元,予以追缴。 根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司少缴的税款从税款滞纳之日起至实际缴纳税款之日止按日加收滞纳税款万分之五的滞纳金,滞纳金由金三系统自动计算加收。 (四)你公司无法联系且实地核查无实际生产地址、无生产能力、查无下落,短期开票金额大,无法核实资金流,未进行纳税申报,根据《国家税务总局关于走逃(失联)企业开具增值税专用发票认定处理有关问题的公告》(国家税务总局公告2016年第76号),将你公司按走逃(失联)处理,根据《中华人民共和国发票管理办法》(国函〔1993〕174号)第二十一条第(一)项,你公司无生产能力,却为他人开具与实际经营业务情况不符的发票,属于虚开发票的行为。</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="n">
-        <v>208235.34</v>
-      </c>
+          <t>南市税三稽处〔2026〕18号</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>南市税三稽罚〔2026〕9号</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="3" t="n"/>
       <c r="S13" s="3" t="n"/>
       <c r="T13" s="3" t="n"/>
       <c r="U13" s="3" t="n"/>
       <c r="V13" s="2" t="inlineStr"/>
       <c r="W13" s="4" t="n"/>
       <c r="X13" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="Y13" s="4" t="n"/>
       <c r="Z13" s="4" t="n">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2231,16 +2231,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AF13" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG13" s="2" t="inlineStr"/>
       <c r="AH13" s="2" t="inlineStr">
         <is>
-          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕14号)_国家税务总局北海市税务局</t>
+          <t>国家税务总局南宁市税务局第三稽查局 税务文书送达公告_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI13" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ13" s="2" t="inlineStr">
@@ -2251,101 +2255,91 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASE-eb9cfd5295d501e5</t>
+          <t>CASE-f7f5d80ec431a14d</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DOC-4a8cf53b445afc63</t>
+          <t>DOC-3a61d3452c421a37</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>北海市</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>海城区</t>
-        </is>
-      </c>
+          <t>福州市</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局北海市税务局</t>
+          <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局北海市税务局稽查局</t>
+          <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>广西轩易科技有限公司</t>
+          <t>福州吉伦多德贸易有限公司</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>91450500MAK3N9UJ2T</t>
+          <t>91350102MA33G4RD13</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>北市税稽处〔2026〕6号</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>北市税稽处〔2026〕6号</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr"/>
+          <t>榕税一稽罚〔2026〕39号</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>榕税一稽罚〔2026〕39号</t>
+        </is>
+      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>我局于2026年1月23日起对你公司(地址:北海市海城区北部湾东路“金宝小区”B幢B804号20北海汇算账商务秘书有限公司托管)2025年12月11日至2025年12月31日期间的涉税情况进行了检查,发现你公司存在税收违法行为,原《税务处理决定书》(北市税稽处〔2026〕6号)认定的违法事实有误,经重新调查核实,违法事实及处理决定如下: 经查询,你公司2026年1月20日通过网络方式零申报所属期2025年10月1日-2025年12月31日的增值税、城市维护建设税及附加,入库税款0元,申报金额与实际不符,存在虚假申报的情况。 你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 (一)根据《中华人民共和国发票管理办法》(财政部令第6号发布,经国务院令第587号、第709号、第764号修订)第二十一条第二款第(一)项的规定,认定你公司为他人开具与实际经营业务情况不符的前述13份增值税普通电子发票为虚开发票(金额合计571550.49元,税额合计5715.51元,价税合计577266.00元)。 根据《中华人民共和国税收征收管理法》第三十二条、第六十三条第一款、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,已构成偷税,向你公司追缴少缴的税款合计5915.56元,并从滞纳税款之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
+          <t>经我局于2022年5月20日起对你公司[地址:福建省福州市鼓楼区温泉街道东城边街39号(原东城边街东侧与温泉支路交叉处)恒宇国际2#楼5层10商务办公-1]2019年1月1日至2022年12月31日期间的涉税情况进行检查,你公司存在违法事实及处罚决定如下: 你公司假报出口骗取国家出口退税款4064566.77元。 你公司取得的已证实虚开发票、出口退税数据、报关单证资料比对结果等证据。</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>6058.46</v>
-      </c>
+          <t>增值税、企业所得税、消费税</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="n"/>
       <c r="S14" s="3" t="n"/>
       <c r="T14" s="3" t="n"/>
       <c r="U14" s="3" t="n"/>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《中华人民共和国城市维护建设税法》(中华人民共和国主席令第五十一号)第一条、第二条、第四条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×7%×50%=200.05元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)、《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×3%×50%=85.74元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳地方教育附加5715.51×2%×50%=57.16元。</t>
-        </is>
-      </c>
+      <c r="V14" s="2" t="inlineStr"/>
       <c r="W14" s="4" t="n"/>
       <c r="X14" s="4" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="Y14" s="4" t="n"/>
       <c r="Z14" s="4" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -2371,7 +2365,9 @@
       <c r="AG14" s="2" t="inlineStr"/>
       <c r="AH14" s="2" t="inlineStr">
         <is>
-          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕13号)_国家税务总局北海市税务局</t>
+          <t>关于送达福州吉伦多德贸易有限公司《税务行政处罚决定书》的公告 _
+ 其他类 _
+ 国家税务总局福州市税务局</t>
         </is>
       </c>
       <c r="AI14" s="2" t="inlineStr">
@@ -2381,22 +2377,22 @@
       </c>
       <c r="AJ14" s="2" t="inlineStr">
         <is>
-          <t>字段“决定书文号”存在冲突:保留原值“北市税稽处〔2026〕6号”,新值“北市税稽处〔2026〕13号”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CASE-6e854d911c44fb48</t>
+          <t>CASE-89fc66bfc8dad80d</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>DOC-4bf991cc37f1a595</t>
+          <t>DOC-6e5b966cd65a4366</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2406,30 +2402,30 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>南宁市</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr"/>
+          <t>北海市</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>银海区</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第四稽查局</t>
+          <t>国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第四稽查局</t>
+          <t>国家税务总局北海市税务局稽查局</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>南宁敏顺睿商务服务有限公司</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>91450128MAA79KD08F</t>
-        </is>
-      </c>
+          <t>广西耿仁建材有限公司</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -2438,36 +2434,46 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>南市税四稽处〔2025〕4号</t>
+          <t>北市税稽处〔2026〕14号</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>南市税四稽处〔2025〕4号</t>
+          <t>北市税稽处〔2026〕14号</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="3" t="n"/>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>我局于2026年2月11日至2026年7月15日对你公司(地址:北海市银海区新世纪大道15号辰宸花园3幢二单元0901号)2026年1月1日至2026年1月31日期间的涉税情况进行了检查,违法事实及处理决定如下: (2)短时间开具大量大额发票且未申报 你公司未进行纳税申报,不缴或者少缴2026年1月增值税194612.47元,2026年1月城市维护建设税13622.87元,合计208235.34元。 根据《中华人民共和国税收征收管理法》第六十三条第一款规定,对上述行为定性为偷税,向你公司追缴少缴的2026年增值税194612.47元,城市维护建设税13622.87元,合计208235.34元。 1.根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)的规定,对你公司少缴所属期2026年1月的教育费附加5838.37元,予以追缴。 2.根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条的规定,对你公司少缴所属期2026年1月地方教育附加3892.25元,予以追缴。 根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司少缴的税款从税款滞纳之日起至实际缴纳税款之日止按日加收滞纳税款万分之五的滞纳金,滞纳金由金三系统自动计算加收。 (四)你公司无法联系且实地核查无实际生产地址、无生产能力、查无下落,短期开票金额大,无法核实资金流,未进行纳税申报,根据《国家税务总局关于走逃(失联)企业开具增值税专用发票认定处理有关问题的公告》(国家税务总局公告2016年第76号),将你公司按走逃(失联)处理,根据《中华人民共和国发票管理办法》(国函〔1993〕174号)第二十一条第(一)项,你公司无生产能力,却为他人开具与实际经营业务情况不符的发票,属于虚开发票的行为。</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>208235.34</v>
+      </c>
       <c r="S15" s="3" t="n"/>
       <c r="T15" s="3" t="n"/>
       <c r="U15" s="3" t="n"/>
       <c r="V15" s="2" t="inlineStr"/>
       <c r="W15" s="4" t="n"/>
       <c r="X15" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="Y15" s="4" t="n"/>
       <c r="Z15" s="4" t="n">
-        <v>46238</v>
+        <v>46233</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2477,7 +2483,7 @@
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE15" s="5" t="inlineStr">
@@ -2489,32 +2495,32 @@
       <c r="AG15" s="2" t="inlineStr"/>
       <c r="AH15" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第四稽查局公告更正告知书(南宁敏顺睿商务服务有限公司)_国家税务总局南宁市税务局</t>
+          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕14号)_国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="AI15" s="2" t="inlineStr">
         <is>
-          <t>内容不匹配</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ15" s="2" t="inlineStr">
         <is>
-          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CASE-85fda8617056d119</t>
+          <t>CASE-eb9cfd5295d501e5</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>DOC-9057f0b6746c97de</t>
+          <t>DOC-4a8cf53b445afc63</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2524,68 +2530,86 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>南宁市</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr"/>
+          <t>北海市</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>海城区</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第四稽查局</t>
+          <t>国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第四稽查局</t>
+          <t>国家税务总局北海市税务局稽查局</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>南宁敏顺睿商务服务有限公司</t>
+          <t>广西轩易科技有限公司</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>91450128MAA79KD08F</t>
+          <t>91450500MAK3N9UJ2T</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>南市税四稽罚〔2026〕4号</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>南市税四稽罚〔2026〕4号</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="3" t="n"/>
+          <t>北市税稽处〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>北市税稽处〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>我局于2026年1月23日起对你公司(地址:北海市海城区北部湾东路“金宝小区”B幢B804号20北海汇算账商务秘书有限公司托管)2025年12月11日至2025年12月31日期间的涉税情况进行了检查,发现你公司存在税收违法行为,原《税务处理决定书》(北市税稽处〔2026〕6号)认定的违法事实有误,经重新调查核实,违法事实及处理决定如下: 经查询,你公司2026年1月20日通过网络方式零申报所属期2025年10月1日-2025年12月31日的增值税、城市维护建设税及附加,入库税款0元,申报金额与实际不符,存在虚假申报的情况。 你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 (一)根据《中华人民共和国发票管理办法》(财政部令第6号发布,经国务院令第587号、第709号、第764号修订)第二十一条第二款第(一)项的规定,认定你公司为他人开具与实际经营业务情况不符的前述13份增值税普通电子发票为虚开发票(金额合计571550.49元,税额合计5715.51元,价税合计577266.00元)。 根据《中华人民共和国税收征收管理法》第三十二条、第六十三条第一款、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,已构成偷税,向你公司追缴少缴的税款合计5915.56元,并从滞纳税款之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>6058.46</v>
+      </c>
       <c r="S16" s="3" t="n"/>
       <c r="T16" s="3" t="n"/>
       <c r="U16" s="3" t="n"/>
-      <c r="V16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>你公司2025年12月虚开增值税普通电子发票10份,金额571550.49元,税额5715.51元,根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条,《财政部税务总局关于增值税小规模纳税人减免增值税政策的公告》(财政部税务总局公告2023年第19号)第二条的规定,应缴所属期2025年12月增值税571550.49*1%=5715.51元,已缴增值税0元,应补缴2025年12月增值税5715.51元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《中华人民共和国城市维护建设税法》(中华人民共和国主席令第五十一号)第一条、第二条、第四条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×7%×50%=200.05元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《征收教育费附加的暂行规定》(国发〔1986〕50号)第二条、第三条及《国务院关于修改〈征收教育费附加的暂行规定〉的决定(2005)》(国务院令第448号)、《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳城市维护建设税5715.51×3%×50%=85.74元。 你公司所属期2025年12月应补缴增值税5715.51元。 根据《广西壮族自治区人民政府关于印发广西壮族自治区地方教育附加征收使用管理办法的通知》(桂政发〔2004〕1号)第五条第(一)项和《关于调整我区地方教育附加征收标准有关问题的通知》(桂财综〔2011〕13号)第一条、第三条,《财政部税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部税务总局公告2023年第12号)第二条的规定,你公司所属期2025年12月应补缴纳地方教育附加5715.51×2%×50%=57.16元。</t>
+        </is>
+      </c>
       <c r="W16" s="4" t="n"/>
       <c r="X16" s="4" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="Y16" s="4" t="n"/>
       <c r="Z16" s="4" t="n">
-        <v>46238</v>
+        <v>46234</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2595,7 +2619,7 @@
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE16" s="5" t="inlineStr">
@@ -2607,67 +2631,63 @@
       <c r="AG16" s="2" t="inlineStr"/>
       <c r="AH16" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第四稽查局公告更正告知书(南宁敏顺睿商务服务有限公司)_国家税务总局南宁市税务局</t>
+          <t>【市稽查】国家税务总局北海市税务局稽查局税务处理决定书(北市税稽处〔2026〕13号)_国家税务总局北海市税务局</t>
         </is>
       </c>
       <c r="AI16" s="2" t="inlineStr">
         <is>
-          <t>内容不匹配</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ16" s="2" t="inlineStr">
         <is>
-          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>字段“决定书文号”存在冲突:保留原值“北市税稽处〔2026〕6号”,新值“北市税稽处〔2026〕13号”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CASE-97651030667b6c98</t>
+          <t>CASE-6e854d911c44fb48</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>DOC-f9817c8cadf0fc74</t>
+          <t>DOC-4bf991cc37f1a595</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>福州市</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>仓山区</t>
-        </is>
-      </c>
+          <t>南宁市</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局南宁市税务局第四稽查局</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局福州市税务局第一稽查局</t>
+          <t>国家税务总局南宁市税务局第四稽查局</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>福州盛广弘贸易有限公司</t>
+          <t>南宁敏顺睿商务服务有限公司</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>91350104MA34D5PT77</t>
+          <t>91450128MAA79KD08F</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
@@ -2678,36 +2698,22 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽处〔2025〕233号</t>
+          <t>南市税四稽处〔2025〕4号</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>榕税一稽处〔2025〕233号</t>
+          <t>南市税四稽处〔2025〕4号</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>我局于2023年12月25日起对你公司(地址:福建省福州市仓山区信平路6号二层41室)2022年1月1日至2023年11月30日期间的涉税情况进行检查,违法事实及处理决定如下: (二)你公司于2022年至2023年取得新余伟宏服装有限公司已证实虚开的254份正常状态增值税专用发票(金额合计24261915.72元,税额合计3154049.38元,价税合计27415965.10元)用于出口退税,通过假报出口或者其他欺骗手段骗取国家出口退税款3154049.14元。 (三)你公司于2022年至2023年取得宜春润悟服饰有限公司已证实虚开的220份正常状态增值税专用发票(金额合计20853824.88元,税额合计2710997.42元,价税合计23564822.30元),上述发票你公司均用于申报出口退税,取得已退税额2710997.41元。 (一)根据《中华人民共和国税收征收管理法》第六十六条规定,认定你公司取得新余伟宏服装有限公司已证实虚开的增值税专用发票254份(金额合计24261915.72元,税额合计3154049.38元,价税合计27415965.10元,取得退税款3154049.14元)并用于出口退税的属于骗取国家出口退税。 追缴你公司骗取的出口退税款3154049.14元,具体明细如下(单位:元): (二)根据《财政部 国家税务总局关于出口货物劳务增值税和消费税政策的通知》(财税〔2012〕39号)第七条第(一)项第5目、第九条第(二)项第5目、《国家税务总局关于&lt;出口货物劳务增值税和消费税管理办法&gt;有关问题的公告》(国家税务总局公告2013年第12号)第五条第(九)项第1目规定,你公司取得宜春润悟服饰有限公司已证实虚开的220份增值税专用发票(金额合计20853824.88元,税额合计2710997.42元,价税合计23564822.30元),申报出口退税并取得退税款2710997.41元,适用增值税征税政策,追缴已退税款2710997.41元,具体明细如下(单位:元):</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="n">
-        <v>2710997.41</v>
-      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="3" t="n"/>
       <c r="S17" s="3" t="n"/>
       <c r="T17" s="3" t="n"/>
       <c r="U17" s="3" t="n"/>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《征收教育费附加的暂行规定》第二条、第三条、《福建省人民政府关于调整地方教育附加征收标准有关问题的通知》(闽政文〔2011〕230号)第一条、第二条、《财政部 税务总局关于进一步实施小微企业“六税两费”减免政策的公告》(财政部 税务总局公告2022年第10号)第一条规定,你公司应补缴相应属期城市维护建设税合计83631.38元、教育费附加合计35842.03元、地方教育附加合计23894.68元,具体明细如下(单位:元):</t>
-        </is>
-      </c>
+      <c r="V17" s="2" t="inlineStr"/>
       <c r="W17" s="4" t="n"/>
       <c r="X17" s="4" t="n">
         <v>46231</v>
@@ -2717,11 +2723,11 @@
         <v>46238</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2731,7 +2737,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE17" s="5" t="inlineStr">
@@ -2743,90 +2749,84 @@
       <c r="AG17" s="2" t="inlineStr"/>
       <c r="AH17" s="2" t="inlineStr">
         <is>
-          <t>关于送达福州盛广弘贸易有限公司《税务处理决定书》的公告 _
- 其他类 _
- 国家税务总局福州市税务局</t>
+          <t>国家税务总局南宁市税务局第四稽查局公告更正告知书(南宁敏顺睿商务服务有限公司)_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI17" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>内容不匹配</t>
         </is>
       </c>
       <c r="AJ17" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CASE-3e050a699b29b0d0</t>
+          <t>CASE-85fda8617056d119</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>DOC-96a3089a0e2b37cd</t>
+          <t>DOC-9057f0b6746c97de</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>河南省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>平顶山市</t>
+          <t>南宁市</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局平顶山市税务局第一稽查局</t>
+          <t>国家税务总局南宁市税务局第四稽查局</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局平顶山市税务局第一稽查局</t>
+          <t>国家税务总局南宁市税务局第四稽查局</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>汝州泰隆实业有限公司</t>
+          <t>南宁敏顺睿商务服务有限公司</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>91410482MA40K4KA3B</t>
+          <t>91450128MAA79KD08F</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>平税稽一局处〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>平税稽一局处〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr"/>
+          <t>南市税四稽罚〔2026〕4号</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>南市税四稽罚〔2026〕4号</t>
+        </is>
+      </c>
       <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>增值税、个人所得税</t>
-        </is>
-      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
       <c r="R18" s="3" t="n"/>
       <c r="S18" s="3" t="n"/>
       <c r="T18" s="3" t="n"/>
@@ -2834,14 +2834,14 @@
       <c r="V18" s="2" t="inlineStr"/>
       <c r="W18" s="4" t="n"/>
       <c r="X18" s="4" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="Y18" s="4" t="n"/>
       <c r="Z18" s="4" t="n">
-        <v>46229</v>
+        <v>46238</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE18" s="5" t="inlineStr">
@@ -2867,63 +2867,67 @@
       <c r="AG18" s="2" t="inlineStr"/>
       <c r="AH18" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局平顶山市税务局第一稽查局关于送达汝州泰隆实业有限公司《税务处理决定书》的公告 - 国家税务总局平顶山市税务局</t>
+          <t>国家税务总局南宁市税务局第四稽查局公告更正告知书(南宁敏顺睿商务服务有限公司)_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI18" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>内容不匹配</t>
         </is>
       </c>
       <c r="AJ18" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CASE-1a685b98e7b293c8</t>
+          <t>CASE-97651030667b6c98</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>DOC-9b5fab8065382bd9</t>
+          <t>DOC-f9817c8cadf0fc74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>辽宁省</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>铁岭市</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
+          <t>福州市</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>仓山区</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局铁岭市税务局第一稽查局</t>
+          <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局铁岭市税务局第一稽查局</t>
+          <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>辽宁恒慧专用车箱有限公司</t>
+          <t>福州盛广弘贸易有限公司</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>91211200683741982W</t>
+          <t>91350104MA34D5PT77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
@@ -2934,52 +2938,46 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>铁税一稽处〔2026〕35号</t>
+          <t>榕税一稽处〔2025〕233号</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>铁税一稽处〔2026〕35号</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>铁税一稽罚〔2026〕17号</t>
-        </is>
-      </c>
+          <t>榕税一稽处〔2025〕233号</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>查属期内违法行为均定性偷税, 需要对原处罚决定中的罚款数额 以变更,你(单位)存在违法事实及处罚决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 〔2022〕59号) 第一条、 第三条之规定, 你单位存在少缴属期2010 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。 月属期申报数据,用于证明你单位未申报缴纳印花税。 报,不缴或者少缴应纳税款的,是偷税。 务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴 内首次因偷税被税务机关处罚,并能够配合税务机关检查的,处 不缴或者少缴的税款百分之五十的罚款”之规定,对你单位城镇 土地使用税和印花税处不缴或者少缴的税款50%的罚款。 你单位印花税偷税违法行为发生于2009年11月26日,至立案 位检查属期内违法行为均定性偷税, 需要对原处理决定中的查补 情况进行了检查,违法事实及处理决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 定, 你单位存在少缴属期2010年1月至2022年6月城镇土地使 用税5,710,765.50元的违法事实。 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 该地块未缴纳契税,你单位存在少缴契税509,984.64元的违法 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。</t>
+          <t>我局于2023年12月25日起对你公司(地址:福建省福州市仓山区信平路6号二层41室)2022年1月1日至2023年11月30日期间的涉税情况进行检查,违法事实及处理决定如下: (二)你公司于2022年至2023年取得新余伟宏服装有限公司已证实虚开的254份正常状态增值税专用发票(金额合计24261915.72元,税额合计3154049.38元,价税合计27415965.10元)用于出口退税,通过假报出口或者其他欺骗手段骗取国家出口退税款3154049.14元。 (三)你公司于2022年至2023年取得宜春润悟服饰有限公司已证实虚开的220份正常状态增值税专用发票(金额合计20853824.88元,税额合计2710997.42元,价税合计23564822.30元),上述发票你公司均用于申报出口退税,取得已退税额2710997.41元。 (一)根据《中华人民共和国税收征收管理法》第六十六条规定,认定你公司取得新余伟宏服装有限公司已证实虚开的增值税专用发票254份(金额合计24261915.72元,税额合计3154049.38元,价税合计27415965.10元,取得退税款3154049.14元)并用于出口退税的属于骗取国家出口退税。 追缴你公司骗取的出口退税款3154049.14元,具体明细如下(单位:元): (二)根据《财政部 国家税务总局关于出口货物劳务增值税和消费税政策的通知》(财税〔2012〕39号)第七条第(一)项第5目、第九条第(二)项第5目、《国家税务总局关于&lt;出口货物劳务增值税和消费税管理办法&gt;有关问题的公告》(国家税务总局公告2013年第12号)第五条第(九)项第1目规定,你公司取得宜春润悟服饰有限公司已证实虚开的220份增值税专用发票(金额合计20853824.88元,税额合计2710997.42元,价税合计23564822.30元),申报出口退税并取得退税款2710997.41元,适用增值税征税政策,追缴已退税款2710997.41元,具体明细如下(单位:元):</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>增值税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、契税、教育费附加、地方教育附加</t>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R19" s="3" t="n">
-        <v>44269.5</v>
+        <v>2710997.41</v>
       </c>
       <c r="S19" s="3" t="n"/>
       <c r="T19" s="3" t="n"/>
       <c r="U19" s="3" t="n"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>定,每日按罚款数额的百分之三加处罚款。 日”之规定,你单位每月应补缴城镇土地使用税44,269.50元 征收城镇土地使用税, 自2010年1月至2022年6月应补缴城镇 所载金额的万分之五,你单位应补缴2009年11月26日印花税 日”之规定,你单位每月应补缴城镇土地使用税44,269.50元 征收城镇土地使用税, 自2010年1月至2022年6月应补缴城镇 所载金额的万分之五,你单位应补缴2009年11月26日印花税</t>
-        </is>
-      </c>
-      <c r="W19" s="4" t="n">
-        <v>46183</v>
-      </c>
+          <t>根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《征收教育费附加的暂行规定》第二条、第三条、《福建省人民政府关于调整地方教育附加征收标准有关问题的通知》(闽政文〔2011〕230号)第一条、第二条、《财政部 税务总局关于进一步实施小微企业“六税两费”减免政策的公告》(财政部 税务总局公告2022年第10号)第一条规定,你公司应补缴相应属期城市维护建设税合计83631.38元、教育费附加合计35842.03元、地方教育附加合计23894.68元,具体明细如下(单位:元):</t>
+        </is>
+      </c>
+      <c r="W19" s="4" t="n"/>
       <c r="X19" s="4" t="n">
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="Y19" s="4" t="n"/>
       <c r="Z19" s="4" t="n">
-        <v>46240</v>
+        <v>46238</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -3001,131 +2999,113 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF19" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF19" s="2" t="inlineStr"/>
       <c r="AG19" s="2" t="inlineStr"/>
       <c r="AH19" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局辽宁省税务局 通知公告 国家税务总局铁岭市税务局税务文书送达公告</t>
+          <t>关于送达福州盛广弘贸易有限公司《税务处理决定书》的公告 _
+ 其他类 _
+ 国家税务总局福州市税务局</t>
         </is>
       </c>
       <c r="AI19" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ19" s="2" t="inlineStr">
         <is>
-          <t>字段“决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处理决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处罚决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CASE-1a685b98e7b293c8</t>
+          <t>CASE-3e050a699b29b0d0</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>DOC-8fc89a4906937181</t>
+          <t>DOC-96a3089a0e2b37cd</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>辽宁省</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>铁岭市</t>
+          <t>平顶山市</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局铁岭市税务局第一稽查局</t>
+          <t>国家税务总局平顶山市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局铁岭市税务局第一稽查局</t>
+          <t>国家税务总局平顶山市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>辽宁恒慧专用车箱有限公司</t>
+          <t>汝州泰隆实业有限公司</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>91211200683741982W</t>
+          <t>91410482MA40K4KA3B</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>铁税一稽罚〔2026〕17号</t>
+          <t>平税稽一局处〔2026〕1号</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>铁税一稽处〔2026〕35号</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>铁税一稽罚〔2026〕17号</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>查属期内违法行为均定性偷税, 需要对原处罚决定中的罚款数额 以变更,你(单位)存在违法事实及处罚决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 〔2022〕59号) 第一条、 第三条之规定, 你单位存在少缴属期2010 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。 月属期申报数据,用于证明你单位未申报缴纳印花税。 报,不缴或者少缴应纳税款的,是偷税。 务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴 内首次因偷税被税务机关处罚,并能够配合税务机关检查的,处 不缴或者少缴的税款百分之五十的罚款”之规定,对你单位城镇 土地使用税和印花税处不缴或者少缴的税款50%的罚款。 你单位印花税偷税违法行为发生于2009年11月26日,至立案 位检查属期内违法行为均定性偷税, 需要对原处理决定中的查补 情况进行了检查,违法事实及处理决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 定, 你单位存在少缴属期2010年1月至2022年6月城镇土地使 用税5,710,765.50元的违法事实。 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 该地块未缴纳契税,你单位存在少缴契税509,984.64元的违法 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。</t>
-        </is>
-      </c>
+          <t>平税稽一局处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>增值税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、契税、教育费附加、地方教育附加</t>
+          <t>增值税、个人所得税</t>
         </is>
       </c>
       <c r="R20" s="3" t="n"/>
       <c r="S20" s="3" t="n"/>
-      <c r="T20" s="3" t="n">
-        <v>2855382.83</v>
-      </c>
+      <c r="T20" s="3" t="n"/>
       <c r="U20" s="3" t="n"/>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>定,每日按罚款数额的百分之三加处罚款。 日”之规定,你单位每月应补缴城镇土地使用税44,269.50元 征收城镇土地使用税, 自2010年1月至2022年6月应补缴城镇 所载金额的万分之五,你单位应补缴2009年11月26日印花税 定,每日按罚款数额的百分之三加处罚款。</t>
-        </is>
-      </c>
-      <c r="W20" s="4" t="n">
-        <v>46183</v>
-      </c>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="4" t="n"/>
       <c r="X20" s="4" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="Y20" s="4" t="n"/>
       <c r="Z20" s="4" t="n">
-        <v>46240</v>
+        <v>46229</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -3143,71 +3123,67 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF20" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF20" s="2" t="inlineStr"/>
       <c r="AG20" s="2" t="inlineStr"/>
       <c r="AH20" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局辽宁省税务局 通知公告 国家税务总局铁岭市税务局税务文书送达公告</t>
+          <t>国家税务总局平顶山市税务局第一稽查局关于送达汝州泰隆实业有限公司《税务处理决定书》的公告 - 国家税务总局平顶山市税务局</t>
         </is>
       </c>
       <c r="AI20" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ20" s="2" t="inlineStr">
         <is>
-          <t>字段“决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。 字段“关联处理决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处罚决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CASE-365e8a924cf64611</t>
+          <t>CASE-1a685b98e7b293c8</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>DOC-4d14eba16f9aa8a0</t>
+          <t>DOC-9b5fab8065382bd9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>辽宁省</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>铁岭市</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局铁岭市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局铁岭市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>贵州博泰工贸有限公司</t>
+          <t>辽宁恒慧专用车箱有限公司</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>91520115587255589F</t>
+          <t>91211200683741982W</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
@@ -3218,36 +3194,56 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕38号</t>
+          <t>铁税一稽处〔2026〕35号</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕38号</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="3" t="n"/>
+          <t>铁税一稽处〔2026〕35号</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>铁税一稽罚〔2026〕17号</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>查属期内违法行为均定性偷税, 需要对原处罚决定中的罚款数额 以变更,你(单位)存在违法事实及处罚决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 〔2022〕59号) 第一条、 第三条之规定, 你单位存在少缴属期2010 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。 月属期申报数据,用于证明你单位未申报缴纳印花税。 报,不缴或者少缴应纳税款的,是偷税。 务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴 内首次因偷税被税务机关处罚,并能够配合税务机关检查的,处 不缴或者少缴的税款百分之五十的罚款”之规定,对你单位城镇 土地使用税和印花税处不缴或者少缴的税款50%的罚款。 你单位印花税偷税违法行为发生于2009年11月26日,至立案 位检查属期内违法行为均定性偷税, 需要对原处理决定中的查补 情况进行了检查,违法事实及处理决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 定, 你单位存在少缴属期2010年1月至2022年6月城镇土地使 用税5,710,765.50元的违法事实。 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 该地块未缴纳契税,你单位存在少缴契税509,984.64元的违法 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>增值税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、契税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44269.5</v>
+      </c>
       <c r="S21" s="3" t="n"/>
       <c r="T21" s="3" t="n"/>
       <c r="U21" s="3" t="n"/>
-      <c r="V21" s="2" t="inlineStr"/>
-      <c r="W21" s="4" t="n"/>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>定,每日按罚款数额的百分之三加处罚款。 日”之规定,你单位每月应补缴城镇土地使用税44,269.50元 征收城镇土地使用税, 自2010年1月至2022年6月应补缴城镇 所载金额的万分之五,你单位应补缴2009年11月26日印花税 日”之规定,你单位每月应补缴城镇土地使用税44,269.50元 征收城镇土地使用税, 自2010年1月至2022年6月应补缴城镇 所载金额的万分之五,你单位应补缴2009年11月26日印花税</t>
+        </is>
+      </c>
+      <c r="W21" s="4" t="n">
+        <v>46183</v>
+      </c>
       <c r="X21" s="4" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="Y21" s="4" t="n"/>
       <c r="Z21" s="4" t="n">
-        <v>46229</v>
+        <v>46240</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3265,117 +3261,127 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AF21" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG21" s="2" t="inlineStr"/>
       <c r="AH21" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书、税务行政处罚决定书的公告</t>
+          <t>国家税务总局辽宁省税务局 通知公告 国家税务总局铁岭市税务局税务文书送达公告</t>
         </is>
       </c>
       <c r="AI21" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ21" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>字段“决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处理决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处罚决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CASE-7b9a26f2ac401107</t>
+          <t>CASE-1a685b98e7b293c8</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>DOC-f6c6ea472b2ca04a</t>
+          <t>DOC-8fc89a4906937181</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>辽宁省</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>三明市</t>
+          <t>铁岭市</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局三明市税务局第一稽查局</t>
+          <t>国家税务总局铁岭市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局三明市税务局第一稽查局</t>
+          <t>国家税务总局铁岭市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>三明众祥房地产开发有限公司</t>
+          <t>辽宁恒慧专用车箱有限公司</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>91350400678473231W</t>
+          <t>91211200683741982W</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>明税一稽处〔2026〕20号</t>
+          <t>铁税一稽罚〔2026〕17号</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>明税一稽处〔2026〕20号</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr"/>
+          <t>铁税一稽处〔2026〕35号</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>铁税一稽罚〔2026〕17号</t>
+        </is>
+      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2016年期间,在没有真实业务情况下,取得重庆市博海建设工程(集团)有限公司、福建九九建设有限公司三明分公司开具的不符合规定的发票,发票金额400252379元,在企业所得税税前扣除,造成少缴纳企业所得税100063094.75元,该行为违反《中华人民共和国税收征收管理法》(2015年4月24日主席令第二十三号修改)第六十三条第一款 纳税人伪造、变造、隐匿、擅自销毁账簿、记账凭证,或者在账簿上多列支出或者不列、少列收入,或者经税务机关通知申报而拒不申报或者进行虚假的纳税申报,不缴或者少缴应纳税款的,是偷税。 对纳税人偷税的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款; 之规定,对你公司在账上多列支出,造成少缴企业所得税100063094.75元的行为认定为偷税。 之规定,对你公司少缴的企业所得税从滞纳之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
+          <t>查属期内违法行为均定性偷税, 需要对原处罚决定中的罚款数额 以变更,你(单位)存在违法事实及处罚决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 〔2022〕59号) 第一条、 第三条之规定, 你单位存在少缴属期2010 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。 月属期申报数据,用于证明你单位未申报缴纳印花税。 报,不缴或者少缴应纳税款的,是偷税。 务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴 内首次因偷税被税务机关处罚,并能够配合税务机关检查的,处 不缴或者少缴的税款百分之五十的罚款”之规定,对你单位城镇 土地使用税和印花税处不缴或者少缴的税款50%的罚款。 你单位印花税偷税违法行为发生于2009年11月26日,至立案 位检查属期内违法行为均定性偷税, 需要对原处理决定中的查补 情况进行了检查,违法事实及处理决定如下: 月至2011年8月和2016年6月未申报城镇土地使用税,2011 定, 你单位存在少缴属期2010年1月至2022年6月城镇土地使 用税5,710,765.50元的违法事实。 签订了 TLTN200907《国有建设用地使用权出让合同》 , 未申报缴 之规定, 你单位存在少缴2009年11月26日印花税6,374.80元 该地块未缴纳契税,你单位存在少缴契税509,984.64元的违法 用于证明你单位采用虚假纳税申报或未申报方式申报2010年1 你单位未申报2010年1月1日至2022年6月30日印花税。</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>企业所得税</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="n">
-        <v>100063094.75</v>
-      </c>
+          <t>增值税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、契税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="n"/>
       <c r="S22" s="3" t="n"/>
-      <c r="T22" s="3" t="n"/>
+      <c r="T22" s="3" t="n">
+        <v>2855382.83</v>
+      </c>
       <c r="U22" s="3" t="n"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>据《中华人民共和国税收征收管理法实施细则》第106条规定,将该文书予以公告送达,自公告之日起满30日视为送达。</t>
-        </is>
-      </c>
-      <c r="W22" s="4" t="n"/>
+          <t>定,每日按罚款数额的百分之三加处罚款。 日”之规定,你单位每月应补缴城镇土地使用税44,269.50元 征收城镇土地使用税, 自2010年1月至2022年6月应补缴城镇 所载金额的万分之五,你单位应补缴2009年11月26日印花税 定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W22" s="4" t="n">
+        <v>46183</v>
+      </c>
       <c r="X22" s="4" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="Y22" s="4" t="n"/>
       <c r="Z22" s="4" t="n">
-        <v>46229</v>
+        <v>46240</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
@@ -3397,404 +3403,406 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AF22" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG22" s="2" t="inlineStr"/>
       <c r="AH22" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局辽宁省税务局 通知公告 国家税务总局铁岭市税务局税务文书送达公告</t>
+        </is>
+      </c>
+      <c r="AI22" s="2" t="inlineStr">
+        <is>
+          <t>附件正常</t>
+        </is>
+      </c>
+      <c r="AJ22" s="2" t="inlineStr">
+        <is>
+          <t>字段“决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。 字段“关联处理决定书文号”存在冲突:保留原值“铁税一稽处〔2026〕35号”,新值“铁税一稽处〔2024〕9号”未静默覆盖。 字段“关联处罚决定书文号”存在冲突:保留原值“铁税一稽罚〔2026〕17号”,新值“铁税一稽罚〔2024〕8号”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>CASE-365e8a924cf64611</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>DOC-4d14eba16f9aa8a0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>贵州省</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>贵阳市</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>贵州博泰工贸有限公司</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>91520115587255589F</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>筑税三稽处〔2026〕38号</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>筑税三稽处〔2026〕38号</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="3" t="n"/>
+      <c r="S23" s="3" t="n"/>
+      <c r="T23" s="3" t="n"/>
+      <c r="U23" s="3" t="n"/>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="4" t="n"/>
+      <c r="X23" s="4" t="n">
+        <v>46224</v>
+      </c>
+      <c r="Y23" s="4" t="n"/>
+      <c r="Z23" s="4" t="n">
+        <v>46229</v>
+      </c>
+      <c r="AA23" s="4" t="n">
+        <v>46243</v>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>仅公告送达/仅文号线索</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AE23" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF23" s="2" t="inlineStr"/>
+      <c r="AG23" s="2" t="inlineStr"/>
+      <c r="AH23" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书、税务行政处罚决定书的公告</t>
+        </is>
+      </c>
+      <c r="AI23" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ23" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7b9a26f2ac401107</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>DOC-f6c6ea472b2ca04a</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>福建省</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>三明市</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局三明市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局三明市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>三明众祥房地产开发有限公司</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>91350400678473231W</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>税务处理决定书</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>明税一稽处〔2026〕20号</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>明税一稽处〔2026〕20号</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>情况进行了检查,违法事实及处理决定如下: 2016年期间,在没有真实业务情况下,取得重庆市博海建设工程(集团)有限公司、福建九九建设有限公司三明分公司开具的不符合规定的发票,发票金额400252379元,在企业所得税税前扣除,造成少缴纳企业所得税100063094.75元,该行为违反《中华人民共和国税收征收管理法》(2015年4月24日主席令第二十三号修改)第六十三条第一款 纳税人伪造、变造、隐匿、擅自销毁账簿、记账凭证,或者在账簿上多列支出或者不列、少列收入,或者经税务机关通知申报而拒不申报或者进行虚假的纳税申报,不缴或者少缴应纳税款的,是偷税。 对纳税人偷税的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款; 之规定,对你公司在账上多列支出,造成少缴企业所得税100063094.75元的行为认定为偷税。 之规定,对你公司少缴的企业所得税从滞纳之日起至实际缴纳之日止按日加收万分之五的滞纳金。</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>企业所得税</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>100063094.75</v>
+      </c>
+      <c r="S24" s="3" t="n"/>
+      <c r="T24" s="3" t="n"/>
+      <c r="U24" s="3" t="n"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>据《中华人民共和国税收征收管理法实施细则》第106条规定,将该文书予以公告送达,自公告之日起满30日视为送达。</t>
+        </is>
+      </c>
+      <c r="W24" s="4" t="n"/>
+      <c r="X24" s="4" t="n">
+        <v>46223</v>
+      </c>
+      <c r="Y24" s="4" t="n"/>
+      <c r="Z24" s="4" t="n">
+        <v>46229</v>
+      </c>
+      <c r="AA24" s="4" t="n">
+        <v>46243</v>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AE24" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF24" s="2" t="inlineStr"/>
+      <c r="AG24" s="2" t="inlineStr"/>
+      <c r="AH24" s="2" t="inlineStr">
         <is>
           <t>关于送达三明众祥房地产开发有限公司 《税务处理决定书》的公告 _
  其他公告 _
  国家税务总局三明市税务局</t>
         </is>
       </c>
-      <c r="AI22" s="2" t="inlineStr">
+      <c r="AI24" s="2" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ22" s="2" t="inlineStr">
+      <c r="AJ24" s="2" t="inlineStr">
         <is>
           <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
+    <row r="25">
+      <c r="A25" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>CASE-31e4a827dfd253f2</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>DOC-3ec54358fce2350d</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>福建省</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>福州市</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>国家税务总局福州市税务局第一稽查局</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>福州顺路汽车运输有限公司</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>91350102MA31MF6611</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>税务处理决定书</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>榕税一稽处〔2026〕137号</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>榕税一稽处〔2026〕137号</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr"/>
-      <c r="P23" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>我局于2025年7月10日起对你公司(地址:福建省闽侯县青口镇祥宏南路922号)2023年1月1日至2024年12月31日期间的发票涉税情况进行检查,违法事实及处理决定如下: (二)你公司取得毕节七星关区辰楚汽车服务部(个人独资)、毕节七星关锦悦汽车服务部(个人独资)、贵州杨亭汽车销售有限公司、贵州楠鑫汽车销售有限公司已证实虚开的35份机动车发票。 (二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 (三)根据《中华人民共和国企业所得税法》第五条、第八条、《企业所得税税前扣除凭证管理办法》(国家税务总局公告2018年第28号发布)第四条、第十二条的规定,你公司取得上述虚开的发票不得作为税前扣除凭证。</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R25" s="3" t="n">
         <v>3778.22</v>
       </c>
-      <c r="S23" s="3" t="n"/>
-      <c r="T23" s="3" t="n"/>
-      <c r="U23" s="3" t="n"/>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="S25" s="3" t="n"/>
+      <c r="T25" s="3" t="n"/>
+      <c r="U25" s="3" t="n"/>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>(二)根据《中华人民共和国增值税暂行条例》第九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)的规定,你公司取得上述12份已证实虚开的发票不得作为增值税合法有效的扣税凭证抵扣其进项税额,应追缴你公司2024年1月属期增值税3564.36元。 根据《中华人民共和国城市维护建设税法》第一条、第二条、第四条、第五条、《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期城市维护建设税124.75元。 根据《征收教育费附加的暂行规定》第二条、第三条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期教育费附加53.47元。 根据《福建省人民政府关于调整地方教育附加征收标准等有关问题的通知》(闽政文〔2011〕230号)第一条、第二条,《财政部 税务总局关于进一步支持小微企业和个体工商户发展有关税费政策的公告》(财政部 税务总局公告2023年第12号)第二条、第四条、《国家税务总局关于进一步实施小微企业“六税两费”减免政策有关征管问题的公告》(国家税务总局公告2022年第3号)的规定,你公司应补缴2024年1月属期地方教育附加35.64元。</t>
         </is>
       </c>
-      <c r="W23" s="4" t="n"/>
-      <c r="X23" s="4" t="n">
+      <c r="W25" s="4" t="n"/>
+      <c r="X25" s="4" t="n">
         <v>46218</v>
       </c>
-      <c r="Y23" s="4" t="n"/>
-      <c r="Z23" s="4" t="n">
+      <c r="Y25" s="4" t="n"/>
+      <c r="Z25" s="4" t="n">
         <v>46229</v>
       </c>
-      <c r="AA23" s="4" t="n">
-        <v>46242</v>
-      </c>
-      <c r="AB23" s="2" t="inlineStr">
+      <c r="AA25" s="4" t="n">
+        <v>46243</v>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>完整文书</t>
         </is>
       </c>
-      <c r="AC23" s="2" t="inlineStr">
+      <c r="AC25" s="2" t="inlineStr">
         <is>
           <t>税务机关官网</t>
         </is>
       </c>
-      <c r="AD23" s="2" t="inlineStr">
+      <c r="AD25" s="2" t="inlineStr">
         <is>
           <t>已核验</t>
         </is>
       </c>
-      <c r="AE23" s="5" t="inlineStr">
+      <c r="AE25" s="5" t="inlineStr">
         <is>
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF23" s="2" t="inlineStr"/>
-      <c r="AG23" s="2" t="inlineStr"/>
-      <c r="AH23" s="2" t="inlineStr">
+      <c r="AF25" s="2" t="inlineStr"/>
+      <c r="AG25" s="2" t="inlineStr"/>
+      <c r="AH25" s="2" t="inlineStr">
         <is>
           <t>关于送达福州顺路汽车运输有限公司《税务处理决定书》的公告 _
  其他类 _
  国家税务总局福州市税务局</t>
         </is>
       </c>
-      <c r="AI23" s="2" t="inlineStr">
+      <c r="AI25" s="2" t="inlineStr">
         <is>
           <t>正常</t>
-        </is>
-      </c>
-      <c r="AJ23" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>CASE-089a3b9692e76ac4</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>DOC-d21cdc5988b1e304</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>江苏省</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>淮安市</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局江苏省税务局</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局淮安市税务局稽查局</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>淮安市百亦金商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>91320804MA1WEH7Y3U</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>税务处理决定书</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽处〔2026〕26号</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽处〔2026〕26号</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽罚〔2026〕6号</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr"/>
-      <c r="Q24" s="2" t="inlineStr"/>
-      <c r="R24" s="3" t="n"/>
-      <c r="S24" s="3" t="n"/>
-      <c r="T24" s="3" t="n"/>
-      <c r="U24" s="3" t="n"/>
-      <c r="V24" s="2" t="inlineStr"/>
-      <c r="W24" s="4" t="n"/>
-      <c r="X24" s="4" t="n">
-        <v>46216</v>
-      </c>
-      <c r="Y24" s="4" t="n"/>
-      <c r="Z24" s="4" t="n">
-        <v>46229</v>
-      </c>
-      <c r="AA24" s="4" t="n">
-        <v>46242</v>
-      </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>仅公告送达/仅文号线索</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD24" s="2" t="inlineStr">
-        <is>
-          <t>已核验</t>
-        </is>
-      </c>
-      <c r="AE24" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF24" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
-      <c r="AG24" s="2" t="inlineStr"/>
-      <c r="AH24" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
-        </is>
-      </c>
-      <c r="AI24" s="2" t="inlineStr">
-        <is>
-          <t>附件正常</t>
-        </is>
-      </c>
-      <c r="AJ24" s="2" t="inlineStr">
-        <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>CASE-089a3b9692e76ac4</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>DOC-9f8e8958d8ff89b6</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>江苏省</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>淮安市</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局江苏省税务局</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局淮安市税务局稽查局</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>淮安市百亦金商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>91320804MA1WEH7Y3U</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>税务行政处罚决定书</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽罚〔2026〕6号</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽处〔2026〕26号</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>淮税稽罚〔2026〕6号</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr"/>
-      <c r="Q25" s="2" t="inlineStr"/>
-      <c r="R25" s="3" t="n"/>
-      <c r="S25" s="3" t="n"/>
-      <c r="T25" s="3" t="n"/>
-      <c r="U25" s="3" t="n"/>
-      <c r="V25" s="2" t="inlineStr"/>
-      <c r="W25" s="4" t="n"/>
-      <c r="X25" s="4" t="n">
-        <v>46216</v>
-      </c>
-      <c r="Y25" s="4" t="n"/>
-      <c r="Z25" s="4" t="n">
-        <v>46229</v>
-      </c>
-      <c r="AA25" s="4" t="n">
-        <v>46242</v>
-      </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>仅公告送达/仅文号线索</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr">
-        <is>
-          <t>税务机关官网</t>
-        </is>
-      </c>
-      <c r="AD25" s="2" t="inlineStr">
-        <is>
-          <t>已核验</t>
-        </is>
-      </c>
-      <c r="AE25" s="5" t="inlineStr">
-        <is>
-          <t>打开原文</t>
-        </is>
-      </c>
-      <c r="AF25" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
-      <c r="AG25" s="2" t="inlineStr"/>
-      <c r="AH25" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
-        </is>
-      </c>
-      <c r="AI25" s="2" t="inlineStr">
-        <is>
-          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ25" s="2" t="inlineStr">
@@ -3805,47 +3813,47 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CASE-3f564fd9992b1ae3</t>
+          <t>CASE-089a3b9692e76ac4</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>DOC-c34e1d13286aafe2</t>
+          <t>DOC-d21cdc5988b1e304</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>泉州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局第二稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泉州市税务局第二稽查局</t>
+          <t>国家税务总局淮安市税务局稽查局</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>泉州隆鸿服装制造有限公司</t>
+          <t>淮安市百亦金商贸有限公司</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>91350525MA8U3U963L</t>
+          <t>91320804MA1WEH7Y3U</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
@@ -3856,48 +3864,40 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>泉税二稽处〔2026〕107号</t>
+          <t>淮税稽处〔2026〕26号</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>泉税二稽处〔2026〕107号</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr"/>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>日对你公司税收违法事实依法作出《税务处理决定书》(泉税二稽处〔 涉税情况进行了检查,查明违法事实及处理决定如下: 年你公司在无真实货物交易的情况下,取得河南中弘纺织有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 年期间,你公司在无真实货物交易的情况下,取得开封兴旺纺织品有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 上述违法事实有检查人员实地检查资料、电话拨打记录、邮寄退回函件、《已证实虚开通知单》等相关受托协查资料、主管税务机关出具的《已抵扣证明》、《情况说明》和你公司的申报纳税资料、银行账户流水等 号第三次修订)第二十一条第二款第二项之规定,认定你公司让他人为自己虚开 号第二次修订)第九条和《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告〔 号)之规定,对你公司取得上述已证实虚开的 之规定,决定向你公司追缴少缴的城市维护建设税-增值税附征 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 规定,决定向你公司追缴少缴的教育费附加-增值税附征 规定,决定向你公司追缴少缴的地方教育附加-增值税附征</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
+          <t>淮税稽处〔2026〕26号</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>淮税稽罚〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr"/>
       <c r="R26" s="3" t="n"/>
       <c r="S26" s="3" t="n"/>
       <c r="T26" s="3" t="n"/>
       <c r="U26" s="3" t="n"/>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>由于你公司走逃失联、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 (五)根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司上述应补缴税款按税款所属时间从税款滞纳之日起按日加收万分之五滞纳金</t>
-        </is>
-      </c>
+      <c r="V26" s="2" t="inlineStr"/>
       <c r="W26" s="4" t="n"/>
       <c r="X26" s="4" t="n">
-        <v>46202</v>
+        <v>46216</v>
       </c>
       <c r="Y26" s="4" t="n"/>
       <c r="Z26" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3915,18 +3915,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF26" s="2" t="inlineStr"/>
+      <c r="AF26" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG26" s="2" t="inlineStr"/>
       <c r="AH26" s="2" t="inlineStr">
         <is>
-          <t>关于对泉州隆鸿服装制造有限公司《税务处理决定书》送达的公告 _
- 其他公告 _
- 国家税务总局泉州市税务局</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
         </is>
       </c>
       <c r="AI26" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ26" s="2" t="inlineStr">
@@ -3937,16 +3939,16 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CASE-717dfe3250926214</t>
+          <t>CASE-089a3b9692e76ac4</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>DOC-7df9c075e55777a1</t>
+          <t>DOC-9f8e8958d8ff89b6</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3956,28 +3958,28 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>泰州市</t>
+          <t>淮安市</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泰州市税务局第一稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局泰州市税务局第一稽查局</t>
+          <t>国家税务总局淮安市税务局稽查局</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>靖江市长凌金属材料有限公司</t>
+          <t>淮安市百亦金商贸有限公司</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>91321282742461893K</t>
+          <t>91320804MA1WEH7Y3U</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
@@ -3988,13 +3990,17 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>泰税一稽罚〔2025〕54号</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>淮税稽罚〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>淮税稽处〔2026〕26号</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>泰税一稽罚〔2025〕54号</t>
+          <t>淮税稽罚〔2026〕6号</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr"/>
@@ -4003,21 +4009,17 @@
       <c r="S27" s="3" t="n"/>
       <c r="T27" s="3" t="n"/>
       <c r="U27" s="3" t="n"/>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>接上级通知,经我局研究决定,撤销上述《税务行政处罚决定书》。</t>
-        </is>
-      </c>
+      <c r="V27" s="2" t="inlineStr"/>
       <c r="W27" s="4" t="n"/>
       <c r="X27" s="4" t="n">
-        <v>46191</v>
+        <v>46216</v>
       </c>
       <c r="Y27" s="4" t="n"/>
       <c r="Z27" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
@@ -4039,67 +4041,71 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF27" s="2" t="inlineStr"/>
+      <c r="AF27" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG27" s="2" t="inlineStr"/>
       <c r="AH27" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 关于撤销《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局淮安市税务局稽查局《税务处理决定书》、《税务行政处罚决定书》送达公告</t>
         </is>
       </c>
       <c r="AI27" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ27" s="2" t="inlineStr">
         <is>
-          <t>官方页面显示该决定书已被撤销。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CASE-a62e569c195adc3c</t>
+          <t>CASE-3f564fd9992b1ae3</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>DOC-b1dda915d4e6117d</t>
+          <t>DOC-c34e1d13286aafe2</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>遵义市</t>
+          <t>泉州市</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局泉州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局</t>
+          <t>国家税务总局泉州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>贵州服格定商贸有限公司</t>
+          <t>泉州隆鸿服装制造有限公司</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>91520302MABUEHN034</t>
+          <t>91350525MA8U3U963L</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
@@ -4110,40 +4116,44 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>遵税一稽处〔2026〕30号</t>
+          <t>泉税二稽处〔2026〕107号</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>遵税一稽处〔2026〕30号</t>
+          <t>泉税二稽处〔2026〕107号</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
+          <t>日对你公司税收违法事实依法作出《税务处理决定书》(泉税二稽处〔 涉税情况进行了检查,查明违法事实及处理决定如下: 年你公司在无真实货物交易的情况下,取得河南中弘纺织有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 年期间,你公司在无真实货物交易的情况下,取得开封兴旺纺织品有限公司虚开的 项之规定,你公司上述受票行为已构成让他人为自己开具与实际经营业务情况不符的发票,属于让他人为自己虚开发票行为 上述违法事实有检查人员实地检查资料、电话拨打记录、邮寄退回函件、《已证实虚开通知单》等相关受托协查资料、主管税务机关出具的《已抵扣证明》、《情况说明》和你公司的申报纳税资料、银行账户流水等 号第三次修订)第二十一条第二款第二项之规定,认定你公司让他人为自己虚开 号第二次修订)第九条和《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告〔 号)之规定,对你公司取得上述已证实虚开的 之规定,决定向你公司追缴少缴的城市维护建设税-增值税附征 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 规定,决定向你公司追缴少缴的教育费附加-增值税附征 规定,决定向你公司追缴少缴的地方教育附加-增值税附征</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
+          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R28" s="3" t="n"/>
       <c r="S28" s="3" t="n"/>
       <c r="T28" s="3" t="n"/>
       <c r="U28" s="3" t="n"/>
-      <c r="V28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>由于你公司走逃失联、相关人员无法联系,致使上述文书采取直接送达、邮寄送达等其他方式均无法送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条第二项的规定,将上述文书主要内容予以公告送达,自公告之日起满 号)第一条之规定,你公司已走逃失联,取得虚开增值税专用发票不得作为税前扣除凭证,且未提供相关资料证实其支出真实性,相应支出不得在发生年度税前扣除,应调增企业所得税应纳税所得额,决定追缴你公司 (五)根据《中华人民共和国税收征收管理法》第三十二条之规定,对你公司上述应补缴税款按税款所属时间从税款滞纳之日起按日加收万分之五滞纳金</t>
+        </is>
+      </c>
       <c r="W28" s="4" t="n"/>
       <c r="X28" s="4" t="n">
-        <v>46185</v>
+        <v>46202</v>
       </c>
       <c r="Y28" s="4" t="n"/>
       <c r="Z28" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
@@ -4169,7 +4179,9 @@
       <c r="AG28" s="2" t="inlineStr"/>
       <c r="AH28" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
+          <t>关于对泉州隆鸿服装制造有限公司《税务处理决定书》送达的公告 _
+ 其他公告 _
+ 国家税务总局泉州市税务局</t>
         </is>
       </c>
       <c r="AI28" s="2" t="inlineStr">
@@ -4185,64 +4197,64 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CASE-13a8aac51595155a</t>
+          <t>CASE-717dfe3250926214</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>DOC-7189c9a2cee8e8ce</t>
+          <t>DOC-7df9c075e55777a1</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>温州市</t>
+          <t>泰州市</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局泰州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局泰州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>温作潘</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr"/>
+          <t>靖江市长凌金属材料有限公司</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>91321282742461893K</t>
+        </is>
+      </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>温税三稽处〔2026〕100号</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>温税三稽处〔2026〕100号</t>
-        </is>
-      </c>
+          <t>泰税一稽罚〔2025〕54号</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>温税三稽罚〔2026〕65号</t>
+          <t>泰税一稽罚〔2025〕54号</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr"/>
@@ -4251,17 +4263,21 @@
       <c r="S29" s="3" t="n"/>
       <c r="T29" s="3" t="n"/>
       <c r="U29" s="3" t="n"/>
-      <c r="V29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>接上级通知,经我局研究决定,撤销上述《税务行政处罚决定书》。</t>
+        </is>
+      </c>
       <c r="W29" s="4" t="n"/>
       <c r="X29" s="4" t="n">
-        <v>46175</v>
+        <v>46191</v>
       </c>
       <c r="Y29" s="4" t="n"/>
       <c r="Z29" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
@@ -4283,92 +4299,96 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF29" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF29" s="2" t="inlineStr"/>
       <c r="AG29" s="2" t="inlineStr"/>
       <c r="AH29" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 关于撤销《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI29" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ29" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>官方页面显示该决定书已被撤销。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CASE-13a8aac51595155a</t>
+          <t>CASE-a62e569c195adc3c</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>DOC-02fc2468fd0396a6</t>
+          <t>DOC-b1dda915d4e6117d</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>温州市</t>
+          <t>遵义市</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局遵义市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局温州市税务局第三稽查局</t>
+          <t>国家税务总局遵义市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>温作潘</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr"/>
+          <t>贵州服格定商贸有限公司</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>91520302MABUEHN034</t>
+        </is>
+      </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>温税三稽罚〔2026〕65号</t>
+          <t>遵税一稽处〔2026〕30号</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>温税三稽处〔2026〕100号</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>温税三稽罚〔2026〕65号</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr"/>
-      <c r="Q30" s="2" t="inlineStr"/>
+          <t>遵税一稽处〔2026〕30号</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>情况进行了检查,违法事实及处理决定如下: 2023年度开具增值税电子普通发票合计金额36,788.18元,税额905.82元,价税37,694.00元,未申报纳税,并且你公司从2023年起所有税种没有进行纳税申报。</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>增值税</t>
+        </is>
+      </c>
       <c r="R30" s="3" t="n"/>
       <c r="S30" s="3" t="n"/>
       <c r="T30" s="3" t="n"/>
@@ -4376,18 +4396,18 @@
       <c r="V30" s="2" t="inlineStr"/>
       <c r="W30" s="4" t="n"/>
       <c r="X30" s="4" t="n">
-        <v>46175</v>
+        <v>46185</v>
       </c>
       <c r="Y30" s="4" t="n"/>
       <c r="Z30" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4405,20 +4425,16 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF30" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF30" s="2" t="inlineStr"/>
       <c r="AG30" s="2" t="inlineStr"/>
       <c r="AH30" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
+          <t>国家税务总局遵义市税务局第一稽查局税务处理决定书(遵税一稽处〔2026〕30 号)</t>
         </is>
       </c>
       <c r="AI30" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ30" s="2" t="inlineStr">
@@ -4429,49 +4445,45 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CASE-f8625e66b291a216</t>
+          <t>CASE-13a8aac51595155a</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>DOC-7970511393924720</t>
+          <t>DOC-7189c9a2cee8e8ce</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>温州市</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>贵州翰缤商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>91520114MAAK1C546F</t>
-        </is>
-      </c>
+          <t>温作潘</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
@@ -4480,15 +4492,19 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>筑税二稽处〔2026〕27号</t>
+          <t>温税三稽处〔2026〕100号</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>筑税二稽处〔2026〕27号</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr"/>
+          <t>温税三稽处〔2026〕100号</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>温税三稽罚〔2026〕65号</t>
+        </is>
+      </c>
       <c r="P31" s="2" t="inlineStr"/>
       <c r="Q31" s="2" t="inlineStr"/>
       <c r="R31" s="3" t="n"/>
@@ -4498,14 +4514,14 @@
       <c r="V31" s="2" t="inlineStr"/>
       <c r="W31" s="4" t="n"/>
       <c r="X31" s="4" t="n">
-        <v>46156</v>
+        <v>46175</v>
       </c>
       <c r="Y31" s="4" t="n"/>
       <c r="Z31" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4543,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF31" s="2" t="inlineStr"/>
+      <c r="AF31" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG31" s="2" t="inlineStr"/>
       <c r="AH31" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第二稽查局关于送达《税务处理决定书》的公告</t>
+          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
         </is>
       </c>
       <c r="AI31" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ31" s="2" t="inlineStr">
@@ -4547,68 +4567,64 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CASE-0f4867f7b70d12f3</t>
+          <t>CASE-13a8aac51595155a</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>DOC-6f25d6b79e123d03</t>
+          <t>DOC-02fc2468fd0396a6</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>温州市</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局温州市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>贵州铂朗物流有限公司</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>91520115MAAK0DB335</t>
-        </is>
-      </c>
+          <t>温作潘</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
+          <t>温税三稽罚〔2026〕65号</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
+          <t>温税三稽处〔2026〕100号</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽罚〔2026〕22号</t>
+          <t>温税三稽罚〔2026〕65号</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr"/>
@@ -4620,14 +4636,14 @@
       <c r="V32" s="2" t="inlineStr"/>
       <c r="W32" s="4" t="n"/>
       <c r="X32" s="4" t="n">
-        <v>46122</v>
+        <v>46175</v>
       </c>
       <c r="Y32" s="4" t="n"/>
       <c r="Z32" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA32" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
@@ -4649,16 +4665,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF32" s="2" t="inlineStr"/>
+      <c r="AF32" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG32" s="2" t="inlineStr"/>
       <c r="AH32" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
+          <t>国家税务总局浙江省税务局 通知公告 国家税务总局温州市税务局第三稽查局关于对温作潘的税务文书送达公告</t>
         </is>
       </c>
       <c r="AI32" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ32" s="2" t="inlineStr">
@@ -4669,16 +4689,16 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>CASE-0f4867f7b70d12f3</t>
+          <t>CASE-f8625e66b291a216</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>DOC-e8233eb0e06b6e3e</t>
+          <t>DOC-7970511393924720</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4694,45 +4714,41 @@
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局贵阳市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局贵阳市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>贵州铂朗物流有限公司</t>
+          <t>贵州翰缤商贸有限公司</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>91520115MAAK0DB335</t>
+          <t>91520114MAAK1C546F</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽罚〔2026〕22号</t>
+          <t>筑税二稽处〔2026〕27号</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>筑税三稽罚〔2026〕22号</t>
-        </is>
-      </c>
+          <t>筑税二稽处〔2026〕27号</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr"/>
       <c r="Q33" s="2" t="inlineStr"/>
       <c r="R33" s="3" t="n"/>
@@ -4742,14 +4758,14 @@
       <c r="V33" s="2" t="inlineStr"/>
       <c r="W33" s="4" t="n"/>
       <c r="X33" s="4" t="n">
-        <v>46122</v>
+        <v>46156</v>
       </c>
       <c r="Y33" s="4" t="n"/>
       <c r="Z33" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
@@ -4775,7 +4791,7 @@
       <c r="AG33" s="2" t="inlineStr"/>
       <c r="AH33" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
+          <t>国家税务总局贵阳市税务局第二稽查局关于送达《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI33" s="2" t="inlineStr">
@@ -4791,47 +4807,47 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CASE-136615addd5d0c0e</t>
+          <t>CASE-0f4867f7b70d12f3</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>DOC-551df7dc5c028b27</t>
+          <t>DOC-6f25d6b79e123d03</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>来宾市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>广西欣瑞木业有限公司</t>
+          <t>贵州铂朗物流有限公司</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>91451322MAD89XWX07</t>
+          <t>91520115MAAK0DB335</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
@@ -4842,17 +4858,17 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr"/>
@@ -4864,14 +4880,14 @@
       <c r="V34" s="2" t="inlineStr"/>
       <c r="W34" s="4" t="n"/>
       <c r="X34" s="4" t="n">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="Y34" s="4" t="n"/>
       <c r="Z34" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
@@ -4897,7 +4913,7 @@
       <c r="AG34" s="2" t="inlineStr"/>
       <c r="AH34" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
         </is>
       </c>
       <c r="AI34" s="2" t="inlineStr">
@@ -4913,47 +4929,47 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>CASE-136615addd5d0c0e</t>
+          <t>CASE-0f4867f7b70d12f3</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>DOC-21f0193b66d5c3e9</t>
+          <t>DOC-e8233eb0e06b6e3e</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>来宾市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>广西欣瑞木业有限公司</t>
+          <t>贵州铂朗物流有限公司</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>91451322MAD89XWX07</t>
+          <t>91520115MAAK0DB335</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
@@ -4964,17 +4980,17 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr"/>
@@ -4986,14 +5002,14 @@
       <c r="V35" s="2" t="inlineStr"/>
       <c r="W35" s="4" t="n"/>
       <c r="X35" s="4" t="n">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="Y35" s="4" t="n"/>
       <c r="Z35" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
@@ -5019,7 +5035,7 @@
       <c r="AG35" s="2" t="inlineStr"/>
       <c r="AH35" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
         </is>
       </c>
       <c r="AI35" s="2" t="inlineStr">
@@ -5035,64 +5051,68 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CASE-393a878d93a22709</t>
+          <t>CASE-136615addd5d0c0e</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>DOC-cda8cba853896b18</t>
+          <t>DOC-551df7dc5c028b27</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>广州市</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>番禺区</t>
-        </is>
-      </c>
+          <t>来宾市</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
+        </is>
+      </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>广州赞荣服装有限公司</t>
+          <t>广西欣瑞木业有限公司</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>91440113MA59AJFJ1J</t>
+          <t>91451322MAD89XWX07</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>穗番税退罚字〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>来市税二稽处〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>来市税二稽处〔2026〕6号</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>穗番税退罚字〔2026〕1号</t>
+          <t>来市税二稽罚〔2026〕4号</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr"/>
@@ -5104,14 +5124,14 @@
       <c r="V36" s="2" t="inlineStr"/>
       <c r="W36" s="4" t="n"/>
       <c r="X36" s="4" t="n">
-        <v>46091</v>
+        <v>46119</v>
       </c>
       <c r="Y36" s="4" t="n"/>
       <c r="Z36" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA36" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
@@ -5125,7 +5145,7 @@
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE36" s="5" t="inlineStr">
@@ -5133,131 +5153,111 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF36" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF36" s="2" t="inlineStr"/>
       <c r="AG36" s="2" t="inlineStr"/>
       <c r="AH36" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
+          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
         </is>
       </c>
       <c r="AI36" s="2" t="inlineStr">
         <is>
-          <t>内容不匹配</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ36" s="2" t="inlineStr">
         <is>
-          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CASE-f94bf08964abff5a</t>
+          <t>CASE-136615addd5d0c0e</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>DOC-4574b1aadef8f30d</t>
+          <t>DOC-21f0193b66d5c3e9</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
+          <t>来宾市</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局稽查局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>常州市文杰车辆配件厂</t>
+          <t>广西欣瑞木业有限公司</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>91320411799075280A</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>朱某</t>
-        </is>
-      </c>
+          <t>91451322MAD89XWX07</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕73号</t>
+          <t>来市税二稽罚〔2026〕4号</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕73号</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr"/>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公 月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R37" s="3" t="n">
-        <v>179137.12</v>
-      </c>
+          <t>来市税二稽处〔2026〕6号</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>来市税二稽罚〔2026〕4号</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="3" t="n"/>
       <c r="S37" s="3" t="n"/>
       <c r="T37" s="3" t="n"/>
       <c r="U37" s="3" t="n"/>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市 份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元,</t>
-        </is>
-      </c>
-      <c r="W37" s="4" t="n">
-        <v>46044</v>
-      </c>
+      <c r="V37" s="2" t="inlineStr"/>
+      <c r="W37" s="4" t="n"/>
       <c r="X37" s="4" t="n">
-        <v>46090</v>
+        <v>46119</v>
       </c>
       <c r="Y37" s="4" t="n"/>
       <c r="Z37" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -5275,20 +5275,16 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF37" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF37" s="2" t="inlineStr"/>
       <c r="AG37" s="2" t="inlineStr"/>
       <c r="AH37" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
+          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
         </is>
       </c>
       <c r="AI37" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ37" s="2" t="inlineStr">
@@ -5299,66 +5295,66 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>CASE-0b4a4519ba4f5ad9</t>
+          <t>CASE-393a878d93a22709</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>DOC-5376b9bae81cfc82</t>
+          <t>DOC-cda8cba853896b18</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>广东省</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr"/>
+          <t>广州市</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>番禺区</t>
+        </is>
+      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局常州市税务局稽查局</t>
-        </is>
-      </c>
+          <t>国家税务总局广州市番禺区税务局</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>常州好佳车辆配件有限公司</t>
+          <t>广州赞荣服装有限公司</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>91320411094264460B</t>
+          <t>91440113MA59AJFJ1J</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕71号</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>常税稽处〔2026〕71号</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr"/>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
       <c r="P38" s="2" t="inlineStr"/>
       <c r="Q38" s="2" t="inlineStr"/>
       <c r="R38" s="3" t="n"/>
@@ -5368,14 +5364,14 @@
       <c r="V38" s="2" t="inlineStr"/>
       <c r="W38" s="4" t="n"/>
       <c r="X38" s="4" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="Y38" s="4" t="n"/>
       <c r="Z38" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
@@ -5389,7 +5385,7 @@
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE38" s="5" t="inlineStr">
@@ -5405,32 +5401,32 @@
       <c r="AG38" s="2" t="inlineStr"/>
       <c r="AH38" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州好佳车辆配件有限公司《税务处理决定书》的公告</t>
+          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
         </is>
       </c>
       <c r="AI38" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>内容不匹配</t>
         </is>
       </c>
       <c r="AJ38" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>CASE-61b9b55a9d3357c7</t>
+          <t>CASE-f94bf08964abff5a</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>DOC-1228a9c92b2b0632</t>
+          <t>DOC-4574b1aadef8f30d</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5446,25 +5442,29 @@
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局常州市税务局稽查局</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>常州市三鹏机械有限公司</t>
+          <t>常州市文杰车辆配件厂</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>91320404732260748Q</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr"/>
+          <t>91320411799075280A</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>朱某</t>
+        </is>
+      </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
           <t>税务处理决定书</t>
@@ -5472,46 +5472,48 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
+          <t>常税稽处〔2026〕73号</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>常税稽一罚〔2026〕14号</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr"/>
+          <t>常税稽处〔2026〕73号</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr"/>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公 月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
+        </is>
+      </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R39" s="3" t="n">
-        <v>63464.09</v>
+        <v>179137.12</v>
       </c>
       <c r="S39" s="3" t="n"/>
       <c r="T39" s="3" t="n"/>
       <c r="U39" s="3" t="n"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
-        </is>
-      </c>
-      <c r="W39" s="4" t="n"/>
+          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市 份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元,</t>
+        </is>
+      </c>
+      <c r="W39" s="4" t="n">
+        <v>46044</v>
+      </c>
       <c r="X39" s="4" t="n">
-        <v>46066</v>
+        <v>46090</v>
       </c>
       <c r="Y39" s="4" t="n"/>
       <c r="Z39" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
@@ -5533,16 +5535,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF39" s="2" t="inlineStr"/>
+      <c r="AF39" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG39" s="2" t="inlineStr"/>
       <c r="AH39" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI39" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ39" s="2" t="inlineStr">
@@ -5553,16 +5559,16 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>CASE-61b9b55a9d3357c7</t>
+          <t>CASE-0b4a4519ba4f5ad9</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>DOC-b97456a64b153f67</t>
+          <t>DOC-5376b9bae81cfc82</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5578,76 +5584,62 @@
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局常州市税务局稽查局</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>常州市三鹏机械有限公司</t>
+          <t>常州好佳车辆配件有限公司</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>91320404732260748Q</t>
+          <t>91320411094264460B</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>常税稽一罚〔2026〕14号</t>
+          <t>常税稽处〔2026〕71号</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>常税稽一罚〔2026〕14号</t>
-        </is>
-      </c>
+          <t>常税稽处〔2026〕71号</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr"/>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
       <c r="R40" s="3" t="n"/>
       <c r="S40" s="3" t="n"/>
-      <c r="T40" s="3" t="n">
-        <v>20000</v>
-      </c>
+      <c r="T40" s="3" t="n"/>
       <c r="U40" s="3" t="n"/>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
-        </is>
-      </c>
+      <c r="V40" s="2" t="inlineStr"/>
       <c r="W40" s="4" t="n"/>
       <c r="X40" s="4" t="n">
-        <v>46066</v>
+        <v>46087</v>
       </c>
       <c r="Y40" s="4" t="n"/>
       <c r="Z40" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA40" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5665,16 +5657,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF40" s="2" t="inlineStr"/>
+      <c r="AF40" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG40" s="2" t="inlineStr"/>
       <c r="AH40" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州好佳车辆配件有限公司《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI40" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ40" s="2" t="inlineStr">
@@ -5685,47 +5681,47 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>CASE-f78ec1a594442165</t>
+          <t>CASE-61b9b55a9d3357c7</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>DOC-fbbe4a664b14f54b</t>
+          <t>DOC-1228a9c92b2b0632</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>安顺市</t>
+          <t>常州市</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
+          <t>常州市三鹏机械有限公司</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>91520423MA6DLH799Q</t>
+          <t>91320404732260748Q</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
@@ -5736,52 +5732,46 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
-        </is>
-      </c>
+          <t>常税稽一罚〔2026〕14号</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr"/>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R41" s="3" t="n">
-        <v>64884.41</v>
+        <v>63464.09</v>
       </c>
       <c r="S41" s="3" t="n"/>
       <c r="T41" s="3" t="n"/>
       <c r="U41" s="3" t="n"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
-        </is>
-      </c>
-      <c r="W41" s="4" t="n">
-        <v>45898</v>
-      </c>
+          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
+        </is>
+      </c>
+      <c r="W41" s="4" t="n"/>
       <c r="X41" s="4" t="n">
-        <v>46043</v>
+        <v>46066</v>
       </c>
       <c r="Y41" s="4" t="n"/>
       <c r="Z41" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA41" s="4" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
@@ -5803,71 +5793,67 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF41" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF41" s="2" t="inlineStr"/>
       <c r="AG41" s="2" t="inlineStr"/>
       <c r="AH41" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI41" s="2" t="inlineStr">
         